--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 52.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 52.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,8 +526,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -557,6 +555,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-334.601</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.84075e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-79.773</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1077116415683324</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6518866171161721</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.361689680904509</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.406004169851856</v>
+      </c>
+      <c r="J2" t="n">
+        <v>19.28910850925628</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.71780556973803</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 13.355x + -8803.943</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>551.6818235263696</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>139537132.2274952</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>7.206532355596467e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.85816184219313</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-292.971</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.77854e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-80.539</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.4272669778615087</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7999474036324167</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.366054331025567</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.250844360526219</v>
+      </c>
+      <c r="J3" t="n">
+        <v>22.59817211319202</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.23158024381881</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 15.182x + -9879.710</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>545.3859073851647</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>33031208.38257015</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>6.267127526616215e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8758214799464826</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-277.398</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.76208e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-80.872</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4890609858176024</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.029845875984965</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.589590399057144</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.285280965774317</v>
+      </c>
+      <c r="J4" t="n">
+        <v>23.63660727639768</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.49600551653742</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 16.331x + -10470.742</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>537.7848296526171</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>41283398.12183786</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>5.890070855591323e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.884317078852627</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-264.223</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.75569e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-81.166</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6532594778035842</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9846070513247311</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.614344501968056</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.633609835071168</v>
+      </c>
+      <c r="J5" t="n">
+        <v>26.25858233225374</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.59700764419834</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 16.817x + -10543.290</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>529.0813057894175</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>74804313.00622916</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>5.5989793164035e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8916542873903337</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-257.091</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.75198e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-81.42100000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2646206235817959</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7864205413431739</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.409777523825267</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.583704772998686</v>
+      </c>
+      <c r="J6" t="n">
+        <v>27.56465611791123</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.59963449745547</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 16.830x + -10285.131</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>520.1197093400756</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>39945648.51106961</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>5.362107796516958e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.898021353319397</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-254.6809999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.74793e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-81.61199999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.04709302761063643</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7121444368742766</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.351456900234701</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.449566565491548</v>
+      </c>
+      <c r="J7" t="n">
+        <v>27.62588929546976</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.56151000208058</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 16.643x + -9915.337</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>511.449997744861</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>46634350.48192126</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>5.18164608234583e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9030302469420093</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-245.98</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.74725e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-81.803</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2796282016090528</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8875499568735453</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.557723373739822</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.674023716456706</v>
+      </c>
+      <c r="J8" t="n">
+        <v>29.10375179787384</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.79121995036104</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 17.837x + -10467.278</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>503.0960003368983</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>208007705.727629</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>5.032855244703399e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9074293255804917</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-242.769</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.74542e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-81.974</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2573723202517896</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6032054909236702</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.450659519057139</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.500255520570139</v>
+      </c>
+      <c r="J9" t="n">
+        <v>29.1839628677693</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.75443229110743</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 17.635x + -10109.590</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>495.2601629230304</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>44565443.13058098</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4.903602942740081e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9112882571601162</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-238.725</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.7434e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-82.11499999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2053870292526725</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7780658282570935</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.327044836310776</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.398212515352944</v>
+      </c>
+      <c r="J10" t="n">
+        <v>28.4131595292618</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.86399061391251</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 18.252x + -10290.041</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>487.5726900698414</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>34386439.88839921</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4.798176144455605e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9144936368071772</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-234.853</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.74116e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-82.271</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.133032469425554</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.6824983883146285</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.301623762324569</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.441370433324076</v>
+      </c>
+      <c r="J11" t="n">
+        <v>29.75051584272774</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.86201561837873</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 18.241x + -10084.219</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>480.5862591691507</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>26881734.4222526</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.696682508126709e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9176214688840652</v>
       </c>
     </row>
   </sheetData>
@@ -570,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,8 +1192,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -705,6 +1221,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-234.155</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.77466e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-81.107</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3646641243372972</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7251264235091125</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.550065178291847</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.067064086647614</v>
+      </c>
+      <c r="J2" t="n">
+        <v>28.53892997069431</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.65426769437698</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 17.106x + -11249.976</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>547.6190726842345</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>41080721.47866023</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>5.843129485523733e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.886157461389472</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-230.4929999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.79344e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-81.34999999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1173761142040936</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5923521197805374</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.498109138202306</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.216075493420218</v>
+      </c>
+      <c r="J3" t="n">
+        <v>28.23523860810725</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.67621761930589</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 17.219x + -10861.799</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>536.3130500260861</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>41194474.90584817</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>5.549820417865719e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8950503314533955</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-221.836</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.79701e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-81.54000000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.26662440540254</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8154961094764286</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.438123460479906</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.611938835102172</v>
+      </c>
+      <c r="J4" t="n">
+        <v>32.39167685925389</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.75859743134012</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 17.657x + -10951.553</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>530.5014166093951</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>67697417.42539169</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>5.38037091704937e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8999537002764342</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-220.027</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.79651e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-81.626</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3834914931934432</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8863198084297643</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.549038772716065</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.54771113642053</v>
+      </c>
+      <c r="J5" t="n">
+        <v>31.41815720079416</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.88584835855085</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 18.380x + -11286.664</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>525.0447999738915</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>38322631.85220434</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>5.280000921525257e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9028218588589982</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-220.256</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.79475e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-81.721</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5402857253549586</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8183457114063589</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.623650468130502</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.399994365508291</v>
+      </c>
+      <c r="J6" t="n">
+        <v>30.66436886401196</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.89498427597836</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 18.435x + -11158.796</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>519.1276913944876</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>22421880.91333796</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>5.18061558625732e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9056400709941076</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-218.9880000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.79772e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-81.831</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4848179854485541</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7243756060623281</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.49151770155132</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.444205209972915</v>
+      </c>
+      <c r="J7" t="n">
+        <v>32.03935267951744</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.85517826461805</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 18.201x + -10830.426</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>512.8851005325013</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>61754128.69018628</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>5.098815646727138e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9082258353444421</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-218.954</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.79625e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-81.91800000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4142040674860089</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.959176311335216</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.70507176123462</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.830437571038976</v>
+      </c>
+      <c r="J8" t="n">
+        <v>32.77906336879487</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.93421380474906</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 18.671x + -10961.225</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>506.692379193322</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>279841143.0356812</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>5.014855124558051e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.910701142904584</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-215.292</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.79657e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-82.029</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3962789591840545</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.177679689373743</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.56172012376785</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.478570601234709</v>
+      </c>
+      <c r="J9" t="n">
+        <v>31.553635806468</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.03752674193467</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 19.323x + -11209.177</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>500.7779678278371</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>27874041.96337112</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4.928337765878669e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9133725852778088</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-212.5799999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.79686e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-82.13500000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4891615492411115</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9932531250554146</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.703838150795357</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.446474212731569</v>
+      </c>
+      <c r="J10" t="n">
+        <v>31.96252829709818</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.08724637754925</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 19.654x + -11255.070</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>495.285121895397</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>271600469.696499</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4.859172518199393e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9155414574974581</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-210.2869999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.798e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-82.241</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4222334805292197</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.6911635918395393</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.647270509741012</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.553904853196996</v>
+      </c>
+      <c r="J11" t="n">
+        <v>32.59861249661172</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.04147941380815</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 19.349x + -10902.551</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>489.9210250392429</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>29405537.75678721</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.787743942065891e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9178572889243085</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-209.203</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.7984e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-82.331</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4971178368169251</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.729008311367605</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.513776200531758</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.669948619836324</v>
+      </c>
+      <c r="J12" t="n">
+        <v>32.91398293315098</v>
+      </c>
+      <c r="K12" t="n">
+        <v>87.07824229333619</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 19.593x + -10902.467</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>484.5950792194721</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>65902059.67108587</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4.732247315029527e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9196587717102108</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-207.611</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.79997e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-82.407</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3122113290418967</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9393860275435358</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.625416128472002</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.519431500090476</v>
+      </c>
+      <c r="J13" t="n">
+        <v>33.19445488533625</v>
+      </c>
+      <c r="K13" t="n">
+        <v>87.11377880852471</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 19.835x + -10907.048</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>479.2207077071099</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>24082961.64675545</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.683395449795387e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9213274675745137</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-205.4829999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.79936e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-82.492</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.5913892969043912</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.262488880478221</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.796444808982691</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.923380988965439</v>
+      </c>
+      <c r="J14" t="n">
+        <v>34.88876901786428</v>
+      </c>
+      <c r="K14" t="n">
+        <v>87.21412335674272</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 20.550x + -11178.803</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>474.0124014865988</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>48531238.15834387</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4.630164582235506e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9230456419053145</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-204.12</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.79942e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-82.586</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.2018899949128029</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9493521760255583</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.501039895304626</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.408359283169756</v>
+      </c>
+      <c r="J15" t="n">
+        <v>32.44179783334324</v>
+      </c>
+      <c r="K15" t="n">
+        <v>87.15981267349734</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 20.157x + -10797.024</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>469.0075452841498</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>28576826.45869574</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4.576311750516199e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9248273123145193</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-207.12</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.79985e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-82.65600000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.4674271789645191</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.17400882993678</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.178605895158181</v>
+      </c>
+      <c r="J16" t="n">
+        <v>31.85222550650592</v>
+      </c>
+      <c r="K16" t="n">
+        <v>86.99169329717583</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 19.028x + -10004.553</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>464.0837279452896</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>41656734.77073652</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4.537056640989806e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9261707582920037</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-198.9010000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.80122e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-82.752</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.574094098662207</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.02471410018959</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.788403102681607</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.669856097256436</v>
+      </c>
+      <c r="J17" t="n">
+        <v>34.64996948124505</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87.28457759564253</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 21.084x + -11054.079</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>459.2088586320658</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>73142621.77350013</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>4.491448263308566e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9277754535995723</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-202.994</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.80068e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-82.79900000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.2183510577673462</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.8283458706172394</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.708807776463827</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.807955456257609</v>
+      </c>
+      <c r="J18" t="n">
+        <v>35.03307956912273</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87.23301847851154</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 20.691x + -10695.261</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>454.2969709553919</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>38835982.37046302</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>4.459785110598263e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9288390395482373</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-195.3389999999999</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.8028e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-82.913</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.5027793968845387</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.230302937265868</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.884773727162765</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.9191155272148</v>
+      </c>
+      <c r="J19" t="n">
+        <v>36.06874250908724</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.37575716610981</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 21.818x + -11183.551</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>449.4719906849796</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>369854107.262041</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>4.413194965873209e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.930533840555642</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-199.119</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.80156e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-82.96599999999999</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.2700673515886521</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.7809265010128872</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.413067855121629</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.534432574990799</v>
+      </c>
+      <c r="J20" t="n">
+        <v>33.80302682497498</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.24963659107635</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 20.816x + -10488.219</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>444.6512127779001</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>730005415.09552</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.380704721093446e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.931611207274547</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-198.011</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.80049e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-83.032</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.3154162282915391</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.8684173492303625</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.633895355605208</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.705870431938876</v>
+      </c>
+      <c r="J21" t="n">
+        <v>35.22895459104724</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.32376809483063</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 21.394x + -10670.263</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>439.9087363251003</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>134598211.1798755</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>4.34392041140991e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9328343364818265</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-195.548</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.80206e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-83.133</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1442157191348044</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9656591906001689</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.479633122993012</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.539282747890528</v>
+      </c>
+      <c r="J22" t="n">
+        <v>35.53031468556073</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.26219463846495</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 20.912x + -10266.411</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>411.244001256769</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>5842.653011486986</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>4.641218700590199e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9984261786744993</v>
       </c>
     </row>
   </sheetData>
@@ -718,7 +2326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -822,8 +2430,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -853,6 +2459,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-263.9880000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.75911e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-80.986</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1952450869479741</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.755266670279675</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.248481444564074</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.296674542326991</v>
+      </c>
+      <c r="J2" t="n">
+        <v>26.8280798110669</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.36910546666731</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 15.759x + -10152.088</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>543.0744978851715</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>56623007.34436025</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>5.820828483546218e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8859197612966854</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-243.1039999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.75569e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-81.366</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1920432695997757</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6710820972775473</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.411099546441634</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.496970371869915</v>
+      </c>
+      <c r="J3" t="n">
+        <v>29.64686197193164</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.60296144379556</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 16.847x + -10602.849</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>535.3777738037471</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>26357392.43708407</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>5.475926748889934e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8949616793716735</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-237.33</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.74958e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-81.541</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2223139853987595</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7773508707494463</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.383399446852563</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.417329657635067</v>
+      </c>
+      <c r="J4" t="n">
+        <v>29.76918164810563</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.67231898498879</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 17.199x + -10667.685</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>529.6461565578179</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>72818556.39952733</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>5.311393192374377e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8992685023209542</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-235.2190000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.74428e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-81.67400000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.008931117234622345</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5530911112892096</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.160591641717726</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.084806897229841</v>
+      </c>
+      <c r="J5" t="n">
+        <v>28.73746863546007</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.66415580087778</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 17.156x + -10474.874</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>523.4266567912304</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>122210555.2592653</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>5.185988259768235e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9026224396203708</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-234.439</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.74171e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-81.78400000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.06045750545179958</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6343597426922</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.406397569105598</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.505667571765391</v>
+      </c>
+      <c r="J6" t="n">
+        <v>30.49610782680917</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.66871586387042</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 17.180x + -10319.194</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>516.9120811162061</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>40063527.89311381</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>5.082977602685361e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9055414459293201</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-231.372</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.73569e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-81.923</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.005391165117129095</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5412262003611511</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.244551027971449</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.195137048314126</v>
+      </c>
+      <c r="J7" t="n">
+        <v>28.84999281911304</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.76167165566486</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 17.674x + -10475.098</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>510.8136599619593</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>284246405.3912622</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>4.968564906094457e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.908680243748182</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-224.895</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.73308e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-82.05</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.6134521518027856</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8228770755907237</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.616802831919998</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.340761584129079</v>
+      </c>
+      <c r="J8" t="n">
+        <v>30.18632258650494</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.95632860802702</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 18.807x + -11051.800</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>505.1418191579408</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>277296170.3229762</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>4.877483991057653e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9113429296945486</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-224.9209999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.72884e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-82.154</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2198065149320281</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7795732594248805</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.444678998424194</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.150044116883293</v>
+      </c>
+      <c r="J9" t="n">
+        <v>29.91495115848994</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.87427225247617</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 18.312x + -10583.594</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>500.0446173133178</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>274974229.9535233</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4.79742023833454e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9136306050108158</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-222.99</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.7248e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-82.262</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1076727226060694</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6600488731801287</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.341842334481293</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.445986974429182</v>
+      </c>
+      <c r="J10" t="n">
+        <v>31.94805434110291</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.86927920047472</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 18.283x + -10423.537</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>494.8353524461027</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>40287277.71094939</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4.718427542435358e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9159318818718266</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-221.408</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.7219e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-82.327</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4163943174783296</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8539200072988365</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.607577426455</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.222730055011878</v>
+      </c>
+      <c r="J11" t="n">
+        <v>31.06880622720697</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.0820691243071</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 19.619x + -11127.105</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>489.6967757098946</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>93252368.58251798</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.667191217373455e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9174435870548666</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-223.4059999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.71584e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-82.41200000000001</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.2526872500180329</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.7825747882664581</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.50307297325042</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.644058196896711</v>
+      </c>
+      <c r="J12" t="n">
+        <v>32.55070289707726</v>
+      </c>
+      <c r="K12" t="n">
+        <v>86.96906348641619</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 18.886x + -10527.286</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>484.7401896710014</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>43591990.13423891</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4.60055500071584e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.91930711753258</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-223.115</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.71535e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-82.491</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2122254888761856</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.6937080879290778</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.396195697138807</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.466276642088455</v>
+      </c>
+      <c r="J13" t="n">
+        <v>31.37231042767696</v>
+      </c>
+      <c r="K13" t="n">
+        <v>86.96053611362325</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 18.833x + -10361.677</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>479.8687543644011</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>34107853.48462652</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.551564263780891e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9209059499127603</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-221.7230000000001</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.71117e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-82.563</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3605236730214341</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.81914103853259</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.497141849556639</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.330786566685132</v>
+      </c>
+      <c r="J14" t="n">
+        <v>30.79310693495376</v>
+      </c>
+      <c r="K14" t="n">
+        <v>87.06517073585158</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 19.506x + -10639.553</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>474.935735704342</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>34295332.13532727</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4.500449046646251e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9224025859855683</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-221.58</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.70973e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-82.655</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.03119398884721605</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.6325437411909773</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.258445199355586</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.140474610872851</v>
+      </c>
+      <c r="J15" t="n">
+        <v>30.53707035080581</v>
+      </c>
+      <c r="K15" t="n">
+        <v>86.99561330577383</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 19.053x + -10227.207</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>469.9476069863769</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>98475152.46562451</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4.451062441172622e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9239978165989882</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-223.1289999999999</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.70639e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-82.697</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.2086057357723226</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.7308941824797699</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.531891265620881</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.414295395977082</v>
+      </c>
+      <c r="J16" t="n">
+        <v>31.45527966216478</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87.05295416989037</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 19.425x + -10325.280</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>465.0514139133583</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>255587382.3131509</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4.415980302388228e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9250293871557737</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-214.172</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.70397e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-82.833</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4761021165864978</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.7736434726547265</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.658303749209617</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.676899113999296</v>
+      </c>
+      <c r="J17" t="n">
+        <v>33.23544817772977</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87.23156072950334</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 20.680x + -10911.608</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>460.1691662592226</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>15734840.3135771</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>4.344326980192154e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9273668514751624</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-222.645</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.70245e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-82.843</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.2173577897072485</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.673331281426839</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.537745280389815</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.621278129482117</v>
+      </c>
+      <c r="J18" t="n">
+        <v>31.58711232036303</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87.12206384450741</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 19.892x + -10328.823</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>455.2142059110784</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>48458271.54523466</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>4.330306852580111e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9278024985076893</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-218.611</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.70042e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-82.923</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.4854376457308592</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.8736735109193742</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.602755377449514</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.674300618719865</v>
+      </c>
+      <c r="J19" t="n">
+        <v>31.87093104326145</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.24135507798749</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 20.753x + -10687.451</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>450.3106340980862</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>246346300.6498589</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>4.289298240777591e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9291421875612191</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-217.1019999999999</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.6985e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-83</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.6699678097066287</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.14843603787232</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.829178323611019</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.004469770141549</v>
+      </c>
+      <c r="J20" t="n">
+        <v>32.66376243186441</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.30505889277259</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 21.245x + -10821.880</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>445.3910988715893</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>195607532.1833709</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.248476336062204e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9304842063363656</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-217.189</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.69851e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-83.083</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2784258307472733</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.9862472841372104</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.460607840254294</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.442787857798665</v>
+      </c>
+      <c r="J21" t="n">
+        <v>31.91599480951547</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.21328819958147</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 20.544x + -10284.192</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>440.4655235058564</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>362063644.571839</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>4.211295957905756e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9318223302954682</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-220.836</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.69608e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-83.119</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.2182466866922736</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.8359932495732775</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.620453241204297</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.512436863852853</v>
+      </c>
+      <c r="J22" t="n">
+        <v>31.41175870035528</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.22402722824856</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 20.624x + -10197.540</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>435.5708022825369</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>178925621.5317138</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>4.18400320375367e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9326973080804603</v>
       </c>
     </row>
   </sheetData>
@@ -866,7 +3564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -970,8 +3668,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1001,6 +3697,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-469.704</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.73912e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-77.087</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2394452597977123</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.718123391121404</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.199218326272361</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.874774092295481</v>
+      </c>
+      <c r="J2" t="n">
+        <v>13.50043637479386</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.45633435361003</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 10.303x + -8414.234</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>604.3463217163657</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>323573447.6931999</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.882895778045228e-06</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.71001629784389</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-350.398</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.78028e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-79.06999999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.4254204703069858</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.017892081940738</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.646956998032436</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.584431778307111</v>
+      </c>
+      <c r="J3" t="n">
+        <v>19.32425483525176</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.68401314913133</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 13.250x + -9702.424</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>589.3048081097292</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>75420614.09982227</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>8.76482784692416e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8252689815935689</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-306.0550000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.77557e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-79.871</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3789533712106087</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6935831395145033</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.484149597122343</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.327218347529435</v>
+      </c>
+      <c r="J4" t="n">
+        <v>21.22569861951163</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.07626047625904</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 14.580x + -10234.312</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>577.1142193154957</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>190376014.7478443</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>7.30842803239554e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8523495598391753</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-286.706</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.76524e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-80.327</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1999261977950024</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.624035922274585</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.243128395234571</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.348688563061177</v>
+      </c>
+      <c r="J5" t="n">
+        <v>23.3149796036984</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.21622237633349</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 15.120x + -10318.560</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>567.9871590781264</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>76725641.15732116</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>6.634786282406896e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8663904509871001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-271.024</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.7542e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-80.64100000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5185912786437098</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.148055060453172</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.743900104916341</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.56564840233844</v>
+      </c>
+      <c r="J6" t="n">
+        <v>25.39182131709459</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.53569117561379</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 16.519x + -11107.115</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>559.6763142710811</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>133734960.9734585</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>6.206783793336595e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8759026763141121</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-259.5440000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.74779e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-80.917</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.5248157113527188</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9742962094062639</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.522607771635615</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.387124752332773</v>
+      </c>
+      <c r="J7" t="n">
+        <v>26.07510066512191</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.64416046751572</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 17.054x + -11236.524</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>551.4612662733882</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>79667415.47283565</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>5.886170529079986e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8835919572235396</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-259.509</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.74066e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-81.066</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.6912408118216696</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.011634495532713</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.716135483563617</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.570084925832572</v>
+      </c>
+      <c r="J8" t="n">
+        <v>26.16977029646472</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.7000471683982</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 17.343x + -11214.333</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>543.3157354088189</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>110229427.7902048</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>5.676922735456703e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8887380136564915</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-250.301</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.73609e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-81.31999999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5565863482426715</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.005052117092767</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.694985968697947</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.574527120443393</v>
+      </c>
+      <c r="J9" t="n">
+        <v>28.303952681974</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.73254258456815</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 17.516x + -11079.724</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>535.332687899152</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>151031625.3812257</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>5.446282324568905e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8947642841424477</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-250.181</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.73151e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-81.48999999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1661809382073509</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5560566862638964</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.255961439573271</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.193166714234211</v>
+      </c>
+      <c r="J10" t="n">
+        <v>26.95813718913088</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.60887503835845</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 16.876x + -10421.289</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>527.7492158615748</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>69139694.95995358</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>5.283929184470241e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8991159299724438</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-244.0300000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.72605e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-81.657</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1796956324297025</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8236838196539223</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.543243869597549</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.605687402695676</v>
+      </c>
+      <c r="J11" t="n">
+        <v>29.66644705868204</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.77269245723578</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 17.735x + -10800.379</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>520.5777571939508</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>38550024.03899003</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>5.133228685586095e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9032165774683129</v>
       </c>
     </row>
   </sheetData>
@@ -1014,7 +4230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,8 +4334,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1149,6 +4363,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-308.104</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.82333e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-80.155</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1480065881251066</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6184711703810529</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.190463002417081</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.959255446452011</v>
+      </c>
+      <c r="J2" t="n">
+        <v>20.66399810028872</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.95620854890785</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 14.145x + -9296.020</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>548.4584993393676</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>33868013.95077544</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>6.64534361249985e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8695419148826943</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-262.4930000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.80172e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-80.95399999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5945747585605637</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7989869056139646</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.436103946416004</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.409456906870179</v>
+      </c>
+      <c r="J3" t="n">
+        <v>25.47369559745187</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.49145820315111</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 16.310x + -10345.659</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>537.210201868043</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>118712454.8685306</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>5.822641005546925e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8882925461712646</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-251.874</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.79093e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-81.247</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.04475386701330318</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.4474005023919039</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.306113553636478</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.250669108736399</v>
+      </c>
+      <c r="J4" t="n">
+        <v>26.54368780814999</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.50976978264542</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 16.396x + -10165.137</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>530.4059993973187</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>71146535.65390402</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>5.538610796403511e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8952877626884116</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-245.47</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.78399e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-81.43600000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1718421532318919</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.575281691954896</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.386214729935252</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.280156691620395</v>
+      </c>
+      <c r="J5" t="n">
+        <v>27.50556780112495</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.60947427756916</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 16.879x + -10311.454</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>523.9412351233299</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>43833349.28309046</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>5.362085377543871e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.899832289012949</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-241.8200000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.77939e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-81.598</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.0008480084571811993</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6133649844643168</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.235025241366735</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.007506567442336</v>
+      </c>
+      <c r="J6" t="n">
+        <v>26.88487240049644</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.62786991769364</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 16.971x + -10188.710</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>517.1734637849278</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>19941641.97983824</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>5.216831471385929e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9037554014635155</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-232.804</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.77535e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-81.77</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.279754028690307</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8427904217164078</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.712400177479131</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.563045867169572</v>
+      </c>
+      <c r="J7" t="n">
+        <v>30.64101401472917</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.82750704386147</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 18.042x + -10713.039</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>510.9371799472771</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>21364185.31590111</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>5.085709092644983e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9073974975782982</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-229.415</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.77186e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-81.886</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4307655497281935</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.073175209306629</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.62988854556142</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.583530438871635</v>
+      </c>
+      <c r="J8" t="n">
+        <v>29.67299491876751</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.94132693735772</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 18.714x + -10988.871</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>505.1936294296866</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>217794310.3336492</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>4.996646735832783e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9099088804737524</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-230.1909999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.76888e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-81.999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1037792887837186</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7378286696870985</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.31555351608316</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.417579565898255</v>
+      </c>
+      <c r="J9" t="n">
+        <v>30.06210026716074</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.79270814982048</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 17.846x + -10275.022</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>499.971990244395</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>207989369.6311161</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4.913081306985214e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9123017949281753</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-226.432</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.76517e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-82.107</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2326520747812153</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5767229050967563</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.321168350906908</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.395783542886007</v>
+      </c>
+      <c r="J10" t="n">
+        <v>29.90307718048344</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.90390655366456</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 18.488x + -10551.788</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>495.0602961609386</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>577435629.8490283</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4.836258111412862e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9144973029286818</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-224.937</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.76424e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-82.178</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3295642291360428</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8018268774242603</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.410299930142739</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.544548248891823</v>
+      </c>
+      <c r="J11" t="n">
+        <v>30.76605962322778</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.96352012577218</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 18.851x + -10651.036</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>490.3719480906841</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>37340201.01544112</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.782830294183207e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9161392209830217</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-225.2009999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.76201e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-82.26900000000001</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.09334017514359411</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.6052048035585326</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.411817629523775</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.29289560403533</v>
+      </c>
+      <c r="J12" t="n">
+        <v>30.42196149880862</v>
+      </c>
+      <c r="K12" t="n">
+        <v>86.89395331886263</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 18.428x + -10260.209</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>485.7195061657517</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>106225137.1154371</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4.72514108836623e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9178656589727766</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-218.064</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.76011e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-82.378</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.4779291113143069</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9475026324955045</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.502996261598081</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.58493543618786</v>
+      </c>
+      <c r="J13" t="n">
+        <v>31.874831423442</v>
+      </c>
+      <c r="K13" t="n">
+        <v>87.06754657440469</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 19.521x + -10800.953</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>481.1161959089837</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>265683551.0406118</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.662560501647432e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9197786808082647</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-223.1080000000001</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.75803e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-82.408</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1885649332177697</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.820328195165526</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.572249959275457</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.691917886643043</v>
+      </c>
+      <c r="J14" t="n">
+        <v>31.86344855652163</v>
+      </c>
+      <c r="K14" t="n">
+        <v>87.00386093441517</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 19.106x + -10430.512</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>476.4290111059876</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>526242721.4847798</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4.631060404567869e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.920719844573925</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-218.167</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.7569e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-82.524</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3172306018566933</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.8603021687014626</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.701133247103844</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.769937778514372</v>
+      </c>
+      <c r="J15" t="n">
+        <v>32.74213295275063</v>
+      </c>
+      <c r="K15" t="n">
+        <v>87.06671331105046</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 19.516x + -10538.269</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>471.6699504570026</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>31788854.7874673</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4.567488918996206e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9227444327739828</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-214.9640000000001</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.7559e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-82.608</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.3857815678992043</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9185470588657649</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.471825837423314</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.526736664463396</v>
+      </c>
+      <c r="J16" t="n">
+        <v>31.79101885728002</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87.14698387776581</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 20.066x + -10734.585</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>466.8813678268625</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>81748662.55577137</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4.522718850824425e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.924189238953277</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-217.1379999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.75323e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-82.67</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.200965335231733</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.7795074404851906</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.508042156668263</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.637989471856198</v>
+      </c>
+      <c r="J17" t="n">
+        <v>32.35365371836457</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87.10999092493243</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 19.809x + -10452.166</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>462.0965369417456</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>42544192.1390802</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>4.478297767029729e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.925561736088242</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-216.206</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.75338e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-82.732</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.2145788724569198</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.7986337698236529</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.50649135308134</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.421428960657555</v>
+      </c>
+      <c r="J18" t="n">
+        <v>31.1979492897199</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87.17600098309205</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 20.272x + -10593.935</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>457.324415910957</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>189718246.9381725</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>4.445128379655021e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9267053171687356</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-211.967</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.75325e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-82.828</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.3700492165788518</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.9178204596698674</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.652987064956971</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.75519494650435</v>
+      </c>
+      <c r="J19" t="n">
+        <v>33.05184377310506</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.26571630256188</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 20.939x + -10835.838</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>452.6053765604874</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>38423494.24429484</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>4.396161957261621e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9283776068270748</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-216.501</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.75103e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-82.867</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.2283033407230188</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.8119957830412502</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.390421213085904</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.405597356992305</v>
+      </c>
+      <c r="J20" t="n">
+        <v>31.3722171242797</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.15350563982575</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 20.112x + -10237.475</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>447.8181885829125</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>49822100.56803484</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.366229156045198e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9293218080570352</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-210.951</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.75269e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-82.977</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.248071469195649</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.9417931337290134</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.599420066569363</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.714641222050696</v>
+      </c>
+      <c r="J21" t="n">
+        <v>33.43691358010342</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.2522598512541</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 20.836x + -10501.652</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>443.0544249987667</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>250687932.7284362</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>4.321799788876768e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9309547576262238</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-211.449</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.75223e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-83.033</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.3438557794158425</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.836114503640598</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.580761181412363</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.670578959570229</v>
+      </c>
+      <c r="J22" t="n">
+        <v>32.73695390408071</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.24976640333482</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 20.817x + -10356.465</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>438.2193279052158</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>135399575.902739</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>4.291012941134729e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9320235453091141</v>
       </c>
     </row>
   </sheetData>
@@ -1162,7 +5468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,8 +5572,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1297,6 +5601,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-565.4799999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.9838e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-74.63500000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.04741256435754312</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.508532107511081</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.8981918884373131</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.659636695122562</v>
+      </c>
+      <c r="J2" t="n">
+        <v>9.941213962257471</v>
+      </c>
+      <c r="K2" t="n">
+        <v>82.6651157206109</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 7.769x + -6345.806</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>548.8373652719168</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>192761399.6507388</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>5.92952917704346e-06</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.5614386576330698</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-391.0300000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.01216e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-77.77200000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3515822914237077</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8473114252423656</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.395973443438216</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.345227069257654</v>
+      </c>
+      <c r="J3" t="n">
+        <v>15.13136401855535</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.89370956873204</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 11.191x + -8039.176</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>579.9562874628609</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>380073926.8092821</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.185401619888726e-06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.7925344467128782</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-324.691</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.962e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-79.065</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5742783448708927</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9712441287652233</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.536560585505663</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.411377294103572</v>
+      </c>
+      <c r="J4" t="n">
+        <v>19.12874077286414</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.74320987217183</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 13.435x + -9287.798</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>570.6200555914047</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>141121040.1946451</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>8.598524766326485e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8379822082664997</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-292.1700000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.92195e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-79.76900000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4894847180105825</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8766474731967944</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.550825802843558</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.288281463445935</v>
+      </c>
+      <c r="J5" t="n">
+        <v>21.21268600853546</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.09600229280805</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 14.653x + -9894.437</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>563.2548048657297</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>37285288.0460481</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>7.420131769015894e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8580603224351908</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-279.1559999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.88889e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-80.203</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.0704548828773396</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.4997124771237685</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.210831630212569</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.115676787314087</v>
+      </c>
+      <c r="J6" t="n">
+        <v>22.05264544928506</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.14418938835858</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 14.837x + -9780.091</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>556.1471854430796</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>54022908.28903898</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>6.766352163401629e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8702731380809851</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-258.9640000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.86417e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-80.577</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.8305018133887543</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.175274742315297</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.818349909479372</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.712361553625984</v>
+      </c>
+      <c r="J7" t="n">
+        <v>26.08245321436695</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.58717447072914</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 16.769x + -10961.284</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>548.8851700371114</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>48425086.81621543</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>6.298505710540088e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.87980008112735</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-253.134</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.84804e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-80.84099999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2957717498267839</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8480996540261118</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.490247907421995</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.472165735623615</v>
+      </c>
+      <c r="J8" t="n">
+        <v>26.67650156012775</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.56080407443896</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 16.640x + -10639.291</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>541.7276949713749</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>41906008.05530718</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>5.98746115629063e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8866153613256428</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-245.8810000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.83701e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-81.092</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2047370001775109</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.4854828281835391</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.285765672454759</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.065452863759254</v>
+      </c>
+      <c r="J9" t="n">
+        <v>26.13891120181252</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.60186424003736</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 16.841x + -10566.119</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>534.9589497520589</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>108692580.7518235</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>5.73714269171323e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8924828407205273</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-238.38</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.82732e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-81.27500000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2758296477875841</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8290016796894822</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.782799875193498</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.59586819193714</v>
+      </c>
+      <c r="J10" t="n">
+        <v>28.98433912098287</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.78168544461973</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 17.784x + -11034.016</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>528.7058654593757</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>52218997.73365314</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>5.552519750927198e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.89692991190356</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-239.2380000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.81897e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-81.429</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.02088451409209654</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5372813070639214</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.271555828449094</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.050277892677634</v>
+      </c>
+      <c r="J11" t="n">
+        <v>26.92460837186266</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.63028576451273</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 16.984x + -10313.156</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>522.8425911722518</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>33625030.64626577</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>5.399516033166096e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9007305074242201</v>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +6134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,8 +6238,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1445,6 +6267,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-346.3549999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.99723e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-79.05</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2262220644112059</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7818591832894812</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.355866046274577</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.210709949160665</v>
+      </c>
+      <c r="J2" t="n">
+        <v>17.4040703072683</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.41998583830714</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 12.483x + -8225.624</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>547.3472225548547</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>397961733.3448045</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>8.274102823993408e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8457666789407142</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-274.2910000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.91984e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-80.374</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.7441229220657029</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9079495240979366</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.823571920107478</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.465172239906871</v>
+      </c>
+      <c r="J3" t="n">
+        <v>23.32013914477994</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.38672044718129</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 15.836x + -10121.954</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>537.8199450089054</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>74128569.15747638</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>6.527902110359519e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8773862851911465</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-251.7089999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.89069e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-80.866</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4244491384048252</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8361864141065306</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.58110355055373</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.47599103599696</v>
+      </c>
+      <c r="J4" t="n">
+        <v>26.42779676288146</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.55930970150752</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 16.632x + -10407.166</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>532.0826246452998</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>56612086.9927252</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>6.00545680042186e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8884423940681052</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-243.583</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.87552e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-81.096</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3939383617169469</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.79921883095817</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.573492281634406</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.54365395675777</v>
+      </c>
+      <c r="J5" t="n">
+        <v>27.6932367502131</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.69298291892619</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 17.306x + -10690.690</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>526.7603610991472</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>15084464.71567873</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>5.745483423175343e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8943638664328679</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-235.6479999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.8644e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-81.304</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5007586314062575</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.947261371890523</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.471886460020031</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.457924013549032</v>
+      </c>
+      <c r="J6" t="n">
+        <v>28.28473065339613</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.76941509436701</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 17.717x + -10786.673</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>520.894097614307</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>58145772.69805376</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>5.551725047422679e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8989872840468733</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-235.096</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.8567e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-81.46299999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5305982286515071</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.299279190028358</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.074665440765484</v>
+      </c>
+      <c r="J7" t="n">
+        <v>27.68217023174792</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.6801818769266</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 17.239x + -10288.053</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>514.6214062575486</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>29230952.67993838</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>5.399810808069631e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9027972753956297</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-223.103</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.8523e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-81.655</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.5908817561571318</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.004374315184937</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.47331940538358</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.679128791133663</v>
+      </c>
+      <c r="J8" t="n">
+        <v>30.96904628457192</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.96933328543356</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 18.888x + -11188.641</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>508.4598098639956</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>75423441.15448593</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>5.25718116813532e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.906611705339431</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-224.5070000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.84916e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-81.765</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1327707013557816</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7138140989047358</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.416899029378875</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.38596112975209</v>
+      </c>
+      <c r="J9" t="n">
+        <v>29.756369616927</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.85703226049561</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 18.212x + -10581.556</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>502.6282180827429</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>423603549.2168085</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>5.164684199479608e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9091528766849323</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-216.336</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.84593e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-81.908</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.689797609434404</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.178333251814904</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.644787859351534</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.644050388784462</v>
+      </c>
+      <c r="J10" t="n">
+        <v>31.35358023965321</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.0597237926864</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 19.469x + -11217.458</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>497.0874087230442</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>38368921.81256433</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>5.057314874306787e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.91216491664324</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-216.908</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.84275e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-82.01600000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3712415722778009</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7681077186466254</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.572560674978716</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.407791097233519</v>
+      </c>
+      <c r="J11" t="n">
+        <v>31.12591706524201</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.98087440031027</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 18.960x + -10739.298</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>491.7177670637182</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>75870617.73092788</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.976821138541326e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9144402532602752</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-216.77</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.84088e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-82.105</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1844831919820626</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.6739857610040001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.313280617144318</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.214114982038684</v>
+      </c>
+      <c r="J12" t="n">
+        <v>29.95762994529726</v>
+      </c>
+      <c r="K12" t="n">
+        <v>86.97241186449907</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 18.907x + -10565.599</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>486.5325252174118</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>204753851.1892565</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4.914478213336615e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9162589858672073</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-213.1899999999999</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.83809e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-82.199</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.4249880013605527</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9254426721455306</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.789217464113309</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.681695116388304</v>
+      </c>
+      <c r="J13" t="n">
+        <v>32.24005672723251</v>
+      </c>
+      <c r="K13" t="n">
+        <v>87.08989229112142</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 19.672x + -10893.423</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>481.5806828529448</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>63532016.46220312</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.847425979721743e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.91820321490492</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-213.2859999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.83662e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-82.285</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.2229958180739045</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.8098783898493622</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.483479980518545</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.51127637279823</v>
+      </c>
+      <c r="J14" t="n">
+        <v>31.16428450665931</v>
+      </c>
+      <c r="K14" t="n">
+        <v>87.08037495563323</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 19.607x + -10716.672</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>476.6142989058284</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>34719040.07934395</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4.789190806279649e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9199680325807008</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-207.846</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.83538e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-82.411</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1069132563020457</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.7566330338715134</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.49826997454913</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.414161421709404</v>
+      </c>
+      <c r="J15" t="n">
+        <v>32.20463424072356</v>
+      </c>
+      <c r="K15" t="n">
+        <v>87.14815463831815</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 20.074x + -10846.598</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>471.7503690363056</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>95155789.09695755</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4.721850160619705e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9220384885666901</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-207.2959999999999</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.83431e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-82.485</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.2599953909208527</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.6665271927382748</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.624212073871782</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.33935618651951</v>
+      </c>
+      <c r="J16" t="n">
+        <v>31.68626882161808</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87.15835274382547</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 20.146x + -10754.076</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>466.858430803799</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>31668267.24169507</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4.674301422127175e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9235213414672513</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-204.08</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.83203e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-82.575</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.5487363464406083</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.7594661872060658</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.735428617760149</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.629560626821093</v>
+      </c>
+      <c r="J17" t="n">
+        <v>33.42599918333797</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87.23197544047315</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 20.683x + -10933.572</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>462.0786899282044</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>84156379.74575013</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>4.623054450161197e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9250786051867066</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-206.425</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.82888e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-82.639</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.2259114136117077</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.921238223870265</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.533997681767349</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.593084344481601</v>
+      </c>
+      <c r="J18" t="n">
+        <v>33.26216382530165</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87.18183856214445</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 20.315x + -10585.008</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>457.3176790141066</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>71593270.90499125</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>4.578859941137327e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9263837980573263</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-202.2570000000001</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.82876e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-82.735</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.4846865284452188</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.6691511700532605</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.436285367942148</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.407571705129951</v>
+      </c>
+      <c r="J19" t="n">
+        <v>32.62174428416477</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.27012388388947</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 20.973x + -10822.605</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>452.6051858130465</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>127173917.7358479</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>4.531406817193074e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9279547040001043</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-199.603</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.82837e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-82.818</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.5685480551489587</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.9180277085792961</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.591984254281147</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.923081827536488</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34.25909381495194</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.34861679587324</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 21.594x + -11034.117</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>447.888471151404</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>491751706.2692647</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.488572168994832e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9293801009791647</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-202.359</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.82964e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-82.854</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.3304687489578453</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.037952017509317</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.711705619666134</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.921410984988565</v>
+      </c>
+      <c r="J21" t="n">
+        <v>34.32273751937691</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.3059686203291</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 21.252x + -10710.446</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>443.1211373369848</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>363911524.2865228</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>4.467858562237523e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9301653671972997</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-197.902</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.82777e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-82.958</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.703854115327763</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.114315075708262</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.796272688206721</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.812855008274102</v>
+      </c>
+      <c r="J22" t="n">
+        <v>34.52979177923569</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.40956623821799</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 22.103x + -11038.316</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>438.4015632563413</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>960195021.2010366</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>4.417689184530119e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9317673639640885</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +7372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,8 +7476,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1593,6 +7505,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-534.7510000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.05948e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-75.065</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1518543036625503</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5030252414278642</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.987279417240101</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.014955436750503</v>
+      </c>
+      <c r="J2" t="n">
+        <v>10.32629293475272</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.00603305668103</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 8.151x + -6335.223</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>569.5051116101438</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>116659959.6340644</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.515485762593364e-06</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.6372204845117558</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-377.962</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.01741e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-78.05800000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.4177179302916743</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.006972064821538</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.586522401151598</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.24382481230065</v>
+      </c>
+      <c r="J3" t="n">
+        <v>15.38354492705494</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.05074517941036</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 11.548x + -8134.556</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>575.3641575183071</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>38379155.83272927</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.067160613020955e-06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8085534560056014</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-312.7379999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.95421e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-79.31399999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5292454447679594</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9925065900218332</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.809440231966596</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.73799029204986</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20.41165572665592</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.92343413290865</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 14.031x + -9593.415</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>566.8042478641837</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>145897571.268115</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>8.073620234051986e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8470916785309134</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-286.981</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.91133e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-79.932</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4695683648931734</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7735580288927741</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.445354528228086</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.220838604786055</v>
+      </c>
+      <c r="J5" t="n">
+        <v>21.69378397708031</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.19816502605812</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 15.048x + -10061.966</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>560.3672242138649</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>176992424.1180134</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>7.099148494990775e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8642478143366645</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-265.9299999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.88235e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-80.39</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5007873700635117</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9605240468773862</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.457390950220939</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.157568150560628</v>
+      </c>
+      <c r="J6" t="n">
+        <v>23.51125867157126</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.42196559657212</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 15.992x + -10519.636</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>554.4775658602906</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>88895794.08971889</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>6.514220746783614e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.875691921496806</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-256.8040000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.86237e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-80.697</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1335457464475696</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6238033039451328</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.213781876480791</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.145311953224406</v>
+      </c>
+      <c r="J7" t="n">
+        <v>24.56617961729293</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.43352190917442</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 16.044x + -10352.698</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>548.2570902789527</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>99909522.09402075</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>6.150168519841109e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.883332063904636</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-250.348</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.84878e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-80.92100000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.02729329449694735</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7175362925637234</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.455353011685736</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.438201751048676</v>
+      </c>
+      <c r="J8" t="n">
+        <v>27.34888835308378</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.52270585445856</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 16.457x + -10443.751</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>541.2648713405404</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>92491285.65868892</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>5.88622311340895e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8892723593308981</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-243.2700000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.83987e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-81.14</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1774313961354733</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.4927069235837447</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.485669829019479</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.440324562956664</v>
+      </c>
+      <c r="J9" t="n">
+        <v>27.83838411295151</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.60543639433614</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 16.859x + -10521.287</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>534.0357262020848</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>166929280.4379201</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>5.667962330145158e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8945255653987479</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-233.41</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.83373e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-81.357</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.249257961380702</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5994697987555112</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.356443215093501</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.225371912564541</v>
+      </c>
+      <c r="J10" t="n">
+        <v>27.78227501361389</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.76147297195421</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 17.673x + -10874.552</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>527.2528466196694</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>74775660.93545045</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>5.473545957582736e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8994824292256811</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-231.587</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.82702e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-81.491</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.318691603017051</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8583919801009906</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.29536267660153</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.469898299306311</v>
+      </c>
+      <c r="J11" t="n">
+        <v>28.72742933942593</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.84743022847248</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 18.156x + -11013.884</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>520.7736857570653</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>26706286.64102941</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>5.332004591149701e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.903122309726817</v>
       </c>
     </row>
   </sheetData>
@@ -1606,7 +8038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,8 +8142,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1741,6 +8171,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-295.1759999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.91342e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-80.018</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.08583374704064571</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7829651845536957</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.10893314663245</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.370116833858698</v>
+      </c>
+      <c r="J2" t="n">
+        <v>21.990196249151</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.92556024130452</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 14.039x + -9158.240</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>547.9664443253914</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>93215787.65588757</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>6.939635490601613e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8678363533763579</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-255.207</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.87842e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-80.774</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5684313717551485</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9510172703587961</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.59014429248337</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.726232349617719</v>
+      </c>
+      <c r="J3" t="n">
+        <v>26.65632666340922</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.54639774254363</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 16.570x + -10509.761</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>537.4991265785268</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>57862755.58246504</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>6.065691900142197e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8862993888904903</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-245.075</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.86379e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-81.065</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5149237268149065</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8786640115978337</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.810999044456023</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.389445780248062</v>
+      </c>
+      <c r="J4" t="n">
+        <v>26.97480283591474</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.64529956532516</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 17.060x + -10608.342</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>530.7109260023144</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>105488576.7142147</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>5.758173367481633e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8934160988964353</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-239.784</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.85662e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-81.26600000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2537474531380859</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7214757517989263</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.570993226422273</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.610347507715892</v>
+      </c>
+      <c r="J5" t="n">
+        <v>28.71085235771254</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.66181290831521</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 17.144x + -10474.329</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>524.4008169650932</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>47287926.86292861</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>5.56448183668114e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8982269507417618</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-229.625</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.85421e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-81.471</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.390886244769942</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6909849067743499</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.751235407039793</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.537893845766785</v>
+      </c>
+      <c r="J6" t="n">
+        <v>30.23758459678186</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.76197193521575</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 17.676x + -10643.999</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>518.024247500451</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>428383340.7938696</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>5.40652754576415e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.902444843648141</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-225.261</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.85006e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-81.589</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9555756428957459</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.315045042119148</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.740183587122337</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.497459214884556</v>
+      </c>
+      <c r="J7" t="n">
+        <v>28.9663123889992</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.979944462888</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 18.954x + -11313.892</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>511.5433413446364</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>92248114.62733148</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>5.29188017937728e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9055003374462205</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-224.1279999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.84715e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-81.73699999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3377625930171204</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8250755894989609</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.58372775744833</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.67876767812929</v>
+      </c>
+      <c r="J8" t="n">
+        <v>31.27072749060132</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.87741783852587</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 18.331x + -10727.105</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>505.6986830688899</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>139970948.6951483</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>5.177933248446756e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9086471723769123</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-221.967</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.84692e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-81.85299999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1541840015388972</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6755157107586849</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.477613104122139</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.127527944177472</v>
+      </c>
+      <c r="J9" t="n">
+        <v>28.95393640399235</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.84655555079907</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 18.151x + -10454.029</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>500.4768936297417</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>108357798.1978788</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>5.092375615205946e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9111627086939513</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-218.792</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.84423e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-81.946</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4078655944126217</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7587368305605975</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.5902169262813</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.590321538996946</v>
+      </c>
+      <c r="J10" t="n">
+        <v>31.39616091349507</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.95966110405199</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 18.828x + -10752.447</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>495.8316412890505</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>49117446.11016729</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>5.016604731941381e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9133084016510483</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-215.9069999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.84401e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-82.04300000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2331292660330547</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7903272215680843</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.315222596289086</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.46922396422195</v>
+      </c>
+      <c r="J11" t="n">
+        <v>31.20982597677958</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.98409628041334</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 18.980x + -10717.797</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>491.507998089093</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>69117573.21617594</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.952188704965358e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9152588834803289</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-208.4490000000001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.84125e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-82.16200000000001</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.5189268514432951</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.186529876436508</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.500284793196752</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.816318850603243</v>
+      </c>
+      <c r="J12" t="n">
+        <v>32.80240563919204</v>
+      </c>
+      <c r="K12" t="n">
+        <v>87.17852881340522</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 20.291x + -11401.316</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>487.2697428654787</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>46273212.63543476</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4.875897573513626e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9174627818825303</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-211.398</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.84049e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-82.22199999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1225979136795229</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.6805490771345694</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.341136698616225</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.225850623824885</v>
+      </c>
+      <c r="J13" t="n">
+        <v>30.80337973747905</v>
+      </c>
+      <c r="K13" t="n">
+        <v>87.02715300243224</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 19.256x + -10647.365</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>483.0456321632749</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>24849814.10408894</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.829111383721641e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9189007219389907</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-211.178</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.83889e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-82.27500000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3863263557016656</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.7653547624323053</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.465837289713333</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.377468336201795</v>
+      </c>
+      <c r="J14" t="n">
+        <v>31.3376871048653</v>
+      </c>
+      <c r="K14" t="n">
+        <v>87.08219185903415</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 19.620x + -10752.265</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>478.8588952335851</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>266380733.539689</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4.789943805447928e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9200706906958396</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-209.9589999999999</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.83738e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-82.34999999999999</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.2210537063047321</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.8412132280423287</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.651851807897816</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.614445095231277</v>
+      </c>
+      <c r="J15" t="n">
+        <v>32.2778547799313</v>
+      </c>
+      <c r="K15" t="n">
+        <v>87.14457214625331</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 20.049x + -10888.254</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>474.4818621580082</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>40832017.37799203</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4.739697264837431e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9215977562384815</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-208.5889999999999</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.83853e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-82.437</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1455696549551709</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.7204313095915499</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.514286690175575</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.430058043174661</v>
+      </c>
+      <c r="J16" t="n">
+        <v>32.71924555210143</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87.08989090121656</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 19.672x + -10537.927</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>470.0625771674634</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>21239918.33952826</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4.690785734777748e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9232297164426132</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-201.9459999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.83517e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-82.554</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.353172966429084</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.8533170836166445</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.646468480853425</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.50989477090713</v>
+      </c>
+      <c r="J17" t="n">
+        <v>33.05630545225473</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87.21773574782559</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 20.577x + -10935.075</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>465.4910873318984</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>34362732.61023357</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>4.626030484468354e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9251609817807634</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-205.5700000000001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.83744e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-82.595</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.249862290531432</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.8059037501360673</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.527767362974654</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.645346230897843</v>
+      </c>
+      <c r="J18" t="n">
+        <v>33.35405405651718</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87.16706724953259</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 20.208x + -10590.591</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>460.6489042436971</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>43335205.01146992</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>4.601242245427078e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9261112268002031</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-201.932</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.83754e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-82.68899999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.05633686578266573</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.8239710625401686</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.537285179329418</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.592286347858283</v>
+      </c>
+      <c r="J19" t="n">
+        <v>33.9469875343128</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.21032039201737</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 20.522x + -10635.707</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>455.8594330283174</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>256573807.4067802</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>4.554384756374948e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9276727639520341</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-198.461</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.83824e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-82.788</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3593255064743227</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.9421891549012992</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.532018026854516</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.618802209315676</v>
+      </c>
+      <c r="J20" t="n">
+        <v>33.33530995131347</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.30069984518549</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 21.210x + -10879.134</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>450.9635551348287</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>988076045.3561549</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.50762229766592e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9292712810907091</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-199.328</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.83751e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-82.851</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.09811535866251042</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.6981661394167925</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.382915312401741</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.407994697939833</v>
+      </c>
+      <c r="J21" t="n">
+        <v>33.2093896900528</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.2441757536334</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 20.775x + -10495.122</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>445.9830181602341</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>488326387.5058805</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>4.470452847620055e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9305060312548025</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-199.673</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.83923e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-82.907</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.2261935463304488</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9866104066092124</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.815770215577326</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.776880432012301</v>
+      </c>
+      <c r="J22" t="n">
+        <v>34.3193966369405</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.31182169016245</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 21.298x + -10645.465</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>440.9473525323475</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1206183583.512786</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>4.441706051422483e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9315892506785497</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +9276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,8 +9380,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1889,6 +9409,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-429.665</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.03843e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-77.922</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2804483917255284</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6635737981781917</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.38673179752035</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.208060107760302</v>
+      </c>
+      <c r="J2" t="n">
+        <v>13.17569599186616</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.5133461030688</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 10.411x + -6824.026</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>542.5417400869246</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>31871926.16182702</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>9.934221897037078e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8205913635682168</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-307.0839999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.91101e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-80.047</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.611664857453694</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.111596759432212</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.624201966847215</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.611650661924425</v>
+      </c>
+      <c r="J3" t="n">
+        <v>20.37658608731827</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.0943897065048</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 14.647x + -9346.520</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>534.5275004114219</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>54168483.1330822</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>6.836591868196212e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8699732645591437</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-269.687</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.87153e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-80.747</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3707517293675382</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9462329514761778</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.678657016922006</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.385048439899204</v>
+      </c>
+      <c r="J4" t="n">
+        <v>23.23822786510243</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.47226453130855</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 16.221x + -10130.083</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>527.5934801188311</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>72966020.88517547</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>6.103850501617336e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8849539937637688</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-254.099</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.84839e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-81.136</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1330456800647542</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7390981951279173</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.490593317097356</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.57145575400193</v>
+      </c>
+      <c r="J5" t="n">
+        <v>26.71279136562681</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.53266663490025</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 16.504x + -10076.725</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>520.8682801464658</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>114785839.3222648</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>5.721278687584216e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8935185642558439</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-243.399</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.83502e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-81.398</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2795717234870711</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8701302910010361</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.580532251859992</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.610014391063092</v>
+      </c>
+      <c r="J6" t="n">
+        <v>28.25574333708228</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.67475184115797</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 17.211x + -10335.544</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>513.7502163522338</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>38077614.66728316</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>5.474057726749312e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8995070606125547</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-236.676</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.82778e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-81.61799999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.08815178501487596</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6052080682534858</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.253285817308732</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.428300129408596</v>
+      </c>
+      <c r="J7" t="n">
+        <v>28.23193793284035</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.72904003429538</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 17.497x + -10308.856</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>506.1801091238793</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>50003174.50793667</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>5.289251399962977e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9043317162757228</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-227.811</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.82205e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-81.819</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4564670861251693</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.034316496873777</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.553107539381966</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.209308547262005</v>
+      </c>
+      <c r="J8" t="n">
+        <v>28.65632431673984</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.90958148089945</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 18.522x + -10751.881</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>498.7623392797444</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>275023896.081173</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>5.13280953960211e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9085852952268905</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-224.901</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.81724e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-81.982</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4548659900338863</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8524282890547806</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.414799412093713</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.475347469072354</v>
+      </c>
+      <c r="J9" t="n">
+        <v>30.11344160407834</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.91030666967617</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 18.526x + -10547.317</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>491.8533849089092</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>36139828.88406774</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>5.003821300762556e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9122007141068961</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-219.343</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.81539e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-82.143</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1569785937668468</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5507096735849466</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.459997404191794</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.248624820078149</v>
+      </c>
+      <c r="J10" t="n">
+        <v>29.74833637696018</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.93694325489693</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 18.688x + -10459.670</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>485.409008110134</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>233911311.9730988</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4.900493783458515e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9152618739857541</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-209.6030000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.81199e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-82.31</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4286097703818519</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.952006245847078</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.697808270918003</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.889110563778867</v>
+      </c>
+      <c r="J11" t="n">
+        <v>33.93411923311126</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.12345974629464</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 19.902x + -11019.945</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>479.4517673951738</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>273971676.1830353</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.794897629054564e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.918381809651342</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 52.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 52.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -588,19 +588,19 @@
       <c r="K2" t="n">
         <v>85.71780556973803</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 13.355x + -8803.943</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-8803.943089349516</v>
       </c>
       <c r="Y2" t="n">
         <v>551.6818235263696</v>
       </c>
       <c r="Z2" t="n">
-        <v>139537132.2274952</v>
+        <v>334.601</v>
       </c>
       <c r="AA2" t="n">
         <v>7.206532355596467e-07</v>
@@ -640,19 +640,19 @@
       <c r="K3" t="n">
         <v>86.23158024381881</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 15.182x + -9879.710</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-9879.710328565614</v>
       </c>
       <c r="Y3" t="n">
         <v>545.3859073851647</v>
       </c>
       <c r="Z3" t="n">
-        <v>33031208.38257015</v>
+        <v>292.971</v>
       </c>
       <c r="AA3" t="n">
         <v>6.267127526616215e-07</v>
@@ -692,19 +692,19 @@
       <c r="K4" t="n">
         <v>86.49600551653742</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 16.331x + -10470.742</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-10470.7424904319</v>
       </c>
       <c r="Y4" t="n">
         <v>537.7848296526171</v>
       </c>
       <c r="Z4" t="n">
-        <v>41283398.12183786</v>
+        <v>277.398</v>
       </c>
       <c r="AA4" t="n">
         <v>5.890070855591323e-07</v>
@@ -744,19 +744,19 @@
       <c r="K5" t="n">
         <v>86.59700764419834</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 16.817x + -10543.290</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-10543.2899082422</v>
       </c>
       <c r="Y5" t="n">
         <v>529.0813057894175</v>
       </c>
       <c r="Z5" t="n">
-        <v>74804313.00622916</v>
+        <v>264.223</v>
       </c>
       <c r="AA5" t="n">
         <v>5.5989793164035e-07</v>
@@ -796,19 +796,19 @@
       <c r="K6" t="n">
         <v>86.59963449745547</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 16.830x + -10285.131</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-10285.13111244457</v>
       </c>
       <c r="Y6" t="n">
         <v>520.1197093400756</v>
       </c>
       <c r="Z6" t="n">
-        <v>39945648.51106961</v>
+        <v>257.091</v>
       </c>
       <c r="AA6" t="n">
         <v>5.362107796516958e-07</v>
@@ -848,19 +848,19 @@
       <c r="K7" t="n">
         <v>86.56151000208058</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 16.643x + -9915.337</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-9915.337206015489</v>
       </c>
       <c r="Y7" t="n">
         <v>511.449997744861</v>
       </c>
       <c r="Z7" t="n">
-        <v>46634350.48192126</v>
+        <v>254.6809999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>5.18164608234583e-07</v>
@@ -900,19 +900,19 @@
       <c r="K8" t="n">
         <v>86.79121995036104</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 17.837x + -10467.278</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-10467.27842527503</v>
       </c>
       <c r="Y8" t="n">
         <v>503.0960003368983</v>
       </c>
       <c r="Z8" t="n">
-        <v>208007705.727629</v>
+        <v>245.98</v>
       </c>
       <c r="AA8" t="n">
         <v>5.032855244703399e-07</v>
@@ -952,19 +952,19 @@
       <c r="K9" t="n">
         <v>86.75443229110743</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 17.635x + -10109.590</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-10109.59046943449</v>
       </c>
       <c r="Y9" t="n">
         <v>495.2601629230304</v>
       </c>
       <c r="Z9" t="n">
-        <v>44565443.13058098</v>
+        <v>242.769</v>
       </c>
       <c r="AA9" t="n">
         <v>4.903602942740081e-07</v>
@@ -1004,19 +1004,19 @@
       <c r="K10" t="n">
         <v>86.86399061391251</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 18.252x + -10290.041</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-10290.04093702186</v>
       </c>
       <c r="Y10" t="n">
         <v>487.5726900698414</v>
       </c>
       <c r="Z10" t="n">
-        <v>34386439.88839921</v>
+        <v>238.725</v>
       </c>
       <c r="AA10" t="n">
         <v>4.798176144455605e-07</v>
@@ -1056,19 +1056,19 @@
       <c r="K11" t="n">
         <v>86.86201561837873</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 18.241x + -10084.219</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-10084.21876871057</v>
       </c>
       <c r="Y11" t="n">
         <v>480.5862591691507</v>
       </c>
       <c r="Z11" t="n">
-        <v>26881734.4222526</v>
+        <v>234.853</v>
       </c>
       <c r="AA11" t="n">
         <v>4.696682508126709e-07</v>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1254,19 +1254,19 @@
       <c r="K2" t="n">
         <v>86.65426769437698</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 17.106x + -11249.976</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-11249.97607059805</v>
       </c>
       <c r="Y2" t="n">
         <v>547.6190726842345</v>
       </c>
       <c r="Z2" t="n">
-        <v>41080721.47866023</v>
+        <v>234.155</v>
       </c>
       <c r="AA2" t="n">
         <v>5.843129485523733e-07</v>
@@ -1306,19 +1306,19 @@
       <c r="K3" t="n">
         <v>86.67621761930589</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 17.219x + -10861.799</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-10861.79937310117</v>
       </c>
       <c r="Y3" t="n">
         <v>536.3130500260861</v>
       </c>
       <c r="Z3" t="n">
-        <v>41194474.90584817</v>
+        <v>230.4929999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>5.549820417865719e-07</v>
@@ -1358,19 +1358,19 @@
       <c r="K4" t="n">
         <v>86.75859743134012</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 17.657x + -10951.553</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-10951.55297359674</v>
       </c>
       <c r="Y4" t="n">
         <v>530.5014166093951</v>
       </c>
       <c r="Z4" t="n">
-        <v>67697417.42539169</v>
+        <v>221.836</v>
       </c>
       <c r="AA4" t="n">
         <v>5.38037091704937e-07</v>
@@ -1410,19 +1410,19 @@
       <c r="K5" t="n">
         <v>86.88584835855085</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 18.380x + -11286.664</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-11286.66355718546</v>
       </c>
       <c r="Y5" t="n">
         <v>525.0447999738915</v>
       </c>
       <c r="Z5" t="n">
-        <v>38322631.85220434</v>
+        <v>220.027</v>
       </c>
       <c r="AA5" t="n">
         <v>5.280000921525257e-07</v>
@@ -1462,19 +1462,19 @@
       <c r="K6" t="n">
         <v>86.89498427597836</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 18.435x + -11158.796</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-11158.79633193113</v>
       </c>
       <c r="Y6" t="n">
         <v>519.1276913944876</v>
       </c>
       <c r="Z6" t="n">
-        <v>22421880.91333796</v>
+        <v>220.256</v>
       </c>
       <c r="AA6" t="n">
         <v>5.18061558625732e-07</v>
@@ -1514,19 +1514,19 @@
       <c r="K7" t="n">
         <v>86.85517826461805</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 18.201x + -10830.426</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-10830.42604100653</v>
       </c>
       <c r="Y7" t="n">
         <v>512.8851005325013</v>
       </c>
       <c r="Z7" t="n">
-        <v>61754128.69018628</v>
+        <v>218.9880000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>5.098815646727138e-07</v>
@@ -1566,19 +1566,19 @@
       <c r="K8" t="n">
         <v>86.93421380474906</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 18.671x + -10961.225</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-10961.22474682713</v>
       </c>
       <c r="Y8" t="n">
         <v>506.692379193322</v>
       </c>
       <c r="Z8" t="n">
-        <v>279841143.0356812</v>
+        <v>218.954</v>
       </c>
       <c r="AA8" t="n">
         <v>5.014855124558051e-07</v>
@@ -1618,19 +1618,19 @@
       <c r="K9" t="n">
         <v>87.03752674193467</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 19.323x + -11209.177</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-11209.17712077081</v>
       </c>
       <c r="Y9" t="n">
         <v>500.7779678278371</v>
       </c>
       <c r="Z9" t="n">
-        <v>27874041.96337112</v>
+        <v>215.292</v>
       </c>
       <c r="AA9" t="n">
         <v>4.928337765878669e-07</v>
@@ -1670,19 +1670,19 @@
       <c r="K10" t="n">
         <v>87.08724637754925</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 19.654x + -11255.070</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-11255.07046605867</v>
       </c>
       <c r="Y10" t="n">
         <v>495.285121895397</v>
       </c>
       <c r="Z10" t="n">
-        <v>271600469.696499</v>
+        <v>212.5799999999999</v>
       </c>
       <c r="AA10" t="n">
         <v>4.859172518199393e-07</v>
@@ -1722,19 +1722,19 @@
       <c r="K11" t="n">
         <v>87.04147941380815</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 19.349x + -10902.551</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-10902.55060148231</v>
       </c>
       <c r="Y11" t="n">
         <v>489.9210250392429</v>
       </c>
       <c r="Z11" t="n">
-        <v>29405537.75678721</v>
+        <v>210.2869999999999</v>
       </c>
       <c r="AA11" t="n">
         <v>4.787743942065891e-07</v>
@@ -1774,19 +1774,19 @@
       <c r="K12" t="n">
         <v>87.07824229333619</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 19.593x + -10902.467</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-10902.4667195866</v>
       </c>
       <c r="Y12" t="n">
         <v>484.5950792194721</v>
       </c>
       <c r="Z12" t="n">
-        <v>65902059.67108587</v>
+        <v>209.203</v>
       </c>
       <c r="AA12" t="n">
         <v>4.732247315029527e-07</v>
@@ -1826,19 +1826,19 @@
       <c r="K13" t="n">
         <v>87.11377880852471</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 19.835x + -10907.048</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-10907.04836233583</v>
       </c>
       <c r="Y13" t="n">
         <v>479.2207077071099</v>
       </c>
       <c r="Z13" t="n">
-        <v>24082961.64675545</v>
+        <v>207.611</v>
       </c>
       <c r="AA13" t="n">
         <v>4.683395449795387e-07</v>
@@ -1878,19 +1878,19 @@
       <c r="K14" t="n">
         <v>87.21412335674272</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 20.550x + -11178.803</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-11178.80252208924</v>
       </c>
       <c r="Y14" t="n">
         <v>474.0124014865988</v>
       </c>
       <c r="Z14" t="n">
-        <v>48531238.15834387</v>
+        <v>205.4829999999999</v>
       </c>
       <c r="AA14" t="n">
         <v>4.630164582235506e-07</v>
@@ -1930,19 +1930,19 @@
       <c r="K15" t="n">
         <v>87.15981267349734</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 20.157x + -10797.024</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-10797.02377499621</v>
       </c>
       <c r="Y15" t="n">
         <v>469.0075452841498</v>
       </c>
       <c r="Z15" t="n">
-        <v>28576826.45869574</v>
+        <v>204.12</v>
       </c>
       <c r="AA15" t="n">
         <v>4.576311750516199e-07</v>
@@ -1982,19 +1982,19 @@
       <c r="K16" t="n">
         <v>86.99169329717583</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 19.028x + -10004.553</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-10004.5531730878</v>
       </c>
       <c r="Y16" t="n">
         <v>464.0837279452896</v>
       </c>
       <c r="Z16" t="n">
-        <v>41656734.77073652</v>
+        <v>207.12</v>
       </c>
       <c r="AA16" t="n">
         <v>4.537056640989806e-07</v>
@@ -2034,19 +2034,19 @@
       <c r="K17" t="n">
         <v>87.28457759564253</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 21.084x + -11054.079</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-11054.07949912203</v>
       </c>
       <c r="Y17" t="n">
         <v>459.2088586320658</v>
       </c>
       <c r="Z17" t="n">
-        <v>73142621.77350013</v>
+        <v>198.9010000000001</v>
       </c>
       <c r="AA17" t="n">
         <v>4.491448263308566e-07</v>
@@ -2086,19 +2086,19 @@
       <c r="K18" t="n">
         <v>87.23301847851154</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 20.691x + -10695.261</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-10695.26111207464</v>
       </c>
       <c r="Y18" t="n">
         <v>454.2969709553919</v>
       </c>
       <c r="Z18" t="n">
-        <v>38835982.37046302</v>
+        <v>202.994</v>
       </c>
       <c r="AA18" t="n">
         <v>4.459785110598263e-07</v>
@@ -2138,19 +2138,19 @@
       <c r="K19" t="n">
         <v>87.37575716610981</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 21.818x + -11183.551</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-11183.55084380444</v>
       </c>
       <c r="Y19" t="n">
         <v>449.4719906849796</v>
       </c>
       <c r="Z19" t="n">
-        <v>369854107.262041</v>
+        <v>195.3389999999999</v>
       </c>
       <c r="AA19" t="n">
         <v>4.413194965873209e-07</v>
@@ -2190,19 +2190,19 @@
       <c r="K20" t="n">
         <v>87.24963659107635</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 20.816x + -10488.219</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-10488.21905324031</v>
       </c>
       <c r="Y20" t="n">
         <v>444.6512127779001</v>
       </c>
       <c r="Z20" t="n">
-        <v>730005415.09552</v>
+        <v>199.119</v>
       </c>
       <c r="AA20" t="n">
         <v>4.380704721093446e-07</v>
@@ -2242,19 +2242,19 @@
       <c r="K21" t="n">
         <v>87.32376809483063</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 21.394x + -10670.263</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-10670.26348242676</v>
       </c>
       <c r="Y21" t="n">
         <v>439.9087363251003</v>
       </c>
       <c r="Z21" t="n">
-        <v>134598211.1798755</v>
+        <v>198.011</v>
       </c>
       <c r="AA21" t="n">
         <v>4.34392041140991e-07</v>
@@ -2294,19 +2294,19 @@
       <c r="K22" t="n">
         <v>87.26219463846495</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 20.912x + -10266.411</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-10266.41063451135</v>
       </c>
       <c r="Y22" t="n">
         <v>411.244001256769</v>
       </c>
       <c r="Z22" t="n">
-        <v>5842.653011486986</v>
+        <v>195.548</v>
       </c>
       <c r="AA22" t="n">
         <v>4.641218700590199e-07</v>
@@ -2432,12 +2432,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2492,19 +2492,19 @@
       <c r="K2" t="n">
         <v>86.36910546666731</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 15.759x + -10152.088</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-10152.08803456429</v>
       </c>
       <c r="Y2" t="n">
         <v>543.0744978851715</v>
       </c>
       <c r="Z2" t="n">
-        <v>56623007.34436025</v>
+        <v>263.9880000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>5.820828483546218e-07</v>
@@ -2544,19 +2544,19 @@
       <c r="K3" t="n">
         <v>86.60296144379556</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 16.847x + -10602.849</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-10602.84886892514</v>
       </c>
       <c r="Y3" t="n">
         <v>535.3777738037471</v>
       </c>
       <c r="Z3" t="n">
-        <v>26357392.43708407</v>
+        <v>243.1039999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>5.475926748889934e-07</v>
@@ -2596,19 +2596,19 @@
       <c r="K4" t="n">
         <v>86.67231898498879</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 17.199x + -10667.685</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-10667.68510282975</v>
       </c>
       <c r="Y4" t="n">
         <v>529.6461565578179</v>
       </c>
       <c r="Z4" t="n">
-        <v>72818556.39952733</v>
+        <v>237.33</v>
       </c>
       <c r="AA4" t="n">
         <v>5.311393192374377e-07</v>
@@ -2648,19 +2648,19 @@
       <c r="K5" t="n">
         <v>86.66415580087778</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 17.156x + -10474.874</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-10474.87440678367</v>
       </c>
       <c r="Y5" t="n">
         <v>523.4266567912304</v>
       </c>
       <c r="Z5" t="n">
-        <v>122210555.2592653</v>
+        <v>235.2190000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>5.185988259768235e-07</v>
@@ -2700,19 +2700,19 @@
       <c r="K6" t="n">
         <v>86.66871586387042</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 17.180x + -10319.194</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-10319.1937841465</v>
       </c>
       <c r="Y6" t="n">
         <v>516.9120811162061</v>
       </c>
       <c r="Z6" t="n">
-        <v>40063527.89311381</v>
+        <v>234.439</v>
       </c>
       <c r="AA6" t="n">
         <v>5.082977602685361e-07</v>
@@ -2752,19 +2752,19 @@
       <c r="K7" t="n">
         <v>86.76167165566486</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 17.674x + -10475.098</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-10475.09841175652</v>
       </c>
       <c r="Y7" t="n">
         <v>510.8136599619593</v>
       </c>
       <c r="Z7" t="n">
-        <v>284246405.3912622</v>
+        <v>231.372</v>
       </c>
       <c r="AA7" t="n">
         <v>4.968564906094457e-07</v>
@@ -2804,19 +2804,19 @@
       <c r="K8" t="n">
         <v>86.95632860802702</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 18.807x + -11051.800</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-11051.79958285651</v>
       </c>
       <c r="Y8" t="n">
         <v>505.1418191579408</v>
       </c>
       <c r="Z8" t="n">
-        <v>277296170.3229762</v>
+        <v>224.895</v>
       </c>
       <c r="AA8" t="n">
         <v>4.877483991057653e-07</v>
@@ -2856,19 +2856,19 @@
       <c r="K9" t="n">
         <v>86.87427225247617</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 18.312x + -10583.594</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-10583.59431202855</v>
       </c>
       <c r="Y9" t="n">
         <v>500.0446173133178</v>
       </c>
       <c r="Z9" t="n">
-        <v>274974229.9535233</v>
+        <v>224.9209999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>4.79742023833454e-07</v>
@@ -2908,19 +2908,19 @@
       <c r="K10" t="n">
         <v>86.86927920047472</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 18.283x + -10423.537</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-10423.537255714</v>
       </c>
       <c r="Y10" t="n">
         <v>494.8353524461027</v>
       </c>
       <c r="Z10" t="n">
-        <v>40287277.71094939</v>
+        <v>222.99</v>
       </c>
       <c r="AA10" t="n">
         <v>4.718427542435358e-07</v>
@@ -2960,19 +2960,19 @@
       <c r="K11" t="n">
         <v>87.0820691243071</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 19.619x + -11127.105</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-11127.10472409307</v>
       </c>
       <c r="Y11" t="n">
         <v>489.6967757098946</v>
       </c>
       <c r="Z11" t="n">
-        <v>93252368.58251798</v>
+        <v>221.408</v>
       </c>
       <c r="AA11" t="n">
         <v>4.667191217373455e-07</v>
@@ -3012,19 +3012,19 @@
       <c r="K12" t="n">
         <v>86.96906348641619</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 18.886x + -10527.286</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-10527.28559566131</v>
       </c>
       <c r="Y12" t="n">
         <v>484.7401896710014</v>
       </c>
       <c r="Z12" t="n">
-        <v>43591990.13423891</v>
+        <v>223.4059999999999</v>
       </c>
       <c r="AA12" t="n">
         <v>4.60055500071584e-07</v>
@@ -3064,19 +3064,19 @@
       <c r="K13" t="n">
         <v>86.96053611362325</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 18.833x + -10361.677</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-10361.67708609466</v>
       </c>
       <c r="Y13" t="n">
         <v>479.8687543644011</v>
       </c>
       <c r="Z13" t="n">
-        <v>34107853.48462652</v>
+        <v>223.115</v>
       </c>
       <c r="AA13" t="n">
         <v>4.551564263780891e-07</v>
@@ -3116,19 +3116,19 @@
       <c r="K14" t="n">
         <v>87.06517073585158</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 19.506x + -10639.553</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-10639.55258907091</v>
       </c>
       <c r="Y14" t="n">
         <v>474.935735704342</v>
       </c>
       <c r="Z14" t="n">
-        <v>34295332.13532727</v>
+        <v>221.7230000000001</v>
       </c>
       <c r="AA14" t="n">
         <v>4.500449046646251e-07</v>
@@ -3168,19 +3168,19 @@
       <c r="K15" t="n">
         <v>86.99561330577383</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 19.053x + -10227.207</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-10227.20672708117</v>
       </c>
       <c r="Y15" t="n">
         <v>469.9476069863769</v>
       </c>
       <c r="Z15" t="n">
-        <v>98475152.46562451</v>
+        <v>221.58</v>
       </c>
       <c r="AA15" t="n">
         <v>4.451062441172622e-07</v>
@@ -3220,19 +3220,19 @@
       <c r="K16" t="n">
         <v>87.05295416989037</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 19.425x + -10325.280</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-10325.28024842519</v>
       </c>
       <c r="Y16" t="n">
         <v>465.0514139133583</v>
       </c>
       <c r="Z16" t="n">
-        <v>255587382.3131509</v>
+        <v>223.1289999999999</v>
       </c>
       <c r="AA16" t="n">
         <v>4.415980302388228e-07</v>
@@ -3272,19 +3272,19 @@
       <c r="K17" t="n">
         <v>87.23156072950334</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 20.680x + -10911.608</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-10911.60845700028</v>
       </c>
       <c r="Y17" t="n">
         <v>460.1691662592226</v>
       </c>
       <c r="Z17" t="n">
-        <v>15734840.3135771</v>
+        <v>214.172</v>
       </c>
       <c r="AA17" t="n">
         <v>4.344326980192154e-07</v>
@@ -3324,19 +3324,19 @@
       <c r="K18" t="n">
         <v>87.12206384450741</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 19.892x + -10328.823</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-10328.82297298489</v>
       </c>
       <c r="Y18" t="n">
         <v>455.2142059110784</v>
       </c>
       <c r="Z18" t="n">
-        <v>48458271.54523466</v>
+        <v>222.645</v>
       </c>
       <c r="AA18" t="n">
         <v>4.330306852580111e-07</v>
@@ -3376,19 +3376,19 @@
       <c r="K19" t="n">
         <v>87.24135507798749</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 20.753x + -10687.451</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-10687.45139629967</v>
       </c>
       <c r="Y19" t="n">
         <v>450.3106340980862</v>
       </c>
       <c r="Z19" t="n">
-        <v>246346300.6498589</v>
+        <v>218.611</v>
       </c>
       <c r="AA19" t="n">
         <v>4.289298240777591e-07</v>
@@ -3428,19 +3428,19 @@
       <c r="K20" t="n">
         <v>87.30505889277259</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 21.245x + -10821.880</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-10821.87992804147</v>
       </c>
       <c r="Y20" t="n">
         <v>445.3910988715893</v>
       </c>
       <c r="Z20" t="n">
-        <v>195607532.1833709</v>
+        <v>217.1019999999999</v>
       </c>
       <c r="AA20" t="n">
         <v>4.248476336062204e-07</v>
@@ -3480,19 +3480,19 @@
       <c r="K21" t="n">
         <v>87.21328819958147</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 20.544x + -10284.192</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-10284.19174682864</v>
       </c>
       <c r="Y21" t="n">
         <v>440.4655235058564</v>
       </c>
       <c r="Z21" t="n">
-        <v>362063644.571839</v>
+        <v>217.189</v>
       </c>
       <c r="AA21" t="n">
         <v>4.211295957905756e-07</v>
@@ -3532,19 +3532,19 @@
       <c r="K22" t="n">
         <v>87.22402722824856</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 20.624x + -10197.540</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-10197.54011435341</v>
       </c>
       <c r="Y22" t="n">
         <v>435.5708022825369</v>
       </c>
       <c r="Z22" t="n">
-        <v>178925621.5317138</v>
+        <v>220.836</v>
       </c>
       <c r="AA22" t="n">
         <v>4.18400320375367e-07</v>
@@ -3670,12 +3670,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -3730,19 +3730,19 @@
       <c r="K2" t="n">
         <v>84.45633435361003</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 10.303x + -8414.234</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-8414.234368814468</v>
       </c>
       <c r="Y2" t="n">
         <v>604.3463217163657</v>
       </c>
       <c r="Z2" t="n">
-        <v>323573447.6931999</v>
+        <v>469.704</v>
       </c>
       <c r="AA2" t="n">
         <v>1.882895778045228e-06</v>
@@ -3782,19 +3782,19 @@
       <c r="K3" t="n">
         <v>85.68401314913133</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 13.250x + -9702.424</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-9702.424239303427</v>
       </c>
       <c r="Y3" t="n">
         <v>589.3048081097292</v>
       </c>
       <c r="Z3" t="n">
-        <v>75420614.09982227</v>
+        <v>350.398</v>
       </c>
       <c r="AA3" t="n">
         <v>8.76482784692416e-07</v>
@@ -3834,19 +3834,19 @@
       <c r="K4" t="n">
         <v>86.07626047625904</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 14.580x + -10234.312</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-10234.31203384862</v>
       </c>
       <c r="Y4" t="n">
         <v>577.1142193154957</v>
       </c>
       <c r="Z4" t="n">
-        <v>190376014.7478443</v>
+        <v>306.0550000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>7.30842803239554e-07</v>
@@ -3886,19 +3886,19 @@
       <c r="K5" t="n">
         <v>86.21622237633349</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 15.120x + -10318.560</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-10318.5601255436</v>
       </c>
       <c r="Y5" t="n">
         <v>567.9871590781264</v>
       </c>
       <c r="Z5" t="n">
-        <v>76725641.15732116</v>
+        <v>286.706</v>
       </c>
       <c r="AA5" t="n">
         <v>6.634786282406896e-07</v>
@@ -3938,19 +3938,19 @@
       <c r="K6" t="n">
         <v>86.53569117561379</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 16.519x + -11107.115</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-11107.11539047141</v>
       </c>
       <c r="Y6" t="n">
         <v>559.6763142710811</v>
       </c>
       <c r="Z6" t="n">
-        <v>133734960.9734585</v>
+        <v>271.024</v>
       </c>
       <c r="AA6" t="n">
         <v>6.206783793336595e-07</v>
@@ -3990,19 +3990,19 @@
       <c r="K7" t="n">
         <v>86.64416046751572</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 17.054x + -11236.524</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-11236.52387553937</v>
       </c>
       <c r="Y7" t="n">
         <v>551.4612662733882</v>
       </c>
       <c r="Z7" t="n">
-        <v>79667415.47283565</v>
+        <v>259.5440000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>5.886170529079986e-07</v>
@@ -4042,19 +4042,19 @@
       <c r="K8" t="n">
         <v>86.7000471683982</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 17.343x + -11214.333</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-11214.33325122697</v>
       </c>
       <c r="Y8" t="n">
         <v>543.3157354088189</v>
       </c>
       <c r="Z8" t="n">
-        <v>110229427.7902048</v>
+        <v>259.509</v>
       </c>
       <c r="AA8" t="n">
         <v>5.676922735456703e-07</v>
@@ -4094,19 +4094,19 @@
       <c r="K9" t="n">
         <v>86.73254258456815</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 17.516x + -11079.724</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-11079.7237515102</v>
       </c>
       <c r="Y9" t="n">
         <v>535.332687899152</v>
       </c>
       <c r="Z9" t="n">
-        <v>151031625.3812257</v>
+        <v>250.301</v>
       </c>
       <c r="AA9" t="n">
         <v>5.446282324568905e-07</v>
@@ -4146,19 +4146,19 @@
       <c r="K10" t="n">
         <v>86.60887503835845</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 16.876x + -10421.289</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-10421.2894128726</v>
       </c>
       <c r="Y10" t="n">
         <v>527.7492158615748</v>
       </c>
       <c r="Z10" t="n">
-        <v>69139694.95995358</v>
+        <v>250.181</v>
       </c>
       <c r="AA10" t="n">
         <v>5.283929184470241e-07</v>
@@ -4198,19 +4198,19 @@
       <c r="K11" t="n">
         <v>86.77269245723578</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 17.735x + -10800.379</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-10800.37868419815</v>
       </c>
       <c r="Y11" t="n">
         <v>520.5777571939508</v>
       </c>
       <c r="Z11" t="n">
-        <v>38550024.03899003</v>
+        <v>244.0300000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>5.133228685586095e-07</v>
@@ -4336,12 +4336,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4396,19 +4396,19 @@
       <c r="K2" t="n">
         <v>85.95620854890785</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 14.145x + -9296.020</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-9296.019665877137</v>
       </c>
       <c r="Y2" t="n">
         <v>548.4584993393676</v>
       </c>
       <c r="Z2" t="n">
-        <v>33868013.95077544</v>
+        <v>308.104</v>
       </c>
       <c r="AA2" t="n">
         <v>6.64534361249985e-07</v>
@@ -4448,19 +4448,19 @@
       <c r="K3" t="n">
         <v>86.49145820315111</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 16.310x + -10345.659</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-10345.65935742836</v>
       </c>
       <c r="Y3" t="n">
         <v>537.210201868043</v>
       </c>
       <c r="Z3" t="n">
-        <v>118712454.8685306</v>
+        <v>262.4930000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>5.822641005546925e-07</v>
@@ -4500,19 +4500,19 @@
       <c r="K4" t="n">
         <v>86.50976978264542</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 16.396x + -10165.137</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-10165.13698237332</v>
       </c>
       <c r="Y4" t="n">
         <v>530.4059993973187</v>
       </c>
       <c r="Z4" t="n">
-        <v>71146535.65390402</v>
+        <v>251.874</v>
       </c>
       <c r="AA4" t="n">
         <v>5.538610796403511e-07</v>
@@ -4552,19 +4552,19 @@
       <c r="K5" t="n">
         <v>86.60947427756916</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 16.879x + -10311.454</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-10311.45445201213</v>
       </c>
       <c r="Y5" t="n">
         <v>523.9412351233299</v>
       </c>
       <c r="Z5" t="n">
-        <v>43833349.28309046</v>
+        <v>245.47</v>
       </c>
       <c r="AA5" t="n">
         <v>5.362085377543871e-07</v>
@@ -4604,19 +4604,19 @@
       <c r="K6" t="n">
         <v>86.62786991769364</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 16.971x + -10188.710</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-10188.70953644262</v>
       </c>
       <c r="Y6" t="n">
         <v>517.1734637849278</v>
       </c>
       <c r="Z6" t="n">
-        <v>19941641.97983824</v>
+        <v>241.8200000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>5.216831471385929e-07</v>
@@ -4656,19 +4656,19 @@
       <c r="K7" t="n">
         <v>86.82750704386147</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 18.042x + -10713.039</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-10713.03892349086</v>
       </c>
       <c r="Y7" t="n">
         <v>510.9371799472771</v>
       </c>
       <c r="Z7" t="n">
-        <v>21364185.31590111</v>
+        <v>232.804</v>
       </c>
       <c r="AA7" t="n">
         <v>5.085709092644983e-07</v>
@@ -4708,19 +4708,19 @@
       <c r="K8" t="n">
         <v>86.94132693735772</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 18.714x + -10988.871</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-10988.87092254372</v>
       </c>
       <c r="Y8" t="n">
         <v>505.1936294296866</v>
       </c>
       <c r="Z8" t="n">
-        <v>217794310.3336492</v>
+        <v>229.415</v>
       </c>
       <c r="AA8" t="n">
         <v>4.996646735832783e-07</v>
@@ -4760,19 +4760,19 @@
       <c r="K9" t="n">
         <v>86.79270814982048</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 17.846x + -10275.022</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-10275.02179171626</v>
       </c>
       <c r="Y9" t="n">
         <v>499.971990244395</v>
       </c>
       <c r="Z9" t="n">
-        <v>207989369.6311161</v>
+        <v>230.1909999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>4.913081306985214e-07</v>
@@ -4812,19 +4812,19 @@
       <c r="K10" t="n">
         <v>86.90390655366456</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 18.488x + -10551.788</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-10551.78846650073</v>
       </c>
       <c r="Y10" t="n">
         <v>495.0602961609386</v>
       </c>
       <c r="Z10" t="n">
-        <v>577435629.8490283</v>
+        <v>226.432</v>
       </c>
       <c r="AA10" t="n">
         <v>4.836258111412862e-07</v>
@@ -4864,19 +4864,19 @@
       <c r="K11" t="n">
         <v>86.96352012577218</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 18.851x + -10651.036</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-10651.03648055586</v>
       </c>
       <c r="Y11" t="n">
         <v>490.3719480906841</v>
       </c>
       <c r="Z11" t="n">
-        <v>37340201.01544112</v>
+        <v>224.937</v>
       </c>
       <c r="AA11" t="n">
         <v>4.782830294183207e-07</v>
@@ -4916,19 +4916,19 @@
       <c r="K12" t="n">
         <v>86.89395331886263</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 18.428x + -10260.209</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-10260.20862746471</v>
       </c>
       <c r="Y12" t="n">
         <v>485.7195061657517</v>
       </c>
       <c r="Z12" t="n">
-        <v>106225137.1154371</v>
+        <v>225.2009999999999</v>
       </c>
       <c r="AA12" t="n">
         <v>4.72514108836623e-07</v>
@@ -4968,19 +4968,19 @@
       <c r="K13" t="n">
         <v>87.06754657440469</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 19.521x + -10800.953</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-10800.95263639708</v>
       </c>
       <c r="Y13" t="n">
         <v>481.1161959089837</v>
       </c>
       <c r="Z13" t="n">
-        <v>265683551.0406118</v>
+        <v>218.064</v>
       </c>
       <c r="AA13" t="n">
         <v>4.662560501647432e-07</v>
@@ -5020,19 +5020,19 @@
       <c r="K14" t="n">
         <v>87.00386093441517</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 19.106x + -10430.512</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-10430.51170212585</v>
       </c>
       <c r="Y14" t="n">
         <v>476.4290111059876</v>
       </c>
       <c r="Z14" t="n">
-        <v>526242721.4847798</v>
+        <v>223.1080000000001</v>
       </c>
       <c r="AA14" t="n">
         <v>4.631060404567869e-07</v>
@@ -5072,19 +5072,19 @@
       <c r="K15" t="n">
         <v>87.06671331105046</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 19.516x + -10538.269</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-10538.2687754834</v>
       </c>
       <c r="Y15" t="n">
         <v>471.6699504570026</v>
       </c>
       <c r="Z15" t="n">
-        <v>31788854.7874673</v>
+        <v>218.167</v>
       </c>
       <c r="AA15" t="n">
         <v>4.567488918996206e-07</v>
@@ -5124,19 +5124,19 @@
       <c r="K16" t="n">
         <v>87.14698387776581</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 20.066x + -10734.585</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-10734.58450027679</v>
       </c>
       <c r="Y16" t="n">
         <v>466.8813678268625</v>
       </c>
       <c r="Z16" t="n">
-        <v>81748662.55577137</v>
+        <v>214.9640000000001</v>
       </c>
       <c r="AA16" t="n">
         <v>4.522718850824425e-07</v>
@@ -5176,19 +5176,19 @@
       <c r="K17" t="n">
         <v>87.10999092493243</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 19.809x + -10452.166</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-10452.16587075695</v>
       </c>
       <c r="Y17" t="n">
         <v>462.0965369417456</v>
       </c>
       <c r="Z17" t="n">
-        <v>42544192.1390802</v>
+        <v>217.1379999999999</v>
       </c>
       <c r="AA17" t="n">
         <v>4.478297767029729e-07</v>
@@ -5228,19 +5228,19 @@
       <c r="K18" t="n">
         <v>87.17600098309205</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 20.272x + -10593.935</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-10593.93515313758</v>
       </c>
       <c r="Y18" t="n">
         <v>457.324415910957</v>
       </c>
       <c r="Z18" t="n">
-        <v>189718246.9381725</v>
+        <v>216.206</v>
       </c>
       <c r="AA18" t="n">
         <v>4.445128379655021e-07</v>
@@ -5280,19 +5280,19 @@
       <c r="K19" t="n">
         <v>87.26571630256188</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 20.939x + -10835.838</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-10835.83790072471</v>
       </c>
       <c r="Y19" t="n">
         <v>452.6053765604874</v>
       </c>
       <c r="Z19" t="n">
-        <v>38423494.24429484</v>
+        <v>211.967</v>
       </c>
       <c r="AA19" t="n">
         <v>4.396161957261621e-07</v>
@@ -5332,19 +5332,19 @@
       <c r="K20" t="n">
         <v>87.15350563982575</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 20.112x + -10237.475</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-10237.4753925544</v>
       </c>
       <c r="Y20" t="n">
         <v>447.8181885829125</v>
       </c>
       <c r="Z20" t="n">
-        <v>49822100.56803484</v>
+        <v>216.501</v>
       </c>
       <c r="AA20" t="n">
         <v>4.366229156045198e-07</v>
@@ -5384,19 +5384,19 @@
       <c r="K21" t="n">
         <v>87.2522598512541</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 20.836x + -10501.652</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-10501.65173754466</v>
       </c>
       <c r="Y21" t="n">
         <v>443.0544249987667</v>
       </c>
       <c r="Z21" t="n">
-        <v>250687932.7284362</v>
+        <v>210.951</v>
       </c>
       <c r="AA21" t="n">
         <v>4.321799788876768e-07</v>
@@ -5436,19 +5436,19 @@
       <c r="K22" t="n">
         <v>87.24976640333482</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 20.817x + -10356.465</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-10356.46480867213</v>
       </c>
       <c r="Y22" t="n">
         <v>438.2193279052158</v>
       </c>
       <c r="Z22" t="n">
-        <v>135399575.902739</v>
+        <v>211.449</v>
       </c>
       <c r="AA22" t="n">
         <v>4.291012941134729e-07</v>
@@ -5574,12 +5574,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -5634,19 +5634,19 @@
       <c r="K2" t="n">
         <v>82.6651157206109</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 7.769x + -6345.806</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-6345.806386151228</v>
       </c>
       <c r="Y2" t="n">
         <v>548.8373652719168</v>
       </c>
       <c r="Z2" t="n">
-        <v>192761399.6507388</v>
+        <v>565.4799999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>5.92952917704346e-06</v>
@@ -5686,19 +5686,19 @@
       <c r="K3" t="n">
         <v>84.89370956873204</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 11.191x + -8039.176</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-8039.17587700782</v>
       </c>
       <c r="Y3" t="n">
         <v>579.9562874628609</v>
       </c>
       <c r="Z3" t="n">
-        <v>380073926.8092821</v>
+        <v>391.0300000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>1.185401619888726e-06</v>
@@ -5738,19 +5738,19 @@
       <c r="K4" t="n">
         <v>85.74320987217183</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 13.435x + -9287.798</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-9287.798107413642</v>
       </c>
       <c r="Y4" t="n">
         <v>570.6200555914047</v>
       </c>
       <c r="Z4" t="n">
-        <v>141121040.1946451</v>
+        <v>324.691</v>
       </c>
       <c r="AA4" t="n">
         <v>8.598524766326485e-07</v>
@@ -5790,19 +5790,19 @@
       <c r="K5" t="n">
         <v>86.09600229280805</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 14.653x + -9894.437</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-9894.437174768706</v>
       </c>
       <c r="Y5" t="n">
         <v>563.2548048657297</v>
       </c>
       <c r="Z5" t="n">
-        <v>37285288.0460481</v>
+        <v>292.1700000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>7.420131769015894e-07</v>
@@ -5842,19 +5842,19 @@
       <c r="K6" t="n">
         <v>86.14418938835858</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 14.837x + -9780.091</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-9780.090674851996</v>
       </c>
       <c r="Y6" t="n">
         <v>556.1471854430796</v>
       </c>
       <c r="Z6" t="n">
-        <v>54022908.28903898</v>
+        <v>279.1559999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>6.766352163401629e-07</v>
@@ -5894,19 +5894,19 @@
       <c r="K7" t="n">
         <v>86.58717447072914</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 16.769x + -10961.284</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-10961.2840643544</v>
       </c>
       <c r="Y7" t="n">
         <v>548.8851700371114</v>
       </c>
       <c r="Z7" t="n">
-        <v>48425086.81621543</v>
+        <v>258.9640000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>6.298505710540088e-07</v>
@@ -5946,19 +5946,19 @@
       <c r="K8" t="n">
         <v>86.56080407443896</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 16.640x + -10639.291</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-10639.29098362959</v>
       </c>
       <c r="Y8" t="n">
         <v>541.7276949713749</v>
       </c>
       <c r="Z8" t="n">
-        <v>41906008.05530718</v>
+        <v>253.134</v>
       </c>
       <c r="AA8" t="n">
         <v>5.98746115629063e-07</v>
@@ -5998,19 +5998,19 @@
       <c r="K9" t="n">
         <v>86.60186424003736</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 16.841x + -10566.119</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-10566.11853173201</v>
       </c>
       <c r="Y9" t="n">
         <v>534.9589497520589</v>
       </c>
       <c r="Z9" t="n">
-        <v>108692580.7518235</v>
+        <v>245.8810000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>5.73714269171323e-07</v>
@@ -6050,19 +6050,19 @@
       <c r="K10" t="n">
         <v>86.78168544461973</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 17.784x + -11034.016</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-11034.01640970146</v>
       </c>
       <c r="Y10" t="n">
         <v>528.7058654593757</v>
       </c>
       <c r="Z10" t="n">
-        <v>52218997.73365314</v>
+        <v>238.38</v>
       </c>
       <c r="AA10" t="n">
         <v>5.552519750927198e-07</v>
@@ -6102,19 +6102,19 @@
       <c r="K11" t="n">
         <v>86.63028576451273</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 16.984x + -10313.156</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-10313.1555306142</v>
       </c>
       <c r="Y11" t="n">
         <v>522.8425911722518</v>
       </c>
       <c r="Z11" t="n">
-        <v>33625030.64626577</v>
+        <v>239.2380000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>5.399516033166096e-07</v>
@@ -6240,12 +6240,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -6300,19 +6300,19 @@
       <c r="K2" t="n">
         <v>85.41998583830714</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 12.483x + -8225.624</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-8225.623711085243</v>
       </c>
       <c r="Y2" t="n">
         <v>547.3472225548547</v>
       </c>
       <c r="Z2" t="n">
-        <v>397961733.3448045</v>
+        <v>346.3549999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>8.274102823993408e-07</v>
@@ -6352,19 +6352,19 @@
       <c r="K3" t="n">
         <v>86.38672044718129</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 15.836x + -10121.954</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-10121.95418918851</v>
       </c>
       <c r="Y3" t="n">
         <v>537.8199450089054</v>
       </c>
       <c r="Z3" t="n">
-        <v>74128569.15747638</v>
+        <v>274.2910000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>6.527902110359519e-07</v>
@@ -6404,19 +6404,19 @@
       <c r="K4" t="n">
         <v>86.55930970150752</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 16.632x + -10407.166</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-10407.16551787421</v>
       </c>
       <c r="Y4" t="n">
         <v>532.0826246452998</v>
       </c>
       <c r="Z4" t="n">
-        <v>56612086.9927252</v>
+        <v>251.7089999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>6.00545680042186e-07</v>
@@ -6456,19 +6456,19 @@
       <c r="K5" t="n">
         <v>86.69298291892619</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 17.306x + -10690.690</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-10690.68976420769</v>
       </c>
       <c r="Y5" t="n">
         <v>526.7603610991472</v>
       </c>
       <c r="Z5" t="n">
-        <v>15084464.71567873</v>
+        <v>243.583</v>
       </c>
       <c r="AA5" t="n">
         <v>5.745483423175343e-07</v>
@@ -6508,19 +6508,19 @@
       <c r="K6" t="n">
         <v>86.76941509436701</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 17.717x + -10786.673</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-10786.67267908514</v>
       </c>
       <c r="Y6" t="n">
         <v>520.894097614307</v>
       </c>
       <c r="Z6" t="n">
-        <v>58145772.69805376</v>
+        <v>235.6479999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>5.551725047422679e-07</v>
@@ -6560,19 +6560,19 @@
       <c r="K7" t="n">
         <v>86.6801818769266</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 17.239x + -10288.053</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-10288.05260605998</v>
       </c>
       <c r="Y7" t="n">
         <v>514.6214062575486</v>
       </c>
       <c r="Z7" t="n">
-        <v>29230952.67993838</v>
+        <v>235.096</v>
       </c>
       <c r="AA7" t="n">
         <v>5.399810808069631e-07</v>
@@ -6612,19 +6612,19 @@
       <c r="K8" t="n">
         <v>86.96933328543356</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 18.888x + -11188.641</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-11188.64052107184</v>
       </c>
       <c r="Y8" t="n">
         <v>508.4598098639956</v>
       </c>
       <c r="Z8" t="n">
-        <v>75423441.15448593</v>
+        <v>223.103</v>
       </c>
       <c r="AA8" t="n">
         <v>5.25718116813532e-07</v>
@@ -6664,19 +6664,19 @@
       <c r="K9" t="n">
         <v>86.85703226049561</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 18.212x + -10581.556</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-10581.55589589904</v>
       </c>
       <c r="Y9" t="n">
         <v>502.6282180827429</v>
       </c>
       <c r="Z9" t="n">
-        <v>423603549.2168085</v>
+        <v>224.5070000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>5.164684199479608e-07</v>
@@ -6716,19 +6716,19 @@
       <c r="K10" t="n">
         <v>87.0597237926864</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 19.469x + -11217.458</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-11217.45765620496</v>
       </c>
       <c r="Y10" t="n">
         <v>497.0874087230442</v>
       </c>
       <c r="Z10" t="n">
-        <v>38368921.81256433</v>
+        <v>216.336</v>
       </c>
       <c r="AA10" t="n">
         <v>5.057314874306787e-07</v>
@@ -6768,19 +6768,19 @@
       <c r="K11" t="n">
         <v>86.98087440031027</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 18.960x + -10739.298</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-10739.29793640912</v>
       </c>
       <c r="Y11" t="n">
         <v>491.7177670637182</v>
       </c>
       <c r="Z11" t="n">
-        <v>75870617.73092788</v>
+        <v>216.908</v>
       </c>
       <c r="AA11" t="n">
         <v>4.976821138541326e-07</v>
@@ -6820,19 +6820,19 @@
       <c r="K12" t="n">
         <v>86.97241186449907</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 18.907x + -10565.599</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-10565.59914088861</v>
       </c>
       <c r="Y12" t="n">
         <v>486.5325252174118</v>
       </c>
       <c r="Z12" t="n">
-        <v>204753851.1892565</v>
+        <v>216.77</v>
       </c>
       <c r="AA12" t="n">
         <v>4.914478213336615e-07</v>
@@ -6872,19 +6872,19 @@
       <c r="K13" t="n">
         <v>87.08989229112142</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 19.672x + -10893.423</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-10893.42307022485</v>
       </c>
       <c r="Y13" t="n">
         <v>481.5806828529448</v>
       </c>
       <c r="Z13" t="n">
-        <v>63532016.46220312</v>
+        <v>213.1899999999999</v>
       </c>
       <c r="AA13" t="n">
         <v>4.847425979721743e-07</v>
@@ -6924,19 +6924,19 @@
       <c r="K14" t="n">
         <v>87.08037495563323</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 19.607x + -10716.672</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-10716.67217080022</v>
       </c>
       <c r="Y14" t="n">
         <v>476.6142989058284</v>
       </c>
       <c r="Z14" t="n">
-        <v>34719040.07934395</v>
+        <v>213.2859999999999</v>
       </c>
       <c r="AA14" t="n">
         <v>4.789190806279649e-07</v>
@@ -6976,19 +6976,19 @@
       <c r="K15" t="n">
         <v>87.14815463831815</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 20.074x + -10846.598</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-10846.59767874084</v>
       </c>
       <c r="Y15" t="n">
         <v>471.7503690363056</v>
       </c>
       <c r="Z15" t="n">
-        <v>95155789.09695755</v>
+        <v>207.846</v>
       </c>
       <c r="AA15" t="n">
         <v>4.721850160619705e-07</v>
@@ -7028,19 +7028,19 @@
       <c r="K16" t="n">
         <v>87.15835274382547</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 20.146x + -10754.076</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-10754.07584243441</v>
       </c>
       <c r="Y16" t="n">
         <v>466.858430803799</v>
       </c>
       <c r="Z16" t="n">
-        <v>31668267.24169507</v>
+        <v>207.2959999999999</v>
       </c>
       <c r="AA16" t="n">
         <v>4.674301422127175e-07</v>
@@ -7080,19 +7080,19 @@
       <c r="K17" t="n">
         <v>87.23197544047315</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 20.683x + -10933.572</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-10933.5715616793</v>
       </c>
       <c r="Y17" t="n">
         <v>462.0786899282044</v>
       </c>
       <c r="Z17" t="n">
-        <v>84156379.74575013</v>
+        <v>204.08</v>
       </c>
       <c r="AA17" t="n">
         <v>4.623054450161197e-07</v>
@@ -7132,19 +7132,19 @@
       <c r="K18" t="n">
         <v>87.18183856214445</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 20.315x + -10585.008</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-10585.00810576945</v>
       </c>
       <c r="Y18" t="n">
         <v>457.3176790141066</v>
       </c>
       <c r="Z18" t="n">
-        <v>71593270.90499125</v>
+        <v>206.425</v>
       </c>
       <c r="AA18" t="n">
         <v>4.578859941137327e-07</v>
@@ -7184,19 +7184,19 @@
       <c r="K19" t="n">
         <v>87.27012388388947</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 20.973x + -10822.605</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-10822.60466248579</v>
       </c>
       <c r="Y19" t="n">
         <v>452.6051858130465</v>
       </c>
       <c r="Z19" t="n">
-        <v>127173917.7358479</v>
+        <v>202.2570000000001</v>
       </c>
       <c r="AA19" t="n">
         <v>4.531406817193074e-07</v>
@@ -7236,19 +7236,19 @@
       <c r="K20" t="n">
         <v>87.34861679587324</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 21.594x + -11034.117</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-11034.11707855003</v>
       </c>
       <c r="Y20" t="n">
         <v>447.888471151404</v>
       </c>
       <c r="Z20" t="n">
-        <v>491751706.2692647</v>
+        <v>199.603</v>
       </c>
       <c r="AA20" t="n">
         <v>4.488572168994832e-07</v>
@@ -7288,19 +7288,19 @@
       <c r="K21" t="n">
         <v>87.3059686203291</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 21.252x + -10710.446</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-10710.44611308531</v>
       </c>
       <c r="Y21" t="n">
         <v>443.1211373369848</v>
       </c>
       <c r="Z21" t="n">
-        <v>363911524.2865228</v>
+        <v>202.359</v>
       </c>
       <c r="AA21" t="n">
         <v>4.467858562237523e-07</v>
@@ -7340,19 +7340,19 @@
       <c r="K22" t="n">
         <v>87.40956623821799</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 22.103x + -11038.316</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-11038.31622551207</v>
       </c>
       <c r="Y22" t="n">
         <v>438.4015632563413</v>
       </c>
       <c r="Z22" t="n">
-        <v>960195021.2010366</v>
+        <v>197.902</v>
       </c>
       <c r="AA22" t="n">
         <v>4.417689184530119e-07</v>
@@ -7478,12 +7478,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -7538,19 +7538,19 @@
       <c r="K2" t="n">
         <v>83.00603305668103</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 8.151x + -6335.223</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-6335.222807262978</v>
       </c>
       <c r="Y2" t="n">
         <v>569.5051116101438</v>
       </c>
       <c r="Z2" t="n">
-        <v>116659959.6340644</v>
+        <v>534.7510000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>3.515485762593364e-06</v>
@@ -7590,19 +7590,19 @@
       <c r="K3" t="n">
         <v>85.05074517941036</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 11.548x + -8134.556</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-8134.556070058749</v>
       </c>
       <c r="Y3" t="n">
         <v>575.3641575183071</v>
       </c>
       <c r="Z3" t="n">
-        <v>38379155.83272927</v>
+        <v>377.962</v>
       </c>
       <c r="AA3" t="n">
         <v>1.067160613020955e-06</v>
@@ -7642,19 +7642,19 @@
       <c r="K4" t="n">
         <v>85.92343413290865</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 14.031x + -9593.415</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-9593.414924072269</v>
       </c>
       <c r="Y4" t="n">
         <v>566.8042478641837</v>
       </c>
       <c r="Z4" t="n">
-        <v>145897571.268115</v>
+        <v>312.7379999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>8.073620234051986e-07</v>
@@ -7694,19 +7694,19 @@
       <c r="K5" t="n">
         <v>86.19816502605812</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 15.048x + -10061.966</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-10061.96587485877</v>
       </c>
       <c r="Y5" t="n">
         <v>560.3672242138649</v>
       </c>
       <c r="Z5" t="n">
-        <v>176992424.1180134</v>
+        <v>286.981</v>
       </c>
       <c r="AA5" t="n">
         <v>7.099148494990775e-07</v>
@@ -7746,19 +7746,19 @@
       <c r="K6" t="n">
         <v>86.42196559657212</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 15.992x + -10519.636</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-10519.63626502813</v>
       </c>
       <c r="Y6" t="n">
         <v>554.4775658602906</v>
       </c>
       <c r="Z6" t="n">
-        <v>88895794.08971889</v>
+        <v>265.9299999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>6.514220746783614e-07</v>
@@ -7798,19 +7798,19 @@
       <c r="K7" t="n">
         <v>86.43352190917442</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 16.044x + -10352.698</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-10352.69817113405</v>
       </c>
       <c r="Y7" t="n">
         <v>548.2570902789527</v>
       </c>
       <c r="Z7" t="n">
-        <v>99909522.09402075</v>
+        <v>256.8040000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>6.150168519841109e-07</v>
@@ -7850,19 +7850,19 @@
       <c r="K8" t="n">
         <v>86.52270585445856</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 16.457x + -10443.751</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-10443.75143186782</v>
       </c>
       <c r="Y8" t="n">
         <v>541.2648713405404</v>
       </c>
       <c r="Z8" t="n">
-        <v>92491285.65868892</v>
+        <v>250.348</v>
       </c>
       <c r="AA8" t="n">
         <v>5.88622311340895e-07</v>
@@ -7902,19 +7902,19 @@
       <c r="K9" t="n">
         <v>86.60543639433614</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 16.859x + -10521.287</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-10521.2872320515</v>
       </c>
       <c r="Y9" t="n">
         <v>534.0357262020848</v>
       </c>
       <c r="Z9" t="n">
-        <v>166929280.4379201</v>
+        <v>243.2700000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>5.667962330145158e-07</v>
@@ -7954,19 +7954,19 @@
       <c r="K10" t="n">
         <v>86.76147297195421</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 17.673x + -10874.552</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-10874.55213705548</v>
       </c>
       <c r="Y10" t="n">
         <v>527.2528466196694</v>
       </c>
       <c r="Z10" t="n">
-        <v>74775660.93545045</v>
+        <v>233.41</v>
       </c>
       <c r="AA10" t="n">
         <v>5.473545957582736e-07</v>
@@ -8006,19 +8006,19 @@
       <c r="K11" t="n">
         <v>86.84743022847248</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 18.156x + -11013.884</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-11013.8840800332</v>
       </c>
       <c r="Y11" t="n">
         <v>520.7736857570653</v>
       </c>
       <c r="Z11" t="n">
-        <v>26706286.64102941</v>
+        <v>231.587</v>
       </c>
       <c r="AA11" t="n">
         <v>5.332004591149701e-07</v>
@@ -8144,12 +8144,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -8204,19 +8204,19 @@
       <c r="K2" t="n">
         <v>85.92556024130452</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 14.039x + -9158.240</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-9158.239803482922</v>
       </c>
       <c r="Y2" t="n">
         <v>547.9664443253914</v>
       </c>
       <c r="Z2" t="n">
-        <v>93215787.65588757</v>
+        <v>295.1759999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>6.939635490601613e-07</v>
@@ -8256,19 +8256,19 @@
       <c r="K3" t="n">
         <v>86.54639774254363</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 16.570x + -10509.761</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-10509.76117156017</v>
       </c>
       <c r="Y3" t="n">
         <v>537.4991265785268</v>
       </c>
       <c r="Z3" t="n">
-        <v>57862755.58246504</v>
+        <v>255.207</v>
       </c>
       <c r="AA3" t="n">
         <v>6.065691900142197e-07</v>
@@ -8308,19 +8308,19 @@
       <c r="K4" t="n">
         <v>86.64529956532516</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 17.060x + -10608.342</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-10608.34191552096</v>
       </c>
       <c r="Y4" t="n">
         <v>530.7109260023144</v>
       </c>
       <c r="Z4" t="n">
-        <v>105488576.7142147</v>
+        <v>245.075</v>
       </c>
       <c r="AA4" t="n">
         <v>5.758173367481633e-07</v>
@@ -8360,19 +8360,19 @@
       <c r="K5" t="n">
         <v>86.66181290831521</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 17.144x + -10474.329</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-10474.32923802869</v>
       </c>
       <c r="Y5" t="n">
         <v>524.4008169650932</v>
       </c>
       <c r="Z5" t="n">
-        <v>47287926.86292861</v>
+        <v>239.784</v>
       </c>
       <c r="AA5" t="n">
         <v>5.56448183668114e-07</v>
@@ -8412,19 +8412,19 @@
       <c r="K6" t="n">
         <v>86.76197193521575</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 17.676x + -10643.999</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-10643.99865554016</v>
       </c>
       <c r="Y6" t="n">
         <v>518.024247500451</v>
       </c>
       <c r="Z6" t="n">
-        <v>428383340.7938696</v>
+        <v>229.625</v>
       </c>
       <c r="AA6" t="n">
         <v>5.40652754576415e-07</v>
@@ -8464,19 +8464,19 @@
       <c r="K7" t="n">
         <v>86.979944462888</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 18.954x + -11313.892</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-11313.89193898644</v>
       </c>
       <c r="Y7" t="n">
         <v>511.5433413446364</v>
       </c>
       <c r="Z7" t="n">
-        <v>92248114.62733148</v>
+        <v>225.261</v>
       </c>
       <c r="AA7" t="n">
         <v>5.29188017937728e-07</v>
@@ -8516,19 +8516,19 @@
       <c r="K8" t="n">
         <v>86.87741783852587</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 18.331x + -10727.105</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-10727.10461339592</v>
       </c>
       <c r="Y8" t="n">
         <v>505.6986830688899</v>
       </c>
       <c r="Z8" t="n">
-        <v>139970948.6951483</v>
+        <v>224.1279999999999</v>
       </c>
       <c r="AA8" t="n">
         <v>5.177933248446756e-07</v>
@@ -8568,19 +8568,19 @@
       <c r="K9" t="n">
         <v>86.84655555079907</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 18.151x + -10454.029</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-10454.02941256753</v>
       </c>
       <c r="Y9" t="n">
         <v>500.4768936297417</v>
       </c>
       <c r="Z9" t="n">
-        <v>108357798.1978788</v>
+        <v>221.967</v>
       </c>
       <c r="AA9" t="n">
         <v>5.092375615205946e-07</v>
@@ -8620,19 +8620,19 @@
       <c r="K10" t="n">
         <v>86.95966110405199</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 18.828x + -10752.447</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-10752.44736859063</v>
       </c>
       <c r="Y10" t="n">
         <v>495.8316412890505</v>
       </c>
       <c r="Z10" t="n">
-        <v>49117446.11016729</v>
+        <v>218.792</v>
       </c>
       <c r="AA10" t="n">
         <v>5.016604731941381e-07</v>
@@ -8672,19 +8672,19 @@
       <c r="K11" t="n">
         <v>86.98409628041334</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 18.980x + -10717.797</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-10717.79679447714</v>
       </c>
       <c r="Y11" t="n">
         <v>491.507998089093</v>
       </c>
       <c r="Z11" t="n">
-        <v>69117573.21617594</v>
+        <v>215.9069999999999</v>
       </c>
       <c r="AA11" t="n">
         <v>4.952188704965358e-07</v>
@@ -8724,19 +8724,19 @@
       <c r="K12" t="n">
         <v>87.17852881340522</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 20.291x + -11401.316</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-11401.31553036194</v>
       </c>
       <c r="Y12" t="n">
         <v>487.2697428654787</v>
       </c>
       <c r="Z12" t="n">
-        <v>46273212.63543476</v>
+        <v>208.4490000000001</v>
       </c>
       <c r="AA12" t="n">
         <v>4.875897573513626e-07</v>
@@ -8776,19 +8776,19 @@
       <c r="K13" t="n">
         <v>87.02715300243224</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 19.256x + -10647.365</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-10647.36491796495</v>
       </c>
       <c r="Y13" t="n">
         <v>483.0456321632749</v>
       </c>
       <c r="Z13" t="n">
-        <v>24849814.10408894</v>
+        <v>211.398</v>
       </c>
       <c r="AA13" t="n">
         <v>4.829111383721641e-07</v>
@@ -8828,19 +8828,19 @@
       <c r="K14" t="n">
         <v>87.08219185903415</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 19.620x + -10752.265</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-10752.26521999932</v>
       </c>
       <c r="Y14" t="n">
         <v>478.8588952335851</v>
       </c>
       <c r="Z14" t="n">
-        <v>266380733.539689</v>
+        <v>211.178</v>
       </c>
       <c r="AA14" t="n">
         <v>4.789943805447928e-07</v>
@@ -8880,19 +8880,19 @@
       <c r="K15" t="n">
         <v>87.14457214625331</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 20.049x + -10888.254</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-10888.25431383424</v>
       </c>
       <c r="Y15" t="n">
         <v>474.4818621580082</v>
       </c>
       <c r="Z15" t="n">
-        <v>40832017.37799203</v>
+        <v>209.9589999999999</v>
       </c>
       <c r="AA15" t="n">
         <v>4.739697264837431e-07</v>
@@ -8932,19 +8932,19 @@
       <c r="K16" t="n">
         <v>87.08989090121656</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 19.672x + -10537.927</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-10537.92701837069</v>
       </c>
       <c r="Y16" t="n">
         <v>470.0625771674634</v>
       </c>
       <c r="Z16" t="n">
-        <v>21239918.33952826</v>
+        <v>208.5889999999999</v>
       </c>
       <c r="AA16" t="n">
         <v>4.690785734777748e-07</v>
@@ -8984,19 +8984,19 @@
       <c r="K17" t="n">
         <v>87.21773574782559</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 20.577x + -10935.075</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-10935.07456580674</v>
       </c>
       <c r="Y17" t="n">
         <v>465.4910873318984</v>
       </c>
       <c r="Z17" t="n">
-        <v>34362732.61023357</v>
+        <v>201.9459999999999</v>
       </c>
       <c r="AA17" t="n">
         <v>4.626030484468354e-07</v>
@@ -9036,19 +9036,19 @@
       <c r="K18" t="n">
         <v>87.16706724953259</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 20.208x + -10590.591</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-10590.59131400182</v>
       </c>
       <c r="Y18" t="n">
         <v>460.6489042436971</v>
       </c>
       <c r="Z18" t="n">
-        <v>43335205.01146992</v>
+        <v>205.5700000000001</v>
       </c>
       <c r="AA18" t="n">
         <v>4.601242245427078e-07</v>
@@ -9088,19 +9088,19 @@
       <c r="K19" t="n">
         <v>87.21032039201737</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 20.522x + -10635.707</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-10635.70698782171</v>
       </c>
       <c r="Y19" t="n">
         <v>455.8594330283174</v>
       </c>
       <c r="Z19" t="n">
-        <v>256573807.4067802</v>
+        <v>201.932</v>
       </c>
       <c r="AA19" t="n">
         <v>4.554384756374948e-07</v>
@@ -9140,19 +9140,19 @@
       <c r="K20" t="n">
         <v>87.30069984518549</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 21.210x + -10879.134</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-10879.13431316853</v>
       </c>
       <c r="Y20" t="n">
         <v>450.9635551348287</v>
       </c>
       <c r="Z20" t="n">
-        <v>988076045.3561549</v>
+        <v>198.461</v>
       </c>
       <c r="AA20" t="n">
         <v>4.50762229766592e-07</v>
@@ -9192,19 +9192,19 @@
       <c r="K21" t="n">
         <v>87.2441757536334</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 20.775x + -10495.122</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-10495.12215438899</v>
       </c>
       <c r="Y21" t="n">
         <v>445.9830181602341</v>
       </c>
       <c r="Z21" t="n">
-        <v>488326387.5058805</v>
+        <v>199.328</v>
       </c>
       <c r="AA21" t="n">
         <v>4.470452847620055e-07</v>
@@ -9244,19 +9244,19 @@
       <c r="K22" t="n">
         <v>87.31182169016245</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 21.298x + -10645.465</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-10645.46534025562</v>
       </c>
       <c r="Y22" t="n">
         <v>440.9473525323475</v>
       </c>
       <c r="Z22" t="n">
-        <v>1206183583.512786</v>
+        <v>199.673</v>
       </c>
       <c r="AA22" t="n">
         <v>4.441706051422483e-07</v>
@@ -9382,12 +9382,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -9442,19 +9442,19 @@
       <c r="K2" t="n">
         <v>84.5133461030688</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 10.411x + -6824.026</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-6824.026098839277</v>
       </c>
       <c r="Y2" t="n">
         <v>542.5417400869246</v>
       </c>
       <c r="Z2" t="n">
-        <v>31871926.16182702</v>
+        <v>429.665</v>
       </c>
       <c r="AA2" t="n">
         <v>9.934221897037078e-07</v>
@@ -9494,19 +9494,19 @@
       <c r="K3" t="n">
         <v>86.0943897065048</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 14.647x + -9346.520</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-9346.52021162882</v>
       </c>
       <c r="Y3" t="n">
         <v>534.5275004114219</v>
       </c>
       <c r="Z3" t="n">
-        <v>54168483.1330822</v>
+        <v>307.0839999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>6.836591868196212e-07</v>
@@ -9546,19 +9546,19 @@
       <c r="K4" t="n">
         <v>86.47226453130855</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 16.221x + -10130.083</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-10130.08320452879</v>
       </c>
       <c r="Y4" t="n">
         <v>527.5934801188311</v>
       </c>
       <c r="Z4" t="n">
-        <v>72966020.88517547</v>
+        <v>269.687</v>
       </c>
       <c r="AA4" t="n">
         <v>6.103850501617336e-07</v>
@@ -9598,19 +9598,19 @@
       <c r="K5" t="n">
         <v>86.53266663490025</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 16.504x + -10076.725</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-10076.72515870641</v>
       </c>
       <c r="Y5" t="n">
         <v>520.8682801464658</v>
       </c>
       <c r="Z5" t="n">
-        <v>114785839.3222648</v>
+        <v>254.099</v>
       </c>
       <c r="AA5" t="n">
         <v>5.721278687584216e-07</v>
@@ -9650,19 +9650,19 @@
       <c r="K6" t="n">
         <v>86.67475184115797</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 17.211x + -10335.544</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-10335.5440924935</v>
       </c>
       <c r="Y6" t="n">
         <v>513.7502163522338</v>
       </c>
       <c r="Z6" t="n">
-        <v>38077614.66728316</v>
+        <v>243.399</v>
       </c>
       <c r="AA6" t="n">
         <v>5.474057726749312e-07</v>
@@ -9702,19 +9702,19 @@
       <c r="K7" t="n">
         <v>86.72904003429538</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 17.497x + -10308.856</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-10308.8556564917</v>
       </c>
       <c r="Y7" t="n">
         <v>506.1801091238793</v>
       </c>
       <c r="Z7" t="n">
-        <v>50003174.50793667</v>
+        <v>236.676</v>
       </c>
       <c r="AA7" t="n">
         <v>5.289251399962977e-07</v>
@@ -9754,19 +9754,19 @@
       <c r="K8" t="n">
         <v>86.90958148089945</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 18.522x + -10751.881</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-10751.88147196908</v>
       </c>
       <c r="Y8" t="n">
         <v>498.7623392797444</v>
       </c>
       <c r="Z8" t="n">
-        <v>275023896.081173</v>
+        <v>227.811</v>
       </c>
       <c r="AA8" t="n">
         <v>5.13280953960211e-07</v>
@@ -9806,19 +9806,19 @@
       <c r="K9" t="n">
         <v>86.91030666967617</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 18.526x + -10547.317</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-10547.3170095587</v>
       </c>
       <c r="Y9" t="n">
         <v>491.8533849089092</v>
       </c>
       <c r="Z9" t="n">
-        <v>36139828.88406774</v>
+        <v>224.901</v>
       </c>
       <c r="AA9" t="n">
         <v>5.003821300762556e-07</v>
@@ -9858,19 +9858,19 @@
       <c r="K10" t="n">
         <v>86.93694325489693</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 18.688x + -10459.670</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-10459.66993411818</v>
       </c>
       <c r="Y10" t="n">
         <v>485.409008110134</v>
       </c>
       <c r="Z10" t="n">
-        <v>233911311.9730988</v>
+        <v>219.343</v>
       </c>
       <c r="AA10" t="n">
         <v>4.900493783458515e-07</v>
@@ -9910,19 +9910,19 @@
       <c r="K11" t="n">
         <v>87.12345974629464</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 19.902x + -11019.945</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-11019.94505846481</v>
       </c>
       <c r="Y11" t="n">
         <v>479.4517673951738</v>
       </c>
       <c r="Z11" t="n">
-        <v>273971676.1830353</v>
+        <v>209.6030000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>4.794897629054564e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 52.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 52.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -588,10 +588,8 @@
       <c r="K2" t="n">
         <v>85.71780556973803</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 13.355x + -8803.943</t>
-        </is>
+      <c r="W2" t="n">
+        <v>13.35508213238412</v>
       </c>
       <c r="X2" t="n">
         <v>-8803.943089349516</v>
@@ -600,7 +598,7 @@
         <v>551.6818235263696</v>
       </c>
       <c r="Z2" t="n">
-        <v>334.601</v>
+        <v>139537132.2274952</v>
       </c>
       <c r="AA2" t="n">
         <v>7.206532355596467e-07</v>
@@ -640,10 +638,8 @@
       <c r="K3" t="n">
         <v>86.23158024381881</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 15.182x + -9879.710</t>
-        </is>
+      <c r="W3" t="n">
+        <v>15.18226242897974</v>
       </c>
       <c r="X3" t="n">
         <v>-9879.710328565614</v>
@@ -652,7 +648,7 @@
         <v>545.3859073851647</v>
       </c>
       <c r="Z3" t="n">
-        <v>292.971</v>
+        <v>33031208.38257015</v>
       </c>
       <c r="AA3" t="n">
         <v>6.267127526616215e-07</v>
@@ -692,10 +688,8 @@
       <c r="K4" t="n">
         <v>86.49600551653742</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 16.331x + -10470.742</t>
-        </is>
+      <c r="W4" t="n">
+        <v>16.3311704940572</v>
       </c>
       <c r="X4" t="n">
         <v>-10470.7424904319</v>
@@ -704,7 +698,7 @@
         <v>537.7848296526171</v>
       </c>
       <c r="Z4" t="n">
-        <v>277.398</v>
+        <v>41283398.12183786</v>
       </c>
       <c r="AA4" t="n">
         <v>5.890070855591323e-07</v>
@@ -744,10 +738,8 @@
       <c r="K5" t="n">
         <v>86.59700764419834</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 16.817x + -10543.290</t>
-        </is>
+      <c r="W5" t="n">
+        <v>16.81707917454596</v>
       </c>
       <c r="X5" t="n">
         <v>-10543.2899082422</v>
@@ -756,7 +748,7 @@
         <v>529.0813057894175</v>
       </c>
       <c r="Z5" t="n">
-        <v>264.223</v>
+        <v>74804313.00622916</v>
       </c>
       <c r="AA5" t="n">
         <v>5.5989793164035e-07</v>
@@ -796,10 +788,8 @@
       <c r="K6" t="n">
         <v>86.59963449745547</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 16.830x + -10285.131</t>
-        </is>
+      <c r="W6" t="n">
+        <v>16.83010130989706</v>
       </c>
       <c r="X6" t="n">
         <v>-10285.13111244457</v>
@@ -808,7 +798,7 @@
         <v>520.1197093400756</v>
       </c>
       <c r="Z6" t="n">
-        <v>257.091</v>
+        <v>39945648.51106961</v>
       </c>
       <c r="AA6" t="n">
         <v>5.362107796516958e-07</v>
@@ -848,10 +838,8 @@
       <c r="K7" t="n">
         <v>86.56151000208058</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 16.643x + -9915.337</t>
-        </is>
+      <c r="W7" t="n">
+        <v>16.64305504999831</v>
       </c>
       <c r="X7" t="n">
         <v>-9915.337206015489</v>
@@ -860,7 +848,7 @@
         <v>511.449997744861</v>
       </c>
       <c r="Z7" t="n">
-        <v>254.6809999999999</v>
+        <v>46634350.48192126</v>
       </c>
       <c r="AA7" t="n">
         <v>5.18164608234583e-07</v>
@@ -900,10 +888,8 @@
       <c r="K8" t="n">
         <v>86.79121995036104</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 17.837x + -10467.278</t>
-        </is>
+      <c r="W8" t="n">
+        <v>17.83726675920265</v>
       </c>
       <c r="X8" t="n">
         <v>-10467.27842527503</v>
@@ -912,7 +898,7 @@
         <v>503.0960003368983</v>
       </c>
       <c r="Z8" t="n">
-        <v>245.98</v>
+        <v>208007705.727629</v>
       </c>
       <c r="AA8" t="n">
         <v>5.032855244703399e-07</v>
@@ -952,10 +938,8 @@
       <c r="K9" t="n">
         <v>86.75443229110743</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 17.635x + -10109.590</t>
-        </is>
+      <c r="W9" t="n">
+        <v>17.63466021789048</v>
       </c>
       <c r="X9" t="n">
         <v>-10109.59046943449</v>
@@ -964,7 +948,7 @@
         <v>495.2601629230304</v>
       </c>
       <c r="Z9" t="n">
-        <v>242.769</v>
+        <v>44565443.13058098</v>
       </c>
       <c r="AA9" t="n">
         <v>4.903602942740081e-07</v>
@@ -1004,10 +988,8 @@
       <c r="K10" t="n">
         <v>86.86399061391251</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 18.252x + -10290.041</t>
-        </is>
+      <c r="W10" t="n">
+        <v>18.25203496387998</v>
       </c>
       <c r="X10" t="n">
         <v>-10290.04093702186</v>
@@ -1016,7 +998,7 @@
         <v>487.5726900698414</v>
       </c>
       <c r="Z10" t="n">
-        <v>238.725</v>
+        <v>34386439.88839921</v>
       </c>
       <c r="AA10" t="n">
         <v>4.798176144455605e-07</v>
@@ -1056,10 +1038,8 @@
       <c r="K11" t="n">
         <v>86.86201561837873</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 18.241x + -10084.219</t>
-        </is>
+      <c r="W11" t="n">
+        <v>18.24052445250625</v>
       </c>
       <c r="X11" t="n">
         <v>-10084.21876871057</v>
@@ -1068,7 +1048,7 @@
         <v>480.5862591691507</v>
       </c>
       <c r="Z11" t="n">
-        <v>234.853</v>
+        <v>26881734.4222526</v>
       </c>
       <c r="AA11" t="n">
         <v>4.696682508126709e-07</v>
@@ -1194,12 +1174,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1254,10 +1234,8 @@
       <c r="K2" t="n">
         <v>86.65426769437698</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 17.106x + -11249.976</t>
-        </is>
+      <c r="W2" t="n">
+        <v>17.10556489951618</v>
       </c>
       <c r="X2" t="n">
         <v>-11249.97607059805</v>
@@ -1266,7 +1244,7 @@
         <v>547.6190726842345</v>
       </c>
       <c r="Z2" t="n">
-        <v>234.155</v>
+        <v>41080721.47866023</v>
       </c>
       <c r="AA2" t="n">
         <v>5.843129485523733e-07</v>
@@ -1306,10 +1284,8 @@
       <c r="K3" t="n">
         <v>86.67621761930589</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 17.219x + -10861.799</t>
-        </is>
+      <c r="W3" t="n">
+        <v>17.21878468973923</v>
       </c>
       <c r="X3" t="n">
         <v>-10861.79937310117</v>
@@ -1318,7 +1294,7 @@
         <v>536.3130500260861</v>
       </c>
       <c r="Z3" t="n">
-        <v>230.4929999999999</v>
+        <v>41194474.90584817</v>
       </c>
       <c r="AA3" t="n">
         <v>5.549820417865719e-07</v>
@@ -1358,10 +1334,8 @@
       <c r="K4" t="n">
         <v>86.75859743134012</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 17.657x + -10951.553</t>
-        </is>
+      <c r="W4" t="n">
+        <v>17.65736893406811</v>
       </c>
       <c r="X4" t="n">
         <v>-10951.55297359674</v>
@@ -1370,7 +1344,7 @@
         <v>530.5014166093951</v>
       </c>
       <c r="Z4" t="n">
-        <v>221.836</v>
+        <v>67697417.42539169</v>
       </c>
       <c r="AA4" t="n">
         <v>5.38037091704937e-07</v>
@@ -1410,10 +1384,8 @@
       <c r="K5" t="n">
         <v>86.88584835855085</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 18.380x + -11286.664</t>
-        </is>
+      <c r="W5" t="n">
+        <v>18.38039847063652</v>
       </c>
       <c r="X5" t="n">
         <v>-11286.66355718546</v>
@@ -1422,7 +1394,7 @@
         <v>525.0447999738915</v>
       </c>
       <c r="Z5" t="n">
-        <v>220.027</v>
+        <v>38322631.85220434</v>
       </c>
       <c r="AA5" t="n">
         <v>5.280000921525257e-07</v>
@@ -1462,10 +1434,8 @@
       <c r="K6" t="n">
         <v>86.89498427597836</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 18.435x + -11158.796</t>
-        </is>
+      <c r="W6" t="n">
+        <v>18.43458579208651</v>
       </c>
       <c r="X6" t="n">
         <v>-11158.79633193113</v>
@@ -1474,7 +1444,7 @@
         <v>519.1276913944876</v>
       </c>
       <c r="Z6" t="n">
-        <v>220.256</v>
+        <v>22421880.91333796</v>
       </c>
       <c r="AA6" t="n">
         <v>5.18061558625732e-07</v>
@@ -1514,10 +1484,8 @@
       <c r="K7" t="n">
         <v>86.85517826461805</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 18.201x + -10830.426</t>
-        </is>
+      <c r="W7" t="n">
+        <v>18.20078708506399</v>
       </c>
       <c r="X7" t="n">
         <v>-10830.42604100653</v>
@@ -1526,7 +1494,7 @@
         <v>512.8851005325013</v>
       </c>
       <c r="Z7" t="n">
-        <v>218.9880000000001</v>
+        <v>61754128.69018628</v>
       </c>
       <c r="AA7" t="n">
         <v>5.098815646727138e-07</v>
@@ -1566,10 +1534,8 @@
       <c r="K8" t="n">
         <v>86.93421380474906</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 18.671x + -10961.225</t>
-        </is>
+      <c r="W8" t="n">
+        <v>18.67093267443002</v>
       </c>
       <c r="X8" t="n">
         <v>-10961.22474682713</v>
@@ -1578,7 +1544,7 @@
         <v>506.692379193322</v>
       </c>
       <c r="Z8" t="n">
-        <v>218.954</v>
+        <v>279841143.0356812</v>
       </c>
       <c r="AA8" t="n">
         <v>5.014855124558051e-07</v>
@@ -1618,10 +1584,8 @@
       <c r="K9" t="n">
         <v>87.03752674193467</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 19.323x + -11209.177</t>
-        </is>
+      <c r="W9" t="n">
+        <v>19.32328405495187</v>
       </c>
       <c r="X9" t="n">
         <v>-11209.17712077081</v>
@@ -1630,7 +1594,7 @@
         <v>500.7779678278371</v>
       </c>
       <c r="Z9" t="n">
-        <v>215.292</v>
+        <v>27874041.96337112</v>
       </c>
       <c r="AA9" t="n">
         <v>4.928337765878669e-07</v>
@@ -1670,10 +1634,8 @@
       <c r="K10" t="n">
         <v>87.08724637754925</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 19.654x + -11255.070</t>
-        </is>
+      <c r="W10" t="n">
+        <v>19.65370908018021</v>
       </c>
       <c r="X10" t="n">
         <v>-11255.07046605867</v>
@@ -1682,7 +1644,7 @@
         <v>495.285121895397</v>
       </c>
       <c r="Z10" t="n">
-        <v>212.5799999999999</v>
+        <v>271600469.696499</v>
       </c>
       <c r="AA10" t="n">
         <v>4.859172518199393e-07</v>
@@ -1722,10 +1684,8 @@
       <c r="K11" t="n">
         <v>87.04147941380815</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 19.349x + -10902.551</t>
-        </is>
+      <c r="W11" t="n">
+        <v>19.349146578169</v>
       </c>
       <c r="X11" t="n">
         <v>-10902.55060148231</v>
@@ -1734,7 +1694,7 @@
         <v>489.9210250392429</v>
       </c>
       <c r="Z11" t="n">
-        <v>210.2869999999999</v>
+        <v>29405537.75678721</v>
       </c>
       <c r="AA11" t="n">
         <v>4.787743942065891e-07</v>
@@ -1774,10 +1734,8 @@
       <c r="K12" t="n">
         <v>87.07824229333619</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 19.593x + -10902.467</t>
-        </is>
+      <c r="W12" t="n">
+        <v>19.59303690675931</v>
       </c>
       <c r="X12" t="n">
         <v>-10902.4667195866</v>
@@ -1786,7 +1744,7 @@
         <v>484.5950792194721</v>
       </c>
       <c r="Z12" t="n">
-        <v>209.203</v>
+        <v>65902059.67108587</v>
       </c>
       <c r="AA12" t="n">
         <v>4.732247315029527e-07</v>
@@ -1826,10 +1784,8 @@
       <c r="K13" t="n">
         <v>87.11377880852471</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 19.835x + -10907.048</t>
-        </is>
+      <c r="W13" t="n">
+        <v>19.83469178286271</v>
       </c>
       <c r="X13" t="n">
         <v>-10907.04836233583</v>
@@ -1838,7 +1794,7 @@
         <v>479.2207077071099</v>
       </c>
       <c r="Z13" t="n">
-        <v>207.611</v>
+        <v>24082961.64675545</v>
       </c>
       <c r="AA13" t="n">
         <v>4.683395449795387e-07</v>
@@ -1878,10 +1834,8 @@
       <c r="K14" t="n">
         <v>87.21412335674272</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 20.550x + -11178.803</t>
-        </is>
+      <c r="W14" t="n">
+        <v>20.55030693249091</v>
       </c>
       <c r="X14" t="n">
         <v>-11178.80252208924</v>
@@ -1890,7 +1844,7 @@
         <v>474.0124014865988</v>
       </c>
       <c r="Z14" t="n">
-        <v>205.4829999999999</v>
+        <v>48531238.15834387</v>
       </c>
       <c r="AA14" t="n">
         <v>4.630164582235506e-07</v>
@@ -1930,10 +1884,8 @@
       <c r="K15" t="n">
         <v>87.15981267349734</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 20.157x + -10797.024</t>
-        </is>
+      <c r="W15" t="n">
+        <v>20.15671337593599</v>
       </c>
       <c r="X15" t="n">
         <v>-10797.02377499621</v>
@@ -1942,7 +1894,7 @@
         <v>469.0075452841498</v>
       </c>
       <c r="Z15" t="n">
-        <v>204.12</v>
+        <v>28576826.45869574</v>
       </c>
       <c r="AA15" t="n">
         <v>4.576311750516199e-07</v>
@@ -1982,10 +1934,8 @@
       <c r="K16" t="n">
         <v>86.99169329717583</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 19.028x + -10004.553</t>
-        </is>
+      <c r="W16" t="n">
+        <v>19.02835224311032</v>
       </c>
       <c r="X16" t="n">
         <v>-10004.5531730878</v>
@@ -1994,7 +1944,7 @@
         <v>464.0837279452896</v>
       </c>
       <c r="Z16" t="n">
-        <v>207.12</v>
+        <v>41656734.77073652</v>
       </c>
       <c r="AA16" t="n">
         <v>4.537056640989806e-07</v>
@@ -2034,10 +1984,8 @@
       <c r="K17" t="n">
         <v>87.28457759564253</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 21.084x + -11054.079</t>
-        </is>
+      <c r="W17" t="n">
+        <v>21.08433502009381</v>
       </c>
       <c r="X17" t="n">
         <v>-11054.07949912203</v>
@@ -2046,7 +1994,7 @@
         <v>459.2088586320658</v>
       </c>
       <c r="Z17" t="n">
-        <v>198.9010000000001</v>
+        <v>73142621.77350013</v>
       </c>
       <c r="AA17" t="n">
         <v>4.491448263308566e-07</v>
@@ -2086,10 +2034,8 @@
       <c r="K18" t="n">
         <v>87.23301847851154</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 20.691x + -10695.261</t>
-        </is>
+      <c r="W18" t="n">
+        <v>20.6908612336624</v>
       </c>
       <c r="X18" t="n">
         <v>-10695.26111207464</v>
@@ -2098,7 +2044,7 @@
         <v>454.2969709553919</v>
       </c>
       <c r="Z18" t="n">
-        <v>202.994</v>
+        <v>38835982.37046302</v>
       </c>
       <c r="AA18" t="n">
         <v>4.459785110598263e-07</v>
@@ -2138,10 +2084,8 @@
       <c r="K19" t="n">
         <v>87.37575716610981</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 21.818x + -11183.551</t>
-        </is>
+      <c r="W19" t="n">
+        <v>21.81799194079257</v>
       </c>
       <c r="X19" t="n">
         <v>-11183.55084380444</v>
@@ -2150,7 +2094,7 @@
         <v>449.4719906849796</v>
       </c>
       <c r="Z19" t="n">
-        <v>195.3389999999999</v>
+        <v>369854107.262041</v>
       </c>
       <c r="AA19" t="n">
         <v>4.413194965873209e-07</v>
@@ -2190,10 +2134,8 @@
       <c r="K20" t="n">
         <v>87.24963659107635</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 20.816x + -10488.219</t>
-        </is>
+      <c r="W20" t="n">
+        <v>20.8160725578104</v>
       </c>
       <c r="X20" t="n">
         <v>-10488.21905324031</v>
@@ -2202,7 +2144,7 @@
         <v>444.6512127779001</v>
       </c>
       <c r="Z20" t="n">
-        <v>199.119</v>
+        <v>730005415.09552</v>
       </c>
       <c r="AA20" t="n">
         <v>4.380704721093446e-07</v>
@@ -2242,10 +2184,8 @@
       <c r="K21" t="n">
         <v>87.32376809483063</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 21.394x + -10670.263</t>
-        </is>
+      <c r="W21" t="n">
+        <v>21.39355160139858</v>
       </c>
       <c r="X21" t="n">
         <v>-10670.26348242676</v>
@@ -2254,7 +2194,7 @@
         <v>439.9087363251003</v>
       </c>
       <c r="Z21" t="n">
-        <v>198.011</v>
+        <v>134598211.1798755</v>
       </c>
       <c r="AA21" t="n">
         <v>4.34392041140991e-07</v>
@@ -2294,10 +2234,8 @@
       <c r="K22" t="n">
         <v>87.26219463846495</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 20.912x + -10266.411</t>
-        </is>
+      <c r="W22" t="n">
+        <v>20.91170036110754</v>
       </c>
       <c r="X22" t="n">
         <v>-10266.41063451135</v>
@@ -2306,7 +2244,7 @@
         <v>411.244001256769</v>
       </c>
       <c r="Z22" t="n">
-        <v>195.548</v>
+        <v>5842.653011486986</v>
       </c>
       <c r="AA22" t="n">
         <v>4.641218700590199e-07</v>
@@ -2432,12 +2370,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2492,10 +2430,8 @@
       <c r="K2" t="n">
         <v>86.36910546666731</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 15.759x + -10152.088</t>
-        </is>
+      <c r="W2" t="n">
+        <v>15.75894330230318</v>
       </c>
       <c r="X2" t="n">
         <v>-10152.08803456429</v>
@@ -2504,7 +2440,7 @@
         <v>543.0744978851715</v>
       </c>
       <c r="Z2" t="n">
-        <v>263.9880000000001</v>
+        <v>56623007.34436025</v>
       </c>
       <c r="AA2" t="n">
         <v>5.820828483546218e-07</v>
@@ -2544,10 +2480,8 @@
       <c r="K3" t="n">
         <v>86.60296144379556</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 16.847x + -10602.849</t>
-        </is>
+      <c r="W3" t="n">
+        <v>16.84662289809391</v>
       </c>
       <c r="X3" t="n">
         <v>-10602.84886892514</v>
@@ -2556,7 +2490,7 @@
         <v>535.3777738037471</v>
       </c>
       <c r="Z3" t="n">
-        <v>243.1039999999999</v>
+        <v>26357392.43708407</v>
       </c>
       <c r="AA3" t="n">
         <v>5.475926748889934e-07</v>
@@ -2596,10 +2530,8 @@
       <c r="K4" t="n">
         <v>86.67231898498879</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 17.199x + -10667.685</t>
-        </is>
+      <c r="W4" t="n">
+        <v>17.19856620231159</v>
       </c>
       <c r="X4" t="n">
         <v>-10667.68510282975</v>
@@ -2608,7 +2540,7 @@
         <v>529.6461565578179</v>
       </c>
       <c r="Z4" t="n">
-        <v>237.33</v>
+        <v>72818556.39952733</v>
       </c>
       <c r="AA4" t="n">
         <v>5.311393192374377e-07</v>
@@ -2648,10 +2580,8 @@
       <c r="K5" t="n">
         <v>86.66415580087778</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 17.156x + -10474.874</t>
-        </is>
+      <c r="W5" t="n">
+        <v>17.15638447637386</v>
       </c>
       <c r="X5" t="n">
         <v>-10474.87440678367</v>
@@ -2660,7 +2590,7 @@
         <v>523.4266567912304</v>
       </c>
       <c r="Z5" t="n">
-        <v>235.2190000000001</v>
+        <v>122210555.2592653</v>
       </c>
       <c r="AA5" t="n">
         <v>5.185988259768235e-07</v>
@@ -2700,10 +2630,8 @@
       <c r="K6" t="n">
         <v>86.66871586387042</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 17.180x + -10319.194</t>
-        </is>
+      <c r="W6" t="n">
+        <v>17.17992229102028</v>
       </c>
       <c r="X6" t="n">
         <v>-10319.1937841465</v>
@@ -2712,7 +2640,7 @@
         <v>516.9120811162061</v>
       </c>
       <c r="Z6" t="n">
-        <v>234.439</v>
+        <v>40063527.89311381</v>
       </c>
       <c r="AA6" t="n">
         <v>5.082977602685361e-07</v>
@@ -2752,10 +2680,8 @@
       <c r="K7" t="n">
         <v>86.76167165566486</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 17.674x + -10475.098</t>
-        </is>
+      <c r="W7" t="n">
+        <v>17.67416730886164</v>
       </c>
       <c r="X7" t="n">
         <v>-10475.09841175652</v>
@@ -2764,7 +2690,7 @@
         <v>510.8136599619593</v>
       </c>
       <c r="Z7" t="n">
-        <v>231.372</v>
+        <v>284246405.3912622</v>
       </c>
       <c r="AA7" t="n">
         <v>4.968564906094457e-07</v>
@@ -2804,10 +2730,8 @@
       <c r="K8" t="n">
         <v>86.95632860802702</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 18.807x + -11051.800</t>
-        </is>
+      <c r="W8" t="n">
+        <v>18.8068508741302</v>
       </c>
       <c r="X8" t="n">
         <v>-11051.79958285651</v>
@@ -2816,7 +2740,7 @@
         <v>505.1418191579408</v>
       </c>
       <c r="Z8" t="n">
-        <v>224.895</v>
+        <v>277296170.3229762</v>
       </c>
       <c r="AA8" t="n">
         <v>4.877483991057653e-07</v>
@@ -2856,10 +2780,8 @@
       <c r="K9" t="n">
         <v>86.87427225247617</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 18.312x + -10583.594</t>
-        </is>
+      <c r="W9" t="n">
+        <v>18.31219232367608</v>
       </c>
       <c r="X9" t="n">
         <v>-10583.59431202855</v>
@@ -2868,7 +2790,7 @@
         <v>500.0446173133178</v>
       </c>
       <c r="Z9" t="n">
-        <v>224.9209999999999</v>
+        <v>274974229.9535233</v>
       </c>
       <c r="AA9" t="n">
         <v>4.79742023833454e-07</v>
@@ -2908,10 +2830,8 @@
       <c r="K10" t="n">
         <v>86.86927920047472</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 18.283x + -10423.537</t>
-        </is>
+      <c r="W10" t="n">
+        <v>18.28292892189813</v>
       </c>
       <c r="X10" t="n">
         <v>-10423.537255714</v>
@@ -2920,7 +2840,7 @@
         <v>494.8353524461027</v>
       </c>
       <c r="Z10" t="n">
-        <v>222.99</v>
+        <v>40287277.71094939</v>
       </c>
       <c r="AA10" t="n">
         <v>4.718427542435358e-07</v>
@@ -2960,10 +2880,8 @@
       <c r="K11" t="n">
         <v>87.0820691243071</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 19.619x + -11127.105</t>
-        </is>
+      <c r="W11" t="n">
+        <v>19.61877750897923</v>
       </c>
       <c r="X11" t="n">
         <v>-11127.10472409307</v>
@@ -2972,7 +2890,7 @@
         <v>489.6967757098946</v>
       </c>
       <c r="Z11" t="n">
-        <v>221.408</v>
+        <v>93252368.58251798</v>
       </c>
       <c r="AA11" t="n">
         <v>4.667191217373455e-07</v>
@@ -3012,10 +2930,8 @@
       <c r="K12" t="n">
         <v>86.96906348641619</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 18.886x + -10527.286</t>
-        </is>
+      <c r="W12" t="n">
+        <v>18.88601887553665</v>
       </c>
       <c r="X12" t="n">
         <v>-10527.28559566131</v>
@@ -3024,7 +2940,7 @@
         <v>484.7401896710014</v>
       </c>
       <c r="Z12" t="n">
-        <v>223.4059999999999</v>
+        <v>43591990.13423891</v>
       </c>
       <c r="AA12" t="n">
         <v>4.60055500071584e-07</v>
@@ -3064,10 +2980,8 @@
       <c r="K13" t="n">
         <v>86.96053611362325</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 18.833x + -10361.677</t>
-        </is>
+      <c r="W13" t="n">
+        <v>18.83293405652562</v>
       </c>
       <c r="X13" t="n">
         <v>-10361.67708609466</v>
@@ -3076,7 +2990,7 @@
         <v>479.8687543644011</v>
       </c>
       <c r="Z13" t="n">
-        <v>223.115</v>
+        <v>34107853.48462652</v>
       </c>
       <c r="AA13" t="n">
         <v>4.551564263780891e-07</v>
@@ -3116,10 +3030,8 @@
       <c r="K14" t="n">
         <v>87.06517073585158</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 19.506x + -10639.553</t>
-        </is>
+      <c r="W14" t="n">
+        <v>19.50561886040164</v>
       </c>
       <c r="X14" t="n">
         <v>-10639.55258907091</v>
@@ -3128,7 +3040,7 @@
         <v>474.935735704342</v>
       </c>
       <c r="Z14" t="n">
-        <v>221.7230000000001</v>
+        <v>34295332.13532727</v>
       </c>
       <c r="AA14" t="n">
         <v>4.500449046646251e-07</v>
@@ -3168,10 +3080,8 @@
       <c r="K15" t="n">
         <v>86.99561330577383</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 19.053x + -10227.207</t>
-        </is>
+      <c r="W15" t="n">
+        <v>19.05322536563283</v>
       </c>
       <c r="X15" t="n">
         <v>-10227.20672708117</v>
@@ -3180,7 +3090,7 @@
         <v>469.9476069863769</v>
       </c>
       <c r="Z15" t="n">
-        <v>221.58</v>
+        <v>98475152.46562451</v>
       </c>
       <c r="AA15" t="n">
         <v>4.451062441172622e-07</v>
@@ -3220,10 +3130,8 @@
       <c r="K16" t="n">
         <v>87.05295416989037</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 19.425x + -10325.280</t>
-        </is>
+      <c r="W16" t="n">
+        <v>19.42461914638663</v>
       </c>
       <c r="X16" t="n">
         <v>-10325.28024842519</v>
@@ -3232,7 +3140,7 @@
         <v>465.0514139133583</v>
       </c>
       <c r="Z16" t="n">
-        <v>223.1289999999999</v>
+        <v>255587382.3131509</v>
       </c>
       <c r="AA16" t="n">
         <v>4.415980302388228e-07</v>
@@ -3272,10 +3180,8 @@
       <c r="K17" t="n">
         <v>87.23156072950334</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 20.680x + -10911.608</t>
-        </is>
+      <c r="W17" t="n">
+        <v>20.67994929407518</v>
       </c>
       <c r="X17" t="n">
         <v>-10911.60845700028</v>
@@ -3284,7 +3190,7 @@
         <v>460.1691662592226</v>
       </c>
       <c r="Z17" t="n">
-        <v>214.172</v>
+        <v>15734840.3135771</v>
       </c>
       <c r="AA17" t="n">
         <v>4.344326980192154e-07</v>
@@ -3324,10 +3230,8 @@
       <c r="K18" t="n">
         <v>87.12206384450741</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 19.892x + -10328.823</t>
-        </is>
+      <c r="W18" t="n">
+        <v>19.89188869572183</v>
       </c>
       <c r="X18" t="n">
         <v>-10328.82297298489</v>
@@ -3336,7 +3240,7 @@
         <v>455.2142059110784</v>
       </c>
       <c r="Z18" t="n">
-        <v>222.645</v>
+        <v>48458271.54523466</v>
       </c>
       <c r="AA18" t="n">
         <v>4.330306852580111e-07</v>
@@ -3376,10 +3280,8 @@
       <c r="K19" t="n">
         <v>87.24135507798749</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 20.753x + -10687.451</t>
-        </is>
+      <c r="W19" t="n">
+        <v>20.7534860026486</v>
       </c>
       <c r="X19" t="n">
         <v>-10687.45139629967</v>
@@ -3388,7 +3290,7 @@
         <v>450.3106340980862</v>
       </c>
       <c r="Z19" t="n">
-        <v>218.611</v>
+        <v>246346300.6498589</v>
       </c>
       <c r="AA19" t="n">
         <v>4.289298240777591e-07</v>
@@ -3428,10 +3330,8 @@
       <c r="K20" t="n">
         <v>87.30505889277259</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 21.245x + -10821.880</t>
-        </is>
+      <c r="W20" t="n">
+        <v>21.24481325638911</v>
       </c>
       <c r="X20" t="n">
         <v>-10821.87992804147</v>
@@ -3440,7 +3340,7 @@
         <v>445.3910988715893</v>
       </c>
       <c r="Z20" t="n">
-        <v>217.1019999999999</v>
+        <v>195607532.1833709</v>
       </c>
       <c r="AA20" t="n">
         <v>4.248476336062204e-07</v>
@@ -3480,10 +3380,8 @@
       <c r="K21" t="n">
         <v>87.21328819958147</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 20.544x + -10284.192</t>
-        </is>
+      <c r="W21" t="n">
+        <v>20.54413843658191</v>
       </c>
       <c r="X21" t="n">
         <v>-10284.19174682864</v>
@@ -3492,7 +3390,7 @@
         <v>440.4655235058564</v>
       </c>
       <c r="Z21" t="n">
-        <v>217.189</v>
+        <v>362063644.571839</v>
       </c>
       <c r="AA21" t="n">
         <v>4.211295957905756e-07</v>
@@ -3532,10 +3430,8 @@
       <c r="K22" t="n">
         <v>87.22402722824856</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 20.624x + -10197.540</t>
-        </is>
+      <c r="W22" t="n">
+        <v>20.62373998876398</v>
       </c>
       <c r="X22" t="n">
         <v>-10197.54011435341</v>
@@ -3544,7 +3440,7 @@
         <v>435.5708022825369</v>
       </c>
       <c r="Z22" t="n">
-        <v>220.836</v>
+        <v>178925621.5317138</v>
       </c>
       <c r="AA22" t="n">
         <v>4.18400320375367e-07</v>
@@ -3670,12 +3566,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3730,10 +3626,8 @@
       <c r="K2" t="n">
         <v>84.45633435361003</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 10.303x + -8414.234</t>
-        </is>
+      <c r="W2" t="n">
+        <v>10.30308799477091</v>
       </c>
       <c r="X2" t="n">
         <v>-8414.234368814468</v>
@@ -3742,7 +3636,7 @@
         <v>604.3463217163657</v>
       </c>
       <c r="Z2" t="n">
-        <v>469.704</v>
+        <v>323573447.6931999</v>
       </c>
       <c r="AA2" t="n">
         <v>1.882895778045228e-06</v>
@@ -3782,10 +3676,8 @@
       <c r="K3" t="n">
         <v>85.68401314913133</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 13.250x + -9702.424</t>
-        </is>
+      <c r="W3" t="n">
+        <v>13.25012532663609</v>
       </c>
       <c r="X3" t="n">
         <v>-9702.424239303427</v>
@@ -3794,7 +3686,7 @@
         <v>589.3048081097292</v>
       </c>
       <c r="Z3" t="n">
-        <v>350.398</v>
+        <v>75420614.09982227</v>
       </c>
       <c r="AA3" t="n">
         <v>8.76482784692416e-07</v>
@@ -3834,10 +3726,8 @@
       <c r="K4" t="n">
         <v>86.07626047625904</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 14.580x + -10234.312</t>
-        </is>
+      <c r="W4" t="n">
+        <v>14.57950570195715</v>
       </c>
       <c r="X4" t="n">
         <v>-10234.31203384862</v>
@@ -3846,7 +3736,7 @@
         <v>577.1142193154957</v>
       </c>
       <c r="Z4" t="n">
-        <v>306.0550000000001</v>
+        <v>190376014.7478443</v>
       </c>
       <c r="AA4" t="n">
         <v>7.30842803239554e-07</v>
@@ -3886,10 +3776,8 @@
       <c r="K5" t="n">
         <v>86.21622237633349</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 15.120x + -10318.560</t>
-        </is>
+      <c r="W5" t="n">
+        <v>15.12046113779918</v>
       </c>
       <c r="X5" t="n">
         <v>-10318.5601255436</v>
@@ -3898,7 +3786,7 @@
         <v>567.9871590781264</v>
       </c>
       <c r="Z5" t="n">
-        <v>286.706</v>
+        <v>76725641.15732116</v>
       </c>
       <c r="AA5" t="n">
         <v>6.634786282406896e-07</v>
@@ -3938,10 +3826,8 @@
       <c r="K6" t="n">
         <v>86.53569117561379</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 16.519x + -11107.115</t>
-        </is>
+      <c r="W6" t="n">
+        <v>16.51871812494549</v>
       </c>
       <c r="X6" t="n">
         <v>-11107.11539047141</v>
@@ -3950,7 +3836,7 @@
         <v>559.6763142710811</v>
       </c>
       <c r="Z6" t="n">
-        <v>271.024</v>
+        <v>133734960.9734585</v>
       </c>
       <c r="AA6" t="n">
         <v>6.206783793336595e-07</v>
@@ -3990,10 +3876,8 @@
       <c r="K7" t="n">
         <v>86.64416046751572</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 17.054x + -11236.524</t>
-        </is>
+      <c r="W7" t="n">
+        <v>17.05392832233007</v>
       </c>
       <c r="X7" t="n">
         <v>-11236.52387553937</v>
@@ -4002,7 +3886,7 @@
         <v>551.4612662733882</v>
       </c>
       <c r="Z7" t="n">
-        <v>259.5440000000001</v>
+        <v>79667415.47283565</v>
       </c>
       <c r="AA7" t="n">
         <v>5.886170529079986e-07</v>
@@ -4042,10 +3926,8 @@
       <c r="K8" t="n">
         <v>86.7000471683982</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 17.343x + -11214.333</t>
-        </is>
+      <c r="W8" t="n">
+        <v>17.34340300547591</v>
       </c>
       <c r="X8" t="n">
         <v>-11214.33325122697</v>
@@ -4054,7 +3936,7 @@
         <v>543.3157354088189</v>
       </c>
       <c r="Z8" t="n">
-        <v>259.509</v>
+        <v>110229427.7902048</v>
       </c>
       <c r="AA8" t="n">
         <v>5.676922735456703e-07</v>
@@ -4094,10 +3976,8 @@
       <c r="K9" t="n">
         <v>86.73254258456815</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 17.516x + -11079.724</t>
-        </is>
+      <c r="W9" t="n">
+        <v>17.51626622722893</v>
       </c>
       <c r="X9" t="n">
         <v>-11079.7237515102</v>
@@ -4106,7 +3986,7 @@
         <v>535.332687899152</v>
       </c>
       <c r="Z9" t="n">
-        <v>250.301</v>
+        <v>151031625.3812257</v>
       </c>
       <c r="AA9" t="n">
         <v>5.446282324568905e-07</v>
@@ -4146,10 +4026,8 @@
       <c r="K10" t="n">
         <v>86.60887503835845</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 16.876x + -10421.289</t>
-        </is>
+      <c r="W10" t="n">
+        <v>16.87606968855905</v>
       </c>
       <c r="X10" t="n">
         <v>-10421.2894128726</v>
@@ -4158,7 +4036,7 @@
         <v>527.7492158615748</v>
       </c>
       <c r="Z10" t="n">
-        <v>250.181</v>
+        <v>69139694.95995358</v>
       </c>
       <c r="AA10" t="n">
         <v>5.283929184470241e-07</v>
@@ -4198,10 +4076,8 @@
       <c r="K11" t="n">
         <v>86.77269245723578</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 17.735x + -10800.379</t>
-        </is>
+      <c r="W11" t="n">
+        <v>17.7346506119745</v>
       </c>
       <c r="X11" t="n">
         <v>-10800.37868419815</v>
@@ -4210,7 +4086,7 @@
         <v>520.5777571939508</v>
       </c>
       <c r="Z11" t="n">
-        <v>244.0300000000001</v>
+        <v>38550024.03899003</v>
       </c>
       <c r="AA11" t="n">
         <v>5.133228685586095e-07</v>
@@ -4336,12 +4212,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4396,10 +4272,8 @@
       <c r="K2" t="n">
         <v>85.95620854890785</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 14.145x + -9296.020</t>
-        </is>
+      <c r="W2" t="n">
+        <v>14.14529286882315</v>
       </c>
       <c r="X2" t="n">
         <v>-9296.019665877137</v>
@@ -4408,7 +4282,7 @@
         <v>548.4584993393676</v>
       </c>
       <c r="Z2" t="n">
-        <v>308.104</v>
+        <v>33868013.95077544</v>
       </c>
       <c r="AA2" t="n">
         <v>6.64534361249985e-07</v>
@@ -4448,10 +4322,8 @@
       <c r="K3" t="n">
         <v>86.49145820315111</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 16.310x + -10345.659</t>
-        </is>
+      <c r="W3" t="n">
+        <v>16.30995126247214</v>
       </c>
       <c r="X3" t="n">
         <v>-10345.65935742836</v>
@@ -4460,7 +4332,7 @@
         <v>537.210201868043</v>
       </c>
       <c r="Z3" t="n">
-        <v>262.4930000000001</v>
+        <v>118712454.8685306</v>
       </c>
       <c r="AA3" t="n">
         <v>5.822641005546925e-07</v>
@@ -4500,10 +4372,8 @@
       <c r="K4" t="n">
         <v>86.50976978264542</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 16.396x + -10165.137</t>
-        </is>
+      <c r="W4" t="n">
+        <v>16.3957355568649</v>
       </c>
       <c r="X4" t="n">
         <v>-10165.13698237332</v>
@@ -4512,7 +4382,7 @@
         <v>530.4059993973187</v>
       </c>
       <c r="Z4" t="n">
-        <v>251.874</v>
+        <v>71146535.65390402</v>
       </c>
       <c r="AA4" t="n">
         <v>5.538610796403511e-07</v>
@@ -4552,10 +4422,8 @@
       <c r="K5" t="n">
         <v>86.60947427756916</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 16.879x + -10311.454</t>
-        </is>
+      <c r="W5" t="n">
+        <v>16.87905932997939</v>
       </c>
       <c r="X5" t="n">
         <v>-10311.45445201213</v>
@@ -4564,7 +4432,7 @@
         <v>523.9412351233299</v>
       </c>
       <c r="Z5" t="n">
-        <v>245.47</v>
+        <v>43833349.28309046</v>
       </c>
       <c r="AA5" t="n">
         <v>5.362085377543871e-07</v>
@@ -4604,10 +4472,8 @@
       <c r="K6" t="n">
         <v>86.62786991769364</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 16.971x + -10188.710</t>
-        </is>
+      <c r="W6" t="n">
+        <v>16.97135268144558</v>
       </c>
       <c r="X6" t="n">
         <v>-10188.70953644262</v>
@@ -4616,7 +4482,7 @@
         <v>517.1734637849278</v>
       </c>
       <c r="Z6" t="n">
-        <v>241.8200000000001</v>
+        <v>19941641.97983824</v>
       </c>
       <c r="AA6" t="n">
         <v>5.216831471385929e-07</v>
@@ -4656,10 +4522,8 @@
       <c r="K7" t="n">
         <v>86.82750704386147</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 18.042x + -10713.039</t>
-        </is>
+      <c r="W7" t="n">
+        <v>18.04171489569705</v>
       </c>
       <c r="X7" t="n">
         <v>-10713.03892349086</v>
@@ -4668,7 +4532,7 @@
         <v>510.9371799472771</v>
       </c>
       <c r="Z7" t="n">
-        <v>232.804</v>
+        <v>21364185.31590111</v>
       </c>
       <c r="AA7" t="n">
         <v>5.085709092644983e-07</v>
@@ -4708,10 +4572,8 @@
       <c r="K8" t="n">
         <v>86.94132693735772</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 18.714x + -10988.871</t>
-        </is>
+      <c r="W8" t="n">
+        <v>18.71443597128127</v>
       </c>
       <c r="X8" t="n">
         <v>-10988.87092254372</v>
@@ -4720,7 +4582,7 @@
         <v>505.1936294296866</v>
       </c>
       <c r="Z8" t="n">
-        <v>229.415</v>
+        <v>217794310.3336492</v>
       </c>
       <c r="AA8" t="n">
         <v>4.996646735832783e-07</v>
@@ -4760,10 +4622,8 @@
       <c r="K9" t="n">
         <v>86.79270814982048</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 17.846x + -10275.022</t>
-        </is>
+      <c r="W9" t="n">
+        <v>17.8455606674375</v>
       </c>
       <c r="X9" t="n">
         <v>-10275.02179171626</v>
@@ -4772,7 +4632,7 @@
         <v>499.971990244395</v>
       </c>
       <c r="Z9" t="n">
-        <v>230.1909999999999</v>
+        <v>207989369.6311161</v>
       </c>
       <c r="AA9" t="n">
         <v>4.913081306985214e-07</v>
@@ -4812,10 +4672,8 @@
       <c r="K10" t="n">
         <v>86.90390655366456</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 18.488x + -10551.788</t>
-        </is>
+      <c r="W10" t="n">
+        <v>18.4878143226265</v>
       </c>
       <c r="X10" t="n">
         <v>-10551.78846650073</v>
@@ -4824,7 +4682,7 @@
         <v>495.0602961609386</v>
       </c>
       <c r="Z10" t="n">
-        <v>226.432</v>
+        <v>577435629.8490283</v>
       </c>
       <c r="AA10" t="n">
         <v>4.836258111412862e-07</v>
@@ -4864,10 +4722,8 @@
       <c r="K11" t="n">
         <v>86.96352012577218</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 18.851x + -10651.036</t>
-        </is>
+      <c r="W11" t="n">
+        <v>18.85147632454354</v>
       </c>
       <c r="X11" t="n">
         <v>-10651.03648055586</v>
@@ -4876,7 +4732,7 @@
         <v>490.3719480906841</v>
       </c>
       <c r="Z11" t="n">
-        <v>224.937</v>
+        <v>37340201.01544112</v>
       </c>
       <c r="AA11" t="n">
         <v>4.782830294183207e-07</v>
@@ -4916,10 +4772,8 @@
       <c r="K12" t="n">
         <v>86.89395331886263</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 18.428x + -10260.209</t>
-        </is>
+      <c r="W12" t="n">
+        <v>18.42845499719915</v>
       </c>
       <c r="X12" t="n">
         <v>-10260.20862746471</v>
@@ -4928,7 +4782,7 @@
         <v>485.7195061657517</v>
       </c>
       <c r="Z12" t="n">
-        <v>225.2009999999999</v>
+        <v>106225137.1154371</v>
       </c>
       <c r="AA12" t="n">
         <v>4.72514108836623e-07</v>
@@ -4968,10 +4822,8 @@
       <c r="K13" t="n">
         <v>87.06754657440469</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 19.521x + -10800.953</t>
-        </is>
+      <c r="W13" t="n">
+        <v>19.52144974358852</v>
       </c>
       <c r="X13" t="n">
         <v>-10800.95263639708</v>
@@ -4980,7 +4832,7 @@
         <v>481.1161959089837</v>
       </c>
       <c r="Z13" t="n">
-        <v>218.064</v>
+        <v>265683551.0406118</v>
       </c>
       <c r="AA13" t="n">
         <v>4.662560501647432e-07</v>
@@ -5020,10 +4872,8 @@
       <c r="K14" t="n">
         <v>87.00386093441517</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 19.106x + -10430.512</t>
-        </is>
+      <c r="W14" t="n">
+        <v>19.10577030793165</v>
       </c>
       <c r="X14" t="n">
         <v>-10430.51170212585</v>
@@ -5032,7 +4882,7 @@
         <v>476.4290111059876</v>
       </c>
       <c r="Z14" t="n">
-        <v>223.1080000000001</v>
+        <v>526242721.4847798</v>
       </c>
       <c r="AA14" t="n">
         <v>4.631060404567869e-07</v>
@@ -5072,10 +4922,8 @@
       <c r="K15" t="n">
         <v>87.06671331105046</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 19.516x + -10538.269</t>
-        </is>
+      <c r="W15" t="n">
+        <v>19.51589455724594</v>
       </c>
       <c r="X15" t="n">
         <v>-10538.2687754834</v>
@@ -5084,7 +4932,7 @@
         <v>471.6699504570026</v>
       </c>
       <c r="Z15" t="n">
-        <v>218.167</v>
+        <v>31788854.7874673</v>
       </c>
       <c r="AA15" t="n">
         <v>4.567488918996206e-07</v>
@@ -5124,10 +4972,8 @@
       <c r="K16" t="n">
         <v>87.14698387776581</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 20.066x + -10734.585</t>
-        </is>
+      <c r="W16" t="n">
+        <v>20.0659282562475</v>
       </c>
       <c r="X16" t="n">
         <v>-10734.58450027679</v>
@@ -5136,7 +4982,7 @@
         <v>466.8813678268625</v>
       </c>
       <c r="Z16" t="n">
-        <v>214.9640000000001</v>
+        <v>81748662.55577137</v>
       </c>
       <c r="AA16" t="n">
         <v>4.522718850824425e-07</v>
@@ -5176,10 +5022,8 @@
       <c r="K17" t="n">
         <v>87.10999092493243</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 19.809x + -10452.166</t>
-        </is>
+      <c r="W17" t="n">
+        <v>19.80865074437075</v>
       </c>
       <c r="X17" t="n">
         <v>-10452.16587075695</v>
@@ -5188,7 +5032,7 @@
         <v>462.0965369417456</v>
       </c>
       <c r="Z17" t="n">
-        <v>217.1379999999999</v>
+        <v>42544192.1390802</v>
       </c>
       <c r="AA17" t="n">
         <v>4.478297767029729e-07</v>
@@ -5228,10 +5072,8 @@
       <c r="K18" t="n">
         <v>87.17600098309205</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 20.272x + -10593.935</t>
-        </is>
+      <c r="W18" t="n">
+        <v>20.27244880650161</v>
       </c>
       <c r="X18" t="n">
         <v>-10593.93515313758</v>
@@ -5240,7 +5082,7 @@
         <v>457.324415910957</v>
       </c>
       <c r="Z18" t="n">
-        <v>216.206</v>
+        <v>189718246.9381725</v>
       </c>
       <c r="AA18" t="n">
         <v>4.445128379655021e-07</v>
@@ -5280,10 +5122,8 @@
       <c r="K19" t="n">
         <v>87.26571630256188</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 20.939x + -10835.838</t>
-        </is>
+      <c r="W19" t="n">
+        <v>20.938674932858</v>
       </c>
       <c r="X19" t="n">
         <v>-10835.83790072471</v>
@@ -5292,7 +5132,7 @@
         <v>452.6053765604874</v>
       </c>
       <c r="Z19" t="n">
-        <v>211.967</v>
+        <v>38423494.24429484</v>
       </c>
       <c r="AA19" t="n">
         <v>4.396161957261621e-07</v>
@@ -5332,10 +5172,8 @@
       <c r="K20" t="n">
         <v>87.15350563982575</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 20.112x + -10237.475</t>
-        </is>
+      <c r="W20" t="n">
+        <v>20.11197842027876</v>
       </c>
       <c r="X20" t="n">
         <v>-10237.4753925544</v>
@@ -5344,7 +5182,7 @@
         <v>447.8181885829125</v>
       </c>
       <c r="Z20" t="n">
-        <v>216.501</v>
+        <v>49822100.56803484</v>
       </c>
       <c r="AA20" t="n">
         <v>4.366229156045198e-07</v>
@@ -5384,10 +5222,8 @@
       <c r="K21" t="n">
         <v>87.2522598512541</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 20.836x + -10501.652</t>
-        </is>
+      <c r="W21" t="n">
+        <v>20.83597615362318</v>
       </c>
       <c r="X21" t="n">
         <v>-10501.65173754466</v>
@@ -5396,7 +5232,7 @@
         <v>443.0544249987667</v>
       </c>
       <c r="Z21" t="n">
-        <v>210.951</v>
+        <v>250687932.7284362</v>
       </c>
       <c r="AA21" t="n">
         <v>4.321799788876768e-07</v>
@@ -5436,10 +5272,8 @@
       <c r="K22" t="n">
         <v>87.24976640333482</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 20.817x + -10356.465</t>
-        </is>
+      <c r="W22" t="n">
+        <v>20.81705659669926</v>
       </c>
       <c r="X22" t="n">
         <v>-10356.46480867213</v>
@@ -5448,7 +5282,7 @@
         <v>438.2193279052158</v>
       </c>
       <c r="Z22" t="n">
-        <v>211.449</v>
+        <v>135399575.902739</v>
       </c>
       <c r="AA22" t="n">
         <v>4.291012941134729e-07</v>
@@ -5574,12 +5408,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5634,10 +5468,8 @@
       <c r="K2" t="n">
         <v>82.6651157206109</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 7.769x + -6345.806</t>
-        </is>
+      <c r="W2" t="n">
+        <v>7.768689464418952</v>
       </c>
       <c r="X2" t="n">
         <v>-6345.806386151228</v>
@@ -5646,7 +5478,7 @@
         <v>548.8373652719168</v>
       </c>
       <c r="Z2" t="n">
-        <v>565.4799999999999</v>
+        <v>192761399.6507388</v>
       </c>
       <c r="AA2" t="n">
         <v>5.92952917704346e-06</v>
@@ -5686,10 +5518,8 @@
       <c r="K3" t="n">
         <v>84.89370956873204</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 11.191x + -8039.176</t>
-        </is>
+      <c r="W3" t="n">
+        <v>11.19090391352976</v>
       </c>
       <c r="X3" t="n">
         <v>-8039.17587700782</v>
@@ -5698,7 +5528,7 @@
         <v>579.9562874628609</v>
       </c>
       <c r="Z3" t="n">
-        <v>391.0300000000001</v>
+        <v>380073926.8092821</v>
       </c>
       <c r="AA3" t="n">
         <v>1.185401619888726e-06</v>
@@ -5738,10 +5568,8 @@
       <c r="K4" t="n">
         <v>85.74320987217183</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 13.435x + -9287.798</t>
-        </is>
+      <c r="W4" t="n">
+        <v>13.43508126323667</v>
       </c>
       <c r="X4" t="n">
         <v>-9287.798107413642</v>
@@ -5750,7 +5578,7 @@
         <v>570.6200555914047</v>
       </c>
       <c r="Z4" t="n">
-        <v>324.691</v>
+        <v>141121040.1946451</v>
       </c>
       <c r="AA4" t="n">
         <v>8.598524766326485e-07</v>
@@ -5790,10 +5618,8 @@
       <c r="K5" t="n">
         <v>86.09600229280805</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 14.653x + -9894.437</t>
-        </is>
+      <c r="W5" t="n">
+        <v>14.65346207930561</v>
       </c>
       <c r="X5" t="n">
         <v>-9894.437174768706</v>
@@ -5802,7 +5628,7 @@
         <v>563.2548048657297</v>
       </c>
       <c r="Z5" t="n">
-        <v>292.1700000000001</v>
+        <v>37285288.0460481</v>
       </c>
       <c r="AA5" t="n">
         <v>7.420131769015894e-07</v>
@@ -5842,10 +5668,8 @@
       <c r="K6" t="n">
         <v>86.14418938835858</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 14.837x + -9780.091</t>
-        </is>
+      <c r="W6" t="n">
+        <v>14.83715484156516</v>
       </c>
       <c r="X6" t="n">
         <v>-9780.090674851996</v>
@@ -5854,7 +5678,7 @@
         <v>556.1471854430796</v>
       </c>
       <c r="Z6" t="n">
-        <v>279.1559999999999</v>
+        <v>54022908.28903898</v>
       </c>
       <c r="AA6" t="n">
         <v>6.766352163401629e-07</v>
@@ -5894,10 +5718,8 @@
       <c r="K7" t="n">
         <v>86.58717447072914</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 16.769x + -10961.284</t>
-        </is>
+      <c r="W7" t="n">
+        <v>16.76851081017094</v>
       </c>
       <c r="X7" t="n">
         <v>-10961.2840643544</v>
@@ -5906,7 +5728,7 @@
         <v>548.8851700371114</v>
       </c>
       <c r="Z7" t="n">
-        <v>258.9640000000001</v>
+        <v>48425086.81621543</v>
       </c>
       <c r="AA7" t="n">
         <v>6.298505710540088e-07</v>
@@ -5946,10 +5768,8 @@
       <c r="K8" t="n">
         <v>86.56080407443896</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 16.640x + -10639.291</t>
-        </is>
+      <c r="W8" t="n">
+        <v>16.6396306878686</v>
       </c>
       <c r="X8" t="n">
         <v>-10639.29098362959</v>
@@ -5958,7 +5778,7 @@
         <v>541.7276949713749</v>
       </c>
       <c r="Z8" t="n">
-        <v>253.134</v>
+        <v>41906008.05530718</v>
       </c>
       <c r="AA8" t="n">
         <v>5.98746115629063e-07</v>
@@ -5998,10 +5818,8 @@
       <c r="K9" t="n">
         <v>86.60186424003736</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 16.841x + -10566.119</t>
-        </is>
+      <c r="W9" t="n">
+        <v>16.84117062218054</v>
       </c>
       <c r="X9" t="n">
         <v>-10566.11853173201</v>
@@ -6010,7 +5828,7 @@
         <v>534.9589497520589</v>
       </c>
       <c r="Z9" t="n">
-        <v>245.8810000000001</v>
+        <v>108692580.7518235</v>
       </c>
       <c r="AA9" t="n">
         <v>5.73714269171323e-07</v>
@@ -6050,10 +5868,8 @@
       <c r="K10" t="n">
         <v>86.78168544461973</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 17.784x + -11034.016</t>
-        </is>
+      <c r="W10" t="n">
+        <v>17.78431165591698</v>
       </c>
       <c r="X10" t="n">
         <v>-11034.01640970146</v>
@@ -6062,7 +5878,7 @@
         <v>528.7058654593757</v>
       </c>
       <c r="Z10" t="n">
-        <v>238.38</v>
+        <v>52218997.73365314</v>
       </c>
       <c r="AA10" t="n">
         <v>5.552519750927198e-07</v>
@@ -6102,10 +5918,8 @@
       <c r="K11" t="n">
         <v>86.63028576451273</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 16.984x + -10313.156</t>
-        </is>
+      <c r="W11" t="n">
+        <v>16.98354807391167</v>
       </c>
       <c r="X11" t="n">
         <v>-10313.1555306142</v>
@@ -6114,7 +5928,7 @@
         <v>522.8425911722518</v>
       </c>
       <c r="Z11" t="n">
-        <v>239.2380000000001</v>
+        <v>33625030.64626577</v>
       </c>
       <c r="AA11" t="n">
         <v>5.399516033166096e-07</v>
@@ -6240,12 +6054,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6300,10 +6114,8 @@
       <c r="K2" t="n">
         <v>85.41998583830714</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.483x + -8225.624</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.48330004533085</v>
       </c>
       <c r="X2" t="n">
         <v>-8225.623711085243</v>
@@ -6312,7 +6124,7 @@
         <v>547.3472225548547</v>
       </c>
       <c r="Z2" t="n">
-        <v>346.3549999999999</v>
+        <v>397961733.3448045</v>
       </c>
       <c r="AA2" t="n">
         <v>8.274102823993408e-07</v>
@@ -6352,10 +6164,8 @@
       <c r="K3" t="n">
         <v>86.38672044718129</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 15.836x + -10121.954</t>
-        </is>
+      <c r="W3" t="n">
+        <v>15.83597477813128</v>
       </c>
       <c r="X3" t="n">
         <v>-10121.95418918851</v>
@@ -6364,7 +6174,7 @@
         <v>537.8199450089054</v>
       </c>
       <c r="Z3" t="n">
-        <v>274.2910000000001</v>
+        <v>74128569.15747638</v>
       </c>
       <c r="AA3" t="n">
         <v>6.527902110359519e-07</v>
@@ -6404,10 +6214,8 @@
       <c r="K4" t="n">
         <v>86.55930970150752</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 16.632x + -10407.166</t>
-        </is>
+      <c r="W4" t="n">
+        <v>16.63238631148031</v>
       </c>
       <c r="X4" t="n">
         <v>-10407.16551787421</v>
@@ -6416,7 +6224,7 @@
         <v>532.0826246452998</v>
       </c>
       <c r="Z4" t="n">
-        <v>251.7089999999999</v>
+        <v>56612086.9927252</v>
       </c>
       <c r="AA4" t="n">
         <v>6.00545680042186e-07</v>
@@ -6456,10 +6264,8 @@
       <c r="K5" t="n">
         <v>86.69298291892619</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 17.306x + -10690.690</t>
-        </is>
+      <c r="W5" t="n">
+        <v>17.30627293415061</v>
       </c>
       <c r="X5" t="n">
         <v>-10690.68976420769</v>
@@ -6468,7 +6274,7 @@
         <v>526.7603610991472</v>
       </c>
       <c r="Z5" t="n">
-        <v>243.583</v>
+        <v>15084464.71567873</v>
       </c>
       <c r="AA5" t="n">
         <v>5.745483423175343e-07</v>
@@ -6508,10 +6314,8 @@
       <c r="K6" t="n">
         <v>86.76941509436701</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 17.717x + -10786.673</t>
-        </is>
+      <c r="W6" t="n">
+        <v>17.71662103794387</v>
       </c>
       <c r="X6" t="n">
         <v>-10786.67267908514</v>
@@ -6520,7 +6324,7 @@
         <v>520.894097614307</v>
       </c>
       <c r="Z6" t="n">
-        <v>235.6479999999999</v>
+        <v>58145772.69805376</v>
       </c>
       <c r="AA6" t="n">
         <v>5.551725047422679e-07</v>
@@ -6560,10 +6364,8 @@
       <c r="K7" t="n">
         <v>86.6801818769266</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 17.239x + -10288.053</t>
-        </is>
+      <c r="W7" t="n">
+        <v>17.23939214072621</v>
       </c>
       <c r="X7" t="n">
         <v>-10288.05260605998</v>
@@ -6572,7 +6374,7 @@
         <v>514.6214062575486</v>
       </c>
       <c r="Z7" t="n">
-        <v>235.096</v>
+        <v>29230952.67993838</v>
       </c>
       <c r="AA7" t="n">
         <v>5.399810808069631e-07</v>
@@ -6612,10 +6414,8 @@
       <c r="K8" t="n">
         <v>86.96933328543356</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 18.888x + -11188.641</t>
-        </is>
+      <c r="W8" t="n">
+        <v>18.88770330600138</v>
       </c>
       <c r="X8" t="n">
         <v>-11188.64052107184</v>
@@ -6624,7 +6424,7 @@
         <v>508.4598098639956</v>
       </c>
       <c r="Z8" t="n">
-        <v>223.103</v>
+        <v>75423441.15448593</v>
       </c>
       <c r="AA8" t="n">
         <v>5.25718116813532e-07</v>
@@ -6664,10 +6464,8 @@
       <c r="K9" t="n">
         <v>86.85703226049561</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 18.212x + -10581.556</t>
-        </is>
+      <c r="W9" t="n">
+        <v>18.21154508039162</v>
       </c>
       <c r="X9" t="n">
         <v>-10581.55589589904</v>
@@ -6676,7 +6474,7 @@
         <v>502.6282180827429</v>
       </c>
       <c r="Z9" t="n">
-        <v>224.5070000000001</v>
+        <v>423603549.2168085</v>
       </c>
       <c r="AA9" t="n">
         <v>5.164684199479608e-07</v>
@@ -6716,10 +6514,8 @@
       <c r="K10" t="n">
         <v>87.0597237926864</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 19.469x + -11217.458</t>
-        </is>
+      <c r="W10" t="n">
+        <v>19.469420819298</v>
       </c>
       <c r="X10" t="n">
         <v>-11217.45765620496</v>
@@ -6728,7 +6524,7 @@
         <v>497.0874087230442</v>
       </c>
       <c r="Z10" t="n">
-        <v>216.336</v>
+        <v>38368921.81256433</v>
       </c>
       <c r="AA10" t="n">
         <v>5.057314874306787e-07</v>
@@ -6768,10 +6564,8 @@
       <c r="K11" t="n">
         <v>86.98087440031027</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 18.960x + -10739.298</t>
-        </is>
+      <c r="W11" t="n">
+        <v>18.96003931904799</v>
       </c>
       <c r="X11" t="n">
         <v>-10739.29793640912</v>
@@ -6780,7 +6574,7 @@
         <v>491.7177670637182</v>
       </c>
       <c r="Z11" t="n">
-        <v>216.908</v>
+        <v>75870617.73092788</v>
       </c>
       <c r="AA11" t="n">
         <v>4.976821138541326e-07</v>
@@ -6820,10 +6614,8 @@
       <c r="K12" t="n">
         <v>86.97241186449907</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 18.907x + -10565.599</t>
-        </is>
+      <c r="W12" t="n">
+        <v>18.90694497028715</v>
       </c>
       <c r="X12" t="n">
         <v>-10565.59914088861</v>
@@ -6832,7 +6624,7 @@
         <v>486.5325252174118</v>
       </c>
       <c r="Z12" t="n">
-        <v>216.77</v>
+        <v>204753851.1892565</v>
       </c>
       <c r="AA12" t="n">
         <v>4.914478213336615e-07</v>
@@ -6872,10 +6664,8 @@
       <c r="K13" t="n">
         <v>87.08989229112142</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 19.672x + -10893.423</t>
-        </is>
+      <c r="W13" t="n">
+        <v>19.67160933843106</v>
       </c>
       <c r="X13" t="n">
         <v>-10893.42307022485</v>
@@ -6884,7 +6674,7 @@
         <v>481.5806828529448</v>
       </c>
       <c r="Z13" t="n">
-        <v>213.1899999999999</v>
+        <v>63532016.46220312</v>
       </c>
       <c r="AA13" t="n">
         <v>4.847425979721743e-07</v>
@@ -6924,10 +6714,8 @@
       <c r="K14" t="n">
         <v>87.08037495563323</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 19.607x + -10716.672</t>
-        </is>
+      <c r="W14" t="n">
+        <v>19.60737362175578</v>
       </c>
       <c r="X14" t="n">
         <v>-10716.67217080022</v>
@@ -6936,7 +6724,7 @@
         <v>476.6142989058284</v>
       </c>
       <c r="Z14" t="n">
-        <v>213.2859999999999</v>
+        <v>34719040.07934395</v>
       </c>
       <c r="AA14" t="n">
         <v>4.789190806279649e-07</v>
@@ -6976,10 +6764,8 @@
       <c r="K15" t="n">
         <v>87.14815463831815</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 20.074x + -10846.598</t>
-        </is>
+      <c r="W15" t="n">
+        <v>20.07417949855282</v>
       </c>
       <c r="X15" t="n">
         <v>-10846.59767874084</v>
@@ -6988,7 +6774,7 @@
         <v>471.7503690363056</v>
       </c>
       <c r="Z15" t="n">
-        <v>207.846</v>
+        <v>95155789.09695755</v>
       </c>
       <c r="AA15" t="n">
         <v>4.721850160619705e-07</v>
@@ -7028,10 +6814,8 @@
       <c r="K16" t="n">
         <v>87.15835274382547</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 20.146x + -10754.076</t>
-        </is>
+      <c r="W16" t="n">
+        <v>20.14634063930642</v>
       </c>
       <c r="X16" t="n">
         <v>-10754.07584243441</v>
@@ -7040,7 +6824,7 @@
         <v>466.858430803799</v>
       </c>
       <c r="Z16" t="n">
-        <v>207.2959999999999</v>
+        <v>31668267.24169507</v>
       </c>
       <c r="AA16" t="n">
         <v>4.674301422127175e-07</v>
@@ -7080,10 +6864,8 @@
       <c r="K17" t="n">
         <v>87.23197544047315</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 20.683x + -10933.572</t>
-        </is>
+      <c r="W17" t="n">
+        <v>20.68305243264061</v>
       </c>
       <c r="X17" t="n">
         <v>-10933.5715616793</v>
@@ -7092,7 +6874,7 @@
         <v>462.0786899282044</v>
       </c>
       <c r="Z17" t="n">
-        <v>204.08</v>
+        <v>84156379.74575013</v>
       </c>
       <c r="AA17" t="n">
         <v>4.623054450161197e-07</v>
@@ -7132,10 +6914,8 @@
       <c r="K18" t="n">
         <v>87.18183856214445</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 20.315x + -10585.008</t>
-        </is>
+      <c r="W18" t="n">
+        <v>20.31450945639425</v>
       </c>
       <c r="X18" t="n">
         <v>-10585.00810576945</v>
@@ -7144,7 +6924,7 @@
         <v>457.3176790141066</v>
       </c>
       <c r="Z18" t="n">
-        <v>206.425</v>
+        <v>71593270.90499125</v>
       </c>
       <c r="AA18" t="n">
         <v>4.578859941137327e-07</v>
@@ -7184,10 +6964,8 @@
       <c r="K19" t="n">
         <v>87.27012388388947</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 20.973x + -10822.605</t>
-        </is>
+      <c r="W19" t="n">
+        <v>20.9725332709925</v>
       </c>
       <c r="X19" t="n">
         <v>-10822.60466248579</v>
@@ -7196,7 +6974,7 @@
         <v>452.6051858130465</v>
       </c>
       <c r="Z19" t="n">
-        <v>202.2570000000001</v>
+        <v>127173917.7358479</v>
       </c>
       <c r="AA19" t="n">
         <v>4.531406817193074e-07</v>
@@ -7236,10 +7014,8 @@
       <c r="K20" t="n">
         <v>87.34861679587324</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 21.594x + -11034.117</t>
-        </is>
+      <c r="W20" t="n">
+        <v>21.59434203030444</v>
       </c>
       <c r="X20" t="n">
         <v>-11034.11707855003</v>
@@ -7248,7 +7024,7 @@
         <v>447.888471151404</v>
       </c>
       <c r="Z20" t="n">
-        <v>199.603</v>
+        <v>491751706.2692647</v>
       </c>
       <c r="AA20" t="n">
         <v>4.488572168994832e-07</v>
@@ -7288,10 +7064,8 @@
       <c r="K21" t="n">
         <v>87.3059686203291</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 21.252x + -10710.446</t>
-        </is>
+      <c r="W21" t="n">
+        <v>21.25199785051874</v>
       </c>
       <c r="X21" t="n">
         <v>-10710.44611308531</v>
@@ -7300,7 +7074,7 @@
         <v>443.1211373369848</v>
       </c>
       <c r="Z21" t="n">
-        <v>202.359</v>
+        <v>363911524.2865228</v>
       </c>
       <c r="AA21" t="n">
         <v>4.467858562237523e-07</v>
@@ -7340,10 +7114,8 @@
       <c r="K22" t="n">
         <v>87.40956623821799</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 22.103x + -11038.316</t>
-        </is>
+      <c r="W22" t="n">
+        <v>22.10314574339286</v>
       </c>
       <c r="X22" t="n">
         <v>-11038.31622551207</v>
@@ -7352,7 +7124,7 @@
         <v>438.4015632563413</v>
       </c>
       <c r="Z22" t="n">
-        <v>197.902</v>
+        <v>960195021.2010366</v>
       </c>
       <c r="AA22" t="n">
         <v>4.417689184530119e-07</v>
@@ -7478,12 +7250,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7538,10 +7310,8 @@
       <c r="K2" t="n">
         <v>83.00603305668103</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 8.151x + -6335.223</t>
-        </is>
+      <c r="W2" t="n">
+        <v>8.15144218002084</v>
       </c>
       <c r="X2" t="n">
         <v>-6335.222807262978</v>
@@ -7550,7 +7320,7 @@
         <v>569.5051116101438</v>
       </c>
       <c r="Z2" t="n">
-        <v>534.7510000000001</v>
+        <v>116659959.6340644</v>
       </c>
       <c r="AA2" t="n">
         <v>3.515485762593364e-06</v>
@@ -7590,10 +7360,8 @@
       <c r="K3" t="n">
         <v>85.05074517941036</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 11.548x + -8134.556</t>
-        </is>
+      <c r="W3" t="n">
+        <v>11.54783978494475</v>
       </c>
       <c r="X3" t="n">
         <v>-8134.556070058749</v>
@@ -7602,7 +7370,7 @@
         <v>575.3641575183071</v>
       </c>
       <c r="Z3" t="n">
-        <v>377.962</v>
+        <v>38379155.83272927</v>
       </c>
       <c r="AA3" t="n">
         <v>1.067160613020955e-06</v>
@@ -7642,10 +7410,8 @@
       <c r="K4" t="n">
         <v>85.92343413290865</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 14.031x + -9593.415</t>
-        </is>
+      <c r="W4" t="n">
+        <v>14.03118871716508</v>
       </c>
       <c r="X4" t="n">
         <v>-9593.414924072269</v>
@@ -7654,7 +7420,7 @@
         <v>566.8042478641837</v>
       </c>
       <c r="Z4" t="n">
-        <v>312.7379999999999</v>
+        <v>145897571.268115</v>
       </c>
       <c r="AA4" t="n">
         <v>8.073620234051986e-07</v>
@@ -7694,10 +7460,8 @@
       <c r="K5" t="n">
         <v>86.19816502605812</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 15.048x + -10061.966</t>
-        </is>
+      <c r="W5" t="n">
+        <v>15.04843464919558</v>
       </c>
       <c r="X5" t="n">
         <v>-10061.96587485877</v>
@@ -7706,7 +7470,7 @@
         <v>560.3672242138649</v>
       </c>
       <c r="Z5" t="n">
-        <v>286.981</v>
+        <v>176992424.1180134</v>
       </c>
       <c r="AA5" t="n">
         <v>7.099148494990775e-07</v>
@@ -7746,10 +7510,8 @@
       <c r="K6" t="n">
         <v>86.42196559657212</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 15.992x + -10519.636</t>
-        </is>
+      <c r="W6" t="n">
+        <v>15.99237814734996</v>
       </c>
       <c r="X6" t="n">
         <v>-10519.63626502813</v>
@@ -7758,7 +7520,7 @@
         <v>554.4775658602906</v>
       </c>
       <c r="Z6" t="n">
-        <v>265.9299999999999</v>
+        <v>88895794.08971889</v>
       </c>
       <c r="AA6" t="n">
         <v>6.514220746783614e-07</v>
@@ -7798,10 +7560,8 @@
       <c r="K7" t="n">
         <v>86.43352190917442</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 16.044x + -10352.698</t>
-        </is>
+      <c r="W7" t="n">
+        <v>16.04433234548697</v>
       </c>
       <c r="X7" t="n">
         <v>-10352.69817113405</v>
@@ -7810,7 +7570,7 @@
         <v>548.2570902789527</v>
       </c>
       <c r="Z7" t="n">
-        <v>256.8040000000001</v>
+        <v>99909522.09402075</v>
       </c>
       <c r="AA7" t="n">
         <v>6.150168519841109e-07</v>
@@ -7850,10 +7610,8 @@
       <c r="K8" t="n">
         <v>86.52270585445856</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 16.457x + -10443.751</t>
-        </is>
+      <c r="W8" t="n">
+        <v>16.45688110030558</v>
       </c>
       <c r="X8" t="n">
         <v>-10443.75143186782</v>
@@ -7862,7 +7620,7 @@
         <v>541.2648713405404</v>
       </c>
       <c r="Z8" t="n">
-        <v>250.348</v>
+        <v>92491285.65868892</v>
       </c>
       <c r="AA8" t="n">
         <v>5.88622311340895e-07</v>
@@ -7902,10 +7660,8 @@
       <c r="K9" t="n">
         <v>86.60543639433614</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 16.859x + -10521.287</t>
-        </is>
+      <c r="W9" t="n">
+        <v>16.85893446424018</v>
       </c>
       <c r="X9" t="n">
         <v>-10521.2872320515</v>
@@ -7914,7 +7670,7 @@
         <v>534.0357262020848</v>
       </c>
       <c r="Z9" t="n">
-        <v>243.2700000000001</v>
+        <v>166929280.4379201</v>
       </c>
       <c r="AA9" t="n">
         <v>5.667962330145158e-07</v>
@@ -7954,10 +7710,8 @@
       <c r="K10" t="n">
         <v>86.76147297195421</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 17.673x + -10874.552</t>
-        </is>
+      <c r="W10" t="n">
+        <v>17.67308068557021</v>
       </c>
       <c r="X10" t="n">
         <v>-10874.55213705548</v>
@@ -7966,7 +7720,7 @@
         <v>527.2528466196694</v>
       </c>
       <c r="Z10" t="n">
-        <v>233.41</v>
+        <v>74775660.93545045</v>
       </c>
       <c r="AA10" t="n">
         <v>5.473545957582736e-07</v>
@@ -8006,10 +7760,8 @@
       <c r="K11" t="n">
         <v>86.84743022847248</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 18.156x + -11013.884</t>
-        </is>
+      <c r="W11" t="n">
+        <v>18.15596513231331</v>
       </c>
       <c r="X11" t="n">
         <v>-11013.8840800332</v>
@@ -8018,7 +7770,7 @@
         <v>520.7736857570653</v>
       </c>
       <c r="Z11" t="n">
-        <v>231.587</v>
+        <v>26706286.64102941</v>
       </c>
       <c r="AA11" t="n">
         <v>5.332004591149701e-07</v>
@@ -8144,12 +7896,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8204,10 +7956,8 @@
       <c r="K2" t="n">
         <v>85.92556024130452</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 14.039x + -9158.240</t>
-        </is>
+      <c r="W2" t="n">
+        <v>14.03853517934627</v>
       </c>
       <c r="X2" t="n">
         <v>-9158.239803482922</v>
@@ -8216,7 +7966,7 @@
         <v>547.9664443253914</v>
       </c>
       <c r="Z2" t="n">
-        <v>295.1759999999999</v>
+        <v>93215787.65588757</v>
       </c>
       <c r="AA2" t="n">
         <v>6.939635490601613e-07</v>
@@ -8256,10 +8006,8 @@
       <c r="K3" t="n">
         <v>86.54639774254363</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 16.570x + -10509.761</t>
-        </is>
+      <c r="W3" t="n">
+        <v>16.57005289434864</v>
       </c>
       <c r="X3" t="n">
         <v>-10509.76117156017</v>
@@ -8268,7 +8016,7 @@
         <v>537.4991265785268</v>
       </c>
       <c r="Z3" t="n">
-        <v>255.207</v>
+        <v>57862755.58246504</v>
       </c>
       <c r="AA3" t="n">
         <v>6.065691900142197e-07</v>
@@ -8308,10 +8056,8 @@
       <c r="K4" t="n">
         <v>86.64529956532516</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 17.060x + -10608.342</t>
-        </is>
+      <c r="W4" t="n">
+        <v>17.05973229317107</v>
       </c>
       <c r="X4" t="n">
         <v>-10608.34191552096</v>
@@ -8320,7 +8066,7 @@
         <v>530.7109260023144</v>
       </c>
       <c r="Z4" t="n">
-        <v>245.075</v>
+        <v>105488576.7142147</v>
       </c>
       <c r="AA4" t="n">
         <v>5.758173367481633e-07</v>
@@ -8360,10 +8106,8 @@
       <c r="K5" t="n">
         <v>86.66181290831521</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 17.144x + -10474.329</t>
-        </is>
+      <c r="W5" t="n">
+        <v>17.1443160765689</v>
       </c>
       <c r="X5" t="n">
         <v>-10474.32923802869</v>
@@ -8372,7 +8116,7 @@
         <v>524.4008169650932</v>
       </c>
       <c r="Z5" t="n">
-        <v>239.784</v>
+        <v>47287926.86292861</v>
       </c>
       <c r="AA5" t="n">
         <v>5.56448183668114e-07</v>
@@ -8412,10 +8156,8 @@
       <c r="K6" t="n">
         <v>86.76197193521575</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 17.676x + -10643.999</t>
-        </is>
+      <c r="W6" t="n">
+        <v>17.67580982388721</v>
       </c>
       <c r="X6" t="n">
         <v>-10643.99865554016</v>
@@ -8424,7 +8166,7 @@
         <v>518.024247500451</v>
       </c>
       <c r="Z6" t="n">
-        <v>229.625</v>
+        <v>428383340.7938696</v>
       </c>
       <c r="AA6" t="n">
         <v>5.40652754576415e-07</v>
@@ -8464,10 +8206,8 @@
       <c r="K7" t="n">
         <v>86.979944462888</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 18.954x + -11313.892</t>
-        </is>
+      <c r="W7" t="n">
+        <v>18.95419030902354</v>
       </c>
       <c r="X7" t="n">
         <v>-11313.89193898644</v>
@@ -8476,7 +8216,7 @@
         <v>511.5433413446364</v>
       </c>
       <c r="Z7" t="n">
-        <v>225.261</v>
+        <v>92248114.62733148</v>
       </c>
       <c r="AA7" t="n">
         <v>5.29188017937728e-07</v>
@@ -8516,10 +8256,8 @@
       <c r="K8" t="n">
         <v>86.87741783852587</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 18.331x + -10727.105</t>
-        </is>
+      <c r="W8" t="n">
+        <v>18.3306760544104</v>
       </c>
       <c r="X8" t="n">
         <v>-10727.10461339592</v>
@@ -8528,7 +8266,7 @@
         <v>505.6986830688899</v>
       </c>
       <c r="Z8" t="n">
-        <v>224.1279999999999</v>
+        <v>139970948.6951483</v>
       </c>
       <c r="AA8" t="n">
         <v>5.177933248446756e-07</v>
@@ -8568,10 +8306,8 @@
       <c r="K9" t="n">
         <v>86.84655555079907</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 18.151x + -10454.029</t>
-        </is>
+      <c r="W9" t="n">
+        <v>18.15091899315512</v>
       </c>
       <c r="X9" t="n">
         <v>-10454.02941256753</v>
@@ -8580,7 +8316,7 @@
         <v>500.4768936297417</v>
       </c>
       <c r="Z9" t="n">
-        <v>221.967</v>
+        <v>108357798.1978788</v>
       </c>
       <c r="AA9" t="n">
         <v>5.092375615205946e-07</v>
@@ -8620,10 +8356,8 @@
       <c r="K10" t="n">
         <v>86.95966110405199</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 18.828x + -10752.447</t>
-        </is>
+      <c r="W10" t="n">
+        <v>18.82750375431905</v>
       </c>
       <c r="X10" t="n">
         <v>-10752.44736859063</v>
@@ -8632,7 +8366,7 @@
         <v>495.8316412890505</v>
       </c>
       <c r="Z10" t="n">
-        <v>218.792</v>
+        <v>49117446.11016729</v>
       </c>
       <c r="AA10" t="n">
         <v>5.016604731941381e-07</v>
@@ -8672,10 +8406,8 @@
       <c r="K11" t="n">
         <v>86.98409628041334</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 18.980x + -10717.797</t>
-        </is>
+      <c r="W11" t="n">
+        <v>18.98033178936646</v>
       </c>
       <c r="X11" t="n">
         <v>-10717.79679447714</v>
@@ -8684,7 +8416,7 @@
         <v>491.507998089093</v>
       </c>
       <c r="Z11" t="n">
-        <v>215.9069999999999</v>
+        <v>69117573.21617594</v>
       </c>
       <c r="AA11" t="n">
         <v>4.952188704965358e-07</v>
@@ -8724,10 +8456,8 @@
       <c r="K12" t="n">
         <v>87.17852881340522</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 20.291x + -11401.316</t>
-        </is>
+      <c r="W12" t="n">
+        <v>20.29064086241604</v>
       </c>
       <c r="X12" t="n">
         <v>-11401.31553036194</v>
@@ -8736,7 +8466,7 @@
         <v>487.2697428654787</v>
       </c>
       <c r="Z12" t="n">
-        <v>208.4490000000001</v>
+        <v>46273212.63543476</v>
       </c>
       <c r="AA12" t="n">
         <v>4.875897573513626e-07</v>
@@ -8776,10 +8506,8 @@
       <c r="K13" t="n">
         <v>87.02715300243224</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 19.256x + -10647.365</t>
-        </is>
+      <c r="W13" t="n">
+        <v>19.25573498440319</v>
       </c>
       <c r="X13" t="n">
         <v>-10647.36491796495</v>
@@ -8788,7 +8516,7 @@
         <v>483.0456321632749</v>
       </c>
       <c r="Z13" t="n">
-        <v>211.398</v>
+        <v>24849814.10408894</v>
       </c>
       <c r="AA13" t="n">
         <v>4.829111383721641e-07</v>
@@ -8828,10 +8556,8 @@
       <c r="K14" t="n">
         <v>87.08219185903415</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 19.620x + -10752.265</t>
-        </is>
+      <c r="W14" t="n">
+        <v>19.6196041821492</v>
       </c>
       <c r="X14" t="n">
         <v>-10752.26521999932</v>
@@ -8840,7 +8566,7 @@
         <v>478.8588952335851</v>
       </c>
       <c r="Z14" t="n">
-        <v>211.178</v>
+        <v>266380733.539689</v>
       </c>
       <c r="AA14" t="n">
         <v>4.789943805447928e-07</v>
@@ -8880,10 +8606,8 @@
       <c r="K15" t="n">
         <v>87.14457214625331</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 20.049x + -10888.254</t>
-        </is>
+      <c r="W15" t="n">
+        <v>20.04895225299378</v>
       </c>
       <c r="X15" t="n">
         <v>-10888.25431383424</v>
@@ -8892,7 +8616,7 @@
         <v>474.4818621580082</v>
       </c>
       <c r="Z15" t="n">
-        <v>209.9589999999999</v>
+        <v>40832017.37799203</v>
       </c>
       <c r="AA15" t="n">
         <v>4.739697264837431e-07</v>
@@ -8932,10 +8656,8 @@
       <c r="K16" t="n">
         <v>87.08989090121656</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 19.672x + -10537.927</t>
-        </is>
+      <c r="W16" t="n">
+        <v>19.67159992684424</v>
       </c>
       <c r="X16" t="n">
         <v>-10537.92701837069</v>
@@ -8944,7 +8666,7 @@
         <v>470.0625771674634</v>
       </c>
       <c r="Z16" t="n">
-        <v>208.5889999999999</v>
+        <v>21239918.33952826</v>
       </c>
       <c r="AA16" t="n">
         <v>4.690785734777748e-07</v>
@@ -8984,10 +8706,8 @@
       <c r="K17" t="n">
         <v>87.21773574782559</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 20.577x + -10935.075</t>
-        </is>
+      <c r="W17" t="n">
+        <v>20.57703077893204</v>
       </c>
       <c r="X17" t="n">
         <v>-10935.07456580674</v>
@@ -8996,7 +8716,7 @@
         <v>465.4910873318984</v>
       </c>
       <c r="Z17" t="n">
-        <v>201.9459999999999</v>
+        <v>34362732.61023357</v>
       </c>
       <c r="AA17" t="n">
         <v>4.626030484468354e-07</v>
@@ -9036,10 +8756,8 @@
       <c r="K18" t="n">
         <v>87.16706724953259</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 20.208x + -10590.591</t>
-        </is>
+      <c r="W18" t="n">
+        <v>20.20841524723179</v>
       </c>
       <c r="X18" t="n">
         <v>-10590.59131400182</v>
@@ -9048,7 +8766,7 @@
         <v>460.6489042436971</v>
       </c>
       <c r="Z18" t="n">
-        <v>205.5700000000001</v>
+        <v>43335205.01146992</v>
       </c>
       <c r="AA18" t="n">
         <v>4.601242245427078e-07</v>
@@ -9088,10 +8806,8 @@
       <c r="K19" t="n">
         <v>87.21032039201737</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 20.522x + -10635.707</t>
-        </is>
+      <c r="W19" t="n">
+        <v>20.52224797945347</v>
       </c>
       <c r="X19" t="n">
         <v>-10635.70698782171</v>
@@ -9100,7 +8816,7 @@
         <v>455.8594330283174</v>
       </c>
       <c r="Z19" t="n">
-        <v>201.932</v>
+        <v>256573807.4067802</v>
       </c>
       <c r="AA19" t="n">
         <v>4.554384756374948e-07</v>
@@ -9140,10 +8856,8 @@
       <c r="K20" t="n">
         <v>87.30069984518549</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 21.210x + -10879.134</t>
-        </is>
+      <c r="W20" t="n">
+        <v>21.21045472471323</v>
       </c>
       <c r="X20" t="n">
         <v>-10879.13431316853</v>
@@ -9152,7 +8866,7 @@
         <v>450.9635551348287</v>
       </c>
       <c r="Z20" t="n">
-        <v>198.461</v>
+        <v>988076045.3561549</v>
       </c>
       <c r="AA20" t="n">
         <v>4.50762229766592e-07</v>
@@ -9192,10 +8906,8 @@
       <c r="K21" t="n">
         <v>87.2441757536334</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 20.775x + -10495.122</t>
-        </is>
+      <c r="W21" t="n">
+        <v>20.77476071679067</v>
       </c>
       <c r="X21" t="n">
         <v>-10495.12215438899</v>
@@ -9204,7 +8916,7 @@
         <v>445.9830181602341</v>
       </c>
       <c r="Z21" t="n">
-        <v>199.328</v>
+        <v>488326387.5058805</v>
       </c>
       <c r="AA21" t="n">
         <v>4.470452847620055e-07</v>
@@ -9244,10 +8956,8 @@
       <c r="K22" t="n">
         <v>87.31182169016245</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 21.298x + -10645.465</t>
-        </is>
+      <c r="W22" t="n">
+        <v>21.2983388074436</v>
       </c>
       <c r="X22" t="n">
         <v>-10645.46534025562</v>
@@ -9256,7 +8966,7 @@
         <v>440.9473525323475</v>
       </c>
       <c r="Z22" t="n">
-        <v>199.673</v>
+        <v>1206183583.512786</v>
       </c>
       <c r="AA22" t="n">
         <v>4.441706051422483e-07</v>
@@ -9382,12 +9092,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9442,10 +9152,8 @@
       <c r="K2" t="n">
         <v>84.5133461030688</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 10.411x + -6824.026</t>
-        </is>
+      <c r="W2" t="n">
+        <v>10.41081488166332</v>
       </c>
       <c r="X2" t="n">
         <v>-6824.026098839277</v>
@@ -9454,7 +9162,7 @@
         <v>542.5417400869246</v>
       </c>
       <c r="Z2" t="n">
-        <v>429.665</v>
+        <v>31871926.16182702</v>
       </c>
       <c r="AA2" t="n">
         <v>9.934221897037078e-07</v>
@@ -9494,10 +9202,8 @@
       <c r="K3" t="n">
         <v>86.0943897065048</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 14.647x + -9346.520</t>
-        </is>
+      <c r="W3" t="n">
+        <v>14.64739304454518</v>
       </c>
       <c r="X3" t="n">
         <v>-9346.52021162882</v>
@@ -9506,7 +9212,7 @@
         <v>534.5275004114219</v>
       </c>
       <c r="Z3" t="n">
-        <v>307.0839999999999</v>
+        <v>54168483.1330822</v>
       </c>
       <c r="AA3" t="n">
         <v>6.836591868196212e-07</v>
@@ -9546,10 +9252,8 @@
       <c r="K4" t="n">
         <v>86.47226453130855</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 16.221x + -10130.083</t>
-        </is>
+      <c r="W4" t="n">
+        <v>16.22098939133663</v>
       </c>
       <c r="X4" t="n">
         <v>-10130.08320452879</v>
@@ -9558,7 +9262,7 @@
         <v>527.5934801188311</v>
       </c>
       <c r="Z4" t="n">
-        <v>269.687</v>
+        <v>72966020.88517547</v>
       </c>
       <c r="AA4" t="n">
         <v>6.103850501617336e-07</v>
@@ -9598,10 +9302,8 @@
       <c r="K5" t="n">
         <v>86.53266663490025</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 16.504x + -10076.725</t>
-        </is>
+      <c r="W5" t="n">
+        <v>16.50427372073309</v>
       </c>
       <c r="X5" t="n">
         <v>-10076.72515870641</v>
@@ -9610,7 +9312,7 @@
         <v>520.8682801464658</v>
       </c>
       <c r="Z5" t="n">
-        <v>254.099</v>
+        <v>114785839.3222648</v>
       </c>
       <c r="AA5" t="n">
         <v>5.721278687584216e-07</v>
@@ -9650,10 +9352,8 @@
       <c r="K6" t="n">
         <v>86.67475184115797</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 17.211x + -10335.544</t>
-        </is>
+      <c r="W6" t="n">
+        <v>17.21117754508739</v>
       </c>
       <c r="X6" t="n">
         <v>-10335.5440924935</v>
@@ -9662,7 +9362,7 @@
         <v>513.7502163522338</v>
       </c>
       <c r="Z6" t="n">
-        <v>243.399</v>
+        <v>38077614.66728316</v>
       </c>
       <c r="AA6" t="n">
         <v>5.474057726749312e-07</v>
@@ -9702,10 +9402,8 @@
       <c r="K7" t="n">
         <v>86.72904003429538</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 17.497x + -10308.856</t>
-        </is>
+      <c r="W7" t="n">
+        <v>17.4974690255007</v>
       </c>
       <c r="X7" t="n">
         <v>-10308.8556564917</v>
@@ -9714,7 +9412,7 @@
         <v>506.1801091238793</v>
       </c>
       <c r="Z7" t="n">
-        <v>236.676</v>
+        <v>50003174.50793667</v>
       </c>
       <c r="AA7" t="n">
         <v>5.289251399962977e-07</v>
@@ -9754,10 +9452,8 @@
       <c r="K8" t="n">
         <v>86.90958148089945</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 18.522x + -10751.881</t>
-        </is>
+      <c r="W8" t="n">
+        <v>18.5218295635614</v>
       </c>
       <c r="X8" t="n">
         <v>-10751.88147196908</v>
@@ -9766,7 +9462,7 @@
         <v>498.7623392797444</v>
       </c>
       <c r="Z8" t="n">
-        <v>227.811</v>
+        <v>275023896.081173</v>
       </c>
       <c r="AA8" t="n">
         <v>5.13280953960211e-07</v>
@@ -9806,10 +9502,8 @@
       <c r="K9" t="n">
         <v>86.91030666967617</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 18.526x + -10547.317</t>
-        </is>
+      <c r="W9" t="n">
+        <v>18.52618530549196</v>
       </c>
       <c r="X9" t="n">
         <v>-10547.3170095587</v>
@@ -9818,7 +9512,7 @@
         <v>491.8533849089092</v>
       </c>
       <c r="Z9" t="n">
-        <v>224.901</v>
+        <v>36139828.88406774</v>
       </c>
       <c r="AA9" t="n">
         <v>5.003821300762556e-07</v>
@@ -9858,10 +9552,8 @@
       <c r="K10" t="n">
         <v>86.93694325489693</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 18.688x + -10459.670</t>
-        </is>
+      <c r="W10" t="n">
+        <v>18.68760188530378</v>
       </c>
       <c r="X10" t="n">
         <v>-10459.66993411818</v>
@@ -9870,7 +9562,7 @@
         <v>485.409008110134</v>
       </c>
       <c r="Z10" t="n">
-        <v>219.343</v>
+        <v>233911311.9730988</v>
       </c>
       <c r="AA10" t="n">
         <v>4.900493783458515e-07</v>
@@ -9910,10 +9602,8 @@
       <c r="K11" t="n">
         <v>87.12345974629464</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 19.902x + -11019.945</t>
-        </is>
+      <c r="W11" t="n">
+        <v>19.90155790543493</v>
       </c>
       <c r="X11" t="n">
         <v>-11019.94505846481</v>
@@ -9922,7 +9612,7 @@
         <v>479.4517673951738</v>
       </c>
       <c r="Z11" t="n">
-        <v>209.6030000000001</v>
+        <v>273971676.1830353</v>
       </c>
       <c r="AA11" t="n">
         <v>4.794897629054564e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 52.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 52.xlsx
@@ -428,7 +428,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -559,7 +559,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-334.601</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-292.971</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-277.398</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-264.223</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-257.091</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-254.6809999999999</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-245.98</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-242.769</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-238.725</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-234.853</v>
@@ -1074,7 +1074,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2270,7 +2270,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3597,7 +3597,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-469.704</v>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-350.398</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-306.0550000000001</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-286.706</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-271.024</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-259.5440000000001</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-259.509</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-250.301</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-250.181</v>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-244.0300000000001</v>
@@ -4112,7 +4112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5439,7 +5439,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-565.4799999999999</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-391.0300000000001</v>
@@ -5539,7 +5539,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-324.691</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-292.1700000000001</v>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-279.1559999999999</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-258.9640000000001</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-253.134</v>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-245.8810000000001</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-238.38</v>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-239.2380000000001</v>
@@ -5954,7 +5954,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7150,7 +7150,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7281,7 +7281,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-534.7510000000001</v>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-377.962</v>
@@ -7381,7 +7381,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-312.7379999999999</v>
@@ -7431,7 +7431,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-286.981</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-265.9299999999999</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-256.8040000000001</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-250.348</v>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-243.2700000000001</v>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-233.41</v>
@@ -7731,7 +7731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-231.587</v>
@@ -7796,7 +7796,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -8992,7 +8992,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -9123,7 +9123,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-429.665</v>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-307.0839999999999</v>
@@ -9223,7 +9223,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-269.687</v>
@@ -9273,7 +9273,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-254.099</v>
@@ -9323,7 +9323,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-243.399</v>
@@ -9373,7 +9373,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-236.676</v>
@@ -9423,7 +9423,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-227.811</v>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-224.901</v>
@@ -9523,7 +9523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-219.343</v>
@@ -9573,7 +9573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-209.6030000000001</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 52.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 52.xlsx
@@ -562,7 +562,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-334.601</v>
+        <v>207.4320000000001</v>
       </c>
       <c r="D2" t="n">
         <v>2.84075e-07</v>
@@ -612,7 +612,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-292.971</v>
+        <v>201.885</v>
       </c>
       <c r="D3" t="n">
         <v>2.77854e-07</v>
@@ -662,7 +662,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-277.398</v>
+        <v>194.896</v>
       </c>
       <c r="D4" t="n">
         <v>2.76208e-07</v>
@@ -712,7 +712,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-264.223</v>
+        <v>186.004</v>
       </c>
       <c r="D5" t="n">
         <v>2.75569e-07</v>
@@ -762,7 +762,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-257.091</v>
+        <v>174.124</v>
       </c>
       <c r="D6" t="n">
         <v>2.75198e-07</v>
@@ -812,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-254.6809999999999</v>
+        <v>163.76</v>
       </c>
       <c r="D7" t="n">
         <v>2.74793e-07</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-245.98</v>
+        <v>159.049</v>
       </c>
       <c r="D8" t="n">
         <v>2.74725e-07</v>
@@ -912,7 +912,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-242.769</v>
+        <v>150.136</v>
       </c>
       <c r="D9" t="n">
         <v>2.74542e-07</v>
@@ -962,7 +962,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-238.725</v>
+        <v>145.279</v>
       </c>
       <c r="D10" t="n">
         <v>2.7434e-07</v>
@@ -1012,7 +1012,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-234.853</v>
+        <v>139.072</v>
       </c>
       <c r="D11" t="n">
         <v>2.74116e-07</v>
@@ -1208,7 +1208,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-234.155</v>
+        <v>206.432</v>
       </c>
       <c r="D2" t="n">
         <v>2.77466e-07</v>
@@ -1258,7 +1258,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-230.4929999999999</v>
+        <v>184.4160000000001</v>
       </c>
       <c r="D3" t="n">
         <v>2.79344e-07</v>
@@ -1308,7 +1308,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-221.836</v>
+        <v>175.397</v>
       </c>
       <c r="D4" t="n">
         <v>2.79701e-07</v>
@@ -1358,7 +1358,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-220.027</v>
+        <v>171.446</v>
       </c>
       <c r="D5" t="n">
         <v>2.79651e-07</v>
@@ -1408,7 +1408,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-220.256</v>
+        <v>166.47</v>
       </c>
       <c r="D6" t="n">
         <v>2.79475e-07</v>
@@ -1458,7 +1458,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-218.9880000000001</v>
+        <v>159.812</v>
       </c>
       <c r="D7" t="n">
         <v>2.79772e-07</v>
@@ -1508,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-218.954</v>
+        <v>155.379</v>
       </c>
       <c r="D8" t="n">
         <v>2.79625e-07</v>
@@ -1558,7 +1558,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-215.292</v>
+        <v>151.518</v>
       </c>
       <c r="D9" t="n">
         <v>2.79657e-07</v>
@@ -1608,7 +1608,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-212.5799999999999</v>
+        <v>147.951</v>
       </c>
       <c r="D10" t="n">
         <v>2.79686e-07</v>
@@ -1658,7 +1658,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-210.2869999999999</v>
+        <v>142.825</v>
       </c>
       <c r="D11" t="n">
         <v>2.798e-07</v>
@@ -1708,7 +1708,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-209.203</v>
+        <v>138.833</v>
       </c>
       <c r="D12" t="n">
         <v>2.7984e-07</v>
@@ -1758,7 +1758,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-207.611</v>
+        <v>136.215</v>
       </c>
       <c r="D13" t="n">
         <v>2.79997e-07</v>
@@ -1808,7 +1808,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-205.4829999999999</v>
+        <v>133.475</v>
       </c>
       <c r="D14" t="n">
         <v>2.79936e-07</v>
@@ -1858,7 +1858,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-204.12</v>
+        <v>129.5869999999999</v>
       </c>
       <c r="D15" t="n">
         <v>2.79942e-07</v>
@@ -1908,7 +1908,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-207.12</v>
+        <v>122.747</v>
       </c>
       <c r="D16" t="n">
         <v>2.79985e-07</v>
@@ -1958,7 +1958,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-198.9010000000001</v>
+        <v>124.586</v>
       </c>
       <c r="D17" t="n">
         <v>2.80122e-07</v>
@@ -2008,7 +2008,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-202.994</v>
+        <v>119.501</v>
       </c>
       <c r="D18" t="n">
         <v>2.80068e-07</v>
@@ -2058,7 +2058,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-195.3389999999999</v>
+        <v>118.911</v>
       </c>
       <c r="D19" t="n">
         <v>2.8028e-07</v>
@@ -2108,7 +2108,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-199.119</v>
+        <v>114.173</v>
       </c>
       <c r="D20" t="n">
         <v>2.80156e-07</v>
@@ -2158,7 +2158,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-198.011</v>
+        <v>112.521</v>
       </c>
       <c r="D21" t="n">
         <v>2.80049e-07</v>
@@ -2208,7 +2208,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-195.548</v>
+        <v>108.157</v>
       </c>
       <c r="D22" t="n">
         <v>2.80206e-07</v>
@@ -2404,7 +2404,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-263.9880000000001</v>
+        <v>193.3989999999999</v>
       </c>
       <c r="D2" t="n">
         <v>2.75911e-07</v>
@@ -2454,7 +2454,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-243.1039999999999</v>
+        <v>181.307</v>
       </c>
       <c r="D3" t="n">
         <v>2.75569e-07</v>
@@ -2504,7 +2504,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-237.33</v>
+        <v>175.408</v>
       </c>
       <c r="D4" t="n">
         <v>2.74958e-07</v>
@@ -2554,7 +2554,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-235.2190000000001</v>
+        <v>170.3459999999999</v>
       </c>
       <c r="D5" t="n">
         <v>2.74428e-07</v>
@@ -2604,7 +2604,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-234.439</v>
+        <v>164.084</v>
       </c>
       <c r="D6" t="n">
         <v>2.74171e-07</v>
@@ -2654,7 +2654,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-231.372</v>
+        <v>158.844</v>
       </c>
       <c r="D7" t="n">
         <v>2.73569e-07</v>
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-224.895</v>
+        <v>157.0719999999999</v>
       </c>
       <c r="D8" t="n">
         <v>2.73308e-07</v>
@@ -2754,7 +2754,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-224.9209999999999</v>
+        <v>151.429</v>
       </c>
       <c r="D9" t="n">
         <v>2.72884e-07</v>
@@ -2804,7 +2804,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-222.99</v>
+        <v>146.739</v>
       </c>
       <c r="D10" t="n">
         <v>2.7248e-07</v>
@@ -2854,7 +2854,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-221.408</v>
+        <v>145.875</v>
       </c>
       <c r="D11" t="n">
         <v>2.7219e-07</v>
@@ -2904,7 +2904,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-223.4059999999999</v>
+        <v>140.711</v>
       </c>
       <c r="D12" t="n">
         <v>2.71584e-07</v>
@@ -2954,7 +2954,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-223.115</v>
+        <v>136.612</v>
       </c>
       <c r="D13" t="n">
         <v>2.71535e-07</v>
@@ -3004,7 +3004,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-221.7230000000001</v>
+        <v>134.8819999999999</v>
       </c>
       <c r="D14" t="n">
         <v>2.71117e-07</v>
@@ -3054,7 +3054,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-221.58</v>
+        <v>129.588</v>
       </c>
       <c r="D15" t="n">
         <v>2.70973e-07</v>
@@ -3104,7 +3104,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-223.1289999999999</v>
+        <v>128.5050000000001</v>
       </c>
       <c r="D16" t="n">
         <v>2.70639e-07</v>
@@ -3154,7 +3154,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-214.172</v>
+        <v>127.8079999999999</v>
       </c>
       <c r="D17" t="n">
         <v>2.70397e-07</v>
@@ -3204,7 +3204,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-222.645</v>
+        <v>122.131</v>
       </c>
       <c r="D18" t="n">
         <v>2.70245e-07</v>
@@ -3254,7 +3254,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-218.611</v>
+        <v>121.495</v>
       </c>
       <c r="D19" t="n">
         <v>2.70042e-07</v>
@@ -3304,7 +3304,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-217.1019999999999</v>
+        <v>119.636</v>
       </c>
       <c r="D20" t="n">
         <v>2.6985e-07</v>
@@ -3354,7 +3354,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-217.189</v>
+        <v>115.007</v>
       </c>
       <c r="D21" t="n">
         <v>2.69851e-07</v>
@@ -3404,7 +3404,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-220.836</v>
+        <v>111.596</v>
       </c>
       <c r="D22" t="n">
         <v>2.69608e-07</v>
@@ -3600,7 +3600,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-469.704</v>
+        <v>334.134</v>
       </c>
       <c r="D2" t="n">
         <v>2.73912e-07</v>
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-350.398</v>
+        <v>260.447</v>
       </c>
       <c r="D3" t="n">
         <v>2.78028e-07</v>
@@ -3700,7 +3700,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-306.0550000000001</v>
+        <v>236.025</v>
       </c>
       <c r="D4" t="n">
         <v>2.77557e-07</v>
@@ -3750,7 +3750,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-286.706</v>
+        <v>220.16</v>
       </c>
       <c r="D5" t="n">
         <v>2.76524e-07</v>
@@ -3800,7 +3800,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-271.024</v>
+        <v>212.585</v>
       </c>
       <c r="D6" t="n">
         <v>2.7542e-07</v>
@@ -3850,7 +3850,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-259.5440000000001</v>
+        <v>203.701</v>
       </c>
       <c r="D7" t="n">
         <v>2.74779e-07</v>
@@ -3900,7 +3900,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-259.509</v>
+        <v>195.643</v>
       </c>
       <c r="D8" t="n">
         <v>2.74066e-07</v>
@@ -3950,7 +3950,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-250.301</v>
+        <v>185.795</v>
       </c>
       <c r="D9" t="n">
         <v>2.73609e-07</v>
@@ -4000,7 +4000,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-250.181</v>
+        <v>175.393</v>
       </c>
       <c r="D10" t="n">
         <v>2.73151e-07</v>
@@ -4050,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-244.0300000000001</v>
+        <v>170.5479999999999</v>
       </c>
       <c r="D11" t="n">
         <v>2.72605e-07</v>
@@ -4246,7 +4246,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-308.104</v>
+        <v>203.3919999999999</v>
       </c>
       <c r="D2" t="n">
         <v>2.82333e-07</v>
@@ -4296,7 +4296,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-262.4930000000001</v>
+        <v>185.462</v>
       </c>
       <c r="D3" t="n">
         <v>2.80172e-07</v>
@@ -4346,7 +4346,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-251.874</v>
+        <v>174.581</v>
       </c>
       <c r="D4" t="n">
         <v>2.79093e-07</v>
@@ -4396,7 +4396,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-245.47</v>
+        <v>168.443</v>
       </c>
       <c r="D5" t="n">
         <v>2.78399e-07</v>
@@ -4446,7 +4446,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-241.8200000000001</v>
+        <v>161.7929999999999</v>
       </c>
       <c r="D6" t="n">
         <v>2.77939e-07</v>
@@ -4496,7 +4496,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-232.804</v>
+        <v>159.784</v>
       </c>
       <c r="D7" t="n">
         <v>2.77535e-07</v>
@@ -4546,7 +4546,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-229.415</v>
+        <v>156.292</v>
       </c>
       <c r="D8" t="n">
         <v>2.77186e-07</v>
@@ -4596,7 +4596,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-230.1909999999999</v>
+        <v>148.669</v>
       </c>
       <c r="D9" t="n">
         <v>2.76888e-07</v>
@@ -4646,7 +4646,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-226.432</v>
+        <v>145.981</v>
       </c>
       <c r="D10" t="n">
         <v>2.76517e-07</v>
@@ -4696,7 +4696,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-224.937</v>
+        <v>143.8799999999999</v>
       </c>
       <c r="D11" t="n">
         <v>2.76424e-07</v>
@@ -4746,7 +4746,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-225.2009999999999</v>
+        <v>138.4470000000001</v>
       </c>
       <c r="D12" t="n">
         <v>2.76201e-07</v>
@@ -4796,7 +4796,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-218.064</v>
+        <v>138.159</v>
       </c>
       <c r="D13" t="n">
         <v>2.76011e-07</v>
@@ -4846,7 +4846,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-223.1080000000001</v>
+        <v>134.57</v>
       </c>
       <c r="D14" t="n">
         <v>2.75803e-07</v>
@@ -4896,7 +4896,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-218.167</v>
+        <v>131.5069999999999</v>
       </c>
       <c r="D15" t="n">
         <v>2.7569e-07</v>
@@ -4946,7 +4946,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-214.9640000000001</v>
+        <v>129.8489999999999</v>
       </c>
       <c r="D16" t="n">
         <v>2.7559e-07</v>
@@ -4996,7 +4996,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-217.1379999999999</v>
+        <v>125.705</v>
       </c>
       <c r="D17" t="n">
         <v>2.75323e-07</v>
@@ -5046,7 +5046,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-216.206</v>
+        <v>124.137</v>
       </c>
       <c r="D18" t="n">
         <v>2.75338e-07</v>
@@ -5096,7 +5096,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-211.967</v>
+        <v>121.937</v>
       </c>
       <c r="D19" t="n">
         <v>2.75325e-07</v>
@@ -5146,7 +5146,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-216.501</v>
+        <v>117.485</v>
       </c>
       <c r="D20" t="n">
         <v>2.75103e-07</v>
@@ -5196,7 +5196,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-210.951</v>
+        <v>114.98</v>
       </c>
       <c r="D21" t="n">
         <v>2.75269e-07</v>
@@ -5246,7 +5246,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-211.449</v>
+        <v>112.792</v>
       </c>
       <c r="D22" t="n">
         <v>2.75223e-07</v>
@@ -5442,7 +5442,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-565.4799999999999</v>
+        <v>333.346</v>
       </c>
       <c r="D2" t="n">
         <v>2.9838e-07</v>
@@ -5492,7 +5492,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-391.0300000000001</v>
+        <v>246.427</v>
       </c>
       <c r="D3" t="n">
         <v>3.01216e-07</v>
@@ -5542,7 +5542,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-324.691</v>
+        <v>224.73</v>
       </c>
       <c r="D4" t="n">
         <v>2.962e-07</v>
@@ -5592,7 +5592,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-292.1700000000001</v>
+        <v>211.467</v>
       </c>
       <c r="D5" t="n">
         <v>2.92195e-07</v>
@@ -5642,7 +5642,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-279.1559999999999</v>
+        <v>199.57</v>
       </c>
       <c r="D6" t="n">
         <v>2.88889e-07</v>
@@ -5692,7 +5692,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-258.9640000000001</v>
+        <v>197.137</v>
       </c>
       <c r="D7" t="n">
         <v>2.86417e-07</v>
@@ -5742,7 +5742,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-253.134</v>
+        <v>187.569</v>
       </c>
       <c r="D8" t="n">
         <v>2.84804e-07</v>
@@ -5792,7 +5792,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-245.8810000000001</v>
+        <v>178.627</v>
       </c>
       <c r="D9" t="n">
         <v>2.83701e-07</v>
@@ -5842,7 +5842,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-238.38</v>
+        <v>175.395</v>
       </c>
       <c r="D10" t="n">
         <v>2.82732e-07</v>
@@ -5892,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-239.2380000000001</v>
+        <v>165.3759999999999</v>
       </c>
       <c r="D11" t="n">
         <v>2.81897e-07</v>
@@ -6088,7 +6088,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-346.3549999999999</v>
+        <v>206.8460000000001</v>
       </c>
       <c r="D2" t="n">
         <v>2.99723e-07</v>
@@ -6138,7 +6138,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-274.2910000000001</v>
+        <v>189.844</v>
       </c>
       <c r="D3" t="n">
         <v>2.91984e-07</v>
@@ -6188,7 +6188,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-251.7089999999999</v>
+        <v>179.171</v>
       </c>
       <c r="D4" t="n">
         <v>2.89069e-07</v>
@@ -6238,7 +6238,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-243.583</v>
+        <v>173.399</v>
       </c>
       <c r="D5" t="n">
         <v>2.87552e-07</v>
@@ -6288,7 +6288,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-235.6479999999999</v>
+        <v>168.251</v>
       </c>
       <c r="D6" t="n">
         <v>2.8644e-07</v>
@@ -6338,7 +6338,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-235.096</v>
+        <v>160.248</v>
       </c>
       <c r="D7" t="n">
         <v>2.8567e-07</v>
@@ -6388,7 +6388,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-223.103</v>
+        <v>159.213</v>
       </c>
       <c r="D8" t="n">
         <v>2.8523e-07</v>
@@ -6438,7 +6438,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-224.5070000000001</v>
+        <v>152.17</v>
       </c>
       <c r="D9" t="n">
         <v>2.84916e-07</v>
@@ -6488,7 +6488,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-216.336</v>
+        <v>151.238</v>
       </c>
       <c r="D10" t="n">
         <v>2.84593e-07</v>
@@ -6538,7 +6538,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-216.908</v>
+        <v>144.625</v>
       </c>
       <c r="D11" t="n">
         <v>2.84275e-07</v>
@@ -6588,7 +6588,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-216.77</v>
+        <v>140.51</v>
       </c>
       <c r="D12" t="n">
         <v>2.84088e-07</v>
@@ -6638,7 +6638,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-213.1899999999999</v>
+        <v>139.208</v>
       </c>
       <c r="D13" t="n">
         <v>2.83809e-07</v>
@@ -6688,7 +6688,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-213.2859999999999</v>
+        <v>134.528</v>
       </c>
       <c r="D14" t="n">
         <v>2.83662e-07</v>
@@ -6738,7 +6738,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-207.846</v>
+        <v>131.579</v>
       </c>
       <c r="D15" t="n">
         <v>2.83538e-07</v>
@@ -6788,7 +6788,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-207.2959999999999</v>
+        <v>128.748</v>
       </c>
       <c r="D16" t="n">
         <v>2.83431e-07</v>
@@ -6838,7 +6838,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-204.08</v>
+        <v>127.2329999999999</v>
       </c>
       <c r="D17" t="n">
         <v>2.83203e-07</v>
@@ -6888,7 +6888,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-206.425</v>
+        <v>122.799</v>
       </c>
       <c r="D18" t="n">
         <v>2.82888e-07</v>
@@ -6938,7 +6938,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-202.2570000000001</v>
+        <v>121.292</v>
       </c>
       <c r="D19" t="n">
         <v>2.82876e-07</v>
@@ -6988,7 +6988,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-199.603</v>
+        <v>119.8219999999999</v>
       </c>
       <c r="D20" t="n">
         <v>2.82837e-07</v>
@@ -7038,7 +7038,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-202.359</v>
+        <v>116.877</v>
       </c>
       <c r="D21" t="n">
         <v>2.82964e-07</v>
@@ -7088,7 +7088,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-197.902</v>
+        <v>114.616</v>
       </c>
       <c r="D22" t="n">
         <v>2.82777e-07</v>
@@ -7284,7 +7284,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-534.7510000000001</v>
+        <v>298.57</v>
       </c>
       <c r="D2" t="n">
         <v>3.05948e-07</v>
@@ -7334,7 +7334,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-377.962</v>
+        <v>235.207</v>
       </c>
       <c r="D3" t="n">
         <v>3.01741e-07</v>
@@ -7384,7 +7384,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-312.7379999999999</v>
+        <v>217.785</v>
       </c>
       <c r="D4" t="n">
         <v>2.95421e-07</v>
@@ -7434,7 +7434,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-286.981</v>
+        <v>206.568</v>
       </c>
       <c r="D5" t="n">
         <v>2.91133e-07</v>
@@ -7484,7 +7484,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-265.9299999999999</v>
+        <v>197.877</v>
       </c>
       <c r="D6" t="n">
         <v>2.88235e-07</v>
@@ -7534,7 +7534,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-256.8040000000001</v>
+        <v>187.9519999999999</v>
       </c>
       <c r="D7" t="n">
         <v>2.86237e-07</v>
@@ -7584,7 +7584,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-250.348</v>
+        <v>182.118</v>
       </c>
       <c r="D8" t="n">
         <v>2.84878e-07</v>
@@ -7634,7 +7634,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-243.2700000000001</v>
+        <v>175.5549999999999</v>
       </c>
       <c r="D9" t="n">
         <v>2.83987e-07</v>
@@ -7684,7 +7684,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-233.41</v>
+        <v>170.85</v>
       </c>
       <c r="D10" t="n">
         <v>2.83373e-07</v>
@@ -7734,7 +7734,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-231.587</v>
+        <v>165.505</v>
       </c>
       <c r="D11" t="n">
         <v>2.82702e-07</v>
@@ -7930,7 +7930,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-295.1759999999999</v>
+        <v>198.355</v>
       </c>
       <c r="D2" t="n">
         <v>2.91342e-07</v>
@@ -7980,7 +7980,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-255.207</v>
+        <v>184.845</v>
       </c>
       <c r="D3" t="n">
         <v>2.87842e-07</v>
@@ -8030,7 +8030,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-245.075</v>
+        <v>175.218</v>
       </c>
       <c r="D4" t="n">
         <v>2.86379e-07</v>
@@ -8080,7 +8080,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-239.784</v>
+        <v>167.609</v>
       </c>
       <c r="D5" t="n">
         <v>2.85662e-07</v>
@@ -8130,7 +8130,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-229.625</v>
+        <v>163.3939999999999</v>
       </c>
       <c r="D6" t="n">
         <v>2.85421e-07</v>
@@ -8180,7 +8180,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-225.261</v>
+        <v>161.792</v>
       </c>
       <c r="D7" t="n">
         <v>2.85006e-07</v>
@@ -8230,7 +8230,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-224.1279999999999</v>
+        <v>153.253</v>
       </c>
       <c r="D8" t="n">
         <v>2.84715e-07</v>
@@ -8280,7 +8280,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-221.967</v>
+        <v>147.508</v>
       </c>
       <c r="D9" t="n">
         <v>2.84692e-07</v>
@@ -8330,7 +8330,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-218.792</v>
+        <v>145.554</v>
       </c>
       <c r="D10" t="n">
         <v>2.84423e-07</v>
@@ -8380,7 +8380,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-215.9069999999999</v>
+        <v>142.062</v>
       </c>
       <c r="D11" t="n">
         <v>2.84401e-07</v>
@@ -8430,7 +8430,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-208.4490000000001</v>
+        <v>141.682</v>
       </c>
       <c r="D12" t="n">
         <v>2.84125e-07</v>
@@ -8480,7 +8480,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-211.398</v>
+        <v>136.251</v>
       </c>
       <c r="D13" t="n">
         <v>2.84049e-07</v>
@@ -8530,7 +8530,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-211.178</v>
+        <v>134.869</v>
       </c>
       <c r="D14" t="n">
         <v>2.83889e-07</v>
@@ -8580,7 +8580,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-209.9589999999999</v>
+        <v>132.0050000000001</v>
       </c>
       <c r="D15" t="n">
         <v>2.83738e-07</v>
@@ -8630,7 +8630,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-208.5889999999999</v>
+        <v>128.112</v>
       </c>
       <c r="D16" t="n">
         <v>2.83853e-07</v>
@@ -8680,7 +8680,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-201.9459999999999</v>
+        <v>127.595</v>
       </c>
       <c r="D17" t="n">
         <v>2.83517e-07</v>
@@ -8730,7 +8730,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-205.5700000000001</v>
+        <v>122.673</v>
       </c>
       <c r="D18" t="n">
         <v>2.83744e-07</v>
@@ -8780,7 +8780,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-201.932</v>
+        <v>120.7</v>
       </c>
       <c r="D19" t="n">
         <v>2.83754e-07</v>
@@ -8830,7 +8830,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-198.461</v>
+        <v>118.272</v>
       </c>
       <c r="D20" t="n">
         <v>2.83824e-07</v>
@@ -8880,7 +8880,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-199.328</v>
+        <v>114.862</v>
       </c>
       <c r="D21" t="n">
         <v>2.83751e-07</v>
@@ -8930,7 +8930,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-199.673</v>
+        <v>112.232</v>
       </c>
       <c r="D22" t="n">
         <v>2.83923e-07</v>
@@ -9126,7 +9126,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-429.665</v>
+        <v>209.369</v>
       </c>
       <c r="D2" t="n">
         <v>3.03843e-07</v>
@@ -9176,7 +9176,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-307.0839999999999</v>
+        <v>194.602</v>
       </c>
       <c r="D3" t="n">
         <v>2.91101e-07</v>
@@ -9226,7 +9226,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-269.687</v>
+        <v>184.617</v>
       </c>
       <c r="D4" t="n">
         <v>2.87153e-07</v>
@@ -9276,7 +9276,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-254.099</v>
+        <v>174.845</v>
       </c>
       <c r="D5" t="n">
         <v>2.84839e-07</v>
@@ -9326,7 +9326,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-243.399</v>
+        <v>168.8989999999999</v>
       </c>
       <c r="D6" t="n">
         <v>2.83502e-07</v>
@@ -9376,7 +9376,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-236.676</v>
+        <v>161.246</v>
       </c>
       <c r="D7" t="n">
         <v>2.82778e-07</v>
@@ -9426,7 +9426,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-227.811</v>
+        <v>157.234</v>
       </c>
       <c r="D8" t="n">
         <v>2.82205e-07</v>
@@ -9476,7 +9476,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-224.901</v>
+        <v>150.322</v>
       </c>
       <c r="D9" t="n">
         <v>2.81724e-07</v>
@@ -9526,7 +9526,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-219.343</v>
+        <v>144.708</v>
       </c>
       <c r="D10" t="n">
         <v>2.81539e-07</v>
@@ -9576,7 +9576,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-209.6030000000001</v>
+        <v>143.558</v>
       </c>
       <c r="D11" t="n">
         <v>2.81199e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 52.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 52.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -564,6 +564,9 @@
       <c r="B2" t="n">
         <v>207.4320000000001</v>
       </c>
+      <c r="C2" t="n">
+        <v>885.1082429764258</v>
+      </c>
       <c r="D2" t="n">
         <v>2.84075e-07</v>
       </c>
@@ -614,6 +617,9 @@
       <c r="B3" t="n">
         <v>201.885</v>
       </c>
+      <c r="C3" t="n">
+        <v>907.4780775400502</v>
+      </c>
       <c r="D3" t="n">
         <v>2.77854e-07</v>
       </c>
@@ -664,6 +670,9 @@
       <c r="B4" t="n">
         <v>194.896</v>
       </c>
+      <c r="C4" t="n">
+        <v>925.9741935475854</v>
+      </c>
       <c r="D4" t="n">
         <v>2.76208e-07</v>
       </c>
@@ -714,6 +723,9 @@
       <c r="B5" t="n">
         <v>186.004</v>
       </c>
+      <c r="C5" t="n">
+        <v>940.3138725961708</v>
+      </c>
       <c r="D5" t="n">
         <v>2.75569e-07</v>
       </c>
@@ -764,6 +776,9 @@
       <c r="B6" t="n">
         <v>174.124</v>
       </c>
+      <c r="C6" t="n">
+        <v>922.8210851313289</v>
+      </c>
       <c r="D6" t="n">
         <v>2.75198e-07</v>
       </c>
@@ -814,6 +829,9 @@
       <c r="B7" t="n">
         <v>163.76</v>
       </c>
+      <c r="C7" t="n">
+        <v>879.1189659599338</v>
+      </c>
       <c r="D7" t="n">
         <v>2.74793e-07</v>
       </c>
@@ -864,6 +882,9 @@
       <c r="B8" t="n">
         <v>159.049</v>
       </c>
+      <c r="C8" t="n">
+        <v>922.308664005486</v>
+      </c>
       <c r="D8" t="n">
         <v>2.74725e-07</v>
       </c>
@@ -914,6 +935,9 @@
       <c r="B9" t="n">
         <v>150.136</v>
       </c>
+      <c r="C9" t="n">
+        <v>887.0522597080086</v>
+      </c>
       <c r="D9" t="n">
         <v>2.74542e-07</v>
       </c>
@@ -964,6 +988,9 @@
       <c r="B10" t="n">
         <v>145.279</v>
       </c>
+      <c r="C10" t="n">
+        <v>909.0013480941077</v>
+      </c>
       <c r="D10" t="n">
         <v>2.7434e-07</v>
       </c>
@@ -1013,6 +1040,9 @@
       </c>
       <c r="B11" t="n">
         <v>139.072</v>
+      </c>
+      <c r="C11" t="n">
+        <v>891.7112209245018</v>
       </c>
       <c r="D11" t="n">
         <v>2.74116e-07</v>
@@ -1084,7 +1114,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1210,6 +1240,9 @@
       <c r="B2" t="n">
         <v>206.432</v>
       </c>
+      <c r="C2" t="n">
+        <v>1027.197852687076</v>
+      </c>
       <c r="D2" t="n">
         <v>2.77466e-07</v>
       </c>
@@ -1260,6 +1293,9 @@
       <c r="B3" t="n">
         <v>184.4160000000001</v>
       </c>
+      <c r="C3" t="n">
+        <v>902.7940809877579</v>
+      </c>
       <c r="D3" t="n">
         <v>2.79344e-07</v>
       </c>
@@ -1310,6 +1346,9 @@
       <c r="B4" t="n">
         <v>175.397</v>
       </c>
+      <c r="C4" t="n">
+        <v>862.2087501883916</v>
+      </c>
       <c r="D4" t="n">
         <v>2.79701e-07</v>
       </c>
@@ -1360,6 +1399,9 @@
       <c r="B5" t="n">
         <v>171.446</v>
       </c>
+      <c r="C5" t="n">
+        <v>886.3560675515994</v>
+      </c>
       <c r="D5" t="n">
         <v>2.79651e-07</v>
       </c>
@@ -1410,6 +1452,9 @@
       <c r="B6" t="n">
         <v>166.47</v>
       </c>
+      <c r="C6" t="n">
+        <v>888.4724451938284</v>
+      </c>
       <c r="D6" t="n">
         <v>2.79475e-07</v>
       </c>
@@ -1460,6 +1505,9 @@
       <c r="B7" t="n">
         <v>159.812</v>
       </c>
+      <c r="C7" t="n">
+        <v>868.1145075137358</v>
+      </c>
       <c r="D7" t="n">
         <v>2.79772e-07</v>
       </c>
@@ -1510,6 +1558,9 @@
       <c r="B8" t="n">
         <v>155.379</v>
       </c>
+      <c r="C8" t="n">
+        <v>873.3306496121952</v>
+      </c>
       <c r="D8" t="n">
         <v>2.79625e-07</v>
       </c>
@@ -1560,6 +1611,9 @@
       <c r="B9" t="n">
         <v>151.518</v>
       </c>
+      <c r="C9" t="n">
+        <v>908.8998340011626</v>
+      </c>
       <c r="D9" t="n">
         <v>2.79657e-07</v>
       </c>
@@ -1610,6 +1664,9 @@
       <c r="B10" t="n">
         <v>147.951</v>
       </c>
+      <c r="C10" t="n">
+        <v>898.7247833343874</v>
+      </c>
       <c r="D10" t="n">
         <v>2.79686e-07</v>
       </c>
@@ -1660,6 +1717,9 @@
       <c r="B11" t="n">
         <v>142.825</v>
       </c>
+      <c r="C11" t="n">
+        <v>856.1469406850624</v>
+      </c>
       <c r="D11" t="n">
         <v>2.798e-07</v>
       </c>
@@ -1710,6 +1770,9 @@
       <c r="B12" t="n">
         <v>138.833</v>
       </c>
+      <c r="C12" t="n">
+        <v>859.2985711206757</v>
+      </c>
       <c r="D12" t="n">
         <v>2.7984e-07</v>
       </c>
@@ -1760,6 +1823,9 @@
       <c r="B13" t="n">
         <v>136.215</v>
       </c>
+      <c r="C13" t="n">
+        <v>892.7807341741723</v>
+      </c>
       <c r="D13" t="n">
         <v>2.79997e-07</v>
       </c>
@@ -1810,6 +1876,9 @@
       <c r="B14" t="n">
         <v>133.475</v>
       </c>
+      <c r="C14" t="n">
+        <v>895.6816897333391</v>
+      </c>
       <c r="D14" t="n">
         <v>2.79936e-07</v>
       </c>
@@ -1860,6 +1929,9 @@
       <c r="B15" t="n">
         <v>129.5869999999999</v>
       </c>
+      <c r="C15" t="n">
+        <v>860.5237679728359</v>
+      </c>
       <c r="D15" t="n">
         <v>2.79942e-07</v>
       </c>
@@ -1910,6 +1982,9 @@
       <c r="B16" t="n">
         <v>122.747</v>
       </c>
+      <c r="C16" t="n">
+        <v>789.2102893126587</v>
+      </c>
       <c r="D16" t="n">
         <v>2.79985e-07</v>
       </c>
@@ -1960,6 +2035,9 @@
       <c r="B17" t="n">
         <v>124.586</v>
       </c>
+      <c r="C17" t="n">
+        <v>882.1297468374921</v>
+      </c>
       <c r="D17" t="n">
         <v>2.80122e-07</v>
       </c>
@@ -2010,6 +2088,9 @@
       <c r="B18" t="n">
         <v>119.501</v>
       </c>
+      <c r="C18" t="n">
+        <v>868.3567377622001</v>
+      </c>
       <c r="D18" t="n">
         <v>2.80068e-07</v>
       </c>
@@ -2060,6 +2141,9 @@
       <c r="B19" t="n">
         <v>118.911</v>
       </c>
+      <c r="C19" t="n">
+        <v>913.1300660644629</v>
+      </c>
       <c r="D19" t="n">
         <v>2.8028e-07</v>
       </c>
@@ -2110,6 +2194,9 @@
       <c r="B20" t="n">
         <v>114.173</v>
       </c>
+      <c r="C20" t="n">
+        <v>860.0496040013539</v>
+      </c>
       <c r="D20" t="n">
         <v>2.80156e-07</v>
       </c>
@@ -2160,6 +2247,9 @@
       <c r="B21" t="n">
         <v>112.521</v>
       </c>
+      <c r="C21" t="n">
+        <v>863.3511569667393</v>
+      </c>
       <c r="D21" t="n">
         <v>2.80049e-07</v>
       </c>
@@ -2209,6 +2299,9 @@
       </c>
       <c r="B22" t="n">
         <v>108.157</v>
+      </c>
+      <c r="C22" t="n">
+        <v>823.3419010240468</v>
       </c>
       <c r="D22" t="n">
         <v>2.80206e-07</v>
@@ -2280,7 +2373,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2406,6 +2499,9 @@
       <c r="B2" t="n">
         <v>193.3989999999999</v>
       </c>
+      <c r="C2" t="n">
+        <v>961.9770475691951</v>
+      </c>
       <c r="D2" t="n">
         <v>2.75911e-07</v>
       </c>
@@ -2456,6 +2552,9 @@
       <c r="B3" t="n">
         <v>181.307</v>
       </c>
+      <c r="C3" t="n">
+        <v>896.2244429485407</v>
+      </c>
       <c r="D3" t="n">
         <v>2.75569e-07</v>
       </c>
@@ -2506,6 +2605,9 @@
       <c r="B4" t="n">
         <v>175.408</v>
       </c>
+      <c r="C4" t="n">
+        <v>883.8618554998707</v>
+      </c>
       <c r="D4" t="n">
         <v>2.74958e-07</v>
       </c>
@@ -2556,6 +2658,9 @@
       <c r="B5" t="n">
         <v>170.3459999999999</v>
       </c>
+      <c r="C5" t="n">
+        <v>888.6626293262237</v>
+      </c>
       <c r="D5" t="n">
         <v>2.74428e-07</v>
       </c>
@@ -2606,6 +2711,9 @@
       <c r="B6" t="n">
         <v>164.084</v>
       </c>
+      <c r="C6" t="n">
+        <v>878.4530379458594</v>
+      </c>
       <c r="D6" t="n">
         <v>2.74171e-07</v>
       </c>
@@ -2656,6 +2764,9 @@
       <c r="B7" t="n">
         <v>158.844</v>
       </c>
+      <c r="C7" t="n">
+        <v>871.047209119923</v>
+      </c>
       <c r="D7" t="n">
         <v>2.73569e-07</v>
       </c>
@@ -2706,6 +2817,9 @@
       <c r="B8" t="n">
         <v>157.0719999999999</v>
       </c>
+      <c r="C8" t="n">
+        <v>921.1589319619975</v>
+      </c>
       <c r="D8" t="n">
         <v>2.73308e-07</v>
       </c>
@@ -2756,6 +2870,9 @@
       <c r="B9" t="n">
         <v>151.429</v>
       </c>
+      <c r="C9" t="n">
+        <v>874.682731412841</v>
+      </c>
       <c r="D9" t="n">
         <v>2.72884e-07</v>
       </c>
@@ -2806,6 +2923,9 @@
       <c r="B10" t="n">
         <v>146.739</v>
       </c>
+      <c r="C10" t="n">
+        <v>871.4443233979639</v>
+      </c>
       <c r="D10" t="n">
         <v>2.7248e-07</v>
       </c>
@@ -2856,6 +2976,9 @@
       <c r="B11" t="n">
         <v>145.875</v>
       </c>
+      <c r="C11" t="n">
+        <v>923.3660368077719</v>
+      </c>
       <c r="D11" t="n">
         <v>2.7219e-07</v>
       </c>
@@ -2906,6 +3029,9 @@
       <c r="B12" t="n">
         <v>140.711</v>
       </c>
+      <c r="C12" t="n">
+        <v>879.1591037725209</v>
+      </c>
       <c r="D12" t="n">
         <v>2.71584e-07</v>
       </c>
@@ -2956,6 +3082,9 @@
       <c r="B13" t="n">
         <v>136.612</v>
       </c>
+      <c r="C13" t="n">
+        <v>851.5721191262974</v>
+      </c>
       <c r="D13" t="n">
         <v>2.71535e-07</v>
       </c>
@@ -3006,6 +3135,9 @@
       <c r="B14" t="n">
         <v>134.8819999999999</v>
       </c>
+      <c r="C14" t="n">
+        <v>902.353723200184</v>
+      </c>
       <c r="D14" t="n">
         <v>2.71117e-07</v>
       </c>
@@ -3056,6 +3188,9 @@
       <c r="B15" t="n">
         <v>129.588</v>
       </c>
+      <c r="C15" t="n">
+        <v>853.3847582675411</v>
+      </c>
       <c r="D15" t="n">
         <v>2.70973e-07</v>
       </c>
@@ -3106,6 +3241,9 @@
       <c r="B16" t="n">
         <v>128.5050000000001</v>
       </c>
+      <c r="C16" t="n">
+        <v>875.8318886768707</v>
+      </c>
       <c r="D16" t="n">
         <v>2.70639e-07</v>
       </c>
@@ -3156,6 +3294,9 @@
       <c r="B17" t="n">
         <v>127.8079999999999</v>
       </c>
+      <c r="C17" t="n">
+        <v>939.8821002164004</v>
+      </c>
       <c r="D17" t="n">
         <v>2.70397e-07</v>
       </c>
@@ -3206,6 +3347,9 @@
       <c r="B18" t="n">
         <v>122.131</v>
       </c>
+      <c r="C18" t="n">
+        <v>882.0826337771429</v>
+      </c>
       <c r="D18" t="n">
         <v>2.70245e-07</v>
       </c>
@@ -3256,6 +3400,9 @@
       <c r="B19" t="n">
         <v>121.495</v>
       </c>
+      <c r="C19" t="n">
+        <v>915.2092651704854</v>
+      </c>
       <c r="D19" t="n">
         <v>2.70042e-07</v>
       </c>
@@ -3306,6 +3453,9 @@
       <c r="B20" t="n">
         <v>119.636</v>
       </c>
+      <c r="C20" t="n">
+        <v>973.9912139524558</v>
+      </c>
       <c r="D20" t="n">
         <v>2.6985e-07</v>
       </c>
@@ -3356,6 +3506,9 @@
       <c r="B21" t="n">
         <v>115.007</v>
       </c>
+      <c r="C21" t="n">
+        <v>897.6903350067421</v>
+      </c>
       <c r="D21" t="n">
         <v>2.69851e-07</v>
       </c>
@@ -3405,6 +3558,9 @@
       </c>
       <c r="B22" t="n">
         <v>111.596</v>
+      </c>
+      <c r="C22" t="n">
+        <v>910.4690131935323</v>
       </c>
       <c r="D22" t="n">
         <v>2.69608e-07</v>
@@ -3476,7 +3632,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -3602,6 +3758,9 @@
       <c r="B2" t="n">
         <v>334.134</v>
       </c>
+      <c r="C2" t="n">
+        <v>1411.763296967267</v>
+      </c>
       <c r="D2" t="n">
         <v>2.73912e-07</v>
       </c>
@@ -3652,6 +3811,9 @@
       <c r="B3" t="n">
         <v>260.447</v>
       </c>
+      <c r="C3" t="n">
+        <v>1034.975541540962</v>
+      </c>
       <c r="D3" t="n">
         <v>2.78028e-07</v>
       </c>
@@ -3702,6 +3864,9 @@
       <c r="B4" t="n">
         <v>236.025</v>
       </c>
+      <c r="C4" t="n">
+        <v>961.5968795054097</v>
+      </c>
       <c r="D4" t="n">
         <v>2.77557e-07</v>
       </c>
@@ -3752,6 +3917,9 @@
       <c r="B5" t="n">
         <v>220.16</v>
       </c>
+      <c r="C5" t="n">
+        <v>915.5467888440138</v>
+      </c>
       <c r="D5" t="n">
         <v>2.76524e-07</v>
       </c>
@@ -3802,6 +3970,9 @@
       <c r="B6" t="n">
         <v>212.585</v>
       </c>
+      <c r="C6" t="n">
+        <v>948.9006475057885</v>
+      </c>
       <c r="D6" t="n">
         <v>2.7542e-07</v>
       </c>
@@ -3852,6 +4023,9 @@
       <c r="B7" t="n">
         <v>203.701</v>
       </c>
+      <c r="C7" t="n">
+        <v>941.0741790400255</v>
+      </c>
       <c r="D7" t="n">
         <v>2.74779e-07</v>
       </c>
@@ -3902,6 +4076,9 @@
       <c r="B8" t="n">
         <v>195.643</v>
       </c>
+      <c r="C8" t="n">
+        <v>954.868130801176</v>
+      </c>
       <c r="D8" t="n">
         <v>2.74066e-07</v>
       </c>
@@ -3952,6 +4129,9 @@
       <c r="B9" t="n">
         <v>185.795</v>
       </c>
+      <c r="C9" t="n">
+        <v>925.9156525937782</v>
+      </c>
       <c r="D9" t="n">
         <v>2.73609e-07</v>
       </c>
@@ -4002,6 +4182,9 @@
       <c r="B10" t="n">
         <v>175.393</v>
       </c>
+      <c r="C10" t="n">
+        <v>871.2013953610513</v>
+      </c>
       <c r="D10" t="n">
         <v>2.73151e-07</v>
       </c>
@@ -4051,6 +4234,9 @@
       </c>
       <c r="B11" t="n">
         <v>170.5479999999999</v>
+      </c>
+      <c r="C11" t="n">
+        <v>897.2209628481532</v>
       </c>
       <c r="D11" t="n">
         <v>2.72605e-07</v>
@@ -4122,7 +4308,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -4248,6 +4434,9 @@
       <c r="B2" t="n">
         <v>203.3919999999999</v>
       </c>
+      <c r="C2" t="n">
+        <v>1034.313496509902</v>
+      </c>
       <c r="D2" t="n">
         <v>2.82333e-07</v>
       </c>
@@ -4298,6 +4487,9 @@
       <c r="B3" t="n">
         <v>185.462</v>
       </c>
+      <c r="C3" t="n">
+        <v>934.1914174086962</v>
+      </c>
       <c r="D3" t="n">
         <v>2.80172e-07</v>
       </c>
@@ -4348,6 +4540,9 @@
       <c r="B4" t="n">
         <v>174.581</v>
       </c>
+      <c r="C4" t="n">
+        <v>888.3449099277892</v>
+      </c>
       <c r="D4" t="n">
         <v>2.79093e-07</v>
       </c>
@@ -4398,6 +4593,9 @@
       <c r="B5" t="n">
         <v>168.443</v>
       </c>
+      <c r="C5" t="n">
+        <v>873.536478067285</v>
+      </c>
       <c r="D5" t="n">
         <v>2.78399e-07</v>
       </c>
@@ -4448,6 +4646,9 @@
       <c r="B6" t="n">
         <v>161.7929999999999</v>
       </c>
+      <c r="C6" t="n">
+        <v>876.7029475605611</v>
+      </c>
       <c r="D6" t="n">
         <v>2.77939e-07</v>
       </c>
@@ -4498,6 +4699,9 @@
       <c r="B7" t="n">
         <v>159.784</v>
       </c>
+      <c r="C7" t="n">
+        <v>908.395752993568</v>
+      </c>
       <c r="D7" t="n">
         <v>2.77535e-07</v>
       </c>
@@ -4548,6 +4752,9 @@
       <c r="B8" t="n">
         <v>156.292</v>
       </c>
+      <c r="C8" t="n">
+        <v>921.533131025118</v>
+      </c>
       <c r="D8" t="n">
         <v>2.77186e-07</v>
       </c>
@@ -4598,6 +4805,9 @@
       <c r="B9" t="n">
         <v>148.669</v>
       </c>
+      <c r="C9" t="n">
+        <v>857.8666835095696</v>
+      </c>
       <c r="D9" t="n">
         <v>2.76888e-07</v>
       </c>
@@ -4648,6 +4858,9 @@
       <c r="B10" t="n">
         <v>145.981</v>
       </c>
+      <c r="C10" t="n">
+        <v>875.2750800233698</v>
+      </c>
       <c r="D10" t="n">
         <v>2.76517e-07</v>
       </c>
@@ -4698,6 +4911,9 @@
       <c r="B11" t="n">
         <v>143.8799999999999</v>
       </c>
+      <c r="C11" t="n">
+        <v>897.5537747730348</v>
+      </c>
       <c r="D11" t="n">
         <v>2.76424e-07</v>
       </c>
@@ -4748,6 +4964,9 @@
       <c r="B12" t="n">
         <v>138.4470000000001</v>
       </c>
+      <c r="C12" t="n">
+        <v>832.4836723597732</v>
+      </c>
       <c r="D12" t="n">
         <v>2.76201e-07</v>
       </c>
@@ -4798,6 +5017,9 @@
       <c r="B13" t="n">
         <v>138.159</v>
       </c>
+      <c r="C13" t="n">
+        <v>897.1979556182571</v>
+      </c>
       <c r="D13" t="n">
         <v>2.76011e-07</v>
       </c>
@@ -4848,6 +5070,9 @@
       <c r="B14" t="n">
         <v>134.57</v>
       </c>
+      <c r="C14" t="n">
+        <v>875.8002036942403</v>
+      </c>
       <c r="D14" t="n">
         <v>2.75803e-07</v>
       </c>
@@ -4898,6 +5123,9 @@
       <c r="B15" t="n">
         <v>131.5069999999999</v>
       </c>
+      <c r="C15" t="n">
+        <v>859.6603696321208</v>
+      </c>
       <c r="D15" t="n">
         <v>2.7569e-07</v>
       </c>
@@ -4948,6 +5176,9 @@
       <c r="B16" t="n">
         <v>129.8489999999999</v>
       </c>
+      <c r="C16" t="n">
+        <v>906.4475426061808</v>
+      </c>
       <c r="D16" t="n">
         <v>2.7559e-07</v>
       </c>
@@ -4998,6 +5229,9 @@
       <c r="B17" t="n">
         <v>125.705</v>
       </c>
+      <c r="C17" t="n">
+        <v>887.7853172866976</v>
+      </c>
       <c r="D17" t="n">
         <v>2.75323e-07</v>
       </c>
@@ -5048,6 +5282,9 @@
       <c r="B18" t="n">
         <v>124.137</v>
       </c>
+      <c r="C18" t="n">
+        <v>870.8540060670778</v>
+      </c>
       <c r="D18" t="n">
         <v>2.75338e-07</v>
       </c>
@@ -5098,6 +5335,9 @@
       <c r="B19" t="n">
         <v>121.937</v>
       </c>
+      <c r="C19" t="n">
+        <v>901.1720244147524</v>
+      </c>
       <c r="D19" t="n">
         <v>2.75325e-07</v>
       </c>
@@ -5148,6 +5388,9 @@
       <c r="B20" t="n">
         <v>117.485</v>
       </c>
+      <c r="C20" t="n">
+        <v>871.2492314654334</v>
+      </c>
       <c r="D20" t="n">
         <v>2.75103e-07</v>
       </c>
@@ -5198,6 +5441,9 @@
       <c r="B21" t="n">
         <v>114.98</v>
       </c>
+      <c r="C21" t="n">
+        <v>902.0613523425806</v>
+      </c>
       <c r="D21" t="n">
         <v>2.75269e-07</v>
       </c>
@@ -5247,6 +5493,9 @@
       </c>
       <c r="B22" t="n">
         <v>112.792</v>
+      </c>
+      <c r="C22" t="n">
+        <v>878.6789707699892</v>
       </c>
       <c r="D22" t="n">
         <v>2.75223e-07</v>
@@ -5318,7 +5567,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -5444,6 +5693,9 @@
       <c r="B2" t="n">
         <v>333.346</v>
       </c>
+      <c r="C2" t="n">
+        <v>1555.181868833714</v>
+      </c>
       <c r="D2" t="n">
         <v>2.9838e-07</v>
       </c>
@@ -5494,6 +5746,9 @@
       <c r="B3" t="n">
         <v>246.427</v>
       </c>
+      <c r="C3" t="n">
+        <v>1055.265038374031</v>
+      </c>
       <c r="D3" t="n">
         <v>3.01216e-07</v>
       </c>
@@ -5544,6 +5799,9 @@
       <c r="B4" t="n">
         <v>224.73</v>
       </c>
+      <c r="C4" t="n">
+        <v>967.5632220182958</v>
+      </c>
       <c r="D4" t="n">
         <v>2.962e-07</v>
       </c>
@@ -5594,6 +5852,9 @@
       <c r="B5" t="n">
         <v>211.467</v>
       </c>
+      <c r="C5" t="n">
+        <v>923.7861082613437</v>
+      </c>
       <c r="D5" t="n">
         <v>2.92195e-07</v>
       </c>
@@ -5644,6 +5905,9 @@
       <c r="B6" t="n">
         <v>199.57</v>
       </c>
+      <c r="C6" t="n">
+        <v>888.7175136904814</v>
+      </c>
       <c r="D6" t="n">
         <v>2.88889e-07</v>
       </c>
@@ -5694,6 +5958,9 @@
       <c r="B7" t="n">
         <v>197.137</v>
       </c>
+      <c r="C7" t="n">
+        <v>953.8626890533504</v>
+      </c>
       <c r="D7" t="n">
         <v>2.86417e-07</v>
       </c>
@@ -5744,6 +6011,9 @@
       <c r="B8" t="n">
         <v>187.569</v>
       </c>
+      <c r="C8" t="n">
+        <v>919.619126798712</v>
+      </c>
       <c r="D8" t="n">
         <v>2.84804e-07</v>
       </c>
@@ -5794,6 +6064,9 @@
       <c r="B9" t="n">
         <v>178.627</v>
       </c>
+      <c r="C9" t="n">
+        <v>885.1289779863799</v>
+      </c>
       <c r="D9" t="n">
         <v>2.83701e-07</v>
       </c>
@@ -5844,6 +6117,9 @@
       <c r="B10" t="n">
         <v>175.395</v>
       </c>
+      <c r="C10" t="n">
+        <v>922.0514999047031</v>
+      </c>
       <c r="D10" t="n">
         <v>2.82732e-07</v>
       </c>
@@ -5893,6 +6169,9 @@
       </c>
       <c r="B11" t="n">
         <v>165.3759999999999</v>
+      </c>
+      <c r="C11" t="n">
+        <v>841.6588621188024</v>
       </c>
       <c r="D11" t="n">
         <v>2.81897e-07</v>
@@ -5964,7 +6243,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -6090,6 +6369,9 @@
       <c r="B2" t="n">
         <v>206.8460000000001</v>
       </c>
+      <c r="C2" t="n">
+        <v>1020.042582437527</v>
+      </c>
       <c r="D2" t="n">
         <v>2.99723e-07</v>
       </c>
@@ -6140,6 +6422,9 @@
       <c r="B3" t="n">
         <v>189.844</v>
       </c>
+      <c r="C3" t="n">
+        <v>946.00764180644</v>
+      </c>
       <c r="D3" t="n">
         <v>2.91984e-07</v>
       </c>
@@ -6190,6 +6475,9 @@
       <c r="B4" t="n">
         <v>179.171</v>
       </c>
+      <c r="C4" t="n">
+        <v>897.7283850584535</v>
+      </c>
       <c r="D4" t="n">
         <v>2.89069e-07</v>
       </c>
@@ -6240,6 +6528,9 @@
       <c r="B5" t="n">
         <v>173.399</v>
       </c>
+      <c r="C5" t="n">
+        <v>892.0063199428704</v>
+      </c>
       <c r="D5" t="n">
         <v>2.87552e-07</v>
       </c>
@@ -6290,6 +6581,9 @@
       <c r="B6" t="n">
         <v>168.251</v>
       </c>
+      <c r="C6" t="n">
+        <v>905.5730919315628</v>
+      </c>
       <c r="D6" t="n">
         <v>2.8644e-07</v>
       </c>
@@ -6340,6 +6634,9 @@
       <c r="B7" t="n">
         <v>160.248</v>
       </c>
+      <c r="C7" t="n">
+        <v>856.2388532587383</v>
+      </c>
       <c r="D7" t="n">
         <v>2.8567e-07</v>
       </c>
@@ -6390,6 +6687,9 @@
       <c r="B8" t="n">
         <v>159.213</v>
       </c>
+      <c r="C8" t="n">
+        <v>918.8389598953801</v>
+      </c>
       <c r="D8" t="n">
         <v>2.8523e-07</v>
       </c>
@@ -6440,6 +6740,9 @@
       <c r="B9" t="n">
         <v>152.17</v>
       </c>
+      <c r="C9" t="n">
+        <v>867.3743971075091</v>
+      </c>
       <c r="D9" t="n">
         <v>2.84916e-07</v>
       </c>
@@ -6490,6 +6793,9 @@
       <c r="B10" t="n">
         <v>151.238</v>
       </c>
+      <c r="C10" t="n">
+        <v>907.0553502733042</v>
+      </c>
       <c r="D10" t="n">
         <v>2.84593e-07</v>
       </c>
@@ -6540,6 +6846,9 @@
       <c r="B11" t="n">
         <v>144.625</v>
       </c>
+      <c r="C11" t="n">
+        <v>869.9435474858964</v>
+      </c>
       <c r="D11" t="n">
         <v>2.84275e-07</v>
       </c>
@@ -6590,6 +6899,9 @@
       <c r="B12" t="n">
         <v>140.51</v>
       </c>
+      <c r="C12" t="n">
+        <v>843.7806351905666</v>
+      </c>
       <c r="D12" t="n">
         <v>2.84088e-07</v>
       </c>
@@ -6640,6 +6952,9 @@
       <c r="B13" t="n">
         <v>139.208</v>
       </c>
+      <c r="C13" t="n">
+        <v>873.2407912253542</v>
+      </c>
       <c r="D13" t="n">
         <v>2.83809e-07</v>
       </c>
@@ -6690,6 +7005,9 @@
       <c r="B14" t="n">
         <v>134.528</v>
       </c>
+      <c r="C14" t="n">
+        <v>864.3852519757155</v>
+      </c>
       <c r="D14" t="n">
         <v>2.83662e-07</v>
       </c>
@@ -6740,6 +7058,9 @@
       <c r="B15" t="n">
         <v>131.579</v>
       </c>
+      <c r="C15" t="n">
+        <v>869.8770254076319</v>
+      </c>
       <c r="D15" t="n">
         <v>2.83538e-07</v>
       </c>
@@ -6790,6 +7111,9 @@
       <c r="B16" t="n">
         <v>128.748</v>
       </c>
+      <c r="C16" t="n">
+        <v>865.7222437430219</v>
+      </c>
       <c r="D16" t="n">
         <v>2.83431e-07</v>
       </c>
@@ -6840,6 +7164,9 @@
       <c r="B17" t="n">
         <v>127.2329999999999</v>
       </c>
+      <c r="C17" t="n">
+        <v>881.6788881790243</v>
+      </c>
       <c r="D17" t="n">
         <v>2.83203e-07</v>
       </c>
@@ -6890,6 +7217,9 @@
       <c r="B18" t="n">
         <v>122.799</v>
       </c>
+      <c r="C18" t="n">
+        <v>872.450998536572</v>
+      </c>
       <c r="D18" t="n">
         <v>2.82888e-07</v>
       </c>
@@ -6940,6 +7270,9 @@
       <c r="B19" t="n">
         <v>121.292</v>
       </c>
+      <c r="C19" t="n">
+        <v>886.2631420399176</v>
+      </c>
       <c r="D19" t="n">
         <v>2.82876e-07</v>
       </c>
@@ -6990,6 +7323,9 @@
       <c r="B20" t="n">
         <v>119.8219999999999</v>
       </c>
+      <c r="C20" t="n">
+        <v>905.228121659562</v>
+      </c>
       <c r="D20" t="n">
         <v>2.82837e-07</v>
       </c>
@@ -7040,6 +7376,9 @@
       <c r="B21" t="n">
         <v>116.877</v>
       </c>
+      <c r="C21" t="n">
+        <v>868.88449033617</v>
+      </c>
       <c r="D21" t="n">
         <v>2.82964e-07</v>
       </c>
@@ -7089,6 +7428,9 @@
       </c>
       <c r="B22" t="n">
         <v>114.616</v>
+      </c>
+      <c r="C22" t="n">
+        <v>911.1123925756573</v>
       </c>
       <c r="D22" t="n">
         <v>2.82777e-07</v>
@@ -7160,7 +7502,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7286,6 +7628,9 @@
       <c r="B2" t="n">
         <v>298.57</v>
       </c>
+      <c r="C2" t="n">
+        <v>1414.828673842266</v>
+      </c>
       <c r="D2" t="n">
         <v>3.05948e-07</v>
       </c>
@@ -7336,6 +7681,9 @@
       <c r="B3" t="n">
         <v>235.207</v>
       </c>
+      <c r="C3" t="n">
+        <v>1026.015105716084</v>
+      </c>
       <c r="D3" t="n">
         <v>3.01741e-07</v>
       </c>
@@ -7386,6 +7734,9 @@
       <c r="B4" t="n">
         <v>217.785</v>
       </c>
+      <c r="C4" t="n">
+        <v>972.180460540835</v>
+      </c>
       <c r="D4" t="n">
         <v>2.95421e-07</v>
       </c>
@@ -7436,6 +7787,9 @@
       <c r="B5" t="n">
         <v>206.568</v>
       </c>
+      <c r="C5" t="n">
+        <v>934.6983443390566</v>
+      </c>
       <c r="D5" t="n">
         <v>2.91133e-07</v>
       </c>
@@ -7486,6 +7840,9 @@
       <c r="B6" t="n">
         <v>197.877</v>
       </c>
+      <c r="C6" t="n">
+        <v>912.3562816934183</v>
+      </c>
       <c r="D6" t="n">
         <v>2.88235e-07</v>
       </c>
@@ -7536,6 +7893,9 @@
       <c r="B7" t="n">
         <v>187.9519999999999</v>
       </c>
+      <c r="C7" t="n">
+        <v>874.2293425976636</v>
+      </c>
       <c r="D7" t="n">
         <v>2.86237e-07</v>
       </c>
@@ -7586,6 +7946,9 @@
       <c r="B8" t="n">
         <v>182.118</v>
       </c>
+      <c r="C8" t="n">
+        <v>876.2319599699657</v>
+      </c>
       <c r="D8" t="n">
         <v>2.84878e-07</v>
       </c>
@@ -7636,6 +7999,9 @@
       <c r="B9" t="n">
         <v>175.5549999999999</v>
       </c>
+      <c r="C9" t="n">
+        <v>870.2278960003052</v>
+      </c>
       <c r="D9" t="n">
         <v>2.83987e-07</v>
       </c>
@@ -7686,6 +8052,9 @@
       <c r="B10" t="n">
         <v>170.85</v>
       </c>
+      <c r="C10" t="n">
+        <v>873.4495812334183</v>
+      </c>
       <c r="D10" t="n">
         <v>2.83373e-07</v>
       </c>
@@ -7735,6 +8104,9 @@
       </c>
       <c r="B11" t="n">
         <v>165.505</v>
+      </c>
+      <c r="C11" t="n">
+        <v>887.1766248020296</v>
       </c>
       <c r="D11" t="n">
         <v>2.82702e-07</v>
@@ -7806,7 +8178,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7932,6 +8304,9 @@
       <c r="B2" t="n">
         <v>198.355</v>
       </c>
+      <c r="C2" t="n">
+        <v>972.6606102753591</v>
+      </c>
       <c r="D2" t="n">
         <v>2.91342e-07</v>
       </c>
@@ -7982,6 +8357,9 @@
       <c r="B3" t="n">
         <v>184.845</v>
       </c>
+      <c r="C3" t="n">
+        <v>921.0359198788776</v>
+      </c>
       <c r="D3" t="n">
         <v>2.87842e-07</v>
       </c>
@@ -8032,6 +8410,9 @@
       <c r="B4" t="n">
         <v>175.218</v>
       </c>
+      <c r="C4" t="n">
+        <v>891.7956344542929</v>
+      </c>
       <c r="D4" t="n">
         <v>2.86379e-07</v>
       </c>
@@ -8082,6 +8463,9 @@
       <c r="B5" t="n">
         <v>167.609</v>
       </c>
+      <c r="C5" t="n">
+        <v>869.3360857037379</v>
+      </c>
       <c r="D5" t="n">
         <v>2.85662e-07</v>
       </c>
@@ -8132,6 +8516,9 @@
       <c r="B6" t="n">
         <v>163.3939999999999</v>
       </c>
+      <c r="C6" t="n">
+        <v>871.13753525448</v>
+      </c>
       <c r="D6" t="n">
         <v>2.85421e-07</v>
       </c>
@@ -8182,6 +8569,9 @@
       <c r="B7" t="n">
         <v>161.792</v>
       </c>
+      <c r="C7" t="n">
+        <v>924.1471734003914</v>
+      </c>
       <c r="D7" t="n">
         <v>2.85006e-07</v>
       </c>
@@ -8232,6 +8622,9 @@
       <c r="B8" t="n">
         <v>153.253</v>
       </c>
+      <c r="C8" t="n">
+        <v>876.600330661738</v>
+      </c>
       <c r="D8" t="n">
         <v>2.84715e-07</v>
       </c>
@@ -8282,6 +8675,9 @@
       <c r="B9" t="n">
         <v>147.508</v>
       </c>
+      <c r="C9" t="n">
+        <v>843.8766455458048</v>
+      </c>
       <c r="D9" t="n">
         <v>2.84692e-07</v>
       </c>
@@ -8332,6 +8728,9 @@
       <c r="B10" t="n">
         <v>145.554</v>
       </c>
+      <c r="C10" t="n">
+        <v>876.2998409685026</v>
+      </c>
       <c r="D10" t="n">
         <v>2.84423e-07</v>
       </c>
@@ -8382,6 +8781,9 @@
       <c r="B11" t="n">
         <v>142.062</v>
       </c>
+      <c r="C11" t="n">
+        <v>858.802129951642</v>
+      </c>
       <c r="D11" t="n">
         <v>2.84401e-07</v>
       </c>
@@ -8432,6 +8834,9 @@
       <c r="B12" t="n">
         <v>141.682</v>
       </c>
+      <c r="C12" t="n">
+        <v>905.9290830953911</v>
+      </c>
       <c r="D12" t="n">
         <v>2.84125e-07</v>
       </c>
@@ -8482,6 +8887,9 @@
       <c r="B13" t="n">
         <v>136.251</v>
       </c>
+      <c r="C13" t="n">
+        <v>847.8446446182267</v>
+      </c>
       <c r="D13" t="n">
         <v>2.84049e-07</v>
       </c>
@@ -8532,6 +8940,9 @@
       <c r="B14" t="n">
         <v>134.869</v>
       </c>
+      <c r="C14" t="n">
+        <v>851.1279152663077</v>
+      </c>
       <c r="D14" t="n">
         <v>2.83889e-07</v>
       </c>
@@ -8582,6 +8993,9 @@
       <c r="B15" t="n">
         <v>132.0050000000001</v>
       </c>
+      <c r="C15" t="n">
+        <v>869.3548667041561</v>
+      </c>
       <c r="D15" t="n">
         <v>2.83738e-07</v>
       </c>
@@ -8632,6 +9046,9 @@
       <c r="B16" t="n">
         <v>128.112</v>
       </c>
+      <c r="C16" t="n">
+        <v>837.6940219539747</v>
+      </c>
       <c r="D16" t="n">
         <v>2.83853e-07</v>
       </c>
@@ -8682,6 +9099,9 @@
       <c r="B17" t="n">
         <v>127.595</v>
       </c>
+      <c r="C17" t="n">
+        <v>856.8966934918191</v>
+      </c>
       <c r="D17" t="n">
         <v>2.83517e-07</v>
       </c>
@@ -8732,6 +9152,9 @@
       <c r="B18" t="n">
         <v>122.673</v>
       </c>
+      <c r="C18" t="n">
+        <v>831.2265891111224</v>
+      </c>
       <c r="D18" t="n">
         <v>2.83744e-07</v>
       </c>
@@ -8782,6 +9205,9 @@
       <c r="B19" t="n">
         <v>120.7</v>
       </c>
+      <c r="C19" t="n">
+        <v>846.5339455258571</v>
+      </c>
       <c r="D19" t="n">
         <v>2.83754e-07</v>
       </c>
@@ -8832,6 +9258,9 @@
       <c r="B20" t="n">
         <v>118.272</v>
       </c>
+      <c r="C20" t="n">
+        <v>872.5719907046836</v>
+      </c>
       <c r="D20" t="n">
         <v>2.83824e-07</v>
       </c>
@@ -8882,6 +9311,9 @@
       <c r="B21" t="n">
         <v>114.862</v>
       </c>
+      <c r="C21" t="n">
+        <v>859.9432983828518</v>
+      </c>
       <c r="D21" t="n">
         <v>2.83751e-07</v>
       </c>
@@ -8931,6 +9363,9 @@
       </c>
       <c r="B22" t="n">
         <v>112.232</v>
+      </c>
+      <c r="C22" t="n">
+        <v>845.0421699677898</v>
       </c>
       <c r="D22" t="n">
         <v>2.83923e-07</v>
@@ -9002,7 +9437,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -9128,6 +9563,9 @@
       <c r="B2" t="n">
         <v>209.369</v>
       </c>
+      <c r="C2" t="n">
+        <v>963.3500395621181</v>
+      </c>
       <c r="D2" t="n">
         <v>3.03843e-07</v>
       </c>
@@ -9178,6 +9616,9 @@
       <c r="B3" t="n">
         <v>194.602</v>
       </c>
+      <c r="C3" t="n">
+        <v>920.803017745957</v>
+      </c>
       <c r="D3" t="n">
         <v>2.91101e-07</v>
       </c>
@@ -9228,6 +9669,9 @@
       <c r="B4" t="n">
         <v>184.617</v>
       </c>
+      <c r="C4" t="n">
+        <v>883.9439570194403</v>
+      </c>
       <c r="D4" t="n">
         <v>2.87153e-07</v>
       </c>
@@ -9278,6 +9722,9 @@
       <c r="B5" t="n">
         <v>174.845</v>
       </c>
+      <c r="C5" t="n">
+        <v>849.4137613896729</v>
+      </c>
       <c r="D5" t="n">
         <v>2.84839e-07</v>
       </c>
@@ -9328,6 +9775,9 @@
       <c r="B6" t="n">
         <v>168.8989999999999</v>
       </c>
+      <c r="C6" t="n">
+        <v>854.1073843362993</v>
+      </c>
       <c r="D6" t="n">
         <v>2.83502e-07</v>
       </c>
@@ -9378,6 +9828,9 @@
       <c r="B7" t="n">
         <v>161.246</v>
       </c>
+      <c r="C7" t="n">
+        <v>852.9248458446624</v>
+      </c>
       <c r="D7" t="n">
         <v>2.82778e-07</v>
       </c>
@@ -9428,6 +9881,9 @@
       <c r="B8" t="n">
         <v>157.234</v>
       </c>
+      <c r="C8" t="n">
+        <v>872.3296546226109</v>
+      </c>
       <c r="D8" t="n">
         <v>2.82205e-07</v>
       </c>
@@ -9478,6 +9934,9 @@
       <c r="B9" t="n">
         <v>150.322</v>
       </c>
+      <c r="C9" t="n">
+        <v>841.1688802713625</v>
+      </c>
       <c r="D9" t="n">
         <v>2.81724e-07</v>
       </c>
@@ -9528,6 +9987,9 @@
       <c r="B10" t="n">
         <v>144.708</v>
       </c>
+      <c r="C10" t="n">
+        <v>825.3861321747046</v>
+      </c>
       <c r="D10" t="n">
         <v>2.81539e-07</v>
       </c>
@@ -9577,6 +10039,9 @@
       </c>
       <c r="B11" t="n">
         <v>143.558</v>
+      </c>
+      <c r="C11" t="n">
+        <v>865.4519374853718</v>
       </c>
       <c r="D11" t="n">
         <v>2.81199e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 52.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 52.xlsx
@@ -565,7 +565,7 @@
         <v>207.4320000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>885.1082429764258</v>
+        <v>207.4320000000001</v>
       </c>
       <c r="D2" t="n">
         <v>2.84075e-07</v>
@@ -597,11 +597,10 @@
       <c r="X2" t="n">
         <v>-8803.943089349516</v>
       </c>
-      <c r="Y2" t="n">
-        <v>551.6818235263696</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>139537132.2274952</v>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA2" t="n">
         <v>7.206532355596467e-07</v>
@@ -618,7 +617,7 @@
         <v>201.885</v>
       </c>
       <c r="C3" t="n">
-        <v>907.4780775400502</v>
+        <v>405.9828333358562</v>
       </c>
       <c r="D3" t="n">
         <v>2.77854e-07</v>
@@ -651,16 +650,13 @@
         <v>-9879.710328565614</v>
       </c>
       <c r="Y3" t="n">
-        <v>545.3859073851647</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>33031208.38257015</v>
+        <v>211.0304404364515</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.267127526616215e-07</v>
+        <v>5.015854611969194e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8758214799464826</v>
+        <v>0.9090941093135136</v>
       </c>
     </row>
     <row r="4">
@@ -671,7 +667,7 @@
         <v>194.896</v>
       </c>
       <c r="C4" t="n">
-        <v>925.9741935475854</v>
+        <v>396.5686260125572</v>
       </c>
       <c r="D4" t="n">
         <v>2.76208e-07</v>
@@ -704,16 +700,13 @@
         <v>-10470.7424904319</v>
       </c>
       <c r="Y4" t="n">
-        <v>537.7848296526171</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>41283398.12183786</v>
+        <v>209.51858188172</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.890070855591323e-07</v>
+        <v>4.73996449902883e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.884317078852627</v>
+        <v>0.9146831435303198</v>
       </c>
     </row>
     <row r="5">
@@ -724,7 +717,7 @@
         <v>186.004</v>
       </c>
       <c r="C5" t="n">
-        <v>940.3138725961708</v>
+        <v>392.4450165962168</v>
       </c>
       <c r="D5" t="n">
         <v>2.75569e-07</v>
@@ -757,16 +750,13 @@
         <v>-10543.2899082422</v>
       </c>
       <c r="Y5" t="n">
-        <v>529.0813057894175</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>74804313.00622916</v>
+        <v>202.6839874778432</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.5989793164035e-07</v>
+        <v>4.577899571036557e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8916542873903337</v>
+        <v>0.9171607259340263</v>
       </c>
     </row>
     <row r="6">
@@ -777,7 +767,7 @@
         <v>174.124</v>
       </c>
       <c r="C6" t="n">
-        <v>922.8210851313289</v>
+        <v>365.769221879694</v>
       </c>
       <c r="D6" t="n">
         <v>2.75198e-07</v>
@@ -810,16 +800,13 @@
         <v>-10285.13111244457</v>
       </c>
       <c r="Y6" t="n">
-        <v>520.1197093400756</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>39945648.51106961</v>
+        <v>217.8705257009836</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.362107796516958e-07</v>
+        <v>4.588284107318637e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.898021353319397</v>
+        <v>0.9243490715029963</v>
       </c>
     </row>
     <row r="7">
@@ -830,7 +817,7 @@
         <v>163.76</v>
       </c>
       <c r="C7" t="n">
-        <v>879.1189659599338</v>
+        <v>163.76</v>
       </c>
       <c r="D7" t="n">
         <v>2.74793e-07</v>
@@ -862,11 +849,10 @@
       <c r="X7" t="n">
         <v>-9915.337206015489</v>
       </c>
-      <c r="Y7" t="n">
-        <v>511.449997744861</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>46634350.48192126</v>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA7" t="n">
         <v>5.18164608234583e-07</v>
@@ -883,7 +869,7 @@
         <v>159.049</v>
       </c>
       <c r="C8" t="n">
-        <v>922.308664005486</v>
+        <v>159.049</v>
       </c>
       <c r="D8" t="n">
         <v>2.74725e-07</v>
@@ -915,11 +901,10 @@
       <c r="X8" t="n">
         <v>-10467.27842527503</v>
       </c>
-      <c r="Y8" t="n">
-        <v>503.0960003368983</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>208007705.727629</v>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA8" t="n">
         <v>5.032855244703399e-07</v>
@@ -936,7 +921,7 @@
         <v>150.136</v>
       </c>
       <c r="C9" t="n">
-        <v>887.0522597080086</v>
+        <v>336.2289009488626</v>
       </c>
       <c r="D9" t="n">
         <v>2.74542e-07</v>
@@ -969,16 +954,13 @@
         <v>-10109.59046943449</v>
       </c>
       <c r="Y9" t="n">
-        <v>495.2601629230304</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>44565443.13058098</v>
+        <v>216.7100001016818</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.903602942740081e-07</v>
+        <v>4.297647222856175e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9112882571601162</v>
+        <v>0.9368234618023528</v>
       </c>
     </row>
     <row r="10">
@@ -989,7 +971,7 @@
         <v>145.279</v>
       </c>
       <c r="C10" t="n">
-        <v>909.0013480941077</v>
+        <v>145.279</v>
       </c>
       <c r="D10" t="n">
         <v>2.7434e-07</v>
@@ -1021,11 +1003,10 @@
       <c r="X10" t="n">
         <v>-10290.04093702186</v>
       </c>
-      <c r="Y10" t="n">
-        <v>487.5726900698414</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>34386439.88839921</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>4.798176144455605e-07</v>
@@ -1042,7 +1023,7 @@
         <v>139.072</v>
       </c>
       <c r="C11" t="n">
-        <v>891.7112209245018</v>
+        <v>320.6557519287686</v>
       </c>
       <c r="D11" t="n">
         <v>2.74116e-07</v>
@@ -1075,16 +1056,13 @@
         <v>-10084.21876871057</v>
       </c>
       <c r="Y11" t="n">
-        <v>480.5862591691507</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>26881734.4222526</v>
+        <v>212.7638496827794</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.696682508126709e-07</v>
+        <v>3.98306416574066e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9176214688840652</v>
+        <v>0.9427966583077266</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1219,7 @@
         <v>206.432</v>
       </c>
       <c r="C2" t="n">
-        <v>1027.197852687076</v>
+        <v>389.3779048009731</v>
       </c>
       <c r="D2" t="n">
         <v>2.77466e-07</v>
@@ -1274,16 +1252,13 @@
         <v>-11249.97607059805</v>
       </c>
       <c r="Y2" t="n">
-        <v>547.6190726842345</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>41080721.47866023</v>
+        <v>227.1597132830832</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.843129485523733e-07</v>
+        <v>4.740498463040093e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.886157461389472</v>
+        <v>0.9177734978207142</v>
       </c>
     </row>
     <row r="3">
@@ -1294,7 +1269,7 @@
         <v>184.4160000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>902.7940809877579</v>
+        <v>397.6508546436347</v>
       </c>
       <c r="D3" t="n">
         <v>2.79344e-07</v>
@@ -1327,16 +1302,13 @@
         <v>-10861.79937310117</v>
       </c>
       <c r="Y3" t="n">
-        <v>536.3130500260861</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>41194474.90584817</v>
+        <v>206.4849360767597</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.549820417865719e-07</v>
+        <v>5.012658492251914e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8950503314533955</v>
+        <v>0.9100036876046439</v>
       </c>
     </row>
     <row r="4">
@@ -1347,7 +1319,7 @@
         <v>175.397</v>
       </c>
       <c r="C4" t="n">
-        <v>862.2087501883916</v>
+        <v>375.9036627217961</v>
       </c>
       <c r="D4" t="n">
         <v>2.79701e-07</v>
@@ -1380,16 +1352,13 @@
         <v>-10951.55297359674</v>
       </c>
       <c r="Y4" t="n">
-        <v>530.5014166093951</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>67697417.42539169</v>
+        <v>220.5993732132474</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.38037091704937e-07</v>
+        <v>5.160361159626587e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8999537002764342</v>
+        <v>0.9136517205757437</v>
       </c>
     </row>
     <row r="5">
@@ -1400,7 +1369,7 @@
         <v>171.446</v>
       </c>
       <c r="C5" t="n">
-        <v>886.3560675515994</v>
+        <v>382.1550639049772</v>
       </c>
       <c r="D5" t="n">
         <v>2.79651e-07</v>
@@ -1433,16 +1402,13 @@
         <v>-11286.66355718546</v>
       </c>
       <c r="Y5" t="n">
-        <v>525.0447999738915</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>38322631.85220434</v>
+        <v>207.8953836395212</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.280000921525257e-07</v>
+        <v>4.99539369762503e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9028218588589982</v>
+        <v>0.9137291474447489</v>
       </c>
     </row>
     <row r="6">
@@ -1453,7 +1419,7 @@
         <v>166.47</v>
       </c>
       <c r="C6" t="n">
-        <v>888.4724451938284</v>
+        <v>166.47</v>
       </c>
       <c r="D6" t="n">
         <v>2.79475e-07</v>
@@ -1485,11 +1451,10 @@
       <c r="X6" t="n">
         <v>-11158.79633193113</v>
       </c>
-      <c r="Y6" t="n">
-        <v>519.1276913944876</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>22421880.91333796</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>5.18061558625732e-07</v>
@@ -1506,7 +1471,7 @@
         <v>159.812</v>
       </c>
       <c r="C7" t="n">
-        <v>868.1145075137358</v>
+        <v>350.7266478206971</v>
       </c>
       <c r="D7" t="n">
         <v>2.79772e-07</v>
@@ -1539,16 +1504,13 @@
         <v>-10830.42604100653</v>
       </c>
       <c r="Y7" t="n">
-        <v>512.8851005325013</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>61754128.69018628</v>
+        <v>222.6272521141702</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.098815646727138e-07</v>
+        <v>4.863725546276e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9082258353444421</v>
+        <v>0.9241318331810363</v>
       </c>
     </row>
     <row r="8">
@@ -1559,7 +1521,7 @@
         <v>155.379</v>
       </c>
       <c r="C8" t="n">
-        <v>873.3306496121952</v>
+        <v>343.8515527517007</v>
       </c>
       <c r="D8" t="n">
         <v>2.79625e-07</v>
@@ -1592,16 +1554,13 @@
         <v>-10961.22474682713</v>
       </c>
       <c r="Y8" t="n">
-        <v>506.692379193322</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>279841143.0356812</v>
+        <v>221.8621331817158</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.014855124558051e-07</v>
+        <v>4.791249778392341e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.910701142904584</v>
+        <v>0.9267951569998644</v>
       </c>
     </row>
     <row r="9">
@@ -1612,7 +1571,7 @@
         <v>151.518</v>
       </c>
       <c r="C9" t="n">
-        <v>908.8998340011626</v>
+        <v>338.0794677050096</v>
       </c>
       <c r="D9" t="n">
         <v>2.79657e-07</v>
@@ -1645,16 +1604,13 @@
         <v>-11209.17712077081</v>
       </c>
       <c r="Y9" t="n">
-        <v>500.7779678278371</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>27874041.96337112</v>
+        <v>220.9403408873982</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.928337765878669e-07</v>
+        <v>4.733376988166201e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9133725852778088</v>
+        <v>0.9285613360682315</v>
       </c>
     </row>
     <row r="10">
@@ -1665,7 +1621,7 @@
         <v>147.951</v>
       </c>
       <c r="C10" t="n">
-        <v>898.7247833343874</v>
+        <v>331.354733810122</v>
       </c>
       <c r="D10" t="n">
         <v>2.79686e-07</v>
@@ -1698,16 +1654,13 @@
         <v>-11255.07046605867</v>
       </c>
       <c r="Y10" t="n">
-        <v>495.285121895397</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>271600469.696499</v>
+        <v>220.2378013534221</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.859172518199393e-07</v>
+        <v>4.617740517177474e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9155414574974581</v>
+        <v>0.9323209311907492</v>
       </c>
     </row>
     <row r="11">
@@ -1718,7 +1671,7 @@
         <v>142.825</v>
       </c>
       <c r="C11" t="n">
-        <v>856.1469406850624</v>
+        <v>325.8720136763358</v>
       </c>
       <c r="D11" t="n">
         <v>2.798e-07</v>
@@ -1751,16 +1704,13 @@
         <v>-10902.55060148231</v>
       </c>
       <c r="Y11" t="n">
-        <v>489.9210250392429</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>29405537.75678721</v>
+        <v>219.9487776500272</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.787743942065891e-07</v>
+        <v>4.627237563070885e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9178572889243085</v>
+        <v>0.9340507675086528</v>
       </c>
     </row>
     <row r="12">
@@ -1771,7 +1721,7 @@
         <v>138.833</v>
       </c>
       <c r="C12" t="n">
-        <v>859.2985711206757</v>
+        <v>138.833</v>
       </c>
       <c r="D12" t="n">
         <v>2.7984e-07</v>
@@ -1803,11 +1753,10 @@
       <c r="X12" t="n">
         <v>-10902.4667195866</v>
       </c>
-      <c r="Y12" t="n">
-        <v>484.5950792194721</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>65902059.67108587</v>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA12" t="n">
         <v>4.732247315029527e-07</v>
@@ -1824,7 +1773,7 @@
         <v>136.215</v>
       </c>
       <c r="C13" t="n">
-        <v>892.7807341741723</v>
+        <v>314.4870621462944</v>
       </c>
       <c r="D13" t="n">
         <v>2.79997e-07</v>
@@ -1857,16 +1806,13 @@
         <v>-10907.04836233583</v>
       </c>
       <c r="Y13" t="n">
-        <v>479.2207077071099</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>24082961.64675545</v>
+        <v>218.0246360155872</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.683395449795387e-07</v>
+        <v>4.381050633099827e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.9213274675745137</v>
+        <v>0.940766905937671</v>
       </c>
     </row>
     <row r="14">
@@ -1877,7 +1823,7 @@
         <v>133.475</v>
       </c>
       <c r="C14" t="n">
-        <v>895.6816897333391</v>
+        <v>133.475</v>
       </c>
       <c r="D14" t="n">
         <v>2.79936e-07</v>
@@ -1909,11 +1855,10 @@
       <c r="X14" t="n">
         <v>-11178.80252208924</v>
       </c>
-      <c r="Y14" t="n">
-        <v>474.0124014865988</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>48531238.15834387</v>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA14" t="n">
         <v>4.630164582235506e-07</v>
@@ -1930,7 +1875,7 @@
         <v>129.5869999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>860.5237679728359</v>
+        <v>304.6325869554876</v>
       </c>
       <c r="D15" t="n">
         <v>2.79942e-07</v>
@@ -1963,16 +1908,13 @@
         <v>-10797.02377499621</v>
       </c>
       <c r="Y15" t="n">
-        <v>469.0075452841498</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>28576826.45869574</v>
+        <v>215.6877084454803</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.576311750516199e-07</v>
+        <v>4.253768373528263e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9248273123145193</v>
+        <v>0.9454686774914178</v>
       </c>
     </row>
     <row r="16">
@@ -1983,7 +1925,7 @@
         <v>122.747</v>
       </c>
       <c r="C16" t="n">
-        <v>789.2102893126587</v>
+        <v>122.747</v>
       </c>
       <c r="D16" t="n">
         <v>2.79985e-07</v>
@@ -2015,11 +1957,10 @@
       <c r="X16" t="n">
         <v>-10004.5531730878</v>
       </c>
-      <c r="Y16" t="n">
-        <v>464.0837279452896</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>41656734.77073652</v>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA16" t="n">
         <v>4.537056640989806e-07</v>
@@ -2036,7 +1977,7 @@
         <v>124.586</v>
       </c>
       <c r="C17" t="n">
-        <v>882.1297468374921</v>
+        <v>299.2020002387368</v>
       </c>
       <c r="D17" t="n">
         <v>2.80122e-07</v>
@@ -2069,16 +2010,13 @@
         <v>-11054.07949912203</v>
       </c>
       <c r="Y17" t="n">
-        <v>459.2088586320658</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>73142621.77350013</v>
+        <v>208.7799483686697</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.491448263308566e-07</v>
+        <v>3.991913053991227e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9277754535995723</v>
+        <v>0.9489436217694185</v>
       </c>
     </row>
     <row r="18">
@@ -2089,7 +2027,7 @@
         <v>119.501</v>
       </c>
       <c r="C18" t="n">
-        <v>868.3567377622001</v>
+        <v>292.7640199695267</v>
       </c>
       <c r="D18" t="n">
         <v>2.80068e-07</v>
@@ -2122,16 +2060,13 @@
         <v>-10695.26111207464</v>
       </c>
       <c r="Y18" t="n">
-        <v>454.2969709553919</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>38835982.37046302</v>
+        <v>209.4764953857934</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.459785110598263e-07</v>
+        <v>3.930490108170164e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9288390395482373</v>
+        <v>0.9524458865469952</v>
       </c>
     </row>
     <row r="19">
@@ -2142,7 +2077,7 @@
         <v>118.911</v>
       </c>
       <c r="C19" t="n">
-        <v>913.1300660644629</v>
+        <v>401.7194486153734</v>
       </c>
       <c r="D19" t="n">
         <v>2.8028e-07</v>
@@ -2175,16 +2110,13 @@
         <v>-11183.55084380444</v>
       </c>
       <c r="Y19" t="n">
-        <v>449.4719906849796</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>369854107.262041</v>
+        <v>94.46495253330275</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.413194965873209e-07</v>
+        <v>3.06079146008205e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.930533840555642</v>
+        <v>0.9279253940460438</v>
       </c>
     </row>
     <row r="20">
@@ -2195,7 +2127,7 @@
         <v>114.173</v>
       </c>
       <c r="C20" t="n">
-        <v>860.0496040013539</v>
+        <v>416.6258511214436</v>
       </c>
       <c r="D20" t="n">
         <v>2.80156e-07</v>
@@ -2228,16 +2160,13 @@
         <v>-10488.21905324031</v>
       </c>
       <c r="Y20" t="n">
-        <v>444.6512127779001</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>730005415.09552</v>
+        <v>72.98999174113115</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.380704721093446e-07</v>
+        <v>2.80266625691414e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.931611207274547</v>
+        <v>0.927348793976229</v>
       </c>
     </row>
     <row r="21">
@@ -2248,7 +2177,7 @@
         <v>112.521</v>
       </c>
       <c r="C21" t="n">
-        <v>863.3511569667393</v>
+        <v>302.2033767242965</v>
       </c>
       <c r="D21" t="n">
         <v>2.80049e-07</v>
@@ -2281,16 +2210,13 @@
         <v>-10670.26348242676</v>
       </c>
       <c r="Y21" t="n">
-        <v>439.9087363251003</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>134598211.1798755</v>
+        <v>183.0530661744533</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.34392041140991e-07</v>
+        <v>3.542110220747531e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9328343364818265</v>
+        <v>0.9545919877723461</v>
       </c>
     </row>
     <row r="22">
@@ -2301,7 +2227,7 @@
         <v>108.157</v>
       </c>
       <c r="C22" t="n">
-        <v>823.3419010240468</v>
+        <v>312.430490967279</v>
       </c>
       <c r="D22" t="n">
         <v>2.80206e-07</v>
@@ -2334,16 +2260,13 @@
         <v>-10266.41063451135</v>
       </c>
       <c r="Y22" t="n">
-        <v>411.244001256769</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>5842.653011486986</v>
+        <v>167.6706694452399</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.641218700590199e-07</v>
+        <v>3.399773972386244e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9984261786744993</v>
+        <v>0.952707673351593</v>
       </c>
     </row>
   </sheetData>
@@ -2500,7 +2423,7 @@
         <v>193.3989999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>961.9770475691951</v>
+        <v>387.5489984448405</v>
       </c>
       <c r="D2" t="n">
         <v>2.75911e-07</v>
@@ -2533,16 +2456,13 @@
         <v>-10152.08803456429</v>
       </c>
       <c r="Y2" t="n">
-        <v>543.0744978851715</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>56623007.34436025</v>
+        <v>223.4665063633328</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.820828483546218e-07</v>
+        <v>4.774471904283552e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8859197612966854</v>
+        <v>0.9151684123682864</v>
       </c>
     </row>
     <row r="3">
@@ -2553,7 +2473,7 @@
         <v>181.307</v>
       </c>
       <c r="C3" t="n">
-        <v>896.2244429485407</v>
+        <v>397.6128292959498</v>
       </c>
       <c r="D3" t="n">
         <v>2.75569e-07</v>
@@ -2586,16 +2506,13 @@
         <v>-10602.84886892514</v>
       </c>
       <c r="Y3" t="n">
-        <v>535.3777738037471</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>26357392.43708407</v>
+        <v>206.0738861967593</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.475926748889934e-07</v>
+        <v>4.95137510807733e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8949616793716735</v>
+        <v>0.9113313589303484</v>
       </c>
     </row>
     <row r="4">
@@ -2606,7 +2523,7 @@
         <v>175.408</v>
       </c>
       <c r="C4" t="n">
-        <v>883.8618554998707</v>
+        <v>388.6036496488179</v>
       </c>
       <c r="D4" t="n">
         <v>2.74958e-07</v>
@@ -2639,16 +2556,13 @@
         <v>-10667.68510282975</v>
       </c>
       <c r="Y4" t="n">
-        <v>529.6461565578179</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>72818556.39952733</v>
+        <v>207.0315867647625</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.311393192374377e-07</v>
+        <v>4.827659785624812e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8992685023209542</v>
+        <v>0.9147783247954242</v>
       </c>
     </row>
     <row r="5">
@@ -2659,7 +2573,7 @@
         <v>170.3459999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>888.6626293262237</v>
+        <v>364.7402912150372</v>
       </c>
       <c r="D5" t="n">
         <v>2.74428e-07</v>
@@ -2692,16 +2606,13 @@
         <v>-10474.87440678367</v>
       </c>
       <c r="Y5" t="n">
-        <v>523.4266567912304</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>122210555.2592653</v>
+        <v>221.744558449803</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.185988259768235e-07</v>
+        <v>4.729211538758348e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9026224396203708</v>
+        <v>0.9209879765489475</v>
       </c>
     </row>
     <row r="6">
@@ -2712,7 +2623,7 @@
         <v>164.084</v>
       </c>
       <c r="C6" t="n">
-        <v>878.4530379458594</v>
+        <v>357.8390019554388</v>
       </c>
       <c r="D6" t="n">
         <v>2.74171e-07</v>
@@ -2745,16 +2656,13 @@
         <v>-10319.1937841465</v>
       </c>
       <c r="Y6" t="n">
-        <v>516.9120811162061</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>40063527.89311381</v>
+        <v>221.7125822211342</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.082977602685361e-07</v>
+        <v>4.714461988794178e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9055414459293201</v>
+        <v>0.9252606539979942</v>
       </c>
     </row>
     <row r="7">
@@ -2765,7 +2673,7 @@
         <v>158.844</v>
       </c>
       <c r="C7" t="n">
-        <v>871.047209119923</v>
+        <v>351.268791566047</v>
       </c>
       <c r="D7" t="n">
         <v>2.73569e-07</v>
@@ -2798,16 +2706,13 @@
         <v>-10475.09841175652</v>
       </c>
       <c r="Y7" t="n">
-        <v>510.8136599619593</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>284246405.3912622</v>
+        <v>220.6467504194251</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.968564906094457e-07</v>
+        <v>4.628224144713502e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.908680243748182</v>
+        <v>0.9278799724329215</v>
       </c>
     </row>
     <row r="8">
@@ -2818,7 +2723,7 @@
         <v>157.0719999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>921.1589319619975</v>
+        <v>345.3909761510453</v>
       </c>
       <c r="D8" t="n">
         <v>2.73308e-07</v>
@@ -2851,16 +2756,13 @@
         <v>-11051.79958285651</v>
       </c>
       <c r="Y8" t="n">
-        <v>505.1418191579408</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>277296170.3229762</v>
+        <v>219.5499535374763</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.877483991057653e-07</v>
+        <v>4.560626783160047e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9113429296945486</v>
+        <v>0.9301973356435184</v>
       </c>
     </row>
     <row r="9">
@@ -2871,7 +2773,7 @@
         <v>151.429</v>
       </c>
       <c r="C9" t="n">
-        <v>874.682731412841</v>
+        <v>339.2846550050028</v>
       </c>
       <c r="D9" t="n">
         <v>2.72884e-07</v>
@@ -2904,16 +2806,13 @@
         <v>-10583.59431202855</v>
       </c>
       <c r="Y9" t="n">
-        <v>500.0446173133178</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>274974229.9535233</v>
+        <v>218.6593448311224</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.79742023833454e-07</v>
+        <v>4.460578703736248e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9136306050108158</v>
+        <v>0.9332923511942796</v>
       </c>
     </row>
     <row r="10">
@@ -2924,7 +2823,7 @@
         <v>146.739</v>
       </c>
       <c r="C10" t="n">
-        <v>871.4443233979639</v>
+        <v>333.9037540827738</v>
       </c>
       <c r="D10" t="n">
         <v>2.7248e-07</v>
@@ -2957,16 +2856,13 @@
         <v>-10423.537255714</v>
       </c>
       <c r="Y10" t="n">
-        <v>494.8353524461027</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>40287277.71094939</v>
+        <v>217.5902282295325</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.718427542435358e-07</v>
+        <v>4.380184657809627e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9159318818718266</v>
+        <v>0.9358438634551406</v>
       </c>
     </row>
     <row r="11">
@@ -2977,7 +2873,7 @@
         <v>145.875</v>
       </c>
       <c r="C11" t="n">
-        <v>923.3660368077719</v>
+        <v>328.375162320329</v>
       </c>
       <c r="D11" t="n">
         <v>2.7219e-07</v>
@@ -3010,16 +2906,13 @@
         <v>-11127.10472409307</v>
       </c>
       <c r="Y11" t="n">
-        <v>489.6967757098946</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>93252368.58251798</v>
+        <v>216.7905216121919</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.667191217373455e-07</v>
+        <v>4.273468508543873e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9174435870548666</v>
+        <v>0.9389468969080854</v>
       </c>
     </row>
     <row r="12">
@@ -3030,7 +2923,7 @@
         <v>140.711</v>
       </c>
       <c r="C12" t="n">
-        <v>879.1591037725209</v>
+        <v>323.3379943103723</v>
       </c>
       <c r="D12" t="n">
         <v>2.71584e-07</v>
@@ -3063,16 +2956,13 @@
         <v>-10527.28559566131</v>
       </c>
       <c r="Y12" t="n">
-        <v>484.7401896710014</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>43591990.13423891</v>
+        <v>215.8279504940077</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.60055500071584e-07</v>
+        <v>4.198903704327628e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.91930711753258</v>
+        <v>0.9414865287393798</v>
       </c>
     </row>
     <row r="13">
@@ -3083,7 +2973,7 @@
         <v>136.612</v>
       </c>
       <c r="C13" t="n">
-        <v>851.5721191262974</v>
+        <v>330.0576080851326</v>
       </c>
       <c r="D13" t="n">
         <v>2.71535e-07</v>
@@ -3116,16 +3006,13 @@
         <v>-10361.67708609466</v>
       </c>
       <c r="Y13" t="n">
-        <v>479.8687543644011</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>34107853.48462652</v>
+        <v>204.0996691774368</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.551564263780891e-07</v>
+        <v>4.055348148696521e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.9209059499127603</v>
+        <v>0.9411263291944456</v>
       </c>
     </row>
     <row r="14">
@@ -3136,7 +3023,7 @@
         <v>134.8819999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>902.353723200184</v>
+        <v>322.1336605151033</v>
       </c>
       <c r="D14" t="n">
         <v>2.71117e-07</v>
@@ -3169,16 +3056,13 @@
         <v>-10639.55258907091</v>
       </c>
       <c r="Y14" t="n">
-        <v>474.935735704342</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>34295332.13532727</v>
+        <v>204.91494555383</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.500449046646251e-07</v>
+        <v>3.915127019637101e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.9224025859855683</v>
+        <v>0.9432643739851576</v>
       </c>
     </row>
     <row r="15">
@@ -3189,7 +3073,7 @@
         <v>129.588</v>
       </c>
       <c r="C15" t="n">
-        <v>853.3847582675411</v>
+        <v>311.8519691175059</v>
       </c>
       <c r="D15" t="n">
         <v>2.70973e-07</v>
@@ -3222,16 +3106,13 @@
         <v>-10227.20672708117</v>
       </c>
       <c r="Y15" t="n">
-        <v>469.9476069863769</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>98475152.46562451</v>
+        <v>209.9858105040849</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.451062441172622e-07</v>
+        <v>3.929753766000918e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9239978165989882</v>
+        <v>0.9485659944530977</v>
       </c>
     </row>
     <row r="16">
@@ -3242,7 +3123,7 @@
         <v>128.5050000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>875.8318886768707</v>
+        <v>308.3316176039158</v>
       </c>
       <c r="D16" t="n">
         <v>2.70639e-07</v>
@@ -3275,16 +3156,13 @@
         <v>-10325.28024842519</v>
       </c>
       <c r="Y16" t="n">
-        <v>465.0514139133583</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>255587382.3131509</v>
+        <v>207.6624203435085</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.415980302388228e-07</v>
+        <v>3.80914542407422e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9250293871557737</v>
+        <v>0.9519399640994226</v>
       </c>
     </row>
     <row r="17">
@@ -3295,7 +3173,7 @@
         <v>127.8079999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>939.8821002164004</v>
+        <v>127.8079999999999</v>
       </c>
       <c r="D17" t="n">
         <v>2.70397e-07</v>
@@ -3327,11 +3205,10 @@
       <c r="X17" t="n">
         <v>-10911.60845700028</v>
       </c>
-      <c r="Y17" t="n">
-        <v>460.1691662592226</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>15734840.3135771</v>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA17" t="n">
         <v>4.344326980192154e-07</v>
@@ -3348,7 +3225,7 @@
         <v>122.131</v>
       </c>
       <c r="C18" t="n">
-        <v>882.0826337771429</v>
+        <v>122.131</v>
       </c>
       <c r="D18" t="n">
         <v>2.70245e-07</v>
@@ -3380,11 +3257,10 @@
       <c r="X18" t="n">
         <v>-10328.82297298489</v>
       </c>
-      <c r="Y18" t="n">
-        <v>455.2142059110784</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>48458271.54523466</v>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA18" t="n">
         <v>4.330306852580111e-07</v>
@@ -3401,7 +3277,7 @@
         <v>121.495</v>
       </c>
       <c r="C19" t="n">
-        <v>915.2092651704854</v>
+        <v>402.6802820888883</v>
       </c>
       <c r="D19" t="n">
         <v>2.70042e-07</v>
@@ -3434,16 +3310,13 @@
         <v>-10687.45139629967</v>
       </c>
       <c r="Y19" t="n">
-        <v>450.3106340980862</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>246346300.6498589</v>
+        <v>93.65178520806641</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.289298240777591e-07</v>
+        <v>2.751104035746008e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.9291421875612191</v>
+        <v>0.9338749874577053</v>
       </c>
     </row>
     <row r="20">
@@ -3454,7 +3327,7 @@
         <v>119.636</v>
       </c>
       <c r="C20" t="n">
-        <v>973.9912139524558</v>
+        <v>294.7937665128137</v>
       </c>
       <c r="D20" t="n">
         <v>2.6985e-07</v>
@@ -3487,16 +3360,13 @@
         <v>-10821.87992804147</v>
       </c>
       <c r="Y20" t="n">
-        <v>445.3910988715893</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>195607532.1833709</v>
+        <v>197.8249997346669</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.248476336062204e-07</v>
+        <v>3.516176909489229e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9304842063363656</v>
+        <v>0.9605399619818491</v>
       </c>
     </row>
     <row r="21">
@@ -3507,7 +3377,7 @@
         <v>115.007</v>
       </c>
       <c r="C21" t="n">
-        <v>897.6903350067421</v>
+        <v>290.7149540619933</v>
       </c>
       <c r="D21" t="n">
         <v>2.69851e-07</v>
@@ -3540,16 +3410,13 @@
         <v>-10284.19174682864</v>
       </c>
       <c r="Y21" t="n">
-        <v>440.4655235058564</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>362063644.571839</v>
+        <v>195.1238389791234</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.211295957905756e-07</v>
+        <v>3.401573121841537e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9318223302954682</v>
+        <v>0.9629086599654613</v>
       </c>
     </row>
     <row r="22">
@@ -3560,7 +3427,7 @@
         <v>111.596</v>
       </c>
       <c r="C22" t="n">
-        <v>910.4690131935323</v>
+        <v>311.5233884198204</v>
       </c>
       <c r="D22" t="n">
         <v>2.69608e-07</v>
@@ -3593,16 +3460,13 @@
         <v>-10197.54011435341</v>
       </c>
       <c r="Y22" t="n">
-        <v>435.5708022825369</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>178925621.5317138</v>
+        <v>168.8921933885033</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.18400320375367e-07</v>
+        <v>3.091646769330557e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9326973080804603</v>
+        <v>0.9602522016141879</v>
       </c>
     </row>
   </sheetData>
@@ -3759,7 +3623,7 @@
         <v>334.134</v>
       </c>
       <c r="C2" t="n">
-        <v>1411.763296967267</v>
+        <v>615.5007568509953</v>
       </c>
       <c r="D2" t="n">
         <v>2.73912e-07</v>
@@ -3792,16 +3656,13 @@
         <v>-8414.234368814468</v>
       </c>
       <c r="Y2" t="n">
-        <v>604.3463217163657</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>323573447.6931999</v>
+        <v>94.32111200798386</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.882895778045228e-06</v>
+        <v>2.724568672490709e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.71001629784389</v>
+        <v>0.9031316287078346</v>
       </c>
     </row>
     <row r="3">
@@ -3812,7 +3673,7 @@
         <v>260.447</v>
       </c>
       <c r="C3" t="n">
-        <v>1034.975541540962</v>
+        <v>607.0298108689589</v>
       </c>
       <c r="D3" t="n">
         <v>2.78028e-07</v>
@@ -3845,16 +3706,13 @@
         <v>-9702.424239303427</v>
       </c>
       <c r="Y3" t="n">
-        <v>589.3048081097292</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>75420614.09982227</v>
+        <v>65.91435787275439</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.76482784692416e-07</v>
+        <v>3.559776141253993e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8252689815935689</v>
+        <v>0.8846068873002925</v>
       </c>
     </row>
     <row r="4">
@@ -3865,7 +3723,7 @@
         <v>236.025</v>
       </c>
       <c r="C4" t="n">
-        <v>961.5968795054097</v>
+        <v>439.9015790650182</v>
       </c>
       <c r="D4" t="n">
         <v>2.77557e-07</v>
@@ -3898,16 +3756,13 @@
         <v>-10234.31203384862</v>
       </c>
       <c r="Y4" t="n">
-        <v>577.1142193154957</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>190376014.7478443</v>
+        <v>216.2721225368647</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.30842803239554e-07</v>
+        <v>4.968440786236249e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8523495598391753</v>
+        <v>0.903545361354934</v>
       </c>
     </row>
     <row r="5">
@@ -3918,7 +3773,7 @@
         <v>220.16</v>
       </c>
       <c r="C5" t="n">
-        <v>915.5467888440138</v>
+        <v>439.3975455756257</v>
       </c>
       <c r="D5" t="n">
         <v>2.76524e-07</v>
@@ -3951,16 +3806,13 @@
         <v>-10318.5601255436</v>
       </c>
       <c r="Y5" t="n">
-        <v>567.9871590781264</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>76725641.15732116</v>
+        <v>206.7252017486829</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.634786282406896e-07</v>
+        <v>5.295654487442116e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8663904509871001</v>
+        <v>0.897942552876121</v>
       </c>
     </row>
     <row r="6">
@@ -3971,7 +3823,7 @@
         <v>212.585</v>
       </c>
       <c r="C6" t="n">
-        <v>948.9006475057885</v>
+        <v>411.3916509257588</v>
       </c>
       <c r="D6" t="n">
         <v>2.7542e-07</v>
@@ -4004,16 +3856,13 @@
         <v>-11107.11539047141</v>
       </c>
       <c r="Y6" t="n">
-        <v>559.6763142710811</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>133734960.9734585</v>
+        <v>222.1741283105388</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.206783793336595e-07</v>
+        <v>5.136228435314077e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8759026763141121</v>
+        <v>0.9057860243058942</v>
       </c>
     </row>
     <row r="7">
@@ -4024,7 +3873,7 @@
         <v>203.701</v>
       </c>
       <c r="C7" t="n">
-        <v>941.0741790400255</v>
+        <v>400.0875174201154</v>
       </c>
       <c r="D7" t="n">
         <v>2.74779e-07</v>
@@ -4057,16 +3906,13 @@
         <v>-11236.52387553937</v>
       </c>
       <c r="Y7" t="n">
-        <v>551.4612662733882</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>79667415.47283565</v>
+        <v>222.4699532677032</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.886170529079986e-07</v>
+        <v>5.041004737035647e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8835919572235396</v>
+        <v>0.9092496030674228</v>
       </c>
     </row>
     <row r="8">
@@ -4077,7 +3923,7 @@
         <v>195.643</v>
       </c>
       <c r="C8" t="n">
-        <v>954.868130801176</v>
+        <v>389.4990906643764</v>
       </c>
       <c r="D8" t="n">
         <v>2.74066e-07</v>
@@ -4110,16 +3956,13 @@
         <v>-11214.33325122697</v>
       </c>
       <c r="Y8" t="n">
-        <v>543.3157354088189</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>110229427.7902048</v>
+        <v>222.4520587864776</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.676922735456703e-07</v>
+        <v>4.92333622460206e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8887380136564915</v>
+        <v>0.9129651882972155</v>
       </c>
     </row>
     <row r="9">
@@ -4130,7 +3973,7 @@
         <v>185.795</v>
       </c>
       <c r="C9" t="n">
-        <v>925.9156525937782</v>
+        <v>380.2426214008282</v>
       </c>
       <c r="D9" t="n">
         <v>2.73609e-07</v>
@@ -4163,16 +4006,13 @@
         <v>-11079.7237515102</v>
       </c>
       <c r="Y9" t="n">
-        <v>535.332687899152</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>151031625.3812257</v>
+        <v>222.5724806406231</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.446282324568905e-07</v>
+        <v>4.900334574932643e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8947642841424477</v>
+        <v>0.9174976370728964</v>
       </c>
     </row>
     <row r="10">
@@ -4183,7 +4023,7 @@
         <v>175.393</v>
       </c>
       <c r="C10" t="n">
-        <v>871.2013953610513</v>
+        <v>370.8694466570208</v>
       </c>
       <c r="D10" t="n">
         <v>2.73151e-07</v>
@@ -4216,16 +4056,13 @@
         <v>-10421.2894128726</v>
       </c>
       <c r="Y10" t="n">
-        <v>527.7492158615748</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>69139694.95995358</v>
+        <v>221.2458119485184</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.283929184470241e-07</v>
+        <v>4.789595281223965e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8991159299724438</v>
+        <v>0.9207284485554162</v>
       </c>
     </row>
     <row r="11">
@@ -4236,7 +4073,7 @@
         <v>170.5479999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>897.2209628481532</v>
+        <v>362.9450714931979</v>
       </c>
       <c r="D11" t="n">
         <v>2.72605e-07</v>
@@ -4269,16 +4106,13 @@
         <v>-10800.37868419815</v>
       </c>
       <c r="Y11" t="n">
-        <v>520.5777571939508</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>38550024.03899003</v>
+        <v>220.5151995000724</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.133228685586095e-07</v>
+        <v>4.712574429402598e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9032165774683129</v>
+        <v>0.923842181942242</v>
       </c>
     </row>
   </sheetData>
@@ -4435,7 +4269,7 @@
         <v>203.3919999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>1034.313496509902</v>
+        <v>392.6590747528625</v>
       </c>
       <c r="D2" t="n">
         <v>2.82333e-07</v>
@@ -4468,16 +4302,13 @@
         <v>-9296.019665877137</v>
       </c>
       <c r="Y2" t="n">
-        <v>548.4584993393676</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>33868013.95077544</v>
+        <v>225.1379702742187</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.64534361249985e-07</v>
+        <v>4.49341378964445e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8695419148826943</v>
+        <v>0.9197572861108487</v>
       </c>
     </row>
     <row r="3">
@@ -4488,7 +4319,7 @@
         <v>185.462</v>
       </c>
       <c r="C3" t="n">
-        <v>934.1914174086962</v>
+        <v>380.2472101100344</v>
       </c>
       <c r="D3" t="n">
         <v>2.80172e-07</v>
@@ -4521,16 +4352,13 @@
         <v>-10345.65935742836</v>
       </c>
       <c r="Y3" t="n">
-        <v>537.210201868043</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>118712454.8685306</v>
+        <v>223.9505881911046</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.822641005546925e-07</v>
+        <v>5.021488225591923e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8882925461712646</v>
+        <v>0.9132299570461971</v>
       </c>
     </row>
     <row r="4">
@@ -4541,7 +4369,7 @@
         <v>174.581</v>
       </c>
       <c r="C4" t="n">
-        <v>888.3449099277892</v>
+        <v>372.4570223290847</v>
       </c>
       <c r="D4" t="n">
         <v>2.79093e-07</v>
@@ -4574,16 +4402,13 @@
         <v>-10165.13698237332</v>
       </c>
       <c r="Y4" t="n">
-        <v>530.4059993973187</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>71146535.65390402</v>
+        <v>224.3262621081864</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.538610796403511e-07</v>
+        <v>5.077525105140521e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8952877626884116</v>
+        <v>0.916759294299416</v>
       </c>
     </row>
     <row r="5">
@@ -4594,7 +4419,7 @@
         <v>168.443</v>
       </c>
       <c r="C5" t="n">
-        <v>873.536478067285</v>
+        <v>363.8292248759323</v>
       </c>
       <c r="D5" t="n">
         <v>2.78399e-07</v>
@@ -4627,16 +4452,13 @@
         <v>-10311.45445201213</v>
       </c>
       <c r="Y5" t="n">
-        <v>523.9412351233299</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>43833349.28309046</v>
+        <v>224.4853170011958</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.362085377543871e-07</v>
+        <v>4.942248277695149e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.899832289012949</v>
+        <v>0.9206513920422204</v>
       </c>
     </row>
     <row r="6">
@@ -4647,7 +4469,7 @@
         <v>161.7929999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>876.7029475605611</v>
+        <v>356.2478197847407</v>
       </c>
       <c r="D6" t="n">
         <v>2.77939e-07</v>
@@ -4680,16 +4502,13 @@
         <v>-10188.70953644262</v>
       </c>
       <c r="Y6" t="n">
-        <v>517.1734637849278</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>19941641.97983824</v>
+        <v>223.4500439065887</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.216831471385929e-07</v>
+        <v>4.841830473096049e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9037554014635155</v>
+        <v>0.9235415849476366</v>
       </c>
     </row>
     <row r="7">
@@ -4700,7 +4519,7 @@
         <v>159.784</v>
       </c>
       <c r="C7" t="n">
-        <v>908.395752993568</v>
+        <v>349.1688477630988</v>
       </c>
       <c r="D7" t="n">
         <v>2.77535e-07</v>
@@ -4733,16 +4552,13 @@
         <v>-10713.03892349086</v>
       </c>
       <c r="Y7" t="n">
-        <v>510.9371799472771</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>21364185.31590111</v>
+        <v>221.7052782874113</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.085709092644983e-07</v>
+        <v>4.740419732423825e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9073974975782982</v>
+        <v>0.9261944058544305</v>
       </c>
     </row>
     <row r="8">
@@ -4753,7 +4569,7 @@
         <v>156.292</v>
       </c>
       <c r="C8" t="n">
-        <v>921.533131025118</v>
+        <v>343.3753101894026</v>
       </c>
       <c r="D8" t="n">
         <v>2.77186e-07</v>
@@ -4786,16 +4602,13 @@
         <v>-10988.87092254372</v>
       </c>
       <c r="Y8" t="n">
-        <v>505.1936294296866</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>217794310.3336492</v>
+        <v>220.766395060733</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.996646735832783e-07</v>
+        <v>4.68181173414467e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9099088804737524</v>
+        <v>0.928634403698399</v>
       </c>
     </row>
     <row r="9">
@@ -4806,7 +4619,7 @@
         <v>148.669</v>
       </c>
       <c r="C9" t="n">
-        <v>857.8666835095696</v>
+        <v>148.669</v>
       </c>
       <c r="D9" t="n">
         <v>2.76888e-07</v>
@@ -4838,11 +4651,10 @@
       <c r="X9" t="n">
         <v>-10275.02179171626</v>
       </c>
-      <c r="Y9" t="n">
-        <v>499.971990244395</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>207989369.6311161</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>4.913081306985214e-07</v>
@@ -4859,7 +4671,7 @@
         <v>145.981</v>
       </c>
       <c r="C10" t="n">
-        <v>875.2750800233698</v>
+        <v>333.0860261036676</v>
       </c>
       <c r="D10" t="n">
         <v>2.76517e-07</v>
@@ -4892,16 +4704,13 @@
         <v>-10551.78846650073</v>
       </c>
       <c r="Y10" t="n">
-        <v>495.0602961609386</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>577435629.8490283</v>
+        <v>218.6649473516825</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.836258111412862e-07</v>
+        <v>4.53491935165906e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9144973029286818</v>
+        <v>0.9333229535131579</v>
       </c>
     </row>
     <row r="11">
@@ -4912,7 +4721,7 @@
         <v>143.8799999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>897.5537747730348</v>
+        <v>328.1725931555339</v>
       </c>
       <c r="D11" t="n">
         <v>2.76424e-07</v>
@@ -4945,16 +4754,13 @@
         <v>-10651.03648055586</v>
       </c>
       <c r="Y11" t="n">
-        <v>490.3719480906841</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>37340201.01544112</v>
+        <v>218.4930905618583</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.782830294183207e-07</v>
+        <v>4.467126981695163e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9161392209830217</v>
+        <v>0.9362034646545624</v>
       </c>
     </row>
     <row r="12">
@@ -4965,7 +4771,7 @@
         <v>138.4470000000001</v>
       </c>
       <c r="C12" t="n">
-        <v>832.4836723597732</v>
+        <v>323.5307845516327</v>
       </c>
       <c r="D12" t="n">
         <v>2.76201e-07</v>
@@ -4998,16 +4804,13 @@
         <v>-10260.20862746471</v>
       </c>
       <c r="Y12" t="n">
-        <v>485.7195061657517</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>106225137.1154371</v>
+        <v>217.5506584003059</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.72514108836623e-07</v>
+        <v>4.408369034916259e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.9178656589727766</v>
+        <v>0.9382751799243964</v>
       </c>
     </row>
     <row r="13">
@@ -5018,7 +4821,7 @@
         <v>138.159</v>
       </c>
       <c r="C13" t="n">
-        <v>897.1979556182571</v>
+        <v>318.7585858720747</v>
       </c>
       <c r="D13" t="n">
         <v>2.76011e-07</v>
@@ -5051,16 +4854,13 @@
         <v>-10800.95263639708</v>
       </c>
       <c r="Y13" t="n">
-        <v>481.1161959089837</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>265683551.0406118</v>
+        <v>216.6464892417938</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.662560501647432e-07</v>
+        <v>4.320013568060469e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.9197786808082647</v>
+        <v>0.9409138260316897</v>
       </c>
     </row>
     <row r="14">
@@ -5071,7 +4871,7 @@
         <v>134.57</v>
       </c>
       <c r="C14" t="n">
-        <v>875.8002036942403</v>
+        <v>134.57</v>
       </c>
       <c r="D14" t="n">
         <v>2.75803e-07</v>
@@ -5103,11 +4903,10 @@
       <c r="X14" t="n">
         <v>-10430.51170212585</v>
       </c>
-      <c r="Y14" t="n">
-        <v>476.4290111059876</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>526242721.4847798</v>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA14" t="n">
         <v>4.631060404567869e-07</v>
@@ -5124,7 +4923,7 @@
         <v>131.5069999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>859.6603696321208</v>
+        <v>311.6780523254184</v>
       </c>
       <c r="D15" t="n">
         <v>2.7569e-07</v>
@@ -5157,16 +4956,13 @@
         <v>-10538.2687754834</v>
       </c>
       <c r="Y15" t="n">
-        <v>471.6699504570026</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>31788854.7874673</v>
+        <v>211.2714535170515</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.567488918996206e-07</v>
+        <v>4.040440950293293e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9227444327739828</v>
+        <v>0.9442302796678593</v>
       </c>
     </row>
     <row r="16">
@@ -5177,7 +4973,7 @@
         <v>129.8489999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>906.4475426061808</v>
+        <v>308.441712827493</v>
       </c>
       <c r="D16" t="n">
         <v>2.7559e-07</v>
@@ -5210,16 +5006,13 @@
         <v>-10734.58450027679</v>
       </c>
       <c r="Y16" t="n">
-        <v>466.8813678268625</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>81748662.55577137</v>
+        <v>209.8701650101631</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.522718850824425e-07</v>
+        <v>4.033845125042618e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.924189238953277</v>
+        <v>0.94782055325479</v>
       </c>
     </row>
     <row r="17">
@@ -5230,7 +5023,7 @@
         <v>125.705</v>
       </c>
       <c r="C17" t="n">
-        <v>887.7853172866976</v>
+        <v>306.0911401221002</v>
       </c>
       <c r="D17" t="n">
         <v>2.75323e-07</v>
@@ -5263,16 +5056,13 @@
         <v>-10452.16587075695</v>
       </c>
       <c r="Y17" t="n">
-        <v>462.0965369417456</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>42544192.1390802</v>
+        <v>206.5600450629306</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.478297767029729e-07</v>
+        <v>3.931570080206481e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.925561736088242</v>
+        <v>0.9502381198294974</v>
       </c>
     </row>
     <row r="18">
@@ -5283,7 +5073,7 @@
         <v>124.137</v>
       </c>
       <c r="C18" t="n">
-        <v>870.8540060670778</v>
+        <v>410.5781486235234</v>
       </c>
       <c r="D18" t="n">
         <v>2.75338e-07</v>
@@ -5316,16 +5106,13 @@
         <v>-10593.93515313758</v>
       </c>
       <c r="Y18" t="n">
-        <v>457.324415910957</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>189718246.9381725</v>
+        <v>94.28337396165284</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.445128379655021e-07</v>
+        <v>2.942191457178957e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9267053171687356</v>
+        <v>0.9278209239486421</v>
       </c>
     </row>
     <row r="19">
@@ -5336,7 +5123,7 @@
         <v>121.937</v>
       </c>
       <c r="C19" t="n">
-        <v>901.1720244147524</v>
+        <v>121.937</v>
       </c>
       <c r="D19" t="n">
         <v>2.75325e-07</v>
@@ -5368,11 +5155,10 @@
       <c r="X19" t="n">
         <v>-10835.83790072471</v>
       </c>
-      <c r="Y19" t="n">
-        <v>452.6053765604874</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>38423494.24429484</v>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA19" t="n">
         <v>4.396161957261621e-07</v>
@@ -5389,7 +5175,7 @@
         <v>117.485</v>
       </c>
       <c r="C20" t="n">
-        <v>871.2492314654334</v>
+        <v>401.6274929966042</v>
       </c>
       <c r="D20" t="n">
         <v>2.75103e-07</v>
@@ -5422,16 +5208,13 @@
         <v>-10237.4753925544</v>
       </c>
       <c r="Y20" t="n">
-        <v>447.8181885829125</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>49822100.56803484</v>
+        <v>92.34239744690119</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.366229156045198e-07</v>
+        <v>2.886620659427582e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9293218080570352</v>
+        <v>0.9310622965434137</v>
       </c>
     </row>
     <row r="21">
@@ -5442,7 +5225,7 @@
         <v>114.98</v>
       </c>
       <c r="C21" t="n">
-        <v>902.0613523425806</v>
+        <v>306.9741232165539</v>
       </c>
       <c r="D21" t="n">
         <v>2.75269e-07</v>
@@ -5475,16 +5258,13 @@
         <v>-10501.65173754466</v>
       </c>
       <c r="Y21" t="n">
-        <v>443.0544249987667</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>250687932.7284362</v>
+        <v>181.7282457107712</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.321799788876768e-07</v>
+        <v>3.429919517591435e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9309547576262238</v>
+        <v>0.9552977554214119</v>
       </c>
     </row>
     <row r="22">
@@ -5495,7 +5275,7 @@
         <v>112.792</v>
       </c>
       <c r="C22" t="n">
-        <v>878.6789707699892</v>
+        <v>310.1419070934699</v>
       </c>
       <c r="D22" t="n">
         <v>2.75223e-07</v>
@@ -5528,16 +5308,13 @@
         <v>-10356.46480867213</v>
       </c>
       <c r="Y22" t="n">
-        <v>438.2193279052158</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>135399575.902739</v>
+        <v>172.8387816395321</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.291012941134729e-07</v>
+        <v>3.277715613593074e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9320235453091141</v>
+        <v>0.9549502374897825</v>
       </c>
     </row>
   </sheetData>
@@ -5694,7 +5471,7 @@
         <v>333.346</v>
       </c>
       <c r="C2" t="n">
-        <v>1555.181868833714</v>
+        <v>578.5678548358134</v>
       </c>
       <c r="D2" t="n">
         <v>2.9838e-07</v>
@@ -5727,16 +5504,13 @@
         <v>-6345.806386151228</v>
       </c>
       <c r="Y2" t="n">
-        <v>548.8373652719168</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>192761399.6507388</v>
+        <v>129.5404227382165</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.92952917704346e-06</v>
+        <v>2.752691890701562e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5614386576330698</v>
+        <v>0.9089509374134485</v>
       </c>
     </row>
     <row r="3">
@@ -5747,7 +5521,7 @@
         <v>246.427</v>
       </c>
       <c r="C3" t="n">
-        <v>1055.265038374031</v>
+        <v>469.1602863593832</v>
       </c>
       <c r="D3" t="n">
         <v>3.01216e-07</v>
@@ -5780,16 +5554,13 @@
         <v>-8039.17587700782</v>
       </c>
       <c r="Y3" t="n">
-        <v>579.9562874628609</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>380073926.8092821</v>
+        <v>196.2577137493498</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.185401619888726e-06</v>
+        <v>4.895118534918534e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.7925344467128782</v>
+        <v>0.8932947541626418</v>
       </c>
     </row>
     <row r="4">
@@ -5800,7 +5571,7 @@
         <v>224.73</v>
       </c>
       <c r="C4" t="n">
-        <v>967.5632220182958</v>
+        <v>428.7269127352174</v>
       </c>
       <c r="D4" t="n">
         <v>2.962e-07</v>
@@ -5833,16 +5604,13 @@
         <v>-9287.798107413642</v>
       </c>
       <c r="Y4" t="n">
-        <v>570.6200555914047</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>141121040.1946451</v>
+        <v>222.5484472627522</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.598524766326485e-07</v>
+        <v>5.884409068468499e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8379822082664997</v>
+        <v>0.8926145807208605</v>
       </c>
     </row>
     <row r="5">
@@ -5853,7 +5621,7 @@
         <v>211.467</v>
       </c>
       <c r="C5" t="n">
-        <v>923.7861082613437</v>
+        <v>414.2276874315453</v>
       </c>
       <c r="D5" t="n">
         <v>2.92195e-07</v>
@@ -5886,16 +5654,13 @@
         <v>-9894.437174768706</v>
       </c>
       <c r="Y5" t="n">
-        <v>563.2548048657297</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>37285288.0460481</v>
+        <v>227.336574591186</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.420131769015894e-07</v>
+        <v>6.227687065461214e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8580603224351908</v>
+        <v>0.8933233448215717</v>
       </c>
     </row>
     <row r="6">
@@ -5906,7 +5671,7 @@
         <v>199.57</v>
       </c>
       <c r="C6" t="n">
-        <v>888.7175136904814</v>
+        <v>403.9310233145344</v>
       </c>
       <c r="D6" t="n">
         <v>2.88889e-07</v>
@@ -5939,16 +5704,13 @@
         <v>-9780.090674851996</v>
       </c>
       <c r="Y6" t="n">
-        <v>556.1471854430796</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>54022908.28903898</v>
+        <v>225.7402035929827</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.766352163401629e-07</v>
+        <v>5.617524787660488e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8702731380809851</v>
+        <v>0.9011702087224335</v>
       </c>
     </row>
     <row r="7">
@@ -5959,7 +5721,7 @@
         <v>197.137</v>
       </c>
       <c r="C7" t="n">
-        <v>953.8626890533504</v>
+        <v>393.9573425229594</v>
       </c>
       <c r="D7" t="n">
         <v>2.86417e-07</v>
@@ -5992,16 +5754,13 @@
         <v>-10961.2840643544</v>
       </c>
       <c r="Y7" t="n">
-        <v>548.8851700371114</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>48425086.81621543</v>
+        <v>225.4278562710366</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.298505710540088e-07</v>
+        <v>5.512850498834907e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.87980008112735</v>
+        <v>0.9054613445621891</v>
       </c>
     </row>
     <row r="8">
@@ -6012,7 +5771,7 @@
         <v>187.569</v>
       </c>
       <c r="C8" t="n">
-        <v>919.619126798712</v>
+        <v>384.9997379485735</v>
       </c>
       <c r="D8" t="n">
         <v>2.84804e-07</v>
@@ -6045,16 +5804,13 @@
         <v>-10639.29098362959</v>
       </c>
       <c r="Y8" t="n">
-        <v>541.7276949713749</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>41906008.05530718</v>
+        <v>225.0226299964925</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.98746115629063e-07</v>
+        <v>5.40549302269681e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8866153613256428</v>
+        <v>0.9087442796318773</v>
       </c>
     </row>
     <row r="9">
@@ -6065,7 +5821,7 @@
         <v>178.627</v>
       </c>
       <c r="C9" t="n">
-        <v>885.1289779863799</v>
+        <v>377.0755017315777</v>
       </c>
       <c r="D9" t="n">
         <v>2.83701e-07</v>
@@ -6098,16 +5854,13 @@
         <v>-10566.11853173201</v>
       </c>
       <c r="Y9" t="n">
-        <v>534.9589497520589</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>108692580.7518235</v>
+        <v>224.6408846589445</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.73714269171323e-07</v>
+        <v>5.334716100578858e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8924828407205273</v>
+        <v>0.9116388124302655</v>
       </c>
     </row>
     <row r="10">
@@ -6118,7 +5871,7 @@
         <v>175.395</v>
       </c>
       <c r="C10" t="n">
-        <v>922.0514999047031</v>
+        <v>369.5899231766363</v>
       </c>
       <c r="D10" t="n">
         <v>2.82732e-07</v>
@@ -6151,16 +5904,13 @@
         <v>-11034.01640970146</v>
       </c>
       <c r="Y10" t="n">
-        <v>528.7058654593757</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>52218997.73365314</v>
+        <v>224.0499415644786</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.552519750927198e-07</v>
+        <v>5.215604460265037e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.89692991190356</v>
+        <v>0.9148557328794468</v>
       </c>
     </row>
     <row r="11">
@@ -6171,7 +5921,7 @@
         <v>165.3759999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>841.6588621188024</v>
+        <v>362.9658745340622</v>
       </c>
       <c r="D11" t="n">
         <v>2.81897e-07</v>
@@ -6204,16 +5954,13 @@
         <v>-10313.1555306142</v>
       </c>
       <c r="Y11" t="n">
-        <v>522.8425911722518</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>33625030.64626577</v>
+        <v>223.3690154324789</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.399516033166096e-07</v>
+        <v>5.136756062638384e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9007305074242201</v>
+        <v>0.9174643970975015</v>
       </c>
     </row>
   </sheetData>
@@ -6370,7 +6117,7 @@
         <v>206.8460000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>1020.042582437527</v>
+        <v>433.5255090104182</v>
       </c>
       <c r="D2" t="n">
         <v>2.99723e-07</v>
@@ -6403,16 +6150,13 @@
         <v>-8225.623711085243</v>
       </c>
       <c r="Y2" t="n">
-        <v>547.3472225548547</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>397961733.3448045</v>
+        <v>183.8017755451615</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.274102823993408e-07</v>
+        <v>4.363272328077061e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8457666789407142</v>
+        <v>0.9057451061855287</v>
       </c>
     </row>
     <row r="3">
@@ -6423,7 +6167,7 @@
         <v>189.844</v>
       </c>
       <c r="C3" t="n">
-        <v>946.00764180644</v>
+        <v>383.2362705174775</v>
       </c>
       <c r="D3" t="n">
         <v>2.91984e-07</v>
@@ -6456,16 +6200,13 @@
         <v>-10121.95418918851</v>
       </c>
       <c r="Y3" t="n">
-        <v>537.8199450089054</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>74128569.15747638</v>
+        <v>224.1725549036041</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.527902110359519e-07</v>
+        <v>5.72981873705294e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8773862851911465</v>
+        <v>0.9034987611569407</v>
       </c>
     </row>
     <row r="4">
@@ -6476,7 +6217,7 @@
         <v>179.171</v>
       </c>
       <c r="C4" t="n">
-        <v>897.7283850584535</v>
+        <v>376.2720074335154</v>
       </c>
       <c r="D4" t="n">
         <v>2.89069e-07</v>
@@ -6509,16 +6250,13 @@
         <v>-10407.16551787421</v>
       </c>
       <c r="Y4" t="n">
-        <v>532.0826246452998</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>56612086.9927252</v>
+        <v>224.3294700644317</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.00545680042186e-07</v>
+        <v>5.600512184469581e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8884423940681052</v>
+        <v>0.9091628021028703</v>
       </c>
     </row>
     <row r="5">
@@ -6529,7 +6267,7 @@
         <v>173.399</v>
       </c>
       <c r="C5" t="n">
-        <v>892.0063199428704</v>
+        <v>367.962695775083</v>
       </c>
       <c r="D5" t="n">
         <v>2.87552e-07</v>
@@ -6562,16 +6300,13 @@
         <v>-10690.68976420769</v>
       </c>
       <c r="Y5" t="n">
-        <v>526.7603610991472</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>15084464.71567873</v>
+        <v>224.5403465226998</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.745483423175343e-07</v>
+        <v>5.430553223556029e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8943638664328679</v>
+        <v>0.9127039234843098</v>
       </c>
     </row>
     <row r="6">
@@ -6582,7 +6317,7 @@
         <v>168.251</v>
       </c>
       <c r="C6" t="n">
-        <v>905.5730919315628</v>
+        <v>168.251</v>
       </c>
       <c r="D6" t="n">
         <v>2.8644e-07</v>
@@ -6614,11 +6349,10 @@
       <c r="X6" t="n">
         <v>-10786.67267908514</v>
       </c>
-      <c r="Y6" t="n">
-        <v>520.894097614307</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>58145772.69805376</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>5.551725047422679e-07</v>
@@ -6635,7 +6369,7 @@
         <v>160.248</v>
       </c>
       <c r="C7" t="n">
-        <v>856.2388532587383</v>
+        <v>353.1970949184102</v>
       </c>
       <c r="D7" t="n">
         <v>2.8567e-07</v>
@@ -6668,16 +6402,13 @@
         <v>-10288.05260605998</v>
       </c>
       <c r="Y7" t="n">
-        <v>514.6214062575486</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>29230952.67993838</v>
+        <v>223.1471449318606</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.399810808069631e-07</v>
+        <v>5.061700846429857e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9027972753956297</v>
+        <v>0.9198830901963042</v>
       </c>
     </row>
     <row r="8">
@@ -6688,7 +6419,7 @@
         <v>159.213</v>
       </c>
       <c r="C8" t="n">
-        <v>918.8389598953801</v>
+        <v>346.6687840778175</v>
       </c>
       <c r="D8" t="n">
         <v>2.8523e-07</v>
@@ -6721,16 +6452,13 @@
         <v>-11188.64052107184</v>
       </c>
       <c r="Y8" t="n">
-        <v>508.4598098639956</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>75423441.15448593</v>
+        <v>223.067920090747</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.25718116813532e-07</v>
+        <v>5.102059988750954e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.906611705339431</v>
+        <v>0.9223770617574483</v>
       </c>
     </row>
     <row r="9">
@@ -6741,7 +6469,7 @@
         <v>152.17</v>
       </c>
       <c r="C9" t="n">
-        <v>867.3743971075091</v>
+        <v>152.17</v>
       </c>
       <c r="D9" t="n">
         <v>2.84916e-07</v>
@@ -6773,11 +6501,10 @@
       <c r="X9" t="n">
         <v>-10581.55589589904</v>
       </c>
-      <c r="Y9" t="n">
-        <v>502.6282180827429</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>423603549.2168085</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>5.164684199479608e-07</v>
@@ -6794,7 +6521,7 @@
         <v>151.238</v>
       </c>
       <c r="C10" t="n">
-        <v>907.0553502733042</v>
+        <v>151.238</v>
       </c>
       <c r="D10" t="n">
         <v>2.84593e-07</v>
@@ -6826,11 +6553,10 @@
       <c r="X10" t="n">
         <v>-11217.45765620496</v>
       </c>
-      <c r="Y10" t="n">
-        <v>497.0874087230442</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>38368921.81256433</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>5.057314874306787e-07</v>
@@ -6847,7 +6573,7 @@
         <v>144.625</v>
       </c>
       <c r="C11" t="n">
-        <v>869.9435474858964</v>
+        <v>144.625</v>
       </c>
       <c r="D11" t="n">
         <v>2.84275e-07</v>
@@ -6879,11 +6605,10 @@
       <c r="X11" t="n">
         <v>-10739.29793640912</v>
       </c>
-      <c r="Y11" t="n">
-        <v>491.7177670637182</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>75870617.73092788</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>4.976821138541326e-07</v>
@@ -6900,7 +6625,7 @@
         <v>140.51</v>
       </c>
       <c r="C12" t="n">
-        <v>843.7806351905666</v>
+        <v>323.7661583616031</v>
       </c>
       <c r="D12" t="n">
         <v>2.84088e-07</v>
@@ -6933,16 +6658,13 @@
         <v>-10565.59914088861</v>
       </c>
       <c r="Y12" t="n">
-        <v>486.5325252174118</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>204753851.1892565</v>
+        <v>218.7294074395232</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.914478213336615e-07</v>
+        <v>4.70749553748921e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.9162589858672073</v>
+        <v>0.9335005213913257</v>
       </c>
     </row>
     <row r="13">
@@ -6953,7 +6675,7 @@
         <v>139.208</v>
       </c>
       <c r="C13" t="n">
-        <v>873.2407912253542</v>
+        <v>318.5545812181568</v>
       </c>
       <c r="D13" t="n">
         <v>2.83809e-07</v>
@@ -6986,16 +6708,13 @@
         <v>-10893.42307022485</v>
       </c>
       <c r="Y13" t="n">
-        <v>481.5806828529448</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>63532016.46220312</v>
+        <v>217.7929125747451</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.847425979721743e-07</v>
+        <v>4.593761652374049e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.91820321490492</v>
+        <v>0.9365858272447336</v>
       </c>
     </row>
     <row r="14">
@@ -7006,7 +6725,7 @@
         <v>134.528</v>
       </c>
       <c r="C14" t="n">
-        <v>864.3852519757155</v>
+        <v>134.528</v>
       </c>
       <c r="D14" t="n">
         <v>2.83662e-07</v>
@@ -7038,11 +6757,10 @@
       <c r="X14" t="n">
         <v>-10716.67217080022</v>
       </c>
-      <c r="Y14" t="n">
-        <v>476.6142989058284</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>34719040.07934395</v>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA14" t="n">
         <v>4.789190806279649e-07</v>
@@ -7059,7 +6777,7 @@
         <v>131.579</v>
       </c>
       <c r="C15" t="n">
-        <v>869.8770254076319</v>
+        <v>308.8812359463857</v>
       </c>
       <c r="D15" t="n">
         <v>2.83538e-07</v>
@@ -7092,16 +6810,13 @@
         <v>-10846.59767874084</v>
       </c>
       <c r="Y15" t="n">
-        <v>471.7503690363056</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>95155789.09695755</v>
+        <v>215.5840804716229</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.721850160619705e-07</v>
+        <v>4.438559627178148e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9220384885666901</v>
+        <v>0.9415508271495284</v>
       </c>
     </row>
     <row r="16">
@@ -7112,7 +6827,7 @@
         <v>128.748</v>
       </c>
       <c r="C16" t="n">
-        <v>865.7222437430219</v>
+        <v>304.0693577357669</v>
       </c>
       <c r="D16" t="n">
         <v>2.83431e-07</v>
@@ -7145,16 +6860,13 @@
         <v>-10754.07584243441</v>
       </c>
       <c r="Y16" t="n">
-        <v>466.858430803799</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>31668267.24169507</v>
+        <v>214.3857848965749</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.674301422127175e-07</v>
+        <v>4.336529129909651e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9235213414672513</v>
+        <v>0.9443990758156776</v>
       </c>
     </row>
     <row r="17">
@@ -7165,7 +6877,7 @@
         <v>127.2329999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>881.6788881790243</v>
+        <v>302.0397626920189</v>
       </c>
       <c r="D17" t="n">
         <v>2.83203e-07</v>
@@ -7198,16 +6910,13 @@
         <v>-10933.5715616793</v>
       </c>
       <c r="Y17" t="n">
-        <v>462.0786899282044</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>84156379.74575013</v>
+        <v>209.9644354777376</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.623054450161197e-07</v>
+        <v>4.125345061924951e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9250786051867066</v>
+        <v>0.946756154454034</v>
       </c>
     </row>
     <row r="18">
@@ -7218,7 +6927,7 @@
         <v>122.799</v>
       </c>
       <c r="C18" t="n">
-        <v>872.450998536572</v>
+        <v>298.4923658894012</v>
       </c>
       <c r="D18" t="n">
         <v>2.82888e-07</v>
@@ -7251,16 +6960,13 @@
         <v>-10585.00810576945</v>
       </c>
       <c r="Y18" t="n">
-        <v>457.3176790141066</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>71593270.90499125</v>
+        <v>207.4444801296465</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.578859941137327e-07</v>
+        <v>4.068282755455601e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9263837980573263</v>
+        <v>0.9489314854753005</v>
       </c>
     </row>
     <row r="19">
@@ -7271,7 +6977,7 @@
         <v>121.292</v>
       </c>
       <c r="C19" t="n">
-        <v>886.2631420399176</v>
+        <v>121.292</v>
       </c>
       <c r="D19" t="n">
         <v>2.82876e-07</v>
@@ -7303,11 +7009,10 @@
       <c r="X19" t="n">
         <v>-10822.60466248579</v>
       </c>
-      <c r="Y19" t="n">
-        <v>452.6051858130465</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>127173917.7358479</v>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA19" t="n">
         <v>4.531406817193074e-07</v>
@@ -7324,7 +7029,7 @@
         <v>119.8219999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>905.228121659562</v>
+        <v>400.597070547922</v>
       </c>
       <c r="D20" t="n">
         <v>2.82837e-07</v>
@@ -7357,16 +7062,13 @@
         <v>-11034.11707855003</v>
       </c>
       <c r="Y20" t="n">
-        <v>447.888471151404</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>491751706.2692647</v>
+        <v>93.31544441766157</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.488572168994832e-07</v>
+        <v>3.019873317793045e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9293801009791647</v>
+        <v>0.9277629049986549</v>
       </c>
     </row>
     <row r="21">
@@ -7377,7 +7079,7 @@
         <v>116.877</v>
       </c>
       <c r="C21" t="n">
-        <v>868.88449033617</v>
+        <v>420.5759310009191</v>
       </c>
       <c r="D21" t="n">
         <v>2.82964e-07</v>
@@ -7410,16 +7112,13 @@
         <v>-10710.44611308531</v>
       </c>
       <c r="Y21" t="n">
-        <v>443.1211373369848</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>363911524.2865228</v>
+        <v>105.8872094614297</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.467858562237523e-07</v>
+        <v>2.113717813914128e-08</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9301653671972997</v>
+        <v>0.7943942299425691</v>
       </c>
     </row>
     <row r="22">
@@ -7430,7 +7129,7 @@
         <v>114.616</v>
       </c>
       <c r="C22" t="n">
-        <v>911.1123925756573</v>
+        <v>306.5846502795474</v>
       </c>
       <c r="D22" t="n">
         <v>2.82777e-07</v>
@@ -7463,16 +7162,13 @@
         <v>-11038.31622551207</v>
       </c>
       <c r="Y22" t="n">
-        <v>438.4015632563413</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>960195021.2010366</v>
+        <v>177.4192564621077</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.417689184530119e-07</v>
+        <v>3.557423419290632e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9317673639640885</v>
+        <v>0.9521503995626657</v>
       </c>
     </row>
   </sheetData>
@@ -7629,7 +7325,7 @@
         <v>298.57</v>
       </c>
       <c r="C2" t="n">
-        <v>1414.828673842266</v>
+        <v>591.3445694045899</v>
       </c>
       <c r="D2" t="n">
         <v>3.05948e-07</v>
@@ -7662,16 +7358,13 @@
         <v>-6335.222807262978</v>
       </c>
       <c r="Y2" t="n">
-        <v>569.5051116101438</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>116659959.6340644</v>
+        <v>99.09760504330499</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.515485762593364e-06</v>
+        <v>3.046817493610304e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.6372204845117558</v>
+        <v>0.8971706363587245</v>
       </c>
     </row>
     <row r="3">
@@ -7682,7 +7375,7 @@
         <v>235.207</v>
       </c>
       <c r="C3" t="n">
-        <v>1026.015105716084</v>
+        <v>452.673895869564</v>
       </c>
       <c r="D3" t="n">
         <v>3.01741e-07</v>
@@ -7715,16 +7408,13 @@
         <v>-8134.556070058749</v>
       </c>
       <c r="Y3" t="n">
-        <v>575.3641575183071</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>38379155.83272927</v>
+        <v>206.2441417062277</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.067160613020955e-06</v>
+        <v>5.485460148708857e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8085534560056014</v>
+        <v>0.8897331059804273</v>
       </c>
     </row>
     <row r="4">
@@ -7735,7 +7425,7 @@
         <v>217.785</v>
       </c>
       <c r="C4" t="n">
-        <v>972.180460540835</v>
+        <v>423.8220975317315</v>
       </c>
       <c r="D4" t="n">
         <v>2.95421e-07</v>
@@ -7768,16 +7458,13 @@
         <v>-9593.414924072269</v>
       </c>
       <c r="Y4" t="n">
-        <v>566.8042478641837</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>145897571.268115</v>
+        <v>222.7844091727049</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.073620234051986e-07</v>
+        <v>6.098974585970349e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8470916785309134</v>
+        <v>0.8921614361670331</v>
       </c>
     </row>
     <row r="5">
@@ -7788,7 +7475,7 @@
         <v>206.568</v>
       </c>
       <c r="C5" t="n">
-        <v>934.6983443390566</v>
+        <v>409.7154537661993</v>
       </c>
       <c r="D5" t="n">
         <v>2.91133e-07</v>
@@ -7821,16 +7508,13 @@
         <v>-10061.96587485877</v>
       </c>
       <c r="Y5" t="n">
-        <v>560.3672242138649</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>176992424.1180134</v>
+        <v>225.9412369067173</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.099148494990775e-07</v>
+        <v>5.816056833406822e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8642478143366645</v>
+        <v>0.8974932026045107</v>
       </c>
     </row>
     <row r="6">
@@ -7841,7 +7525,7 @@
         <v>197.877</v>
       </c>
       <c r="C6" t="n">
-        <v>912.3562816934183</v>
+        <v>400.9142593384648</v>
       </c>
       <c r="D6" t="n">
         <v>2.88235e-07</v>
@@ -7874,16 +7558,13 @@
         <v>-10519.63626502813</v>
       </c>
       <c r="Y6" t="n">
-        <v>554.4775658602906</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>88895794.08971889</v>
+        <v>226.1222764325431</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.514220746783614e-07</v>
+        <v>5.73012280099023e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.875691921496806</v>
+        <v>0.8997859069910882</v>
       </c>
     </row>
     <row r="7">
@@ -7894,7 +7575,7 @@
         <v>187.9519999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>874.2293425976636</v>
+        <v>391.6734146121671</v>
       </c>
       <c r="D7" t="n">
         <v>2.86237e-07</v>
@@ -7927,16 +7608,13 @@
         <v>-10352.69817113405</v>
       </c>
       <c r="Y7" t="n">
-        <v>548.2570902789527</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>99909522.09402075</v>
+        <v>226.6803722748872</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.150168519841109e-07</v>
+        <v>5.543645227321155e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.883332063904636</v>
+        <v>0.9040738478503463</v>
       </c>
     </row>
     <row r="8">
@@ -7947,7 +7625,7 @@
         <v>182.118</v>
       </c>
       <c r="C8" t="n">
-        <v>876.2319599699657</v>
+        <v>382.6652067944307</v>
       </c>
       <c r="D8" t="n">
         <v>2.84878e-07</v>
@@ -7980,16 +7658,13 @@
         <v>-10443.75143186782</v>
       </c>
       <c r="Y8" t="n">
-        <v>541.2648713405404</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>92491285.65868892</v>
+        <v>226.3724257739932</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.88622311340895e-07</v>
+        <v>5.392980771122276e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8892723593308981</v>
+        <v>0.9077019597890748</v>
       </c>
     </row>
     <row r="9">
@@ -8000,7 +7675,7 @@
         <v>175.5549999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>870.2278960003052</v>
+        <v>373.8592467998699</v>
       </c>
       <c r="D9" t="n">
         <v>2.83987e-07</v>
@@ -8033,16 +7708,13 @@
         <v>-10521.2872320515</v>
       </c>
       <c r="Y9" t="n">
-        <v>534.0357262020848</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>166929280.4379201</v>
+        <v>225.7614375602344</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.667962330145158e-07</v>
+        <v>5.260485955412689e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8945255653987479</v>
+        <v>0.9111074146666227</v>
       </c>
     </row>
     <row r="10">
@@ -8053,7 +7725,7 @@
         <v>170.85</v>
       </c>
       <c r="C10" t="n">
-        <v>873.4495812334183</v>
+        <v>365.8653406182397</v>
       </c>
       <c r="D10" t="n">
         <v>2.83373e-07</v>
@@ -8086,16 +7758,13 @@
         <v>-10874.55213705548</v>
       </c>
       <c r="Y10" t="n">
-        <v>527.2528466196694</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>74775660.93545045</v>
+        <v>225.1407596718486</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.473545957582736e-07</v>
+        <v>5.17210856704766e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8994824292256811</v>
+        <v>0.9140146878717142</v>
       </c>
     </row>
     <row r="11">
@@ -8106,7 +7775,7 @@
         <v>165.505</v>
       </c>
       <c r="C11" t="n">
-        <v>887.1766248020296</v>
+        <v>358.6662503332986</v>
       </c>
       <c r="D11" t="n">
         <v>2.82702e-07</v>
@@ -8139,16 +7808,13 @@
         <v>-11013.8840800332</v>
       </c>
       <c r="Y11" t="n">
-        <v>520.7736857570653</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>26706286.64102941</v>
+        <v>224.6027954739139</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.332004591149701e-07</v>
+        <v>5.144059695604094e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.903122309726817</v>
+        <v>0.9182148164150247</v>
       </c>
     </row>
   </sheetData>
@@ -8305,7 +7971,7 @@
         <v>198.355</v>
       </c>
       <c r="C2" t="n">
-        <v>972.6606102753591</v>
+        <v>198.355</v>
       </c>
       <c r="D2" t="n">
         <v>2.91342e-07</v>
@@ -8337,11 +8003,10 @@
       <c r="X2" t="n">
         <v>-9158.239803482922</v>
       </c>
-      <c r="Y2" t="n">
-        <v>547.9664443253914</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>93215787.65588757</v>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA2" t="n">
         <v>6.939635490601613e-07</v>
@@ -8358,7 +8023,7 @@
         <v>184.845</v>
       </c>
       <c r="C3" t="n">
-        <v>921.0359198788776</v>
+        <v>379.7263725190534</v>
       </c>
       <c r="D3" t="n">
         <v>2.87842e-07</v>
@@ -8391,16 +8056,13 @@
         <v>-10509.76117156017</v>
       </c>
       <c r="Y3" t="n">
-        <v>537.4991265785268</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>57862755.58246504</v>
+        <v>225.9257667445715</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.065691900142197e-07</v>
+        <v>5.405965320721273e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8862993888904903</v>
+        <v>0.9098658065313792</v>
       </c>
     </row>
     <row r="4">
@@ -8411,7 +8073,7 @@
         <v>175.218</v>
       </c>
       <c r="C4" t="n">
-        <v>891.7956344542929</v>
+        <v>371.2068443960413</v>
       </c>
       <c r="D4" t="n">
         <v>2.86379e-07</v>
@@ -8444,16 +8106,13 @@
         <v>-10608.34191552096</v>
       </c>
       <c r="Y4" t="n">
-        <v>530.7109260023144</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>105488576.7142147</v>
+        <v>225.1043776083819</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.758173367481633e-07</v>
+        <v>5.371318254072363e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8934160988964353</v>
+        <v>0.9122982323142322</v>
       </c>
     </row>
     <row r="5">
@@ -8464,7 +8123,7 @@
         <v>167.609</v>
       </c>
       <c r="C5" t="n">
-        <v>869.3360857037379</v>
+        <v>363.2427551640836</v>
       </c>
       <c r="D5" t="n">
         <v>2.85662e-07</v>
@@ -8497,16 +8156,13 @@
         <v>-10474.32923802869</v>
       </c>
       <c r="Y5" t="n">
-        <v>524.4008169650932</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>47287926.86292861</v>
+        <v>224.8531465868462</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.56448183668114e-07</v>
+        <v>5.254935640683609e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8982269507417618</v>
+        <v>0.9155919091414749</v>
       </c>
     </row>
     <row r="6">
@@ -8517,7 +8173,7 @@
         <v>163.3939999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>871.13753525448</v>
+        <v>355.3557599833596</v>
       </c>
       <c r="D6" t="n">
         <v>2.85421e-07</v>
@@ -8550,16 +8206,13 @@
         <v>-10643.99865554016</v>
       </c>
       <c r="Y6" t="n">
-        <v>518.024247500451</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>428383340.7938696</v>
+        <v>224.4653376076632</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.40652754576415e-07</v>
+        <v>5.112114263717042e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.902444843648141</v>
+        <v>0.9192913605976656</v>
       </c>
     </row>
     <row r="7">
@@ -8570,7 +8223,7 @@
         <v>161.792</v>
       </c>
       <c r="C7" t="n">
-        <v>924.1471734003914</v>
+        <v>348.8255784391873</v>
       </c>
       <c r="D7" t="n">
         <v>2.85006e-07</v>
@@ -8603,16 +8256,13 @@
         <v>-11313.89193898644</v>
       </c>
       <c r="Y7" t="n">
-        <v>511.5433413446364</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>92248114.62733148</v>
+        <v>223.4900612320545</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.29188017937728e-07</v>
+        <v>5.01602622703969e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9055003374462205</v>
+        <v>0.9216495253069632</v>
       </c>
     </row>
     <row r="8">
@@ -8623,7 +8273,7 @@
         <v>153.253</v>
       </c>
       <c r="C8" t="n">
-        <v>876.600330661738</v>
+        <v>342.8256139337717</v>
       </c>
       <c r="D8" t="n">
         <v>2.84715e-07</v>
@@ -8656,16 +8306,13 @@
         <v>-10727.10461339592</v>
       </c>
       <c r="Y8" t="n">
-        <v>505.6986830688899</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>139970948.6951483</v>
+        <v>222.2944515879786</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.177933248446756e-07</v>
+        <v>4.956725766187196e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9086471723769123</v>
+        <v>0.9237450267677449</v>
       </c>
     </row>
     <row r="9">
@@ -8676,7 +8323,7 @@
         <v>147.508</v>
       </c>
       <c r="C9" t="n">
-        <v>843.8766455458048</v>
+        <v>147.508</v>
       </c>
       <c r="D9" t="n">
         <v>2.84692e-07</v>
@@ -8708,11 +8355,10 @@
       <c r="X9" t="n">
         <v>-10454.02941256753</v>
       </c>
-      <c r="Y9" t="n">
-        <v>500.4768936297417</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>108357798.1978788</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>5.092375615205946e-07</v>
@@ -8729,7 +8375,7 @@
         <v>145.554</v>
       </c>
       <c r="C10" t="n">
-        <v>876.2998409685026</v>
+        <v>145.554</v>
       </c>
       <c r="D10" t="n">
         <v>2.84423e-07</v>
@@ -8761,11 +8407,10 @@
       <c r="X10" t="n">
         <v>-10752.44736859063</v>
       </c>
-      <c r="Y10" t="n">
-        <v>495.8316412890505</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>49117446.11016729</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>5.016604731941381e-07</v>
@@ -8782,7 +8427,7 @@
         <v>142.062</v>
       </c>
       <c r="C11" t="n">
-        <v>858.802129951642</v>
+        <v>328.2005576305594</v>
       </c>
       <c r="D11" t="n">
         <v>2.84401e-07</v>
@@ -8815,16 +8460,13 @@
         <v>-10717.79679447714</v>
       </c>
       <c r="Y11" t="n">
-        <v>491.507998089093</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>69117573.21617594</v>
+        <v>219.4861677309863</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.952188704965358e-07</v>
+        <v>4.770341220021895e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9152588834803289</v>
+        <v>0.9296861351306988</v>
       </c>
     </row>
     <row r="12">
@@ -8835,7 +8477,7 @@
         <v>141.682</v>
       </c>
       <c r="C12" t="n">
-        <v>905.9290830953911</v>
+        <v>323.6408975605528</v>
       </c>
       <c r="D12" t="n">
         <v>2.84125e-07</v>
@@ -8868,16 +8510,13 @@
         <v>-11401.31553036194</v>
       </c>
       <c r="Y12" t="n">
-        <v>487.2697428654787</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>46273212.63543476</v>
+        <v>218.8377166583437</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.875897573513626e-07</v>
+        <v>4.697390063968145e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.9174627818825303</v>
+        <v>0.9319859382612157</v>
       </c>
     </row>
     <row r="13">
@@ -8888,7 +8527,7 @@
         <v>136.251</v>
       </c>
       <c r="C13" t="n">
-        <v>847.8446446182267</v>
+        <v>319.4184466650023</v>
       </c>
       <c r="D13" t="n">
         <v>2.84049e-07</v>
@@ -8921,16 +8560,13 @@
         <v>-10647.36491796495</v>
       </c>
       <c r="Y13" t="n">
-        <v>483.0456321632749</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>24849814.10408894</v>
+        <v>218.9141869327749</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.829111383721641e-07</v>
+        <v>4.743916008662601e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.9189007219389907</v>
+        <v>0.9341498516288834</v>
       </c>
     </row>
     <row r="14">
@@ -8941,7 +8577,7 @@
         <v>134.869</v>
       </c>
       <c r="C14" t="n">
-        <v>851.1279152663077</v>
+        <v>315.0587701301097</v>
       </c>
       <c r="D14" t="n">
         <v>2.83889e-07</v>
@@ -8974,16 +8610,13 @@
         <v>-10752.26521999932</v>
       </c>
       <c r="Y14" t="n">
-        <v>478.8588952335851</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>266380733.539689</v>
+        <v>217.9162580579998</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.789943805447928e-07</v>
+        <v>4.598267917072487e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.9200706906958396</v>
+        <v>0.9374451568636467</v>
       </c>
     </row>
     <row r="15">
@@ -8994,7 +8627,7 @@
         <v>132.0050000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>869.3548667041561</v>
+        <v>310.5913054700192</v>
       </c>
       <c r="D15" t="n">
         <v>2.83738e-07</v>
@@ -9027,16 +8660,13 @@
         <v>-10888.25431383424</v>
       </c>
       <c r="Y15" t="n">
-        <v>474.4818621580082</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>40832017.37799203</v>
+        <v>217.1932346193272</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.739697264837431e-07</v>
+        <v>4.55868367859011e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9215977562384815</v>
+        <v>0.9392241290801431</v>
       </c>
     </row>
     <row r="16">
@@ -9047,7 +8677,7 @@
         <v>128.112</v>
       </c>
       <c r="C16" t="n">
-        <v>837.6940219539747</v>
+        <v>305.890168013526</v>
       </c>
       <c r="D16" t="n">
         <v>2.83853e-07</v>
@@ -9080,16 +8710,13 @@
         <v>-10537.92701837069</v>
       </c>
       <c r="Y16" t="n">
-        <v>470.0625771674634</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>21239918.33952826</v>
+        <v>216.4729781121437</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.690785734777748e-07</v>
+        <v>4.468934412145015e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9232297164426132</v>
+        <v>0.9418916198503124</v>
       </c>
     </row>
     <row r="17">
@@ -9100,7 +8727,7 @@
         <v>127.595</v>
       </c>
       <c r="C17" t="n">
-        <v>856.8966934918191</v>
+        <v>127.595</v>
       </c>
       <c r="D17" t="n">
         <v>2.83517e-07</v>
@@ -9132,11 +8759,10 @@
       <c r="X17" t="n">
         <v>-10935.07456580674</v>
       </c>
-      <c r="Y17" t="n">
-        <v>465.4910873318984</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>34362732.61023357</v>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA17" t="n">
         <v>4.626030484468354e-07</v>
@@ -9153,7 +8779,7 @@
         <v>122.673</v>
       </c>
       <c r="C18" t="n">
-        <v>831.2265891111224</v>
+        <v>298.5082870286025</v>
       </c>
       <c r="D18" t="n">
         <v>2.83744e-07</v>
@@ -9186,16 +8812,13 @@
         <v>-10590.59131400182</v>
       </c>
       <c r="Y18" t="n">
-        <v>460.6489042436971</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>43335205.01146992</v>
+        <v>211.100965513597</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.601242245427078e-07</v>
+        <v>4.157067905983703e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9261112268002031</v>
+        <v>0.9474975910073822</v>
       </c>
     </row>
     <row r="19">
@@ -9206,7 +8829,7 @@
         <v>120.7</v>
       </c>
       <c r="C19" t="n">
-        <v>846.5339455258571</v>
+        <v>294.0041995172137</v>
       </c>
       <c r="D19" t="n">
         <v>2.83754e-07</v>
@@ -9239,16 +8862,13 @@
         <v>-10635.70698782171</v>
       </c>
       <c r="Y19" t="n">
-        <v>455.8594330283174</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>256573807.4067802</v>
+        <v>209.9122453691693</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.554384756374948e-07</v>
+        <v>4.028770618423885e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.9276727639520341</v>
+        <v>0.9498389410734966</v>
       </c>
     </row>
     <row r="20">
@@ -9259,7 +8879,7 @@
         <v>118.272</v>
       </c>
       <c r="C20" t="n">
-        <v>872.5719907046836</v>
+        <v>289.1025532934245</v>
       </c>
       <c r="D20" t="n">
         <v>2.83824e-07</v>
@@ -9292,16 +8912,13 @@
         <v>-10879.13431316853</v>
       </c>
       <c r="Y20" t="n">
-        <v>450.9635551348287</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>988076045.3561549</v>
+        <v>209.5218299406621</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.50762229766592e-07</v>
+        <v>3.996372669484974e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9292712810907091</v>
+        <v>0.9533250876828538</v>
       </c>
     </row>
     <row r="21">
@@ -9312,7 +8929,7 @@
         <v>114.862</v>
       </c>
       <c r="C21" t="n">
-        <v>859.9432983828518</v>
+        <v>398.8484182438733</v>
       </c>
       <c r="D21" t="n">
         <v>2.83751e-07</v>
@@ -9345,16 +8962,13 @@
         <v>-10495.12215438899</v>
       </c>
       <c r="Y21" t="n">
-        <v>445.9830181602341</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>488326387.5058805</v>
+        <v>92.28905088462834</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.470452847620055e-07</v>
+        <v>2.923384683206203e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9305060312548025</v>
+        <v>0.9308303463748886</v>
       </c>
     </row>
     <row r="22">
@@ -9365,7 +8979,7 @@
         <v>112.232</v>
       </c>
       <c r="C22" t="n">
-        <v>845.0421699677898</v>
+        <v>112.232</v>
       </c>
       <c r="D22" t="n">
         <v>2.83923e-07</v>
@@ -9397,11 +9011,10 @@
       <c r="X22" t="n">
         <v>-10645.46534025562</v>
       </c>
-      <c r="Y22" t="n">
-        <v>440.9473525323475</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1206183583.512786</v>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA22" t="n">
         <v>4.441706051422483e-07</v>
@@ -9564,7 +9177,7 @@
         <v>209.369</v>
       </c>
       <c r="C2" t="n">
-        <v>963.3500395621181</v>
+        <v>574.5803265931189</v>
       </c>
       <c r="D2" t="n">
         <v>3.03843e-07</v>
@@ -9597,16 +9210,13 @@
         <v>-6824.026098839277</v>
       </c>
       <c r="Y2" t="n">
-        <v>542.5417400869246</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>31871926.16182702</v>
+        <v>39.6601135786066</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.934221897037078e-07</v>
+        <v>3.347901253224929e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8205913635682168</v>
+        <v>0.8858208654653857</v>
       </c>
     </row>
     <row r="3">
@@ -9617,7 +9227,7 @@
         <v>194.602</v>
       </c>
       <c r="C3" t="n">
-        <v>920.803017745957</v>
+        <v>387.4963126640399</v>
       </c>
       <c r="D3" t="n">
         <v>2.91101e-07</v>
@@ -9650,16 +9260,13 @@
         <v>-9346.52021162882</v>
       </c>
       <c r="Y3" t="n">
-        <v>534.5275004114219</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>54168483.1330822</v>
+        <v>217.0819353835893</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.836591868196212e-07</v>
+        <v>5.282723768888432e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8699732645591437</v>
+        <v>0.9097499209981879</v>
       </c>
     </row>
     <row r="4">
@@ -9670,7 +9277,7 @@
         <v>184.617</v>
       </c>
       <c r="C4" t="n">
-        <v>883.9439570194403</v>
+        <v>184.617</v>
       </c>
       <c r="D4" t="n">
         <v>2.87153e-07</v>
@@ -9702,11 +9309,10 @@
       <c r="X4" t="n">
         <v>-10130.08320452879</v>
       </c>
-      <c r="Y4" t="n">
-        <v>527.5934801188311</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>72966020.88517547</v>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA4" t="n">
         <v>6.103850501617336e-07</v>
@@ -9723,7 +9329,7 @@
         <v>174.845</v>
       </c>
       <c r="C5" t="n">
-        <v>849.4137613896729</v>
+        <v>366.0760664025915</v>
       </c>
       <c r="D5" t="n">
         <v>2.84839e-07</v>
@@ -9756,16 +9362,13 @@
         <v>-10076.72515870641</v>
       </c>
       <c r="Y5" t="n">
-        <v>520.8682801464658</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>114785839.3222648</v>
+        <v>218.7876279244695</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.721278687584216e-07</v>
+        <v>5.009165779828453e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8935185642558439</v>
+        <v>0.9164201305217835</v>
       </c>
     </row>
     <row r="6">
@@ -9776,7 +9379,7 @@
         <v>168.8989999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>854.1073843362993</v>
+        <v>356.8724205711279</v>
       </c>
       <c r="D6" t="n">
         <v>2.83502e-07</v>
@@ -9809,16 +9412,13 @@
         <v>-10335.5440924935</v>
       </c>
       <c r="Y6" t="n">
-        <v>513.7502163522338</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>38077614.66728316</v>
+        <v>218.6438206121837</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.474057726749312e-07</v>
+        <v>4.860581557300666e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8995070606125547</v>
+        <v>0.9205710092541812</v>
       </c>
     </row>
     <row r="7">
@@ -9829,7 +9429,7 @@
         <v>161.246</v>
       </c>
       <c r="C7" t="n">
-        <v>852.9248458446624</v>
+        <v>348.2669714503894</v>
       </c>
       <c r="D7" t="n">
         <v>2.82778e-07</v>
@@ -9862,16 +9462,13 @@
         <v>-10308.8556564917</v>
       </c>
       <c r="Y7" t="n">
-        <v>506.1801091238793</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>50003174.50793667</v>
+        <v>218.6758077556061</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.289251399962977e-07</v>
+        <v>4.802459047325364e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9043317162757228</v>
+        <v>0.9257154399671497</v>
       </c>
     </row>
     <row r="8">
@@ -9882,7 +9479,7 @@
         <v>157.234</v>
       </c>
       <c r="C8" t="n">
-        <v>872.3296546226109</v>
+        <v>340.0458625962893</v>
       </c>
       <c r="D8" t="n">
         <v>2.82205e-07</v>
@@ -9915,16 +9512,13 @@
         <v>-10751.88147196908</v>
       </c>
       <c r="Y8" t="n">
-        <v>498.7623392797444</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>275023896.081173</v>
+        <v>217.604525744702</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.13280953960211e-07</v>
+        <v>4.69202455704327e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9085852952268905</v>
+        <v>0.9292221959914925</v>
       </c>
     </row>
     <row r="9">
@@ -9935,7 +9529,7 @@
         <v>150.322</v>
       </c>
       <c r="C9" t="n">
-        <v>841.1688802713625</v>
+        <v>150.322</v>
       </c>
       <c r="D9" t="n">
         <v>2.81724e-07</v>
@@ -9967,11 +9561,10 @@
       <c r="X9" t="n">
         <v>-10547.3170095587</v>
       </c>
-      <c r="Y9" t="n">
-        <v>491.8533849089092</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>36139828.88406774</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>5.003821300762556e-07</v>
@@ -9988,7 +9581,7 @@
         <v>144.708</v>
       </c>
       <c r="C10" t="n">
-        <v>825.3861321747046</v>
+        <v>326.3042653248374</v>
       </c>
       <c r="D10" t="n">
         <v>2.81539e-07</v>
@@ -10021,16 +9614,13 @@
         <v>-10459.66993411818</v>
       </c>
       <c r="Y10" t="n">
-        <v>485.409008110134</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>233911311.9730988</v>
+        <v>214.5641141069835</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.900493783458515e-07</v>
+        <v>4.455957469018542e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9152618739857541</v>
+        <v>0.9353972417960523</v>
       </c>
     </row>
     <row r="11">
@@ -10041,7 +9631,7 @@
         <v>143.558</v>
       </c>
       <c r="C11" t="n">
-        <v>865.4519374853718</v>
+        <v>319.7652444095384</v>
       </c>
       <c r="D11" t="n">
         <v>2.81199e-07</v>
@@ -10074,16 +9664,13 @@
         <v>-11019.94505846481</v>
       </c>
       <c r="Y11" t="n">
-        <v>479.4517673951738</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>273971676.1830353</v>
+        <v>214.1313978911375</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.794897629054564e-07</v>
+        <v>4.424018061635538e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.918381809651342</v>
+        <v>0.938290460113876</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 52.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 52.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1124,6 +1124,566 @@
         <v>4.696682508126709e-07</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.9176214688840652</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>207.4320000000001</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>869.3703818669195</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.84075e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-79.773</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1077116415683324</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.6518866171161721</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.361689680904509</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.406004169851856</v>
+      </c>
+      <c r="L12" t="n">
+        <v>19.28910850925628</v>
+      </c>
+      <c r="M12" t="n">
+        <v>85.71780556973803</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>13.35508213238412</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-8803.943089349516</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-182.0265198595381</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.206532355596467e-07</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.85816184219313</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>201.885</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9732587064676613</v>
+      </c>
+      <c r="D13" t="n">
+        <v>900.2321590546948</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.035498997701649</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.77854e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-80.539</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.4272669778615087</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.7999474036324167</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.366054331025567</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.250844360526219</v>
+      </c>
+      <c r="L13" t="n">
+        <v>22.59817211319202</v>
+      </c>
+      <c r="M13" t="n">
+        <v>86.23158024381881</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>15.18226242897974</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-9879.710328565614</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-217.4702265740671</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>6.267127526616215e-07</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8758214799464826</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>194.896</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9395657372054451</v>
+      </c>
+      <c r="D14" t="n">
+        <v>918.2129363095416</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.056181525689587</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.76208e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-80.872</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4890609858176024</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.029845875984965</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.589590399057144</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.285280965774317</v>
+      </c>
+      <c r="L14" t="n">
+        <v>23.63660727639768</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.49600551653742</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>16.3311704940572</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-10470.7424904319</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-242.427073586503</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>5.890070855591323e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.884317078852627</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>186.004</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8966986771568511</v>
+      </c>
+      <c r="D15" t="n">
+        <v>993.1028194191097</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.142324192464991</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.75569e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-81.166</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.6532594778035842</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9846070513247311</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.614344501968056</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.633609835071168</v>
+      </c>
+      <c r="L15" t="n">
+        <v>26.25858233225374</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.59700764419834</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>16.81707917454596</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-10543.2899082422</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-317.4638908256117</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>5.5989793164035e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8916542873903337</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>174.124</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.8394268965251261</v>
+      </c>
+      <c r="D16" t="n">
+        <v>906.8524496212815</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.043114038085668</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.75198e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-81.42100000000001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.2646206235817959</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.7864205413431739</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.409777523825267</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.583704772998686</v>
+      </c>
+      <c r="L16" t="n">
+        <v>27.56465611791123</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.59963449745547</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>16.83010130989706</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-10285.13111244457</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-258.289135171173</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>5.362107796516958e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.898021353319397</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>163.76</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7894635350379883</v>
+      </c>
+      <c r="D17" t="n">
+        <v>866.5453130934029</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9967504428119004</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.74793e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-81.61199999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.04709302761063643</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.7121444368742766</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.351456900234701</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.449566565491548</v>
+      </c>
+      <c r="L17" t="n">
+        <v>27.62588929546976</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.56151000208058</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>16.64305504999831</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-9915.337206015489</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-236.407338960681</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>5.18164608234583e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9030302469420093</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>159.049</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7667524779204751</v>
+      </c>
+      <c r="D18" t="n">
+        <v>904.6051767207681</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.040529095065539</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.74725e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-81.803</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2796282016090528</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8875499568735453</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.557723373739822</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.674023716456706</v>
+      </c>
+      <c r="L18" t="n">
+        <v>29.10375179787384</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.79121995036104</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>17.83726675920265</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-10467.27842527503</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-280.0788707716491</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>5.032855244703399e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9074293255804917</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>150.136</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7237841798758146</v>
+      </c>
+      <c r="D19" t="n">
+        <v>879.4812330233636</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.011630084676604</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.74542e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-81.974</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2573723202517896</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.6032054909236702</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.450659519057139</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.500255520570139</v>
+      </c>
+      <c r="L19" t="n">
+        <v>29.1839628677693</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.75443229110743</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>17.63466021789048</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-10109.59046943449</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-268.7847526018463</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.903602942740081e-07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9112882571601162</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>145.279</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7003692776427936</v>
+      </c>
+      <c r="D20" t="n">
+        <v>917.8887666817836</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.055808647070164</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.7434e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-82.11499999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.2053870292526725</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.7780658282570935</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.327044836310776</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.398212515352944</v>
+      </c>
+      <c r="L20" t="n">
+        <v>28.4131595292618</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.86399061391251</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>18.25203496387998</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-10290.04093702186</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-312.2675017187426</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.798176144455605e-07</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9144936368071772</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>139.072</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.6704462185198039</v>
+      </c>
+      <c r="D21" t="n">
+        <v>882.9119238936443</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.015576263361589</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.74116e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-82.271</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.133032469425554</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.6824983883146285</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.301623762324569</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.441370433324076</v>
+      </c>
+      <c r="L21" t="n">
+        <v>29.75051584272774</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.86201561837873</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>18.24052445250625</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-10084.21876871057</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-291.2895080277733</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>4.696682508126709e-07</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.9176214688840652</v>
       </c>
     </row>
@@ -1138,7 +1698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2456,6 +3016,1182 @@
         <v>4.641218700590199e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9984261786744993</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>206.432</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1016.788007079257</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.77466e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-81.107</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3646641243372972</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.7251264235091125</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.550065178291847</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.067064086647614</v>
+      </c>
+      <c r="L23" t="n">
+        <v>28.53892997069431</v>
+      </c>
+      <c r="M23" t="n">
+        <v>86.65426769437698</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>17.10556489951618</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-11249.97607059805</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-309.6331250763367</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>5.843129485523733e-07</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.886157461389472</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>184.4160000000001</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8933498682374827</v>
+      </c>
+      <c r="D24" t="n">
+        <v>888.6871848444293</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.8740142278007389</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.79344e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-81.34999999999999</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1173761142040936</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.5923521197805374</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.498109138202306</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.216075493420218</v>
+      </c>
+      <c r="L24" t="n">
+        <v>28.23523860810725</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.67621761930589</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>17.21878468973923</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-10861.79937310117</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-227.4938422867345</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>5.549820417865719e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8950503314533955</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>175.397</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8496599364439621</v>
+      </c>
+      <c r="D25" t="n">
+        <v>855.9313036330063</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.841799173154771</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.79701e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-81.54000000000001</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.26662440540254</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.8154961094764286</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.438123460479906</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.611938835102172</v>
+      </c>
+      <c r="L25" t="n">
+        <v>32.39167685925389</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.75859743134012</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>17.65736893406811</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-10951.55297359674</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-209.1222387758585</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>5.38037091704937e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8999537002764342</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>171.446</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8305204619438847</v>
+      </c>
+      <c r="D26" t="n">
+        <v>878.7113330442611</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8642030855265257</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.79651e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-81.626</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.3834914931934432</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8863198084297643</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.549038772716065</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.54771113642053</v>
+      </c>
+      <c r="L26" t="n">
+        <v>31.41815720079416</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.88584835855085</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>18.38039847063652</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-11286.66355718546</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-235.7419337608845</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>5.280000921525257e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9028218588589982</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>166.47</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.806415671988839</v>
+      </c>
+      <c r="D27" t="n">
+        <v>873.1386675826948</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8587224293594906</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.79475e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-81.721</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.5402857253549586</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8183457114063589</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.623650468130502</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.399994365508291</v>
+      </c>
+      <c r="L27" t="n">
+        <v>30.66436886401196</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.89498427597836</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>18.43458579208651</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-11158.79633193113</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-238.5707290619285</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>5.18061558625732e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9056400709941076</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>159.812</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7741629204774451</v>
+      </c>
+      <c r="D28" t="n">
+        <v>861.3567811193914</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8471350715412693</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.79772e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-81.831</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.4848179854485541</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.7243756060623281</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.49151770155132</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.444205209972915</v>
+      </c>
+      <c r="L28" t="n">
+        <v>32.03935267951744</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.85517826461805</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>18.20078708506399</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-10830.42604100653</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-236.3331637197254</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>5.098815646727138e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9082258353444421</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>155.379</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7526885366609828</v>
+      </c>
+      <c r="D29" t="n">
+        <v>865.5406987417479</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8512499092392226</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.79625e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-81.91800000000001</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.4142040674860089</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.959176311335216</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.70507176123462</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.830437571038976</v>
+      </c>
+      <c r="L29" t="n">
+        <v>32.77906336879487</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.93421380474906</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>18.67093267443002</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-10961.22474682713</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-248.1447030234029</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>5.014855124558051e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.910701142904584</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>151.518</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7339850410789023</v>
+      </c>
+      <c r="D30" t="n">
+        <v>899.7825745638933</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8849264235015277</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.79657e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-82.029</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.3962789591840545</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.177679689373743</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.56172012376785</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.478570601234709</v>
+      </c>
+      <c r="L30" t="n">
+        <v>31.553635806468</v>
+      </c>
+      <c r="M30" t="n">
+        <v>87.03752674193467</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>19.32328405495187</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-11209.17712077081</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-285.8287340587896</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4.928337765878669e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9133725852778088</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>147.951</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7167057432956131</v>
+      </c>
+      <c r="D31" t="n">
+        <v>889.617746388085</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8749294250072134</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.79686e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-82.13500000000001</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.4891615492411115</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.9932531250554146</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.703838150795357</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.446474212731569</v>
+      </c>
+      <c r="L31" t="n">
+        <v>31.96252829709818</v>
+      </c>
+      <c r="M31" t="n">
+        <v>87.08724637754925</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>19.65370908018021</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-11255.07046605867</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-283.4295565654019</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>4.859172518199393e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9155414574974581</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>142.825</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6918743218105722</v>
+      </c>
+      <c r="D32" t="n">
+        <v>847.695491937528</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8336993414906114</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.798e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-82.241</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.4222334805292197</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.6911635918395393</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.647270509741012</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.553904853196996</v>
+      </c>
+      <c r="L32" t="n">
+        <v>32.59861249661172</v>
+      </c>
+      <c r="M32" t="n">
+        <v>87.04147941380815</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>19.349146578169</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-10902.55060148231</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-254.0714858833978</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>4.787743942065891e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9178572889243085</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>138.833</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6725362346922956</v>
+      </c>
+      <c r="D33" t="n">
+        <v>843.2591946186822</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8293362910927323</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.7984e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-82.331</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.4971178368169251</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.729008311367605</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.513776200531758</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.669948619836324</v>
+      </c>
+      <c r="L33" t="n">
+        <v>32.91398293315098</v>
+      </c>
+      <c r="M33" t="n">
+        <v>87.07824229333619</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>19.59303690675931</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-10902.4667195866</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-257.1063473176741</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>4.732247315029527e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9196587717102108</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>136.215</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6598540923887768</v>
+      </c>
+      <c r="D34" t="n">
+        <v>883.2569952533182</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8686736951102428</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.79997e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-82.407</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.3122113290418967</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.9393860275435358</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.625416128472002</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.519431500090476</v>
+      </c>
+      <c r="L34" t="n">
+        <v>33.19445488533625</v>
+      </c>
+      <c r="M34" t="n">
+        <v>87.11377880852471</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>19.83469178286271</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-10907.04836233583</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-297.5385971694887</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>4.683395449795387e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9213274675745137</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>133.475</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6465809564408619</v>
+      </c>
+      <c r="D35" t="n">
+        <v>876.0808894999423</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8616160727706664</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.79936e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-82.492</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.5913892969043912</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.262488880478221</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.796444808982691</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.923380988965439</v>
+      </c>
+      <c r="L35" t="n">
+        <v>34.88876901786428</v>
+      </c>
+      <c r="M35" t="n">
+        <v>87.21412335674272</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>20.55030693249091</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-11178.80252208924</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-297.7004630336411</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>4.630164582235506e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9230456419053145</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>129.5869999999999</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.627746667183382</v>
+      </c>
+      <c r="D36" t="n">
+        <v>850.826200121594</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8367783591051671</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.79942e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-82.586</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.2018899949128029</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.9493521760255583</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.501039895304626</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.408359283169756</v>
+      </c>
+      <c r="L36" t="n">
+        <v>32.44179783334324</v>
+      </c>
+      <c r="M36" t="n">
+        <v>87.15981267349734</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>20.15671337593599</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-10797.02377499621</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-282.1479894014755</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>4.576311750516199e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9248273123145193</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>122.747</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.5946122694155945</v>
+      </c>
+      <c r="D37" t="n">
+        <v>776.4503163340307</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7636304823897352</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.79985e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-82.65600000000001</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.4674271789645191</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.17400882993678</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.178605895158181</v>
+      </c>
+      <c r="L37" t="n">
+        <v>31.85222550650592</v>
+      </c>
+      <c r="M37" t="n">
+        <v>86.99169329717583</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>19.02835224311032</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-10004.5531730878</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-223.3960692691617</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>4.537056640989806e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9261707582920037</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>124.586</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6035207719733375</v>
+      </c>
+      <c r="D38" t="n">
+        <v>882.1737534918594</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8676083385620569</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.80122e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-82.752</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.574094098662207</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.02471410018959</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.788403102681607</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.669856097256436</v>
+      </c>
+      <c r="L38" t="n">
+        <v>34.64996948124505</v>
+      </c>
+      <c r="M38" t="n">
+        <v>87.28457759564253</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>21.08433502009381</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-11054.07949912203</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-320.3979993329629</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>4.491448263308566e-07</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9277754535995723</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>119.501</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.5788879631064949</v>
+      </c>
+      <c r="D39" t="n">
+        <v>849.8597053354899</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8358278219436596</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.80068e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-82.79900000000001</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.2183510577673462</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.8283458706172394</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.708807776463827</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.807955456257609</v>
+      </c>
+      <c r="L39" t="n">
+        <v>35.03307956912273</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87.23301847851154</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>20.6908612336624</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-10695.26111207464</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-298.0851234868799</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>4.459785110598263e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9288390395482373</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>118.911</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5760298790885133</v>
+      </c>
+      <c r="D40" t="n">
+        <v>901.0674593893579</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.8861900938207278</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.8028e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-82.913</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.5027793968845387</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.230302937265868</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.884773727162765</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.9191155272148</v>
+      </c>
+      <c r="L40" t="n">
+        <v>36.06874250908724</v>
+      </c>
+      <c r="M40" t="n">
+        <v>87.37575716610981</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>21.81799194079257</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-11183.55084380444</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-348.2756456022721</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>4.413194965873209e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.930533840555642</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>114.173</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5530780111610603</v>
+      </c>
+      <c r="D41" t="n">
+        <v>841.7937096292143</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.8278950024669179</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.80156e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-82.96599999999999</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.2700673515886521</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.7809265010128872</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.413067855121629</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.534432574990799</v>
+      </c>
+      <c r="L41" t="n">
+        <v>33.80302682497498</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.24963659107635</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>20.8160725578104</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-10488.21905324031</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-302.303108718601</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>4.380704721093446e-07</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.931611207274547</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>112.521</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5450753759107115</v>
+      </c>
+      <c r="D42" t="n">
+        <v>853.416947569573</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.8393263311799175</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.80049e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-83.032</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.3154162282915391</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.8684173492303625</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.633895355605208</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.705870431938876</v>
+      </c>
+      <c r="L42" t="n">
+        <v>35.22895459104724</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.32376809483063</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>21.39355160139858</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-10670.26348242676</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-317.5402489555623</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>4.34392041140991e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9328343364818265</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>108.157</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5239352425980469</v>
+      </c>
+      <c r="D43" t="n">
+        <v>815.2194788278629</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.8017595340936369</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.80206e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-83.133</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1442157191348044</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.9656591906001689</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.479633122993012</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.539282747890528</v>
+      </c>
+      <c r="L43" t="n">
+        <v>35.53031468556073</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.26219463846495</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>20.91170036110754</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-10266.41063451135</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-289.9263665279638</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>4.641218700590199e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9984261786744993</v>
       </c>
     </row>
@@ -2470,7 +4206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3788,6 +5524,1182 @@
         <v>4.18400320375367e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9326973080804603</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>193.3989999999999</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>946.1724634760105</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.75911e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-80.986</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1952450869479741</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.755266670279675</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.248481444564074</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.296674542326991</v>
+      </c>
+      <c r="L23" t="n">
+        <v>26.8280798110669</v>
+      </c>
+      <c r="M23" t="n">
+        <v>86.36910546666731</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>15.75894330230318</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-10152.08803456429</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-262.1875426869082</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>5.820828483546218e-07</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8859197612966854</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>181.307</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.937476408874917</v>
+      </c>
+      <c r="D24" t="n">
+        <v>889.7282988469159</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9403447396664533</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.75569e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-81.366</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1920432695997757</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.6710820972775473</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.411099546441634</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.496970371869915</v>
+      </c>
+      <c r="L24" t="n">
+        <v>29.64686197193164</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.60296144379556</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>16.84662289809391</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-10602.84886892514</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-229.6434658636237</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>5.475926748889934e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8949616793716735</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>175.408</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9069746999725958</v>
+      </c>
+      <c r="D25" t="n">
+        <v>877.7237508844726</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9276572556972607</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.74958e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-81.541</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2223139853987595</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.7773508707494463</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.383399446852563</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.417329657635067</v>
+      </c>
+      <c r="L25" t="n">
+        <v>29.76918164810563</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.67231898498879</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>17.19856620231159</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-10667.68510282975</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-227.1263462316131</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>5.311393192374377e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8992685023209542</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>170.3459999999999</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8808008314417344</v>
+      </c>
+      <c r="D26" t="n">
+        <v>868.6969671126076</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.918116940247049</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.74428e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-81.67400000000001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.008931117234622345</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.5530911112892096</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.160591641717726</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.084806897229841</v>
+      </c>
+      <c r="L26" t="n">
+        <v>28.73746863546007</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.66415580087778</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>17.15638447637386</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-10474.87440678367</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-227.022357835916</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>5.185988259768235e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9026224396203708</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>164.084</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8484221738478485</v>
+      </c>
+      <c r="D27" t="n">
+        <v>871.3211496686513</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9208904119526228</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.74171e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-81.78400000000001</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.06045750545179958</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.6343597426922</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.406397569105598</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.505667571765391</v>
+      </c>
+      <c r="L27" t="n">
+        <v>30.49610782680917</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.66871586387042</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>17.17992229102028</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-10319.1937841465</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-237.9959916669581</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>5.082977602685361e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9055414459293201</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>158.844</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8213279282726387</v>
+      </c>
+      <c r="D28" t="n">
+        <v>864.3059588817539</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.91347612855536</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.73569e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-81.923</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.005391165117129095</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.5412262003611511</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.244551027971449</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.195137048314126</v>
+      </c>
+      <c r="L28" t="n">
+        <v>28.84999281911304</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.76167165566486</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>17.67416730886164</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-10475.09841175652</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-240.1117463644446</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>4.968564906094457e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.908680243748182</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>157.0719999999999</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8121655230895712</v>
+      </c>
+      <c r="D29" t="n">
+        <v>912.0889680852489</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.963977502298527</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.73308e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-82.05</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.6134521518027856</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8228770755907237</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.616802831919998</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.340761584129079</v>
+      </c>
+      <c r="L29" t="n">
+        <v>30.18632258650494</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.95632860802702</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>18.8068508741302</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-11051.79958285651</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-288.4173685477271</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>4.877483991057653e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9113429296945486</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>151.429</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7829875025206959</v>
+      </c>
+      <c r="D30" t="n">
+        <v>867.0316450000926</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9163568783378312</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.72884e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-82.154</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2198065149320281</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.7795732594248805</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.444678998424194</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.150044116883293</v>
+      </c>
+      <c r="L30" t="n">
+        <v>29.91495115848994</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.87427225247617</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>18.31219232367608</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-10583.59431202855</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-256.0869099974507</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4.79742023833454e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9136306050108158</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>146.739</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7587371185993727</v>
+      </c>
+      <c r="D31" t="n">
+        <v>863.8465730183781</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9129906083345664</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.7248e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-82.262</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.1076727226060694</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.6600488731801287</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.341842334481293</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.445986974429182</v>
+      </c>
+      <c r="L31" t="n">
+        <v>31.94805434110291</v>
+      </c>
+      <c r="M31" t="n">
+        <v>86.86927920047472</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>18.28292892189813</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-10423.537255714</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-260.2345029376511</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>4.718427542435358e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9159318818718266</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>145.875</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.7542696704739944</v>
+      </c>
+      <c r="D32" t="n">
+        <v>923.1090235508173</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9756244862163249</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.7219e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-82.327</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.4163943174783296</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.8539200072988365</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.607577426455</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.222730055011878</v>
+      </c>
+      <c r="L32" t="n">
+        <v>31.06880622720697</v>
+      </c>
+      <c r="M32" t="n">
+        <v>87.0820691243071</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>19.61877750897923</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-11127.10472409307</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-317.0279181389147</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>4.667191217373455e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9174435870548666</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>140.711</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.7275683948727762</v>
+      </c>
+      <c r="D33" t="n">
+        <v>870.9584962996704</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9205071273158574</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.71584e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-82.41200000000001</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.2526872500180329</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.7825747882664581</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.50307297325042</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.644058196896711</v>
+      </c>
+      <c r="L33" t="n">
+        <v>32.55070289707726</v>
+      </c>
+      <c r="M33" t="n">
+        <v>86.96906348641619</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>18.88601887553665</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-10527.28559566131</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-278.3677434601639</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>4.60055500071584e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.91930711753258</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>136.612</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.7063738695649929</v>
+      </c>
+      <c r="D34" t="n">
+        <v>852.1780111077188</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.9006582245873246</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.71535e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-82.491</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.2122254888761856</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.6937080879290778</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.396195697138807</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.466276642088455</v>
+      </c>
+      <c r="L34" t="n">
+        <v>31.37231042767696</v>
+      </c>
+      <c r="M34" t="n">
+        <v>86.96053611362325</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>18.83293405652562</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-10361.67708609466</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-268.1110424871736</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>4.551564263780891e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9209059499127603</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>134.8819999999999</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6974286319991313</v>
+      </c>
+      <c r="D35" t="n">
+        <v>997.2342314589137</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.053966660364765</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.71117e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-82.563</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.3605236730214341</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.81914103853259</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.497141849556639</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.330786566685132</v>
+      </c>
+      <c r="L35" t="n">
+        <v>30.79310693495376</v>
+      </c>
+      <c r="M35" t="n">
+        <v>87.06517073585158</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>19.50561886040164</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-10639.55258907091</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-398.4256283649759</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>4.500449046646251e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9224025859855683</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>129.588</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6700551709160855</v>
+      </c>
+      <c r="D36" t="n">
+        <v>846.1616485987284</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.894299592581815</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.70973e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-82.655</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.03119398884721605</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.6325437411909773</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.258445199355586</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.140474610872851</v>
+      </c>
+      <c r="L36" t="n">
+        <v>30.53707035080581</v>
+      </c>
+      <c r="M36" t="n">
+        <v>86.99561330577383</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>19.05322536563283</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-10227.20672708117</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-274.3156276978271</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>4.451062441172622e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9239978165989882</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>128.5050000000001</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6644553487867056</v>
+      </c>
+      <c r="D37" t="n">
+        <v>866.4603819036205</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.9157531162135633</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.70639e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-82.697</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.2086057357723226</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.7308941824797699</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.531891265620881</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.414295395977082</v>
+      </c>
+      <c r="L37" t="n">
+        <v>31.45527966216478</v>
+      </c>
+      <c r="M37" t="n">
+        <v>87.05295416989037</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>19.42461914638663</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-10325.28024842519</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-297.6544388670586</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>4.415980302388228e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9250293871557737</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>127.8079999999999</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6608514004725979</v>
+      </c>
+      <c r="D38" t="n">
+        <v>915.3781833116866</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.9674538402320512</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.70397e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-82.833</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.4761021165864978</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.7736434726547265</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.658303749209617</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.676899113999296</v>
+      </c>
+      <c r="L38" t="n">
+        <v>33.23544817772977</v>
+      </c>
+      <c r="M38" t="n">
+        <v>87.23156072950334</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>20.67994929407518</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-10911.60845700028</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-345.3665240220686</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>4.344326980192154e-07</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9273668514751624</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>122.131</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.631497577546937</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1284.640907493511</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.357723836914519</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.70245e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-82.843</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.2173577897072485</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.673331281426839</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.537745280389815</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.621278129482117</v>
+      </c>
+      <c r="L39" t="n">
+        <v>31.58711232036303</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87.12206384450741</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>19.89188869572183</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-10328.82297298489</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-669.9731543998785</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>4.330306852580111e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9278024985076893</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>121.495</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.6282090393435336</v>
+      </c>
+      <c r="D40" t="n">
+        <v>915.5765563811226</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.967663498700347</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.70042e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-82.923</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.4854376457308592</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.8736735109193742</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.602755377449514</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.674300618719865</v>
+      </c>
+      <c r="L40" t="n">
+        <v>31.87093104326145</v>
+      </c>
+      <c r="M40" t="n">
+        <v>87.24135507798749</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>20.7534860026486</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-10687.45139629967</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-356.779792519761</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>4.289298240777591e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9291421875612191</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>119.636</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.6185967869533971</v>
+      </c>
+      <c r="D41" t="n">
+        <v>958.4870023312133</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.013015110173427</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.6985e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-83</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.6699678097066287</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.14843603787232</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.829178323611019</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.004469770141549</v>
+      </c>
+      <c r="L41" t="n">
+        <v>32.66376243186441</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.30505889277259</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>21.24481325638911</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-10821.87992804147</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-399.8841652245093</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>4.248476336062204e-07</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9304842063363656</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>115.007</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5946618131427776</v>
+      </c>
+      <c r="D42" t="n">
+        <v>886.0431904084328</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.9364499862459775</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.69851e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-83.083</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.2784258307472733</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.9862472841372104</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.460607840254294</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.442787857798665</v>
+      </c>
+      <c r="L42" t="n">
+        <v>31.91599480951547</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.21328819958147</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>20.54413843658191</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-10284.19174682864</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-342.434848177788</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>4.211295957905756e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9318223302954682</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>111.596</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5770247002311286</v>
+      </c>
+      <c r="D43" t="n">
+        <v>899.3719167736283</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.9505369808264676</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.69608e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-83.119</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.2182466866922736</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.8359932495732775</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.620453241204297</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.512436863852853</v>
+      </c>
+      <c r="L43" t="n">
+        <v>31.41175870035528</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.22402722824856</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>20.62373998876398</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-10197.54011435341</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-359.9500063689118</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>4.18400320375367e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9326973080804603</v>
       </c>
     </row>
@@ -3802,7 +6714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4504,6 +7416,566 @@
         <v>5.133228685586095e-07</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.9032165774683129</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>334.134</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1398.205056484128</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.73912e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-77.087</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2394452597977123</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.718123391121404</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.199218326272361</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.874774092295481</v>
+      </c>
+      <c r="L12" t="n">
+        <v>13.50043637479386</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.45633435361003</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10.30308799477091</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-8414.234368814468</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-455.9930989748248</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.882895778045228e-06</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.71001629784389</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>260.447</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.7794687161438226</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1026.685024304328</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.7342878782644305</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.78028e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-79.06999999999999</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.4254204703069858</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.017892081940738</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.646956998032436</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.584431778307111</v>
+      </c>
+      <c r="L13" t="n">
+        <v>19.32425483525176</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.68401314913133</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>13.25012532663609</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-9702.424239303427</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-249.8294235579572</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8.76482784692416e-07</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8252689815935689</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>236.025</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.7063782793729462</v>
+      </c>
+      <c r="D14" t="n">
+        <v>946.9176388316002</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.6772380306023801</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.77557e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-79.871</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3789533712106087</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6935831395145033</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.484149597122343</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.327218347529435</v>
+      </c>
+      <c r="L14" t="n">
+        <v>21.22569861951163</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.07626047625904</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>14.57950570195715</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-10234.31203384862</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-212.0335368257886</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>7.30842803239554e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8523495598391753</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>220.16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.6588973286166629</v>
+      </c>
+      <c r="D15" t="n">
+        <v>909.8811565655924</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.6507494393229734</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.76524e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-80.327</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1999261977950024</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.624035922274585</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.243128395234571</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.348688563061177</v>
+      </c>
+      <c r="L15" t="n">
+        <v>23.3149796036984</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.21622237633349</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>15.12046113779918</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-10318.5601255436</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-197.1169384497945</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>6.634786282406896e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8663904509871001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>212.585</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.6362267832665939</v>
+      </c>
+      <c r="D16" t="n">
+        <v>941.5450963743938</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.6733955738523552</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.7542e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-80.64100000000001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5185912786437098</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.148055060453172</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.743900104916341</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.56564840233844</v>
+      </c>
+      <c r="L16" t="n">
+        <v>25.39182131709459</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.53569117561379</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>16.51871812494549</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-11107.11539047141</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-236.2645225210006</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>6.206783793336595e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8759026763141121</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>203.701</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.6096386479675818</v>
+      </c>
+      <c r="D17" t="n">
+        <v>932.8380109534403</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.6671682430466377</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.74779e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-80.917</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.5248157113527188</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9742962094062639</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.522607771635615</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.387124752332773</v>
+      </c>
+      <c r="L17" t="n">
+        <v>26.07510066512191</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.64416046751572</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>17.05392832233007</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-11236.52387553937</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-241.137489729151</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>5.886170529079986e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8835919572235396</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>195.643</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5855225747753895</v>
+      </c>
+      <c r="D18" t="n">
+        <v>937.085339083744</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.6702059434973741</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.74066e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-81.066</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.6912408118216696</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.011634495532713</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.716135483563617</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.570084925832572</v>
+      </c>
+      <c r="L18" t="n">
+        <v>26.16977029646472</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.7000471683982</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>17.34340300547591</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-11214.33325122697</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-255.8206828065163</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>5.676922735456703e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8887380136564915</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>185.795</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5560493694146659</v>
+      </c>
+      <c r="D19" t="n">
+        <v>918.2201487033501</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.6567135088270035</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.73609e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-81.31999999999999</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.5565863482426715</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.005052117092767</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.694985968697947</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.574527120443393</v>
+      </c>
+      <c r="L19" t="n">
+        <v>28.303952681974</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.73254258456815</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>17.51626622722893</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-11079.7237515102</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-251.2857881537331</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>5.446282324568905e-07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8947642841424477</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>175.393</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5249181466118386</v>
+      </c>
+      <c r="D20" t="n">
+        <v>865.4384848473051</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.6189639215177087</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.73151e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-81.48999999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1661809382073509</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5560566862638964</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.255961439573271</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.193166714234211</v>
+      </c>
+      <c r="L20" t="n">
+        <v>26.95813718913088</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.60887503835845</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>16.87606968855905</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-10421.2894128726</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-217.2928656289931</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>5.283929184470241e-07</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8991159299724438</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>170.5479999999999</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.510417976021596</v>
+      </c>
+      <c r="D21" t="n">
+        <v>889.9559831801046</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.6364989019693245</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.72605e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-81.657</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1796956324297025</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.8236838196539223</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.543243869597549</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.605687402695676</v>
+      </c>
+      <c r="L21" t="n">
+        <v>29.66644705868204</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.77269245723578</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>17.7346506119745</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-10800.37868419815</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-247.7077460212109</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>5.133228685586095e-07</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.9032165774683129</v>
       </c>
     </row>
@@ -4518,7 +7990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5836,6 +9308,1182 @@
         <v>4.291012941134729e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9320235453091141</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>203.3919999999999</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1024.539292805522</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.82333e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-80.155</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1480065881251066</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.6184711703810529</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.190463002417081</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.959255446452011</v>
+      </c>
+      <c r="L23" t="n">
+        <v>20.66399810028872</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.95620854890785</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>14.14529286882315</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-9296.019665877137</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-314.6294285863712</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>6.64534361249985e-07</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8695419148826943</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>185.462</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9118451069855257</v>
+      </c>
+      <c r="D24" t="n">
+        <v>925.5566403179536</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9033881343715749</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.80172e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-80.95399999999999</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.5945747585605637</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.7989869056139646</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.436103946416004</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.409456906870179</v>
+      </c>
+      <c r="L24" t="n">
+        <v>25.47369559745187</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.49145820315111</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>16.30995126247214</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-10345.65935742836</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-256.7773751186034</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>5.822641005546925e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8882925461712646</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>174.581</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.858347427627439</v>
+      </c>
+      <c r="D25" t="n">
+        <v>881.25725824157</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.8601497906716691</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.79093e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-81.247</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.04475386701330318</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.4474005023919039</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.306113553636478</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.250669108736399</v>
+      </c>
+      <c r="L25" t="n">
+        <v>26.54368780814999</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.50976978264542</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>16.3957355568649</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-10165.13698237332</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-230.3743262579536</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>5.538610796403511e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8952877626884116</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>168.443</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8281692495280052</v>
+      </c>
+      <c r="D26" t="n">
+        <v>866.7862940903375</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8460254283823456</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.78399e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-81.43600000000001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1718421532318919</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.575281691954896</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.386214729935252</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.280156691620395</v>
+      </c>
+      <c r="L26" t="n">
+        <v>27.50556780112495</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.60947427756916</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>16.87905932997939</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-10311.45445201213</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-225.982413879833</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>5.362085377543871e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.899832289012949</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>161.7929999999999</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7954737649465072</v>
+      </c>
+      <c r="D27" t="n">
+        <v>863.5912663040756</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8429069264286403</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.77939e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-81.598</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.0008480084571811993</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.6133649844643168</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.235025241366735</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.007506567442336</v>
+      </c>
+      <c r="L27" t="n">
+        <v>26.88487240049644</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.62786991769364</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>16.97135268144558</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-10188.70953644262</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-232.7237482721422</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>5.216831471385929e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9037554014635155</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>159.784</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7855962869729395</v>
+      </c>
+      <c r="D28" t="n">
+        <v>899.7158873616581</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8781663072169179</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.77535e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-81.77</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.279754028690307</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.8427904217164078</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.712400177479131</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.563045867169572</v>
+      </c>
+      <c r="L28" t="n">
+        <v>30.64101401472917</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.82750704386147</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>18.04171489569705</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-10713.03892349086</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-271.720628464472</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>5.085709092644983e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9073974975782982</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>156.292</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7684274701069859</v>
+      </c>
+      <c r="D29" t="n">
+        <v>911.6635637054893</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8898278183251103</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.77186e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-81.886</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.4307655497281935</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.073175209306629</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.62988854556142</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.583530438871635</v>
+      </c>
+      <c r="L29" t="n">
+        <v>29.67299491876751</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.94132693735772</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>18.71443597128127</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-10988.87092254372</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-289.4374950092246</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>4.996646735832783e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9099088804737524</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>148.669</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7309481198867216</v>
+      </c>
+      <c r="D30" t="n">
+        <v>844.9741569423365</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8247357254874257</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.76888e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-81.999</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1037792887837186</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.7378286696870985</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.31555351608316</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.417579565898255</v>
+      </c>
+      <c r="L30" t="n">
+        <v>30.06210026716074</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.79270814982048</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>17.8455606674375</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-10275.02179171626</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-239.4022805119821</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4.913081306985214e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9123017949281753</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>145.981</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7177322608558844</v>
+      </c>
+      <c r="D31" t="n">
+        <v>867.833434544545</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8470474882111493</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.76517e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-82.107</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2326520747812153</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.5767229050967563</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.321168350906908</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.395783542886007</v>
+      </c>
+      <c r="L31" t="n">
+        <v>29.90307718048344</v>
+      </c>
+      <c r="M31" t="n">
+        <v>86.90390655366456</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>18.4878143226265</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-10551.78846650073</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-265.1162680842614</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>4.836258111412862e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9144973029286818</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>143.8799999999999</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.7074024543738199</v>
+      </c>
+      <c r="D32" t="n">
+        <v>888.9708730040551</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8676786524895138</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.76424e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-82.178</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.3295642291360428</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.8018268774242603</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.410299930142739</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.544548248891823</v>
+      </c>
+      <c r="L32" t="n">
+        <v>30.76605962322778</v>
+      </c>
+      <c r="M32" t="n">
+        <v>86.96352012577218</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>18.85147632454354</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-10651.03648055586</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-288.6204919582339</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>4.782830294183207e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9161392209830217</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>138.4470000000001</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6806904893014479</v>
+      </c>
+      <c r="D33" t="n">
+        <v>839.5412970127852</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8194329909142358</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.76201e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-82.26900000000001</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.09334017514359411</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.6052048035585326</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.411817629523775</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.29289560403533</v>
+      </c>
+      <c r="L33" t="n">
+        <v>30.42196149880862</v>
+      </c>
+      <c r="M33" t="n">
+        <v>86.89395331886263</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>18.42845499719915</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-10260.20862746471</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-251.8333169856091</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>4.72514108836623e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9178656589727766</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>138.159</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6792745044052868</v>
+      </c>
+      <c r="D34" t="n">
+        <v>886.9849967396046</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8657403410178157</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.76011e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-82.378</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.4779291113143069</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.9475026324955045</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.502996261598081</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.58493543618786</v>
+      </c>
+      <c r="L34" t="n">
+        <v>31.874831423442</v>
+      </c>
+      <c r="M34" t="n">
+        <v>87.06754657440469</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>19.52144974358852</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-10800.95263639708</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-297.9620353880368</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>4.662560501647432e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9197786808082647</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>134.57</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6616287759597232</v>
+      </c>
+      <c r="D35" t="n">
+        <v>849.7968907328452</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8294429473815733</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.75803e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-82.408</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.1885649332177697</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.820328195165526</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.572249959275457</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.691917886643043</v>
+      </c>
+      <c r="L35" t="n">
+        <v>31.86344855652163</v>
+      </c>
+      <c r="M35" t="n">
+        <v>87.00386093441517</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>19.10577030793165</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-10430.51170212585</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-271.1711592840125</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>4.631060404567869e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.920719844573925</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>131.5069999999999</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6465691865953429</v>
+      </c>
+      <c r="D36" t="n">
+        <v>859.6742434278368</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8390837222784971</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.7569e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-82.524</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3172306018566933</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.8603021687014626</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.701133247103844</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.769937778514372</v>
+      </c>
+      <c r="L36" t="n">
+        <v>32.74213295275063</v>
+      </c>
+      <c r="M36" t="n">
+        <v>87.06671331105046</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>19.51589455724594</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-10538.2687754834</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-284.9964619436097</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>4.567488918996206e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9227444327739828</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>129.8489999999999</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.638417440213971</v>
+      </c>
+      <c r="D37" t="n">
+        <v>895.4910645488285</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8740426754123624</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.7559e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-82.608</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.3857815678992043</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.9185470588657649</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.471825837423314</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.526736664463396</v>
+      </c>
+      <c r="L37" t="n">
+        <v>31.79101885728002</v>
+      </c>
+      <c r="M37" t="n">
+        <v>87.14698387776581</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>20.0659282562475</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-10734.58450027679</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-321.4796721554296</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>4.522718850824425e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.924189238953277</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>125.705</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6180429908747644</v>
+      </c>
+      <c r="D38" t="n">
+        <v>867.9360524351417</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8471476482453397</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.75323e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-82.67</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.200965335231733</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.7795074404851906</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.508042156668263</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.637989471856198</v>
+      </c>
+      <c r="L38" t="n">
+        <v>32.35365371836457</v>
+      </c>
+      <c r="M38" t="n">
+        <v>87.10999092493243</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>19.80865074437075</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-10452.16587075695</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-303.4984382056219</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>4.478297767029729e-07</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.925561736088242</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>124.137</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.6103337397734426</v>
+      </c>
+      <c r="D39" t="n">
+        <v>880.2932705562076</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8592088919749264</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.75338e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-82.732</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.2145788724569198</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.7986337698236529</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.50649135308134</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.421428960657555</v>
+      </c>
+      <c r="L39" t="n">
+        <v>31.1979492897199</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87.17600098309205</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>20.27244880650161</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-10593.93515313758</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-319.3000556107726</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>4.445128379655021e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9267053171687356</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>121.937</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.599517188483323</v>
+      </c>
+      <c r="D40" t="n">
+        <v>900.9329386375606</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.879354208241748</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.75325e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-82.828</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.3700492165788518</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.9178204596698674</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.652987064956971</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.75519494650435</v>
+      </c>
+      <c r="L40" t="n">
+        <v>33.05184377310506</v>
+      </c>
+      <c r="M40" t="n">
+        <v>87.26571630256188</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>20.938674932858</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-10835.83790072471</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-342.6727410142642</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>4.396161957261621e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9283776068270748</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>117.485</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5776284219634993</v>
+      </c>
+      <c r="D41" t="n">
+        <v>871.4525109158893</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.8505798821337233</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.75103e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-82.867</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.2283033407230188</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.8119957830412502</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.390421213085904</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.405597356992305</v>
+      </c>
+      <c r="L41" t="n">
+        <v>31.3722171242797</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.15350563982575</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>20.11197842027876</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-10237.4753925544</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-323.1445088064243</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>4.366229156045198e-07</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9293218080570352</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>114.98</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5653123033354314</v>
+      </c>
+      <c r="D42" t="n">
+        <v>891.4716156719428</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.8701194985219192</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.75269e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-82.977</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.248071469195649</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.9417931337290134</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.599420066569363</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.714641222050696</v>
+      </c>
+      <c r="L42" t="n">
+        <v>33.43691358010342</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.2522598512541</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>20.83597615362318</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-10501.65173754466</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-345.5607179486155</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>4.321799788876768e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9309547576262238</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>112.792</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.554554751415985</v>
+      </c>
+      <c r="D43" t="n">
+        <v>878.6211746905727</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.8575768453785914</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.75223e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-83.033</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.3438557794158425</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.836114503640598</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.580761181412363</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.670578959570229</v>
+      </c>
+      <c r="L43" t="n">
+        <v>32.73695390408071</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.24976640333482</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>20.81705659669926</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-10356.46480867213</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-339.7595136356225</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>4.291012941134729e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9320235453091141</v>
       </c>
     </row>
@@ -5850,7 +10498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6552,6 +11200,566 @@
         <v>5.399516033166096e-07</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.9007305074242201</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>333.346</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>578.5678548358134</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.9838e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-74.63500000000001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.04741256435754312</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.508532107511081</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.8981918884373131</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.659636695122562</v>
+      </c>
+      <c r="L12" t="n">
+        <v>9.941213962257471</v>
+      </c>
+      <c r="M12" t="n">
+        <v>82.6651157206109</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>7.768689464418952</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-6345.806386151228</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>129.5404227382165</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.752691890701562e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9089509374134485</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>246.427</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.7392529083894811</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1046.845803155648</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.809374292757283</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3.01216e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-77.77200000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.3515822914237077</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.8473114252423656</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.395973443438216</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.345227069257654</v>
+      </c>
+      <c r="L13" t="n">
+        <v>15.13136401855535</v>
+      </c>
+      <c r="M13" t="n">
+        <v>84.89370956873204</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>11.19090391352976</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-8039.17587700782</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-279.5479197818651</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.185401619888726e-06</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.7925344467128782</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>224.73</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6741643817534932</v>
+      </c>
+      <c r="D14" t="n">
+        <v>959.9237424647976</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.659137704318547</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.962e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-79.065</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.5742783448708927</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9712441287652233</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.536560585505663</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.411377294103572</v>
+      </c>
+      <c r="L14" t="n">
+        <v>19.12874077286414</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.74320987217183</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>13.43508126323667</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-9287.798107413642</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-235.57922578584</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8.598524766326485e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8379822082664997</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>211.467</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.6343768936780402</v>
+      </c>
+      <c r="D15" t="n">
+        <v>924.0776754251893</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.597181156370025</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.92195e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-79.76900000000001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4894847180105825</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8766474731967944</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.550825802843558</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.288281463445935</v>
+      </c>
+      <c r="L15" t="n">
+        <v>21.21268600853546</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.09600229280805</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>14.65346207930561</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-9894.437174768706</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-219.7350816528658</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>7.420131769015894e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8580603224351908</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>199.57</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5986872498845044</v>
+      </c>
+      <c r="D16" t="n">
+        <v>882.9943260497012</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.526172459581734</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.88889e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-80.203</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.0704548828773396</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.4997124771237685</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.210831630212569</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.115676787314087</v>
+      </c>
+      <c r="L16" t="n">
+        <v>22.05264544928506</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.14418938835858</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>14.83715484156516</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-9780.090674851996</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-196.5010417346322</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>6.766352163401629e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8702731380809851</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>197.137</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.591388527235965</v>
+      </c>
+      <c r="D17" t="n">
+        <v>945.0946266513869</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.633506975460271</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.86417e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-80.577</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8305018133887543</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.175274742315297</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.818349909479372</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.712361553625984</v>
+      </c>
+      <c r="L17" t="n">
+        <v>26.08245321436695</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.58717447072914</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>16.76851081017094</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-10961.2840643544</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-258.6937812590159</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>6.298505710540088e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.87980008112735</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>187.569</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5626856179465181</v>
+      </c>
+      <c r="D18" t="n">
+        <v>911.9141729102835</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.576157688831619</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.84804e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-80.84099999999999</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2957717498267839</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8480996540261118</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.490247907421995</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.472165735623615</v>
+      </c>
+      <c r="L18" t="n">
+        <v>26.67650156012775</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.56080407443896</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>16.6396306878686</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-10639.29098362959</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-241.4528144503598</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>5.98746115629063e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8866153613256428</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>178.627</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5358606372957826</v>
+      </c>
+      <c r="D19" t="n">
+        <v>878.9044546998333</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.519103502473793</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.83701e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-81.092</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2047370001775109</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.4854828281835391</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.285765672454759</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.065452863759254</v>
+      </c>
+      <c r="L19" t="n">
+        <v>26.13891120181252</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.60186424003736</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>16.84117062218054</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-10566.11853173201</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-223.2100636154065</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>5.73714269171323e-07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8924828407205273</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>175.395</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5261650057297822</v>
+      </c>
+      <c r="D20" t="n">
+        <v>914.1686033131097</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.580054259275316</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.82732e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-81.27500000000001</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.2758296477875841</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8290016796894822</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.782799875193498</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.59586819193714</v>
+      </c>
+      <c r="L20" t="n">
+        <v>28.98433912098287</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.78168544461973</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>17.78431165591698</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-11034.01640970146</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-261.3412701292316</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>5.552519750927198e-07</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.89692991190356</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>165.3759999999999</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4961091478523814</v>
+      </c>
+      <c r="D21" t="n">
+        <v>836.3922050726685</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.445625086291773</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.81897e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-81.429</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.02088451409209654</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.5372813070639214</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.271555828449094</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.050277892677634</v>
+      </c>
+      <c r="L21" t="n">
+        <v>26.92460837186266</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.63028576451273</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>16.98354807391167</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-10313.1555306142</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-203.0488777358669</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>5.399516033166096e-07</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.9007305074242201</v>
       </c>
     </row>
@@ -6566,7 +11774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7884,6 +13092,1182 @@
         <v>4.417689184530119e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9317673639640885</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>206.8460000000001</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1010.790490581684</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.99723e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-79.05</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2262220644112059</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.7818591832894812</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.355866046274577</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.210709949160665</v>
+      </c>
+      <c r="L23" t="n">
+        <v>17.4040703072683</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.41998583830714</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12.48330004533085</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-8225.623711085243</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-302.2224756868798</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8.274102823993408e-07</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8457666789407142</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>189.844</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9178035833421964</v>
+      </c>
+      <c r="D24" t="n">
+        <v>946.1694008666808</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9360687597309946</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.91984e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-80.374</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.7441229220657029</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.9079495240979366</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.823571920107478</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.465172239906871</v>
+      </c>
+      <c r="L24" t="n">
+        <v>23.32013914477994</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.38672044718129</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>15.83597477813128</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-10121.95418918851</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-272.3652765376455</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>6.527902110359519e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8773862851911465</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>179.171</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8662048093750906</v>
+      </c>
+      <c r="D25" t="n">
+        <v>897.726717250647</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.8881432162406158</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.89069e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-80.866</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.4244491384048252</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.8361864141065306</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.58110355055373</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.47599103599696</v>
+      </c>
+      <c r="L25" t="n">
+        <v>26.42779676288146</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.55930970150752</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>16.63238631148031</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-10407.16551787421</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-242.1146164257102</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>6.00545680042186e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8884423940681052</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>173.399</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8382999912978736</v>
+      </c>
+      <c r="D26" t="n">
+        <v>892.0090083994556</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8824865456402612</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.87552e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-81.096</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.3939383617169469</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.79921883095817</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.573492281634406</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.54365395675777</v>
+      </c>
+      <c r="L26" t="n">
+        <v>27.6932367502131</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.69298291892619</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>17.30627293415061</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-10690.68976420769</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-244.8724405404506</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>5.745483423175343e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8943638664328679</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>168.251</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8134119103100856</v>
+      </c>
+      <c r="D27" t="n">
+        <v>882.3384528232148</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8729192261350335</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.8644e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-81.304</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.5007586314062575</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.947261371890523</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.471886460020031</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.457924013549032</v>
+      </c>
+      <c r="L27" t="n">
+        <v>28.28473065339613</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.76941509436701</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>17.71662103794387</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-10786.67267908514</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-244.1060956655046</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>5.551725047422679e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8989872840468733</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>160.248</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7747212902352472</v>
+      </c>
+      <c r="D28" t="n">
+        <v>849.9870783625872</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8409132122656211</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.8567e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-81.46299999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.5305982286515071</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.299279190028358</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.074665440765484</v>
+      </c>
+      <c r="L28" t="n">
+        <v>27.68217023174792</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.6801818769266</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>17.23939214072621</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-10288.05260605998</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-224.7182076167401</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>5.399810808069631e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9027972753956297</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>159.213</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7697175676590312</v>
+      </c>
+      <c r="D29" t="n">
+        <v>919.1190256729246</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9093071553769713</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.8523e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-81.655</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.5908817561571318</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.004374315184937</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.47331940538358</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.679128791133663</v>
+      </c>
+      <c r="L29" t="n">
+        <v>30.96904628457192</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.96933328543356</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>18.88770330600138</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-11188.64052107184</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-292.0547063088849</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>5.25718116813532e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.906611705339431</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>152.17</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7356680815679294</v>
+      </c>
+      <c r="D30" t="n">
+        <v>852.3470100653776</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.843247950992172</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.84916e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-81.765</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1327707013557816</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.7138140989047358</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.416899029378875</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.38596112975209</v>
+      </c>
+      <c r="L30" t="n">
+        <v>29.756369616927</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.85703226049561</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>18.21154508039162</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-10581.55589589904</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-242.2935583319703</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>5.164684199479608e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9091528766849323</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>151.238</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7311623139920519</v>
+      </c>
+      <c r="D31" t="n">
+        <v>886.2293524015233</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8767685891974714</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.84593e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-81.908</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.689797609434404</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.178333251814904</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.644787859351534</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.644050388784462</v>
+      </c>
+      <c r="L31" t="n">
+        <v>31.35358023965321</v>
+      </c>
+      <c r="M31" t="n">
+        <v>87.0597237926864</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>19.469420819298</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-11217.45765620496</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-278.0241893786374</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>5.057314874306787e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.91216491664324</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>144.625</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.699191669164499</v>
+      </c>
+      <c r="D32" t="n">
+        <v>854.066549100887</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.844949133434559</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.84275e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-82.01600000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.3712415722778009</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.7681077186466254</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.572560674978716</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.407791097233519</v>
+      </c>
+      <c r="L32" t="n">
+        <v>31.12591706524201</v>
+      </c>
+      <c r="M32" t="n">
+        <v>86.98087440031027</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>18.96003931904799</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-10739.29793640912</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-257.3095838304586</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>4.976821138541326e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9144402532602752</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>140.51</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6792976417237943</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1031.377956823935</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.020367688887144</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.84088e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-82.105</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.1844831919820626</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.6739857610040001</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.313280617144318</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.214114982038684</v>
+      </c>
+      <c r="L33" t="n">
+        <v>29.95762994529726</v>
+      </c>
+      <c r="M33" t="n">
+        <v>86.97241186449907</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>18.90694497028715</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-10565.59914088861</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-416.0060975027832</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>4.914478213336615e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9162589858672073</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>139.208</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6730031037583516</v>
+      </c>
+      <c r="D34" t="n">
+        <v>863.6001860571369</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.854380995966985</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.83809e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-82.199</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.4249880013605527</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.9254426721455306</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.789217464113309</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.681695116388304</v>
+      </c>
+      <c r="L34" t="n">
+        <v>32.24005672723251</v>
+      </c>
+      <c r="M34" t="n">
+        <v>87.08989229112142</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>19.67160933843106</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-10893.42307022485</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-277.4077454271965</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>4.847425979721743e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.91820321490492</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>134.528</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6503775755876352</v>
+      </c>
+      <c r="D35" t="n">
+        <v>847.981345193742</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8389288908978063</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.83662e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-82.285</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.2229958180739045</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.8098783898493622</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.483479980518545</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.51127637279823</v>
+      </c>
+      <c r="L35" t="n">
+        <v>31.16428450665931</v>
+      </c>
+      <c r="M35" t="n">
+        <v>87.08037495563323</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>19.60737362175578</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-10716.67217080022</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-269.9061636460779</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>4.789190806279649e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9199680325807008</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>131.579</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.636120592131344</v>
+      </c>
+      <c r="D36" t="n">
+        <v>861.5120911672319</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8523151921140982</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.83538e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-82.411</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.1069132563020457</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.7566330338715134</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.49826997454913</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.414161421709404</v>
+      </c>
+      <c r="L36" t="n">
+        <v>32.20463424072356</v>
+      </c>
+      <c r="M36" t="n">
+        <v>87.14815463831815</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>20.07417949855282</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-10846.59767874084</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-287.3484495558589</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>4.721850160619705e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9220384885666901</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>128.748</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.622434081393887</v>
+      </c>
+      <c r="D37" t="n">
+        <v>866.3238942089041</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8570756277201981</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.83431e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-82.485</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.2599953909208527</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.6665271927382748</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.624212073871782</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.33935618651951</v>
+      </c>
+      <c r="L37" t="n">
+        <v>31.68626882161808</v>
+      </c>
+      <c r="M37" t="n">
+        <v>87.15835274382547</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>20.14634063930642</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-10754.07584243441</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-297.026377495543</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>4.674301422127175e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9235213414672513</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>127.2329999999999</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6151097918258024</v>
+      </c>
+      <c r="D38" t="n">
+        <v>871.1734959633056</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.861873458526472</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.83203e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-82.575</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.5487363464406083</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.7594661872060658</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.735428617760149</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.629560626821093</v>
+      </c>
+      <c r="L38" t="n">
+        <v>33.42599918333797</v>
+      </c>
+      <c r="M38" t="n">
+        <v>87.23197544047315</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>20.68305243264061</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-10933.5715616793</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-306.7470252250671</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>4.623054450161197e-07</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9250786051867066</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>122.799</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.5936735542384186</v>
+      </c>
+      <c r="D39" t="n">
+        <v>844.6396056882228</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8356228254602535</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.82888e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-82.639</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.2259114136117077</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.921238223870265</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.533997681767349</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.593084344481601</v>
+      </c>
+      <c r="L39" t="n">
+        <v>33.26216382530165</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87.18183856214445</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>20.31450945639425</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-10585.00810576945</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-289.2776192262575</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>4.578859941137327e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9263837980573263</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>121.292</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5863879407868653</v>
+      </c>
+      <c r="D40" t="n">
+        <v>855.829108560947</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.8466928770456071</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.82876e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-82.735</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.4846865284452188</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.6691511700532605</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.436285367942148</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.407571705129951</v>
+      </c>
+      <c r="L40" t="n">
+        <v>32.62174428416477</v>
+      </c>
+      <c r="M40" t="n">
+        <v>87.27012388388947</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>20.9725332709925</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-10822.60466248579</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-304.2667791413569</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>4.531406817193074e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9279547040001043</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>119.8219999999999</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5792812043742683</v>
+      </c>
+      <c r="D41" t="n">
+        <v>881.4815382727817</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.8720714594035321</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.82837e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-82.818</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.5685480551489587</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.9180277085792961</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.591984254281147</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.923081827536488</v>
+      </c>
+      <c r="L41" t="n">
+        <v>34.25909381495194</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.34861679587324</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>21.59434203030444</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-11034.11707855003</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-331.5895372423938</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>4.488572168994832e-07</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9293801009791647</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>116.877</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5650435589762428</v>
+      </c>
+      <c r="D42" t="n">
+        <v>996.9191920271059</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.9862767817032034</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.82964e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-82.854</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.3304687489578453</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.037952017509317</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.711705619666134</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.921410984988565</v>
+      </c>
+      <c r="L42" t="n">
+        <v>34.32273751937691</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.3059686203291</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>21.25199785051874</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-10710.44611308531</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-437.4624174780179</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>4.467858562237523e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9301653671972997</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>114.616</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5541127215416298</v>
+      </c>
+      <c r="D43" t="n">
+        <v>898.5573141219492</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.8889649462420764</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.82777e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-82.958</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.703854115327763</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.114315075708262</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.796272688206721</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.812855008274102</v>
+      </c>
+      <c r="L43" t="n">
+        <v>34.52979177923569</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.40956623821799</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>22.10314574339286</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-11038.31622551207</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-357.356520882348</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>4.417689184530119e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9317673639640885</v>
       </c>
     </row>
@@ -7898,7 +14282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8600,6 +14984,566 @@
         <v>5.332004591149701e-07</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.903122309726817</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>298.57</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1399.834676882888</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.05948e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-75.065</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1518543036625503</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.5030252414278642</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.987279417240101</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.014955436750503</v>
+      </c>
+      <c r="L12" t="n">
+        <v>10.32629293475272</v>
+      </c>
+      <c r="M12" t="n">
+        <v>83.00603305668103</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>8.15144218002084</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-6335.222807262978</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-495.5272450082089</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.515485762593364e-06</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.6372204845117558</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>235.207</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.7877784104230163</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1009.337098275458</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.7210402163511345</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3.01741e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-78.05800000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.4177179302916743</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.006972064821538</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.586522401151598</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.24382481230065</v>
+      </c>
+      <c r="L13" t="n">
+        <v>15.38354492705494</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.05074517941036</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>11.54783978494475</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-8134.556070058749</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-262.1294342953379</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.067160613020955e-06</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8085534560056014</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>217.785</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.7294269350571057</v>
+      </c>
+      <c r="D14" t="n">
+        <v>963.943146249254</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.6886121355385589</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.95421e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-79.31399999999999</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.5292454447679594</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9925065900218332</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.809440231966596</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.73799029204986</v>
+      </c>
+      <c r="L14" t="n">
+        <v>20.41165572665592</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.92343413290865</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>14.03118871716508</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-9593.414924072269</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-247.387089996826</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8.073620234051986e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8470916785309134</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>206.568</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.6918578557792144</v>
+      </c>
+      <c r="D15" t="n">
+        <v>920.3823506204884</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.6574936067950322</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.91133e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-79.932</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4695683648931734</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.7735580288927741</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.445354528228086</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.220838604786055</v>
+      </c>
+      <c r="L15" t="n">
+        <v>21.69378397708031</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.19816502605812</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>15.04843464919558</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-10061.96587485877</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-223.1888899986035</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>7.099148494990775e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8642478143366645</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>197.877</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.6627491040626989</v>
+      </c>
+      <c r="D16" t="n">
+        <v>905.5213817878659</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.6468773754085413</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.88235e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-80.39</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5007873700635117</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.9605240468773862</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.457390950220939</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.157568150560628</v>
+      </c>
+      <c r="L16" t="n">
+        <v>23.51125867157126</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.42196559657212</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>15.99237814734996</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-10519.63626502813</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-220.3961709695812</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>6.514220746783614e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.875691921496806</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>187.9519999999999</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.6295073182168334</v>
+      </c>
+      <c r="D17" t="n">
+        <v>869.0186017716956</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.6208008817918425</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.86237e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-80.697</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1335457464475696</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.6238033039451328</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.213781876480791</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.145311953224406</v>
+      </c>
+      <c r="L17" t="n">
+        <v>24.56617961729293</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.43352190917442</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>16.04433234548697</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-10352.69817113405</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-197.8377689769775</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>6.150168519841109e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.883332063904636</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>182.118</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.6099675118062766</v>
+      </c>
+      <c r="D18" t="n">
+        <v>870.3960012948783</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.6217848547894609</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.84878e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-80.92100000000001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.02729329449694735</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.7175362925637234</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.455353011685736</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.438201751048676</v>
+      </c>
+      <c r="L18" t="n">
+        <v>27.34888835308378</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.52270585445856</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>16.45688110030558</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-10443.75143186782</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-208.4708619429463</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>5.88622311340895e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8892723593308981</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>175.5549999999999</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5879860669189804</v>
+      </c>
+      <c r="D19" t="n">
+        <v>864.430828099421</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.6175235135796971</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.83987e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-81.14</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.1774313961354733</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.4927069235837447</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.485669829019479</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.440324562956664</v>
+      </c>
+      <c r="L19" t="n">
+        <v>27.83838411295151</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.60543639433614</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>16.85893446424018</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-10521.2872320515</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-212.7845996755032</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>5.667962330145158e-07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8945255653987479</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>170.85</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5722276183139633</v>
+      </c>
+      <c r="D20" t="n">
+        <v>873.5317598468876</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.6240249468544695</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.83373e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-81.357</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.249257961380702</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5994697987555112</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.356443215093501</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.225371912564541</v>
+      </c>
+      <c r="L20" t="n">
+        <v>27.78227501361389</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.76147297195421</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>17.67308068557021</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-10874.55213705548</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-229.5352709641047</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>5.473545957582736e-07</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8994824292256811</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>165.505</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.554325618782865</v>
+      </c>
+      <c r="D21" t="n">
+        <v>880.1907992401905</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.6287819653104854</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.82702e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-81.491</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.318691603017051</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.8583919801009906</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.29536267660153</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.469898299306311</v>
+      </c>
+      <c r="L21" t="n">
+        <v>28.72742933942593</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.84743022847248</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>18.15596513231331</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-11013.8840800332</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-244.0096900871932</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>5.332004591149701e-07</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.903122309726817</v>
       </c>
     </row>
@@ -8614,7 +15558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9932,6 +16876,1182 @@
         <v>4.441706051422483e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9315892506785497</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>198.355</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>957.9329625887202</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.91342e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-80.018</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.08583374704064571</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.7829651845536957</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.10893314663245</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.370116833858698</v>
+      </c>
+      <c r="L23" t="n">
+        <v>21.990196249151</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.92556024130452</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>14.03853517934627</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-9158.239803482922</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-263.2196496702983</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>6.939635490601613e-07</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8678363533763579</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>184.845</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.931889793551965</v>
+      </c>
+      <c r="D24" t="n">
+        <v>912.9608857544084</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9530530020464281</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.87842e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-80.774</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.5684313717551485</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.9510172703587961</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.59014429248337</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.726232349617719</v>
+      </c>
+      <c r="L24" t="n">
+        <v>26.65632666340922</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.54639774254363</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>16.57005289434864</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-10509.76117156017</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-247.1755793684193</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>6.065691900142197e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8862993888904903</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>175.218</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8833555998084243</v>
+      </c>
+      <c r="D25" t="n">
+        <v>884.6150356162702</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9234623613177321</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.86379e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-81.065</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.5149237268149065</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.8786640115978337</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.810999044456023</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.389445780248062</v>
+      </c>
+      <c r="L25" t="n">
+        <v>26.97480283591474</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.64529956532516</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>17.05973229317107</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-10608.34191552096</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-233.8654060938477</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>5.758173367481633e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8934160988964353</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>167.609</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8449950845705932</v>
+      </c>
+      <c r="D26" t="n">
+        <v>863.136504271228</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9010406134670279</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.85662e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-81.26600000000001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.2537474531380859</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.7214757517989263</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.570993226422273</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.610347507715892</v>
+      </c>
+      <c r="L26" t="n">
+        <v>28.71085235771254</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.66181290831521</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>17.1443160765689</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-10474.32923802869</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-224.346354613571</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>5.56448183668114e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8982269507417618</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>163.3939999999999</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8237453051347329</v>
+      </c>
+      <c r="D27" t="n">
+        <v>870.9724594769583</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.909220679830497</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.85421e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-81.471</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.390886244769942</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.6909849067743499</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.751235407039793</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.537893845766785</v>
+      </c>
+      <c r="L27" t="n">
+        <v>30.23758459678186</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.76197193521575</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>17.67580982388721</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-10643.99865554016</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-239.0710351134336</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>5.40652754576415e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.902444843648141</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>161.792</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.815668876509289</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1188.098231075018</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.240272834817479</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.85006e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-81.589</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.9555756428957459</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.315045042119148</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.740183587122337</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.497459214884556</v>
+      </c>
+      <c r="L28" t="n">
+        <v>28.9663123889992</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.979944462888</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>18.95419030902354</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-11313.89193898644</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-517.9060802804222</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>5.29188017937728e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9055003374462205</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>153.253</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7726197978372112</v>
+      </c>
+      <c r="D29" t="n">
+        <v>922.7120795390929</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9632324135141499</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.84715e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-81.73699999999999</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3377625930171204</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8250755894989609</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.58372775744833</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.67876767812929</v>
+      </c>
+      <c r="L29" t="n">
+        <v>31.27072749060132</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.87741783852587</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>18.3306760544104</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-10727.10461339592</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-299.8579726928266</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>5.177933248446756e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9086471723769123</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>147.508</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7436565753321064</v>
+      </c>
+      <c r="D30" t="n">
+        <v>837.5699800437476</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8743513510384866</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.84692e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-81.85299999999999</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1541840015388972</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.6755157107586849</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.477613104122139</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.127527944177472</v>
+      </c>
+      <c r="L30" t="n">
+        <v>28.95393640399235</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.84655555079907</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>18.15091899315512</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-10454.02941256753</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-233.9402842433156</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>5.092375615205946e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9111627086939513</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>145.554</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.73380555065413</v>
+      </c>
+      <c r="D31" t="n">
+        <v>860.8503127027502</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8986540252006637</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.84423e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-81.946</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.4078655944126217</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.7587368305605975</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.5902169262813</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.590321538996946</v>
+      </c>
+      <c r="L31" t="n">
+        <v>31.39616091349507</v>
+      </c>
+      <c r="M31" t="n">
+        <v>86.95966110405199</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>18.82750375431905</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-10752.44736859063</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-260.0652890105021</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>5.016604731941381e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9133084016510483</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>142.062</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.7162007511784427</v>
+      </c>
+      <c r="D32" t="n">
+        <v>851.3370409679231</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8887229839834178</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.84401e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-82.04300000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.2331292660330547</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.7903272215680843</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.315222596289086</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.46922396422195</v>
+      </c>
+      <c r="L32" t="n">
+        <v>31.20982597677958</v>
+      </c>
+      <c r="M32" t="n">
+        <v>86.98409628041334</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>18.98033178936646</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-10717.79679447714</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-257.1121867428755</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>4.952188704965358e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9152588834803289</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>141.682</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.7142849940762771</v>
+      </c>
+      <c r="D33" t="n">
+        <v>895.8671090715133</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9352085626644686</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.84125e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-82.16200000000001</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.5189268514432951</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.186529876436508</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.500284793196752</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.816318850603243</v>
+      </c>
+      <c r="L33" t="n">
+        <v>32.80240563919204</v>
+      </c>
+      <c r="M33" t="n">
+        <v>87.17852881340522</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>20.29064086241604</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-11401.31553036194</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-300.7569040677772</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>4.875897573513626e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9174627818825303</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>136.251</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6869047919134885</v>
+      </c>
+      <c r="D34" t="n">
+        <v>840.4414453104573</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8773489149378955</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.84049e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-82.22199999999999</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.1225979136795229</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.6805490771345694</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.341136698616225</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.225850623824885</v>
+      </c>
+      <c r="L34" t="n">
+        <v>30.80337973747905</v>
+      </c>
+      <c r="M34" t="n">
+        <v>87.02715300243224</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>19.25573498440319</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-10647.36491796495</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-257.8962232010689</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>4.829111383721641e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9189007219389907</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>134.869</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6799374858208765</v>
+      </c>
+      <c r="D35" t="n">
+        <v>842.3893908872141</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8793824033476613</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.83889e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-82.27500000000001</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.3863263557016656</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.7653547624323053</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.465837289713333</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.377468336201795</v>
+      </c>
+      <c r="L35" t="n">
+        <v>31.3376871048653</v>
+      </c>
+      <c r="M35" t="n">
+        <v>87.08219185903415</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>19.6196041821492</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-10752.26521999932</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-264.4047338871717</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>4.789943805447928e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9200706906958396</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>132.0050000000001</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6654987270298205</v>
+      </c>
+      <c r="D36" t="n">
+        <v>860.4637624959312</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8982504998790437</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.83738e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-82.34999999999999</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.2210537063047321</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.8412132280423287</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.651851807897816</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.614445095231277</v>
+      </c>
+      <c r="L36" t="n">
+        <v>32.2778547799313</v>
+      </c>
+      <c r="M36" t="n">
+        <v>87.14457214625331</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>20.04895225299378</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-10888.25431383424</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-285.1490037178939</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>4.739697264837431e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9215977562384815</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>128.112</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6458722996647426</v>
+      </c>
+      <c r="D37" t="n">
+        <v>837.18965135861</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8739543204528497</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.83853e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-82.437</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.1455696549551709</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.7204313095915499</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.514286690175575</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.430058043174661</v>
+      </c>
+      <c r="L37" t="n">
+        <v>32.71924555210143</v>
+      </c>
+      <c r="M37" t="n">
+        <v>87.08989090121656</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>19.67159992684424</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-10537.92701837069</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-269.9478190317092</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>4.690785734777748e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9232297164426132</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>127.595</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6432658617125862</v>
+      </c>
+      <c r="D38" t="n">
+        <v>837.7016015567797</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8744887526293833</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.83517e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-82.554</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.353172966429084</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.8533170836166445</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.646468480853425</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.50989477090713</v>
+      </c>
+      <c r="L38" t="n">
+        <v>33.05630545225473</v>
+      </c>
+      <c r="M38" t="n">
+        <v>87.21773574782559</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>20.57703077893204</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-10935.07456580674</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-275.2691221519107</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>4.626030484468354e-07</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9251609817807634</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>122.673</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.6184517657734869</v>
+      </c>
+      <c r="D39" t="n">
+        <v>831.3390333461975</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8678467761455718</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.83744e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-82.595</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.249862290531432</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.8059037501360673</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.527767362974654</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.645346230897843</v>
+      </c>
+      <c r="L39" t="n">
+        <v>33.35405405651718</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87.16706724953259</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>20.20841524723179</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-10590.59131400182</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-275.3971414644895</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>4.601242245427078e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9261112268002031</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>120.7</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.6085049532404022</v>
+      </c>
+      <c r="D40" t="n">
+        <v>837.2238393266052</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.8739900097644512</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.83754e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-82.68899999999999</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.05633686578266573</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.8239710625401686</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.537285179329418</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.592286347858283</v>
+      </c>
+      <c r="L40" t="n">
+        <v>33.9469875343128</v>
+      </c>
+      <c r="M40" t="n">
+        <v>87.21032039201737</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>20.52224797945347</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-10635.70698782171</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-285.8619803102878</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>4.554384756374948e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9276727639520341</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>118.272</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5962642736507775</v>
+      </c>
+      <c r="D41" t="n">
+        <v>863.5659784814097</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.901488947773242</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.83824e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-82.788</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.3593255064743227</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.9421891549012992</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.532018026854516</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.618802209315676</v>
+      </c>
+      <c r="L41" t="n">
+        <v>33.33530995131347</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.30069984518549</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>21.21045472471323</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-10879.13431316853</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-314.0566863835878</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>4.50762229766592e-07</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9292712810907091</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>114.862</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5790728743918733</v>
+      </c>
+      <c r="D42" t="n">
+        <v>831.7169857307704</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.868241326076865</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.83751e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-82.851</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.09811535866251042</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.6981661394167925</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.382915312401741</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.407994697939833</v>
+      </c>
+      <c r="L42" t="n">
+        <v>33.2093896900528</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.2441757536334</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>20.77476071679067</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-10495.12215438899</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-292.3231195250186</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>4.470452847620055e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9305060312548025</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>112.232</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5658138186584659</v>
+      </c>
+      <c r="D43" t="n">
+        <v>845.0495388501793</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.8821593700737842</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.83923e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-82.907</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.2261935463304488</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.9866104066092124</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.815770215577326</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.776880432012301</v>
+      </c>
+      <c r="L43" t="n">
+        <v>34.3193966369405</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.31182169016245</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>21.2983388074436</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-10645.46534025562</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-309.5684601963625</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>4.441706051422483e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9315892506785497</v>
       </c>
     </row>
@@ -9946,7 +18066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10651,6 +18771,566 @@
         <v>0.918381809651342</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>209.369</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>956.1052941828938</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.03843e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-77.922</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2804483917255284</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.6635737981781917</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.38673179752035</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.208060107760302</v>
+      </c>
+      <c r="L12" t="n">
+        <v>13.17569599186616</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.5133461030688</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10.41081488166332</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-6824.026098839277</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-255.7614581634738</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>9.934221897037078e-07</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8205913635682168</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>194.602</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9294690235899298</v>
+      </c>
+      <c r="D13" t="n">
+        <v>920.7047689580688</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.962974239929213</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.91101e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-80.047</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.611664857453694</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.111596759432212</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.624201966847215</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.611650661924425</v>
+      </c>
+      <c r="L13" t="n">
+        <v>20.37658608731827</v>
+      </c>
+      <c r="M13" t="n">
+        <v>86.0943897065048</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>14.64739304454518</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-9346.52021162882</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-249.0772592381293</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>6.836591868196212e-07</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8699732645591437</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>184.617</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8817781046859847</v>
+      </c>
+      <c r="D14" t="n">
+        <v>876.1970262303051</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9164231508404315</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.87153e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-80.747</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3707517293675382</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9462329514761778</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.678657016922006</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.385048439899204</v>
+      </c>
+      <c r="L14" t="n">
+        <v>23.23822786510243</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.47226453130855</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>16.22098939133663</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-10130.08320452879</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-223.2561250186567</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>6.103850501617336e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8849539937637688</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>174.845</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8351045283685739</v>
+      </c>
+      <c r="D15" t="n">
+        <v>843.2388928427173</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8819519125907211</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.84839e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-81.136</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1330456800647542</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.7390981951279173</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.490593317097356</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.57145575400193</v>
+      </c>
+      <c r="L15" t="n">
+        <v>26.71279136562681</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.53266663490025</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>16.50427372073309</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-10076.72515870641</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-204.9002805134496</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>5.721278687584216e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8935185642558439</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>168.8989999999999</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.8067049085585732</v>
+      </c>
+      <c r="D16" t="n">
+        <v>847.3568698939372</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8862589455883151</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.83502e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-81.398</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.2795717234870711</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.8701302910010361</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.580532251859992</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.610014391063092</v>
+      </c>
+      <c r="L16" t="n">
+        <v>28.25574333708228</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.67475184115797</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>17.21117754508739</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-10335.5440924935</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-217.6661727691782</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>5.474057726749312e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8995070606125547</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>161.246</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7701522192874779</v>
+      </c>
+      <c r="D17" t="n">
+        <v>840.1150922883493</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8786846986411972</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.82778e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-81.61799999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.08815178501487596</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.6052080682534858</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.253285817308732</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.428300129408596</v>
+      </c>
+      <c r="L17" t="n">
+        <v>28.23193793284035</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.72904003429538</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>17.4974690255007</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-10308.8556564917</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-221.2137935480099</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>5.289251399962977e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9043317162757228</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>157.234</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7509898791129535</v>
+      </c>
+      <c r="D18" t="n">
+        <v>864.807561986255</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9045107973440691</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.82205e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-81.819</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.4564670861251693</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.034316496873777</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.553107539381966</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.209308547262005</v>
+      </c>
+      <c r="L18" t="n">
+        <v>28.65632431673984</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.90958148089945</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>18.5218295635614</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-10751.88147196908</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-251.6949276920419</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>5.13280953960211e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9085852952268905</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>150.322</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7179763957414899</v>
+      </c>
+      <c r="D19" t="n">
+        <v>835.0282166458655</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8733642850074342</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.81724e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-81.982</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.4548659900338863</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.8524282890547806</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.414799412093713</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.475347469072354</v>
+      </c>
+      <c r="L19" t="n">
+        <v>30.11344160407834</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.91030666967617</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>18.52618530549196</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-10547.3170095587</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-235.4343986748095</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>5.003821300762556e-07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9122007141068961</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>144.708</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.6911624930147252</v>
+      </c>
+      <c r="D20" t="n">
+        <v>825.010840516616</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8628870120645931</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.81539e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-82.143</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1569785937668468</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5507096735849466</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.459997404191794</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.248624820078149</v>
+      </c>
+      <c r="L20" t="n">
+        <v>29.74833637696018</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.93694325489693</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>18.68760188530378</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-10459.66993411818</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-235.3089284672906</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.900493783458515e-07</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9152618739857541</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>143.558</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.6856697982986973</v>
+      </c>
+      <c r="D21" t="n">
+        <v>855.952933514065</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8952496536959134</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.81199e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-82.31</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4286097703818519</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.952006245847078</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.697808270918003</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.889110563778867</v>
+      </c>
+      <c r="L21" t="n">
+        <v>33.93411923311126</v>
+      </c>
+      <c r="M21" t="n">
+        <v>87.12345974629464</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>19.90155790543493</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-11019.94505846481</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-269.2078426277388</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>4.794897629054564e-07</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.918381809651342</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
